--- a/2026/ITALIA/Septiembre/Septiembre ITALIA.xlsx
+++ b/2026/ITALIA/Septiembre/Septiembre ITALIA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ITALIA\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\ITALIA\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC80CE40-BC55-40AF-B759-BBC3F3C48DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{561B60AD-3A1F-4CA4-B553-40D5EB757F8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
@@ -19,14 +19,19 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$O$127</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$163</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$168</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="287">
   <si>
     <t>TOTAL</t>
   </si>
@@ -356,9 +361,6 @@
   </si>
   <si>
     <t>Edesur</t>
-  </si>
-  <si>
-    <t>AySa</t>
   </si>
   <si>
     <t>Servicio de interet Claro</t>
@@ -683,9 +685,6 @@
     <t>Gastos bancarios - Santander</t>
   </si>
   <si>
-    <t>Mantenimiento de cuenta - Banco Credicop + Gastos bancarios</t>
-  </si>
-  <si>
     <t>Daniela Dominguez</t>
   </si>
   <si>
@@ -704,37 +703,144 @@
     <t>10A</t>
   </si>
   <si>
-    <t>Matafuegos FIRE - Bota neora s/ puntera OMBU</t>
-  </si>
-  <si>
-    <t>Roxana Goldemberg - Convenio pago 5E</t>
-  </si>
-  <si>
-    <t>Transf 21/08</t>
-  </si>
-  <si>
-    <t>Cuello Natalia - Desobstruccion emergencia de columna en cocina 4C</t>
-  </si>
-  <si>
-    <t>Tramsf 12/08</t>
-  </si>
-  <si>
-    <t>Servisur - retiro de 29 luces de emergencia y reemplazo de las mismas</t>
-  </si>
-  <si>
-    <t>Transf 10/08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Galvan Zaffalon - Instalacion y puesta en marcha de bomba chupadora de calle e instalacion de cañeria con by pass </t>
-  </si>
-  <si>
-    <t>Transf 06/08</t>
-  </si>
-  <si>
-    <t>Debito 12/08</t>
-  </si>
-  <si>
-    <t>Transf 18/08</t>
+    <t>Plan de pago 5E: Consta de 6 cuotas mensuales de $190.000 + expensas en curso</t>
+  </si>
+  <si>
+    <t>Plan de pago 10F: Cosnsta de 9 cuotas mensuales de $130.000 + expensas en curso</t>
+  </si>
+  <si>
+    <t>Alexis Florentino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jorge Luis Otranto </t>
+  </si>
+  <si>
+    <t>ARCA - Plan de pago - Cuota 47/60</t>
+  </si>
+  <si>
+    <t>Ramon Troncoso -  En septiembre debe pagar la 1er cuota de 6 - Consta de 6 cuotas mensuales de $190.000 + expensas en curso</t>
+  </si>
+  <si>
+    <t>Ingreso 25/08</t>
+  </si>
+  <si>
+    <t>Intereses</t>
+  </si>
+  <si>
+    <t>SALDO FINAL AL 31/08</t>
+  </si>
+  <si>
+    <t>FCI - SALDO INICIAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10A deposito $300.000 el 08/09
+</t>
+  </si>
+  <si>
+    <t>4A pago $297.000,02 el 09/08 LE ERRO A LOS CENTAVOS</t>
+  </si>
+  <si>
+    <t>Agregar a panchomorena27@gmail.com a la cadena de mail</t>
+  </si>
+  <si>
+    <t>03 - PB C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deposito $162.000 14/09 y se transfirió saldo $800,03.
+</t>
+  </si>
+  <si>
+    <t>Ricardo Vega transfirio $307.000 el 04/09</t>
+  </si>
+  <si>
+    <t>1A</t>
+  </si>
+  <si>
+    <t>6F - UF 46</t>
+  </si>
+  <si>
+    <t>Deposito 17/09 $250.000</t>
+  </si>
+  <si>
+    <t>VTO 16/10</t>
+  </si>
+  <si>
+    <t>PERÍODO: SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>InOut Control - Comando control y camaras - SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>Honorarios administracion - Se adeuda mes de SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>Gustavo Padron -  Sr. Contador - SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>Transf 15/09</t>
+  </si>
+  <si>
+    <t>Transf 02/09</t>
+  </si>
+  <si>
+    <t>Transf 11/09</t>
+  </si>
+  <si>
+    <t>Suarez Agustin Ignacio - SEPTIEMBRE - Desinsectacion</t>
+  </si>
+  <si>
+    <t>Transf 07/09</t>
+  </si>
+  <si>
+    <t>Transf 05/09</t>
+  </si>
+  <si>
+    <t>Grafica Tauge - Fotocopias Byn</t>
+  </si>
+  <si>
+    <t>El deposito no identificado de $200000 7/7 es del 9F</t>
+  </si>
+  <si>
+    <t>9F</t>
+  </si>
+  <si>
+    <t>Bayeto Gabriela Paola - Aporte notarial sellos, protocolo, testimonio e impresión de fotografias - Honorarios de acta de constatacion</t>
+  </si>
+  <si>
+    <t>Transf 09/09</t>
+  </si>
+  <si>
+    <t>Abono ascensor - Lema Ascensores - Cerradura ascensores: compra y cambios de cerraduras</t>
+  </si>
+  <si>
+    <t>ARCA VEP - Mes 9</t>
+  </si>
+  <si>
+    <t>ARCA VEP - Pagos atrasados ART</t>
+  </si>
+  <si>
+    <t>ARCA VEP - Punitorios periodos 2022/23</t>
+  </si>
+  <si>
+    <t>Envio carta documento correo Argentino</t>
+  </si>
+  <si>
+    <t>Transf 10/09</t>
+  </si>
+  <si>
+    <t>Debito 14/09</t>
+  </si>
+  <si>
+    <t>Sra Silvana - Reemplazo del Sr. Encargado</t>
+  </si>
+  <si>
+    <t>Seguro Sra. Silvana</t>
+  </si>
+  <si>
+    <t>Transf 14/09</t>
+  </si>
+  <si>
+    <t>Efectivo</t>
   </si>
   <si>
     <r>
@@ -759,163 +865,83 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Trabajo de plomeria, albañileria y pintura - 8vo B cambio de desague cocina y lavadero - 8vo f cambio de desague de cocina, lavadero y albañileria - 8vo E cambio de desague de cocina, lavadero y albañileria - 6to c cambio de desague de cocina, lavadero y albañileria + llave de paso - 7mo C cambio de desague de cocina, lavadero y albañileria - 3ro D cambio de desague de cocina, lavadero y albañileria + cambio de cañeria agua fria cocina y lavadero + llaves de paso - 3ro C cambio de desague de cocina, lavadero + Cambio de cañeria agua fria y caliente cocina y lavadero + llaves de paso - 4to D cambio de llaves de paso agua fria y caliente - 1ro C reparacion de llave de paso - Resta abonar $10.000.000</t>
+      <t xml:space="preserve"> Trabajo de plomeria, albañileria y pintura - 8vo B cambio de desague cocina y lavadero - 8vo f cambio de desague de cocina, lavadero y albañileria - 8vo E cambio de desague de cocina, lavadero y albañileria - 6to c cambio de desague de cocina, lavadero y albañileria + llave de paso - 7mo C cambio de desague de cocina, lavadero y albañileria - 3ro D cambio de desague de cocina, lavadero y albañileria + cambio de cañeria agua fria cocina y lavadero + llaves de paso - 3ro C cambio de desague de cocina, lavadero + Cambio de cañeria agua fria y caliente cocina y lavadero + llaves de paso - 4to D cambio de llaves de paso agua fria y caliente - 1ro C reparacion de llave de paso - Resta abonar $7.200.000</t>
     </r>
   </si>
   <si>
-    <t>Transf 26/08</t>
-  </si>
-  <si>
-    <t>Firma escribania Bayeto - Comodato porteria</t>
-  </si>
-  <si>
-    <t>Transf 31/08</t>
-  </si>
-  <si>
-    <t>Plan de pago 5E: Consta de 6 cuotas mensuales de $190.000 + expensas en curso</t>
-  </si>
-  <si>
-    <t>Plan de pago 10F: Cosnsta de 9 cuotas mensuales de $130.000 + expensas en curso</t>
-  </si>
-  <si>
-    <t>Roxana Goldemberg - Convenio pago 10F</t>
-  </si>
-  <si>
-    <t>Alexis Florentino</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El en les de Agosto  abono la 5ta cuota de 7 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">En Agosto paga la primer cuota de 9 cuotas de $130.000 </t>
-  </si>
-  <si>
-    <t>Convenio de pago 10F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">En Agosto abona la 5ta cuota de 10 - Consta de 10 Cuotas de $165.000 + expensas en curso </t>
-  </si>
-  <si>
-    <t>En Agosto abono la cuota 8 de 24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE LE DEBE COBRAR SIEMPR EN PRIMER VTO . - En Agosto abona la 5ta cuota de 24 - Consta de 24 cuotas de $33.000 + expensas en curso </t>
-  </si>
-  <si>
-    <t>Deposito ya identificado mes JUNIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jorge Luis Otranto </t>
-  </si>
-  <si>
-    <t>ARCA - Plan de pago - Cuota 47/60</t>
-  </si>
-  <si>
-    <t>Convenio de pago 5E</t>
-  </si>
-  <si>
-    <t>Ramon Troncoso -  En septiembre debe pagar la 1er cuota de 6 - Consta de 6 cuotas mensuales de $190.000 + expensas en curso</t>
-  </si>
-  <si>
-    <t>Egreso a Fondo comun de inversion</t>
-  </si>
-  <si>
-    <t>Ingreso 25/08</t>
-  </si>
-  <si>
-    <t>Intereses</t>
-  </si>
-  <si>
-    <t>SALDO FINAL AL 31/08</t>
-  </si>
-  <si>
-    <t>FCI - SALDO INICIAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10A deposito $300.000 el 08/09
-</t>
-  </si>
-  <si>
-    <t>4A pago $297.000,02 el 09/08 LE ERRO A LOS CENTAVOS</t>
-  </si>
-  <si>
-    <t>Agregar a panchomorena27@gmail.com a la cadena de mail</t>
-  </si>
-  <si>
-    <t>03 - PB C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deposito $162.000 14/09 y se transfirió saldo $800,03.
-</t>
-  </si>
-  <si>
-    <t>Ricardo Vega transfirio $307.000 el 04/09</t>
-  </si>
-  <si>
-    <t>1A</t>
-  </si>
-  <si>
-    <t>6F - UF 46</t>
-  </si>
-  <si>
-    <t>Deposito 17/09 $250.000</t>
-  </si>
-  <si>
-    <t>VTO 16/10</t>
-  </si>
-  <si>
-    <t>PERÍODO: SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t>InOut Control - Comando control y camaras - SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t>Honorarios administracion - Se adeuda mes de SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t>Gustavo Padron -  Sr. Contador - SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t>ARCA VEP - Mes 8</t>
-  </si>
-  <si>
-    <t>Transf 15/09</t>
-  </si>
-  <si>
-    <t>Transf 02/09</t>
-  </si>
-  <si>
-    <t>Abono ascensor - Lema Ascensores - Cerradura ascensores</t>
-  </si>
-  <si>
-    <t>Transf 11/09</t>
-  </si>
-  <si>
-    <t>Suarez Agustin Ignacio - SEPTIEMBRE - Desinsectacion</t>
-  </si>
-  <si>
-    <t>Transf 07/09</t>
-  </si>
-  <si>
-    <t>Matias Cordoba - Cambio de cañeria e la cocina 3F - Cambio de llave de paso general</t>
-  </si>
-  <si>
-    <t>Transf 05/09</t>
-  </si>
-  <si>
-    <t>Grafica Tauge - Fotocopias Byn</t>
-  </si>
-  <si>
-    <t>El deposito no identificado de $200000 7/7 es del 9F</t>
-  </si>
-  <si>
-    <t>9F</t>
-  </si>
-  <si>
-    <t>Bayeto Gabriela Paola - Aporte notarial sellos, protocolo, testimonio e impresión de fotografias - Honorarios de acta de constatacion</t>
-  </si>
-  <si>
-    <t>Transf 09/09</t>
+    <t>Transf 28/09</t>
+  </si>
+  <si>
+    <t>Federacion Patronal - Seguro accidentes personales Sr. Cristian</t>
+  </si>
+  <si>
+    <t>Transf 21/09</t>
+  </si>
+  <si>
+    <t>Cuello Natalia - Desobstruccion columna cocina en 1A</t>
+  </si>
+  <si>
+    <t>Transf 24/09</t>
+  </si>
+  <si>
+    <t>Cuello Natalia - Desobstruccion colectora cloacal</t>
+  </si>
+  <si>
+    <t>Cuello Natalia - Desobstruccion camara septica</t>
+  </si>
+  <si>
+    <t>AySa - Fc. 0111B26388563A</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mantenimiento de cuenta - Banco Credicop + Gastos bancarios - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ultimo mes: cierre de cuenta</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">El en mes de septiembre abono la 6ta cuota de 7 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">En Septiembre paga la 2da cuota de 9 cuotas de $130.000 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">En Septiembre abona la 6ta cuota de 10 - Consta de 10 Cuotas de $165.000 + expensas en curso </t>
+  </si>
+  <si>
+    <t>Deposito ya identificado (07/07)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SE LE DEBE COBRAR SIEMPR EN PRIMER VTO . - En Septiembre abona la 6ta cuota de 24 - Consta de 24 cuotas de $33.000 + expensas en curso </t>
+  </si>
+  <si>
+    <t>En Septiembre abono la cuota 9 de 24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caja Cocheras </t>
+  </si>
+  <si>
+    <t>Saldo final</t>
+  </si>
+  <si>
+    <t>Comodato porteria - Mes de septiembre</t>
+  </si>
+  <si>
+    <t>AySa - Fc. 0111B22611040</t>
+  </si>
+  <si>
+    <t>Se crea una caja destinada exclusivamente a la gestión de los fondos correspondientes al arreglo del techado de las cocheras.
+La misma contará mensualmente con el ingreso proveniente del alquiler o comodato de la portería. La caja se inicia con dicho ingreso, abonado en efectivo, quedando los fondos afectados exclusivamente a los gastos relacionados con la reparación y mantenimiento del techado de las cocheras.</t>
   </si>
 </sst>
 </file>
@@ -932,7 +958,7 @@
     <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1101,8 +1127,24 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="21">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1223,8 +1265,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="45">
+  <borders count="43">
     <border>
       <left/>
       <right/>
@@ -1762,39 +1810,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="328">
+  <cellXfs count="320">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2047,9 +2069,6 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="17" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2124,21 +2143,6 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="44" fontId="10" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2147,23 +2151,11 @@
     </xf>
     <xf numFmtId="44" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="8" fontId="10" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="44" fontId="10" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="43" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="17" fillId="7" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2171,8 +2163,6 @@
     <xf numFmtId="0" fontId="0" fillId="17" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2180,227 +2170,235 @@
     <xf numFmtId="0" fontId="0" fillId="18" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="44" fontId="7" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="44" fontId="7" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="7" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="44" fontId="7" fillId="21" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="21" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="21" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="7" fillId="21" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="8" fontId="7" fillId="21" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="21" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="21" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="22" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="44" fontId="22" fillId="13" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -2486,9 +2484,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2526,9 +2524,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2561,9 +2559,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2596,9 +2611,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2772,50 +2804,50 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E413A25D-5161-4141-BE0B-6E37A2A76CA5}">
-  <dimension ref="A1:M164"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M169"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.33203125" customWidth="1"/>
+    <col min="10" max="10" width="16.28515625" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="255" t="s">
-        <v>146</v>
-      </c>
-      <c r="C1" s="255"/>
-      <c r="D1" s="255"/>
-      <c r="E1" s="256"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="256" t="s">
+        <v>145</v>
+      </c>
+      <c r="C1" s="256"/>
+      <c r="D1" s="256"/>
+      <c r="E1" s="257"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="4"/>
     </row>
-    <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
-      <c r="B3" s="261" t="s">
-        <v>187</v>
-      </c>
-      <c r="C3" s="261"/>
-      <c r="D3" s="261"/>
-      <c r="E3" s="262"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="260" t="s">
+        <v>186</v>
+      </c>
+      <c r="C3" s="260"/>
+      <c r="D3" s="260"/>
+      <c r="E3" s="261"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>100</v>
       </c>
@@ -2826,12 +2858,12 @@
       <c r="D4" s="7"/>
       <c r="E4" s="8"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>267</v>
+        <v>240</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="3" t="s">
@@ -2839,425 +2871,442 @@
       </c>
       <c r="E5" s="10"/>
     </row>
-    <row r="6" spans="1:5" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="85" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E6" s="8"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="48"/>
-      <c r="B8" s="263" t="s">
-        <v>266</v>
-      </c>
-      <c r="C8" s="263"/>
+      <c r="B8" s="262" t="s">
+        <v>239</v>
+      </c>
+      <c r="C8" s="262"/>
       <c r="D8" s="48"/>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="48"/>
-      <c r="B9" s="263"/>
-      <c r="C9" s="263"/>
+      <c r="B9" s="262"/>
+      <c r="C9" s="262"/>
       <c r="D9" s="48"/>
       <c r="E9" s="48"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="48"/>
-      <c r="B10" s="263"/>
-      <c r="C10" s="263"/>
+      <c r="B10" s="262"/>
+      <c r="C10" s="262"/>
       <c r="D10" s="48"/>
       <c r="E10" s="48"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="48"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
       <c r="E11" s="48"/>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="48"/>
       <c r="B12" s="48"/>
       <c r="C12" s="48"/>
       <c r="D12" s="48"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="264" t="s">
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="263" t="s">
         <v>103</v>
       </c>
-      <c r="B13" s="264"/>
-      <c r="C13" s="264"/>
-      <c r="D13" s="264"/>
-      <c r="E13" s="264"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="264"/>
-      <c r="B14" s="264"/>
-      <c r="C14" s="264"/>
-      <c r="D14" s="264"/>
-      <c r="E14" s="264"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="264"/>
-      <c r="B15" s="264"/>
-      <c r="C15" s="264"/>
-      <c r="D15" s="264"/>
-      <c r="E15" s="264"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="264"/>
-      <c r="B16" s="264"/>
-      <c r="C16" s="264"/>
-      <c r="D16" s="264"/>
-      <c r="E16" s="264"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="263"/>
+      <c r="C13" s="263"/>
+      <c r="D13" s="263"/>
+      <c r="E13" s="263"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="263"/>
+      <c r="B14" s="263"/>
+      <c r="C14" s="263"/>
+      <c r="D14" s="263"/>
+      <c r="E14" s="263"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="263"/>
+      <c r="B15" s="263"/>
+      <c r="C15" s="263"/>
+      <c r="D15" s="263"/>
+      <c r="E15" s="263"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="263"/>
+      <c r="B16" s="263"/>
+      <c r="C16" s="263"/>
+      <c r="D16" s="263"/>
+      <c r="E16" s="263"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="48"/>
       <c r="B17" s="48"/>
       <c r="C17" s="48"/>
       <c r="D17" s="48"/>
       <c r="E17" s="48"/>
     </row>
-    <row r="18" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="169"/>
+    <row r="18" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="168"/>
       <c r="B18" s="48"/>
       <c r="C18" s="48"/>
       <c r="D18" s="48"/>
       <c r="E18" s="48"/>
     </row>
-    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="48"/>
       <c r="B19" s="48"/>
       <c r="C19" s="48"/>
       <c r="D19" s="48"/>
       <c r="E19" s="48"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="170" t="s">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="169" t="s">
         <v>104</v>
       </c>
-      <c r="B20" s="171"/>
-      <c r="C20" s="172"/>
+      <c r="B20" s="170"/>
+      <c r="C20" s="171"/>
       <c r="D20" s="58"/>
       <c r="E20" s="59"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="36" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B21" s="36"/>
       <c r="C21" s="36"/>
       <c r="D21" s="112"/>
       <c r="E21" s="145"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="257" t="s">
-        <v>161</v>
-      </c>
-      <c r="B22" s="258"/>
-      <c r="C22" s="173"/>
-      <c r="D22" s="174">
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="258" t="s">
+        <v>160</v>
+      </c>
+      <c r="B22" s="259"/>
+      <c r="C22" s="172"/>
+      <c r="D22" s="173">
         <v>2415207.52</v>
       </c>
       <c r="E22" s="146"/>
       <c r="H22" s="19"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="257" t="s">
-        <v>162</v>
-      </c>
-      <c r="B23" s="258"/>
-      <c r="C23" s="173"/>
-      <c r="D23" s="174">
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="258" t="s">
+        <v>161</v>
+      </c>
+      <c r="B23" s="259"/>
+      <c r="C23" s="172"/>
+      <c r="D23" s="173">
         <v>-525307.52</v>
       </c>
       <c r="E23" s="20"/>
       <c r="H23" s="19"/>
     </row>
-    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="257" t="s">
+    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="258" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="258"/>
-      <c r="C24" s="173"/>
-      <c r="D24" s="175">
+      <c r="B24" s="259"/>
+      <c r="C24" s="172"/>
+      <c r="D24" s="174">
         <v>0</v>
       </c>
       <c r="E24" s="20"/>
-      <c r="F24" s="198"/>
+      <c r="F24" s="197"/>
       <c r="H24" s="19"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="176" t="s">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="175" t="s">
         <v>105</v>
       </c>
-      <c r="B25" s="176"/>
-      <c r="C25" s="176"/>
+      <c r="B25" s="175"/>
+      <c r="C25" s="175"/>
       <c r="D25" s="22"/>
       <c r="E25" s="147">
         <f>SUM(D22:D24)</f>
         <v>1889900</v>
       </c>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="176" t="s">
-        <v>176</v>
-      </c>
-      <c r="B26" s="176"/>
-      <c r="C26" s="176"/>
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="175" t="s">
+        <v>175</v>
+      </c>
+      <c r="B26" s="175"/>
+      <c r="C26" s="175"/>
       <c r="D26" s="22"/>
       <c r="E26" s="148"/>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="173"/>
-      <c r="B27" s="173"/>
-      <c r="C27" s="173"/>
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="172"/>
+      <c r="B27" s="172"/>
+      <c r="C27" s="172"/>
       <c r="D27" s="35"/>
       <c r="E27" s="160"/>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="173"/>
-      <c r="B28" s="173"/>
-      <c r="C28" s="173"/>
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="172"/>
+      <c r="B28" s="172"/>
+      <c r="C28" s="172"/>
       <c r="D28" s="35"/>
       <c r="E28" s="160"/>
     </row>
-    <row r="29" spans="1:8" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="173"/>
-      <c r="B29" s="173"/>
-      <c r="C29" s="173"/>
+    <row r="29" spans="1:8" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="172"/>
+      <c r="B29" s="172"/>
+      <c r="C29" s="172"/>
       <c r="D29" s="35"/>
       <c r="E29" s="160"/>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="173"/>
-      <c r="B30" s="173"/>
-      <c r="C30" s="173"/>
-      <c r="D30" s="35"/>
-      <c r="E30" s="149"/>
-    </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="173"/>
-      <c r="B31" s="173"/>
-      <c r="C31" s="173"/>
-      <c r="D31" s="35"/>
-      <c r="E31" s="149"/>
-    </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="173"/>
-      <c r="B32" s="173"/>
-      <c r="C32" s="173"/>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="247" t="s">
+        <v>262</v>
+      </c>
+      <c r="B30" s="172"/>
+      <c r="C30" s="172"/>
+      <c r="D30" s="242">
+        <v>237600</v>
+      </c>
+      <c r="E30" s="149" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="172" t="s">
+        <v>263</v>
+      </c>
+      <c r="B31" s="172"/>
+      <c r="C31" s="172"/>
+      <c r="D31" s="242">
+        <v>13000</v>
+      </c>
+      <c r="E31" s="149" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="172"/>
+      <c r="B32" s="172"/>
+      <c r="C32" s="172"/>
       <c r="D32" s="35"/>
       <c r="E32" s="149"/>
     </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="176" t="s">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="175" t="s">
         <v>105</v>
       </c>
-      <c r="B33" s="177"/>
-      <c r="C33" s="177"/>
+      <c r="B33" s="176"/>
+      <c r="C33" s="176"/>
       <c r="D33" s="102"/>
       <c r="E33" s="150">
         <f>SUM(D29:D32)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+        <v>250600</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="36" t="s">
-        <v>139</v>
-      </c>
-      <c r="B34" s="176"/>
-      <c r="C34" s="176"/>
+        <v>138</v>
+      </c>
+      <c r="B34" s="175"/>
+      <c r="C34" s="175"/>
       <c r="D34" s="22"/>
       <c r="E34" s="148"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="173" t="s">
-        <v>249</v>
-      </c>
-      <c r="B35" s="178"/>
-      <c r="C35" s="178"/>
-      <c r="D35" s="35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="172" t="s">
+        <v>224</v>
+      </c>
+      <c r="B35" s="177"/>
+      <c r="C35" s="177"/>
+      <c r="D35" s="249">
         <v>11886</v>
       </c>
-      <c r="E35" s="149" t="str">
-        <f>E42</f>
-        <v>Debito 12/08</v>
-      </c>
+      <c r="E35" s="149"/>
       <c r="G35" s="66"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="173" t="s">
-        <v>271</v>
-      </c>
-      <c r="B36" s="178"/>
-      <c r="C36" s="178"/>
-      <c r="D36" s="318">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="172" t="s">
+        <v>256</v>
+      </c>
+      <c r="B36" s="177"/>
+      <c r="C36" s="177"/>
+      <c r="D36" s="242">
+        <v>1061960.04</v>
+      </c>
+      <c r="E36" s="149" t="s">
+        <v>248</v>
+      </c>
+      <c r="G36" s="66"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="172"/>
+      <c r="B37" s="177"/>
+      <c r="C37" s="177"/>
+      <c r="D37" s="235">
+        <v>392020.44</v>
+      </c>
+      <c r="E37" s="149"/>
+      <c r="F37" s="235"/>
+      <c r="G37" s="66"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="172" t="s">
+        <v>257</v>
+      </c>
+      <c r="B38" s="177"/>
+      <c r="C38" s="177"/>
+      <c r="D38" s="242">
         <v>506489.49</v>
-      </c>
-      <c r="E36" s="149" t="s">
-        <v>272</v>
-      </c>
-      <c r="G36" s="66"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="173"/>
-      <c r="B37" s="178"/>
-      <c r="C37" s="178"/>
-      <c r="D37" s="318">
-        <v>1061960.04</v>
-      </c>
-      <c r="E37" s="149" t="s">
-        <v>277</v>
-      </c>
-      <c r="G37" s="66"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="173"/>
-      <c r="B38" s="178"/>
-      <c r="C38" s="178"/>
-      <c r="D38" s="318">
-        <v>392020.44</v>
       </c>
       <c r="E38" s="149"/>
       <c r="G38" s="66"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="173"/>
-      <c r="B39" s="178"/>
-      <c r="C39" s="178"/>
-      <c r="D39" s="318">
-        <v>114469.05</v>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="172" t="s">
+        <v>258</v>
+      </c>
+      <c r="B39" s="177"/>
+      <c r="C39" s="177"/>
+      <c r="D39" s="242">
+        <v>115902.14</v>
       </c>
       <c r="E39" s="149"/>
       <c r="G39" s="66"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="173"/>
-      <c r="B40" s="178"/>
-      <c r="C40" s="178"/>
-      <c r="D40" s="318">
-        <v>115902.14</v>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="172" t="s">
+        <v>258</v>
+      </c>
+      <c r="B40" s="177"/>
+      <c r="C40" s="177"/>
+      <c r="D40" s="242">
+        <v>61640.3</v>
       </c>
       <c r="E40" s="149"/>
       <c r="G40" s="66"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="173"/>
-      <c r="B41" s="178"/>
-      <c r="C41" s="178"/>
-      <c r="D41" s="318">
-        <v>61640.3</v>
-      </c>
-      <c r="E41" s="149"/>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="172" t="s">
+        <v>140</v>
+      </c>
+      <c r="B41" s="177"/>
+      <c r="C41" s="177"/>
+      <c r="D41" s="242">
+        <v>207318.45</v>
+      </c>
+      <c r="E41" s="149" t="s">
+        <v>261</v>
+      </c>
       <c r="G41" s="66"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="173" t="s">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="172" t="s">
+        <v>142</v>
+      </c>
+      <c r="B42" s="177"/>
+      <c r="C42" s="177"/>
+      <c r="D42" s="242">
+        <v>108684.32</v>
+      </c>
+      <c r="E42" s="149" t="str">
+        <f>E41</f>
+        <v>Debito 14/09</v>
+      </c>
+      <c r="G42" s="50"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="172" t="s">
         <v>141</v>
       </c>
-      <c r="B42" s="178"/>
-      <c r="C42" s="178"/>
-      <c r="D42" s="318">
-        <v>207318.45</v>
-      </c>
-      <c r="E42" s="149" t="s">
-        <v>231</v>
-      </c>
-      <c r="G42" s="66"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="173" t="s">
-        <v>143</v>
-      </c>
-      <c r="B43" s="178"/>
-      <c r="C43" s="178"/>
-      <c r="D43" s="318">
-        <v>108684.32</v>
+      <c r="B43" s="177"/>
+      <c r="C43" s="177"/>
+      <c r="D43" s="242">
+        <v>12076.04</v>
       </c>
       <c r="E43" s="149" t="str">
-        <f>E42</f>
-        <v>Debito 12/08</v>
-      </c>
-      <c r="G43" s="50"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="173" t="s">
-        <v>142</v>
-      </c>
-      <c r="B44" s="178"/>
-      <c r="C44" s="178"/>
-      <c r="D44" s="318">
-        <v>12076.04</v>
-      </c>
-      <c r="E44" s="149" t="str">
-        <f>E42</f>
-        <v>Debito 12/08</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="173" t="s">
-        <v>149</v>
-      </c>
-      <c r="B45" s="178"/>
-      <c r="C45" s="178"/>
-      <c r="D45" s="35"/>
-      <c r="E45" s="149"/>
-    </row>
-    <row r="46" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="176" t="s">
-        <v>140</v>
-      </c>
-      <c r="B46" s="176"/>
-      <c r="C46" s="176"/>
-      <c r="D46" s="22"/>
-      <c r="E46" s="41">
-        <f>SUM(D35:D45)</f>
-        <v>2592446.27</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="14" t="s">
+        <f>E41</f>
+        <v>Debito 14/09</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="172" t="s">
+        <v>148</v>
+      </c>
+      <c r="B44" s="177"/>
+      <c r="C44" s="177"/>
+      <c r="D44" s="35"/>
+      <c r="E44" s="149"/>
+    </row>
+    <row r="45" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="175" t="s">
+        <v>139</v>
+      </c>
+      <c r="B45" s="175"/>
+      <c r="C45" s="175"/>
+      <c r="D45" s="22"/>
+      <c r="E45" s="41">
+        <f>SUM(D35:D44)</f>
+        <v>2477977.2199999997</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="B47" s="21"/>
-      <c r="C47" s="21"/>
-      <c r="D47" s="23"/>
-      <c r="E47" s="150"/>
-    </row>
-    <row r="48" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="265" t="s">
+      <c r="B46" s="21"/>
+      <c r="C46" s="21"/>
+      <c r="D46" s="23"/>
+      <c r="E46" s="150"/>
+    </row>
+    <row r="47" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="250" t="s">
+        <v>182</v>
+      </c>
+      <c r="B47" s="251"/>
+      <c r="C47" s="26"/>
+      <c r="D47" s="246">
+        <v>7805</v>
+      </c>
+      <c r="E47" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="B48" s="266"/>
+    </row>
+    <row r="48" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="250" t="s">
+        <v>268</v>
+      </c>
+      <c r="B48" s="251"/>
       <c r="C48" s="26"/>
-      <c r="D48" s="221">
-        <v>7805</v>
+      <c r="D48" s="246">
+        <v>7129</v>
       </c>
       <c r="E48" s="20" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="250" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="265" t="s">
-        <v>185</v>
-      </c>
-      <c r="B49" s="266"/>
+      <c r="B49" s="251"/>
       <c r="C49" s="26"/>
-      <c r="D49" s="221">
+      <c r="D49" s="246">
         <v>213891</v>
       </c>
       <c r="E49" s="20" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="21" t="s">
         <v>107</v>
       </c>
@@ -3265,11 +3314,11 @@
       <c r="C50" s="21"/>
       <c r="D50" s="22"/>
       <c r="E50" s="41">
-        <f>SUM(D48:D49)</f>
-        <v>221696</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+        <f>SUM(D47:D49)</f>
+        <v>228825</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="14" t="s">
         <v>108</v>
       </c>
@@ -3278,42 +3327,42 @@
       <c r="D51" s="28"/>
       <c r="E51" s="151"/>
     </row>
-    <row r="52" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="29" t="s">
         <v>109</v>
       </c>
       <c r="B52" s="29" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C52" s="29"/>
-      <c r="D52" s="320">
+      <c r="D52" s="241">
         <v>635896.65</v>
       </c>
       <c r="E52" s="113" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="29" t="s">
         <v>109</v>
       </c>
       <c r="B53" s="29" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C53" s="29"/>
-      <c r="D53" s="320">
+      <c r="D53" s="241">
         <v>35000.639999999999</v>
       </c>
       <c r="E53" s="113" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="29" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B54" s="29" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C54" s="29"/>
       <c r="D54" s="30">
@@ -3321,9 +3370,9 @@
       </c>
       <c r="E54" s="20"/>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="29" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B55" s="31"/>
       <c r="C55" s="29"/>
@@ -3332,1006 +3381,1000 @@
       </c>
       <c r="E55" s="20"/>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="265" t="s">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="252" t="s">
+        <v>285</v>
+      </c>
+      <c r="B56" s="253"/>
+      <c r="C56" s="29"/>
+      <c r="D56" s="241">
+        <v>5778358.5099999998</v>
+      </c>
+      <c r="E56" s="113" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="250" t="s">
+        <v>274</v>
+      </c>
+      <c r="B57" s="251"/>
+      <c r="C57" s="29"/>
+      <c r="D57" s="241">
+        <v>4488639.75</v>
+      </c>
+      <c r="E57" s="113" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="B56" s="266"/>
-      <c r="C56" s="29"/>
-      <c r="D56" s="30">
-        <v>5805252.4400000004</v>
-      </c>
-      <c r="E56" s="113" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="32" t="s">
+      <c r="B58" s="25"/>
+      <c r="C58" s="29"/>
+      <c r="D58" s="30"/>
+      <c r="E58" s="20"/>
+    </row>
+    <row r="59" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="B57" s="25"/>
-      <c r="C57" s="29"/>
-      <c r="D57" s="30"/>
-      <c r="E57" s="20"/>
-    </row>
-    <row r="58" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="B58" s="21"/>
-      <c r="C58" s="21"/>
-      <c r="D58" s="33"/>
-      <c r="E58" s="152">
-        <f>SUM(D52:D57)</f>
-        <v>6476149.7300000004</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="14"/>
       <c r="B59" s="21"/>
       <c r="C59" s="21"/>
-      <c r="D59" s="22"/>
-      <c r="E59" s="153"/>
-    </row>
-    <row r="60" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="259" t="s">
-        <v>164</v>
-      </c>
-      <c r="B60" s="260"/>
-      <c r="C60" s="29"/>
-      <c r="D60" s="320">
+      <c r="D59" s="33"/>
+      <c r="E59" s="152">
+        <f>SUM(D52:D58)</f>
+        <v>10937895.550000001</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="14"/>
+      <c r="B60" s="21"/>
+      <c r="C60" s="21"/>
+      <c r="D60" s="22"/>
+      <c r="E60" s="153"/>
+    </row>
+    <row r="61" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="252" t="s">
+        <v>163</v>
+      </c>
+      <c r="B61" s="253"/>
+      <c r="C61" s="29"/>
+      <c r="D61" s="241">
         <v>285000</v>
       </c>
-      <c r="E60" s="159" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="259" t="s">
-        <v>274</v>
-      </c>
-      <c r="B61" s="260"/>
-      <c r="C61" s="29"/>
-      <c r="D61" s="320">
-        <v>430000</v>
-      </c>
       <c r="E61" s="159" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="186.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="259" t="s">
-        <v>233</v>
-      </c>
-      <c r="B62" s="260"/>
+        <v>254</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="252" t="s">
+        <v>255</v>
+      </c>
+      <c r="B62" s="253"/>
       <c r="C62" s="29"/>
-      <c r="D62" s="30">
-        <v>3300000</v>
+      <c r="D62" s="241">
+        <f>430000+430000*15%</f>
+        <v>494500</v>
       </c>
       <c r="E62" s="159" t="s">
-        <v>232</v>
-      </c>
-      <c r="F62" s="50"/>
-    </row>
-    <row r="63" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="16" t="s">
-        <v>210</v>
-      </c>
-      <c r="B63" s="17"/>
+        <v>245</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="186.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="252" t="s">
+        <v>266</v>
+      </c>
+      <c r="B63" s="253"/>
       <c r="C63" s="29"/>
-      <c r="D63" s="30">
-        <v>6990</v>
-      </c>
-      <c r="E63" s="34"/>
-      <c r="F63" s="199"/>
-    </row>
-    <row r="64" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="87" t="s">
-        <v>227</v>
+      <c r="D63" s="241">
+        <v>2800000</v>
+      </c>
+      <c r="E63" s="159" t="s">
+        <v>244</v>
+      </c>
+      <c r="F63" s="50"/>
+    </row>
+    <row r="64" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="16" t="s">
+        <v>209</v>
       </c>
       <c r="B64" s="17"/>
       <c r="C64" s="29"/>
-      <c r="D64" s="30">
-        <v>638000</v>
-      </c>
-      <c r="E64" s="34" t="s">
-        <v>230</v>
-      </c>
-      <c r="F64" s="50"/>
-    </row>
-    <row r="65" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="259" t="s">
-        <v>278</v>
-      </c>
-      <c r="B65" s="260"/>
+      <c r="D64" s="241">
+        <v>6990</v>
+      </c>
+      <c r="E64" s="34"/>
+      <c r="F64" s="198"/>
+    </row>
+    <row r="65" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="252" t="s">
+        <v>273</v>
+      </c>
+      <c r="B65" s="253"/>
       <c r="C65" s="29"/>
-      <c r="D65" s="320">
-        <v>800000</v>
+      <c r="D65" s="241">
+        <v>140000</v>
       </c>
       <c r="E65" s="34" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="F65" s="50"/>
     </row>
-    <row r="66" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="259" t="s">
-        <v>225</v>
-      </c>
-      <c r="B66" s="260"/>
+    <row r="66" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="252" t="s">
+        <v>270</v>
+      </c>
+      <c r="B66" s="253"/>
       <c r="C66" s="29"/>
-      <c r="D66" s="30">
+      <c r="D66" s="241">
         <v>31400</v>
       </c>
       <c r="E66" s="34" t="s">
-        <v>232</v>
+        <v>271</v>
       </c>
       <c r="F66" s="50"/>
     </row>
-    <row r="67" spans="1:7" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="259" t="s">
-        <v>280</v>
-      </c>
-      <c r="B67" s="260"/>
+    <row r="67" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="252" t="s">
+        <v>272</v>
+      </c>
+      <c r="B67" s="253"/>
       <c r="C67" s="29"/>
-      <c r="D67" s="320">
+      <c r="D67" s="241">
+        <v>140000</v>
+      </c>
+      <c r="E67" s="34" t="s">
+        <v>271</v>
+      </c>
+      <c r="F67" s="50"/>
+    </row>
+    <row r="68" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="252" t="s">
+        <v>250</v>
+      </c>
+      <c r="B68" s="253"/>
+      <c r="C68" s="29"/>
+      <c r="D68" s="236">
         <v>9000</v>
       </c>
-      <c r="E67" s="159" t="s">
-        <v>226</v>
-      </c>
-      <c r="F67" s="50"/>
-    </row>
-    <row r="68" spans="1:7" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="87" t="s">
-        <v>276</v>
-      </c>
-      <c r="B68" s="17"/>
-      <c r="C68" s="29"/>
-      <c r="D68" s="320">
+      <c r="E68" s="159" t="s">
+        <v>265</v>
+      </c>
+      <c r="F68" s="50"/>
+    </row>
+    <row r="69" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="87" t="s">
+        <v>247</v>
+      </c>
+      <c r="B69" s="17"/>
+      <c r="C69" s="29"/>
+      <c r="D69" s="241">
         <v>158400</v>
       </c>
-      <c r="E68" s="159" t="s">
-        <v>275</v>
-      </c>
-      <c r="F68" s="50"/>
-    </row>
-    <row r="69" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="259" t="s">
-        <v>229</v>
-      </c>
-      <c r="B69" s="260"/>
-      <c r="C69" s="29"/>
-      <c r="D69" s="30">
-        <v>500000</v>
-      </c>
       <c r="E69" s="159" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="F69" s="50"/>
     </row>
-    <row r="70" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="259" t="s">
-        <v>222</v>
-      </c>
-      <c r="B70" s="260"/>
+    <row r="70" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="87" t="s">
+        <v>198</v>
+      </c>
+      <c r="B70" s="17"/>
       <c r="C70" s="29"/>
       <c r="D70" s="30">
-        <v>27660.41</v>
-      </c>
-      <c r="E70" s="159" t="s">
-        <v>224</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E70" s="159"/>
       <c r="F70" s="50"/>
     </row>
-    <row r="71" spans="1:7" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="87" t="s">
-        <v>199</v>
-      </c>
-      <c r="B71" s="17"/>
+    <row r="71" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="252" t="s">
+        <v>241</v>
+      </c>
+      <c r="B71" s="253"/>
       <c r="C71" s="29"/>
       <c r="D71" s="30">
-        <v>379800</v>
-      </c>
-      <c r="E71" s="159" t="s">
-        <v>234</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E71" s="159"/>
       <c r="F71" s="50"/>
     </row>
-    <row r="72" spans="1:7" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="259" t="s">
-        <v>268</v>
-      </c>
-      <c r="B72" s="260"/>
-      <c r="C72" s="29"/>
-      <c r="D72" s="30">
-        <v>124611.12</v>
-      </c>
-      <c r="E72" s="159" t="s">
-        <v>234</v>
-      </c>
-      <c r="F72" s="50"/>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A73" s="21" t="s">
-        <v>0</v>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B72" s="14"/>
+      <c r="C72" s="14"/>
+      <c r="D72" s="36"/>
+      <c r="E72" s="41">
+        <f>SUM(D61:D71)</f>
+        <v>4065290</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="14" t="s">
+        <v>112</v>
       </c>
       <c r="B73" s="14"/>
       <c r="C73" s="14"/>
-      <c r="D73" s="36"/>
-      <c r="E73" s="41">
-        <f>SUM(D60:D72)</f>
-        <v>6690861.5300000003</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A74" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="B74" s="14"/>
-      <c r="C74" s="14"/>
-      <c r="D74" s="15"/>
-      <c r="E74" s="145"/>
-    </row>
-    <row r="75" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="259" t="s">
-        <v>269</v>
-      </c>
-      <c r="B75" s="260"/>
+      <c r="D73" s="15"/>
+      <c r="E73" s="145"/>
+    </row>
+    <row r="74" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="252" t="s">
+        <v>242</v>
+      </c>
+      <c r="B74" s="253"/>
+      <c r="C74" s="18"/>
+      <c r="D74" s="244">
+        <v>781000</v>
+      </c>
+      <c r="E74" s="159" t="s">
+        <v>248</v>
+      </c>
+      <c r="G74" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="252" t="s">
+        <v>253</v>
+      </c>
+      <c r="B75" s="253"/>
       <c r="C75" s="18"/>
-      <c r="D75" s="319">
-        <v>781000</v>
+      <c r="D75" s="245">
+        <v>630000</v>
       </c>
       <c r="E75" s="159" t="s">
-        <v>228</v>
-      </c>
-      <c r="G75" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="259" t="s">
-        <v>283</v>
-      </c>
-      <c r="B76" s="260"/>
+        <v>248</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="B76" s="17"/>
       <c r="C76" s="18"/>
-      <c r="D76" s="321">
-        <v>850000</v>
+      <c r="D76" s="245">
+        <v>250000</v>
       </c>
       <c r="E76" s="159" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="87" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="B77" s="17"/>
       <c r="C77" s="18"/>
-      <c r="D77" s="222">
-        <v>220000</v>
+      <c r="D77" s="245">
+        <v>50000</v>
       </c>
       <c r="E77" s="159" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="B78" s="17"/>
-      <c r="C78" s="18"/>
-      <c r="D78" s="321">
-        <v>250000</v>
-      </c>
-      <c r="E78" s="159" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="B78" s="21"/>
+      <c r="C78" s="21"/>
+      <c r="D78" s="22"/>
+      <c r="E78" s="147">
+        <f>SUM(D74:D77)</f>
+        <v>1711000</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="B79" s="37"/>
+      <c r="C79" s="21"/>
+      <c r="D79" s="38"/>
+      <c r="E79" s="41"/>
+    </row>
+    <row r="80" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="250" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="87" t="s">
-        <v>270</v>
-      </c>
-      <c r="B79" s="17"/>
-      <c r="C79" s="18"/>
-      <c r="D79" s="321">
-        <v>50000</v>
-      </c>
-      <c r="E79" s="159" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A80" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="B80" s="21"/>
-      <c r="C80" s="21"/>
-      <c r="D80" s="22"/>
-      <c r="E80" s="147">
-        <f>SUM(D75:D79)</f>
-        <v>2151000</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A81" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="B81" s="37"/>
-      <c r="C81" s="21"/>
-      <c r="D81" s="38"/>
-      <c r="E81" s="41"/>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A82" s="29" t="s">
-        <v>215</v>
-      </c>
-      <c r="B82" s="86"/>
-      <c r="C82" s="86"/>
-      <c r="D82" s="223">
+      <c r="B80" s="251"/>
+      <c r="C80" s="86"/>
+      <c r="D80" s="248">
         <f>65000+29590.38</f>
         <v>94590.38</v>
       </c>
-      <c r="E82" s="154"/>
-    </row>
-    <row r="83" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="265" t="s">
-        <v>214</v>
-      </c>
-      <c r="B83" s="266"/>
-      <c r="C83" s="86"/>
-      <c r="D83" s="223">
+      <c r="E80" s="154"/>
+    </row>
+    <row r="81" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="250" t="s">
+        <v>213</v>
+      </c>
+      <c r="B81" s="251"/>
+      <c r="C81" s="86"/>
+      <c r="D81" s="215">
         <v>269207.65999999997</v>
       </c>
-      <c r="E83" s="154"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A84" s="39" t="s">
+      <c r="E81" s="154"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="B84" s="39"/>
-      <c r="C84" s="39"/>
-      <c r="D84" s="40"/>
-      <c r="E84" s="41">
-        <f>SUM(D82:D83)</f>
+      <c r="B82" s="39"/>
+      <c r="C82" s="39"/>
+      <c r="D82" s="40"/>
+      <c r="E82" s="41">
+        <f>SUM(D80:D81)</f>
         <v>363798.04</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A85" s="29"/>
-      <c r="B85" s="29"/>
-      <c r="C85" s="29"/>
-      <c r="D85" s="42"/>
-      <c r="E85" s="43"/>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A86" s="44" t="s">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="29"/>
+      <c r="B83" s="29"/>
+      <c r="C83" s="29"/>
+      <c r="D83" s="42"/>
+      <c r="E83" s="43"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="B84" s="44"/>
+      <c r="C84" s="44"/>
+      <c r="D84" s="45"/>
+      <c r="E84" s="46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="47"/>
+      <c r="D85" s="48"/>
+      <c r="E85" s="49"/>
+      <c r="F85" s="50"/>
+    </row>
+    <row r="86" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="51" t="s">
         <v>115</v>
       </c>
-      <c r="B86" s="44"/>
-      <c r="C86" s="44"/>
-      <c r="D86" s="45"/>
-      <c r="E86" s="46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="47"/>
+      <c r="B86" s="52"/>
+      <c r="C86" s="53"/>
+      <c r="D86" s="54"/>
+      <c r="E86" s="55">
+        <f>(SUM(E21:E84))</f>
+        <v>21925285.809999999</v>
+      </c>
+      <c r="F86" s="56"/>
+      <c r="G86" s="50"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D87" s="48"/>
-      <c r="E87" s="49"/>
-      <c r="F87" s="50"/>
-    </row>
-    <row r="88" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="51" t="s">
+      <c r="E87" s="48"/>
+    </row>
+    <row r="88" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D88" s="48"/>
+      <c r="E88" s="48"/>
+      <c r="H88" s="57"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="B88" s="52"/>
-      <c r="C88" s="53"/>
-      <c r="D88" s="54"/>
-      <c r="E88" s="55">
-        <f>(SUM(E21:E86))</f>
-        <v>20385851.57</v>
-      </c>
-      <c r="F88" s="56"/>
-      <c r="G88" s="50"/>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D89" s="48"/>
-      <c r="E89" s="48"/>
-    </row>
-    <row r="90" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D90" s="48"/>
-      <c r="E90" s="48"/>
-      <c r="H90" s="57"/>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A91" s="11" t="s">
+      <c r="B89" s="12"/>
+      <c r="C89" s="13"/>
+      <c r="D89" s="58"/>
+      <c r="E89" s="59"/>
+    </row>
+    <row r="90" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="268"/>
+      <c r="B90" s="268"/>
+      <c r="C90" s="31"/>
+      <c r="D90" s="264"/>
+      <c r="E90" s="266"/>
+    </row>
+    <row r="91" spans="1:8" ht="1.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="268"/>
+      <c r="B91" s="268"/>
+      <c r="C91" s="31"/>
+      <c r="D91" s="265"/>
+      <c r="E91" s="267"/>
+    </row>
+    <row r="92" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="29"/>
+      <c r="B92" s="29"/>
+      <c r="D92" s="42"/>
+      <c r="E92" s="42"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="24"/>
+      <c r="B93" s="61"/>
+      <c r="C93" s="29"/>
+      <c r="D93" s="35"/>
+      <c r="E93" s="60"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" s="62" t="s">
+        <v>144</v>
+      </c>
+      <c r="B94" s="63"/>
+      <c r="C94" s="63"/>
+      <c r="D94" s="111"/>
+      <c r="E94" s="155">
+        <f>SUM(D90:D93)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D95" s="48"/>
+      <c r="E95" s="48"/>
+    </row>
+    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D96" s="48"/>
+      <c r="E96" s="48"/>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="44" t="s">
         <v>117</v>
       </c>
-      <c r="B91" s="12"/>
-      <c r="C91" s="13"/>
-      <c r="D91" s="58"/>
-      <c r="E91" s="59"/>
-    </row>
-    <row r="92" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="271"/>
-      <c r="B92" s="271"/>
-      <c r="C92" s="31"/>
-      <c r="D92" s="267"/>
-      <c r="E92" s="269"/>
-    </row>
-    <row r="93" spans="1:8" ht="1.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="271"/>
-      <c r="B93" s="271"/>
-      <c r="C93" s="31"/>
-      <c r="D93" s="268"/>
-      <c r="E93" s="270"/>
-    </row>
-    <row r="94" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="29"/>
-      <c r="B94" s="29"/>
-      <c r="D94" s="42"/>
-      <c r="E94" s="42"/>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A95" s="24"/>
-      <c r="B95" s="61"/>
-      <c r="C95" s="29"/>
-      <c r="D95" s="35"/>
-      <c r="E95" s="60"/>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A96" s="62" t="s">
-        <v>145</v>
-      </c>
-      <c r="B96" s="63"/>
-      <c r="C96" s="63"/>
-      <c r="D96" s="111"/>
-      <c r="E96" s="155">
-        <f>SUM(D92:D95)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D97" s="48"/>
-      <c r="E97" s="48"/>
-    </row>
-    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B97" s="44"/>
+      <c r="C97" s="44"/>
+      <c r="D97" s="45"/>
+      <c r="E97" s="158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D98" s="48"/>
       <c r="E98" s="48"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A99" s="44" t="s">
+    <row r="99" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="51" t="s">
         <v>118</v>
       </c>
-      <c r="B99" s="44"/>
-      <c r="C99" s="44"/>
-      <c r="D99" s="45"/>
-      <c r="E99" s="158">
-        <v>4500000</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B99" s="52"/>
+      <c r="C99" s="53"/>
+      <c r="D99" s="54"/>
+      <c r="E99" s="55">
+        <f>E94+E97</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D100" s="48"/>
       <c r="E100" s="48"/>
     </row>
-    <row r="101" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="51" t="s">
+    <row r="101" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="64" t="s">
         <v>119</v>
       </c>
-      <c r="B101" s="52"/>
-      <c r="C101" s="53"/>
-      <c r="D101" s="54"/>
-      <c r="E101" s="55">
-        <f>E96+E99</f>
-        <v>4500000</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B101" s="65">
+        <f>E86</f>
+        <v>21925285.809999999</v>
+      </c>
+      <c r="D101" s="48"/>
+      <c r="E101" s="48"/>
+    </row>
+    <row r="102" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="64" t="s">
+        <v>120</v>
+      </c>
+      <c r="B102" s="65">
+        <f>E86-E84</f>
+        <v>21925285.809999999</v>
+      </c>
       <c r="D102" s="48"/>
       <c r="E102" s="48"/>
     </row>
-    <row r="103" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="64" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B103" s="65">
-        <f>E88</f>
-        <v>20385851.57</v>
+        <f>E99-E97</f>
+        <v>0</v>
       </c>
       <c r="D103" s="48"/>
       <c r="E103" s="48"/>
     </row>
-    <row r="104" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="64" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B104" s="65">
-        <f>E88-E86</f>
-        <v>20385851.57</v>
+        <f>E99</f>
+        <v>0</v>
       </c>
       <c r="D104" s="48"/>
       <c r="E104" s="48"/>
     </row>
-    <row r="105" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="64" t="s">
-        <v>122</v>
-      </c>
-      <c r="B105" s="65">
-        <f>E101-E99</f>
-        <v>0</v>
-      </c>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D105" s="48"/>
       <c r="E105" s="48"/>
     </row>
-    <row r="106" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="64" t="s">
-        <v>123</v>
-      </c>
-      <c r="B106" s="65">
-        <f>E101</f>
-        <v>4500000</v>
-      </c>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D106" s="48"/>
       <c r="E106" s="48"/>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="255" t="s">
+        <v>171</v>
+      </c>
+      <c r="B107" s="255"/>
       <c r="D107" s="48"/>
       <c r="E107" s="48"/>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="255"/>
+      <c r="B108" s="255"/>
       <c r="D108" s="48"/>
       <c r="E108" s="48"/>
     </row>
-    <row r="109" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="254" t="s">
-        <v>172</v>
-      </c>
-      <c r="B109" s="254"/>
+    <row r="109" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="255"/>
+      <c r="B109" s="255"/>
       <c r="D109" s="48"/>
       <c r="E109" s="48"/>
     </row>
-    <row r="110" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="254"/>
-      <c r="B110" s="254"/>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D110" s="48"/>
       <c r="E110" s="48"/>
     </row>
-    <row r="111" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="254"/>
-      <c r="B111" s="254"/>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="255" t="s">
+        <v>220</v>
+      </c>
+      <c r="B111" s="255"/>
       <c r="D111" s="48"/>
       <c r="E111" s="48"/>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="255"/>
+      <c r="B112" s="255"/>
       <c r="D112" s="48"/>
       <c r="E112" s="48"/>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="254" t="s">
-        <v>237</v>
-      </c>
-      <c r="B113" s="254"/>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" s="255"/>
+      <c r="B113" s="255"/>
       <c r="D113" s="48"/>
       <c r="E113" s="48"/>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="254"/>
-      <c r="B114" s="254"/>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D114" s="48"/>
       <c r="E114" s="48"/>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="254"/>
-      <c r="B115" s="254"/>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" s="255" t="s">
+        <v>221</v>
+      </c>
+      <c r="B115" s="255"/>
       <c r="D115" s="48"/>
       <c r="E115" s="48"/>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" s="255"/>
+      <c r="B116" s="255"/>
       <c r="D116" s="48"/>
       <c r="E116" s="48"/>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="254" t="s">
-        <v>238</v>
-      </c>
-      <c r="B117" s="254"/>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" s="255"/>
+      <c r="B117" s="255"/>
       <c r="D117" s="48"/>
       <c r="E117" s="48"/>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="254"/>
-      <c r="B118" s="254"/>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D118" s="48"/>
       <c r="E118" s="48"/>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="254"/>
-      <c r="B119" s="254"/>
+    <row r="119" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="255" t="s">
+        <v>197</v>
+      </c>
+      <c r="B119" s="255"/>
       <c r="D119" s="48"/>
       <c r="E119" s="48"/>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="255"/>
+      <c r="B120" s="255"/>
       <c r="D120" s="48"/>
       <c r="E120" s="48"/>
     </row>
-    <row r="121" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="254" t="s">
-        <v>198</v>
-      </c>
-      <c r="B121" s="254"/>
+    <row r="121" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="255"/>
+      <c r="B121" s="255"/>
       <c r="D121" s="48"/>
       <c r="E121" s="48"/>
     </row>
-    <row r="122" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="254"/>
-      <c r="B122" s="254"/>
+    <row r="122" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D122" s="48"/>
       <c r="E122" s="48"/>
-    </row>
-    <row r="123" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="254"/>
-      <c r="B123" s="254"/>
+      <c r="F122" s="197"/>
+    </row>
+    <row r="123" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="255" t="s">
+        <v>178</v>
+      </c>
+      <c r="B123" s="255"/>
       <c r="D123" s="48"/>
       <c r="E123" s="48"/>
     </row>
-    <row r="124" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="255"/>
+      <c r="B124" s="255"/>
       <c r="D124" s="48"/>
       <c r="E124" s="48"/>
-      <c r="F124" s="198"/>
-    </row>
-    <row r="125" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="254" t="s">
-        <v>179</v>
-      </c>
-      <c r="B125" s="254"/>
+    </row>
+    <row r="125" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="255"/>
+      <c r="B125" s="255"/>
       <c r="D125" s="48"/>
       <c r="E125" s="48"/>
     </row>
-    <row r="126" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="254"/>
-      <c r="B126" s="254"/>
+    <row r="126" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D126" s="48"/>
       <c r="E126" s="48"/>
     </row>
-    <row r="127" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="254"/>
-      <c r="B127" s="254"/>
+    <row r="127" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="255" t="s">
+        <v>181</v>
+      </c>
+      <c r="B127" s="255"/>
       <c r="D127" s="48"/>
       <c r="E127" s="48"/>
     </row>
-    <row r="128" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="255"/>
+      <c r="B128" s="255"/>
       <c r="D128" s="48"/>
       <c r="E128" s="48"/>
     </row>
-    <row r="129" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="254" t="s">
-        <v>182</v>
-      </c>
-      <c r="B129" s="254"/>
+    <row r="129" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="255"/>
+      <c r="B129" s="255"/>
       <c r="D129" s="48"/>
       <c r="E129" s="48"/>
     </row>
-    <row r="130" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="254"/>
-      <c r="B130" s="254"/>
+    <row r="130" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D130" s="48"/>
       <c r="E130" s="48"/>
     </row>
-    <row r="131" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="254"/>
-      <c r="B131" s="254"/>
+    <row r="131" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="255" t="s">
+        <v>180</v>
+      </c>
+      <c r="B131" s="255"/>
       <c r="D131" s="48"/>
       <c r="E131" s="48"/>
     </row>
-    <row r="132" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="255"/>
+      <c r="B132" s="255"/>
       <c r="D132" s="48"/>
       <c r="E132" s="48"/>
     </row>
-    <row r="133" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="254" t="s">
-        <v>181</v>
-      </c>
-      <c r="B133" s="254"/>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" s="255"/>
+      <c r="B133" s="255"/>
       <c r="D133" s="48"/>
       <c r="E133" s="48"/>
     </row>
-    <row r="134" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="254"/>
-      <c r="B134" s="254"/>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D134" s="48"/>
       <c r="E134" s="48"/>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="254"/>
-      <c r="B135" s="254"/>
-      <c r="D135" s="48"/>
-      <c r="E135" s="48"/>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D136" s="48"/>
-      <c r="E136" s="48"/>
-    </row>
-    <row r="137" spans="1:6" s="68" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A137"/>
-      <c r="B137" s="66"/>
-      <c r="C137" s="67"/>
-      <c r="D137" s="156"/>
-      <c r="E137" s="156"/>
-    </row>
-    <row r="138" spans="1:6" s="68" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="207" t="s">
-        <v>188</v>
-      </c>
-      <c r="B138" s="208">
+    <row r="135" spans="1:6" s="68" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A135"/>
+      <c r="B135" s="66"/>
+      <c r="C135" s="67"/>
+      <c r="D135" s="156"/>
+      <c r="E135" s="156"/>
+    </row>
+    <row r="136" spans="1:6" s="68" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="206" t="s">
+        <v>187</v>
+      </c>
+      <c r="B136" s="207">
         <v>1157299.74</v>
       </c>
-      <c r="C138" s="67"/>
-      <c r="D138" s="157"/>
-      <c r="E138" s="157"/>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="209" t="s">
-        <v>144</v>
-      </c>
-      <c r="B139" s="210">
-        <f>-B104-B105</f>
-        <v>-20385851.57</v>
+      <c r="C136" s="67"/>
+      <c r="D136" s="157"/>
+      <c r="E136" s="157"/>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" s="208" t="s">
+        <v>143</v>
+      </c>
+      <c r="B137" s="209">
+        <f>-B102-B103</f>
+        <v>-21925285.809999999</v>
+      </c>
+      <c r="D137" s="48"/>
+      <c r="E137" s="48"/>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" s="208" t="s">
+        <v>123</v>
+      </c>
+      <c r="B138" s="210">
+        <f>B168</f>
+        <v>0</v>
+      </c>
+      <c r="D138" s="48"/>
+      <c r="E138" s="48"/>
+      <c r="F138" s="66"/>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" s="208" t="s">
+        <v>2</v>
+      </c>
+      <c r="B139" s="211">
+        <f>PRORRATEO!F119</f>
+        <v>18974843.529999997</v>
       </c>
       <c r="D139" s="48"/>
       <c r="E139" s="48"/>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="209" t="s">
-        <v>124</v>
-      </c>
-      <c r="B140" s="211">
-        <f>B163</f>
-        <v>0</v>
+      <c r="F139" s="66"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" s="208" t="s">
+        <v>259</v>
+      </c>
+      <c r="B140" s="243">
+        <v>-24000</v>
       </c>
       <c r="D140" s="48"/>
       <c r="E140" s="48"/>
       <c r="F140" s="66"/>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="209" t="s">
-        <v>2</v>
-      </c>
-      <c r="B141" s="212">
-        <f>PRORRATEO!F119</f>
-        <v>21426698.540000003</v>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" s="208" t="s">
+        <v>279</v>
+      </c>
+      <c r="B141" s="243">
+        <v>-200000</v>
       </c>
       <c r="D141" s="48"/>
       <c r="E141" s="48"/>
       <c r="F141" s="66"/>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="209" t="s">
-        <v>223</v>
-      </c>
-      <c r="B142" s="213">
-        <v>-155000</v>
+    <row r="142" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A142" s="208" t="s">
+        <v>216</v>
+      </c>
+      <c r="B142" s="243">
+        <v>-5877</v>
       </c>
       <c r="D142" s="48"/>
       <c r="E142" s="48"/>
       <c r="F142" s="66"/>
     </row>
-    <row r="143" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="209" t="s">
-        <v>239</v>
-      </c>
-      <c r="B143" s="213">
-        <v>-155000</v>
-      </c>
-      <c r="D143" s="48"/>
-      <c r="E143" s="48"/>
-      <c r="F143" s="66"/>
-    </row>
-    <row r="144" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="209" t="s">
-        <v>243</v>
-      </c>
-      <c r="B144" s="214">
-        <v>145000</v>
-      </c>
+    <row r="143" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A143" s="204" t="s">
+        <v>159</v>
+      </c>
+      <c r="B143" s="205">
+        <f>SUM(B136:C142)</f>
+        <v>-2023019.5400000028</v>
+      </c>
+      <c r="D143" s="216"/>
+      <c r="E143" s="50"/>
+      <c r="F143" s="50"/>
+    </row>
+    <row r="144" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D144" s="48"/>
-      <c r="E144" s="48"/>
-      <c r="F144" s="66"/>
-    </row>
-    <row r="145" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="209" t="s">
-        <v>250</v>
-      </c>
-      <c r="B145" s="214">
-        <v>145000</v>
-      </c>
-      <c r="D145" s="48"/>
-      <c r="E145" s="48"/>
-      <c r="F145" s="66"/>
-    </row>
-    <row r="146" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="209" t="s">
-        <v>252</v>
-      </c>
-      <c r="B146" s="213">
-        <v>-1500000</v>
-      </c>
-      <c r="D146" s="48"/>
-      <c r="E146" s="48"/>
-      <c r="F146" s="66"/>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A147" s="209" t="s">
-        <v>218</v>
-      </c>
-      <c r="B147" s="215">
-        <f>-12043-6808-18270</f>
-        <v>-37121</v>
-      </c>
-      <c r="D147" s="48"/>
-      <c r="E147" s="48"/>
-      <c r="F147" s="66"/>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A148" s="209" t="s">
-        <v>247</v>
-      </c>
-      <c r="B148" s="215">
-        <v>-300000</v>
-      </c>
-      <c r="D148" s="48"/>
-      <c r="E148" s="48"/>
-      <c r="F148" s="66"/>
-    </row>
-    <row r="149" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A149" s="216" t="s">
-        <v>217</v>
-      </c>
-      <c r="B149" s="217">
-        <v>-320000</v>
-      </c>
-      <c r="D149" s="48"/>
-      <c r="E149" s="48"/>
-      <c r="F149" s="66"/>
-    </row>
-    <row r="150" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A150" s="205" t="s">
-        <v>160</v>
-      </c>
-      <c r="B150" s="206">
-        <f>SUM(B138:C149)</f>
-        <v>21025.710000000894</v>
-      </c>
-      <c r="D150" s="224"/>
-      <c r="E150" s="50"/>
-      <c r="F150" s="50"/>
-    </row>
-    <row r="151" spans="1:6" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D151" s="48"/>
-    </row>
-    <row r="152" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="207" t="s">
-        <v>256</v>
-      </c>
-      <c r="B152" s="208">
-        <v>0</v>
-      </c>
+    </row>
+    <row r="145" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="319" t="s">
+        <v>286</v>
+      </c>
+      <c r="B145" s="319"/>
+      <c r="C145" s="319"/>
+      <c r="D145" s="319"/>
+    </row>
+    <row r="146" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="319"/>
+      <c r="B146" s="319"/>
+      <c r="C146" s="319"/>
+      <c r="D146" s="319"/>
+    </row>
+    <row r="147" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="319"/>
+      <c r="B147" s="319"/>
+      <c r="C147" s="319"/>
+      <c r="D147" s="319"/>
+    </row>
+    <row r="148" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="319"/>
+      <c r="B148" s="319"/>
+      <c r="C148" s="319"/>
+      <c r="D148" s="319"/>
+    </row>
+    <row r="149" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="319"/>
+      <c r="B149" s="319"/>
+      <c r="C149" s="319"/>
+      <c r="D149" s="319"/>
+    </row>
+    <row r="150" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="319"/>
+      <c r="B150" s="319"/>
+      <c r="C150" s="319"/>
+      <c r="D150" s="319"/>
+    </row>
+    <row r="151" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="319"/>
+      <c r="B151" s="319"/>
+      <c r="C151" s="319"/>
+      <c r="D151" s="319"/>
+    </row>
+    <row r="152" spans="1:4" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D152" s="48"/>
     </row>
-    <row r="153" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="209" t="s">
-        <v>253</v>
-      </c>
-      <c r="B153" s="218">
+    <row r="153" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="206" t="s">
+        <v>282</v>
+      </c>
+      <c r="B153" s="207">
+        <v>0</v>
+      </c>
+      <c r="D153" s="48"/>
+    </row>
+    <row r="154" spans="1:4" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A154" s="208" t="s">
+        <v>284</v>
+      </c>
+      <c r="B154" s="211">
+        <v>320000</v>
+      </c>
+      <c r="D154" s="48"/>
+    </row>
+    <row r="155" spans="1:4" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A155" s="204" t="s">
+        <v>283</v>
+      </c>
+      <c r="B155" s="205">
+        <f>SUM(B153:C154)</f>
+        <v>320000</v>
+      </c>
+      <c r="D155" s="48"/>
+    </row>
+    <row r="156" spans="1:4" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D156" s="48"/>
+    </row>
+    <row r="157" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="206" t="s">
+        <v>229</v>
+      </c>
+      <c r="B157" s="207">
+        <v>0</v>
+      </c>
+      <c r="D157" s="48"/>
+    </row>
+    <row r="158" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="208" t="s">
+        <v>226</v>
+      </c>
+      <c r="B158" s="212">
         <v>1500000</v>
       </c>
-      <c r="D153" s="48"/>
-    </row>
-    <row r="154" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A154" s="219" t="s">
-        <v>254</v>
-      </c>
-      <c r="B154" s="220">
-        <f>1506421.54-B153</f>
+      <c r="D158" s="48"/>
+    </row>
+    <row r="159" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A159" s="213" t="s">
+        <v>227</v>
+      </c>
+      <c r="B159" s="214">
+        <f>1506421.54-B158</f>
         <v>6421.5400000000373</v>
       </c>
-      <c r="D154" s="48"/>
-    </row>
-    <row r="155" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A155" s="205" t="s">
-        <v>255</v>
-      </c>
-      <c r="B155" s="206">
-        <f>SUM(B152:B154)</f>
+      <c r="D159" s="48"/>
+    </row>
+    <row r="160" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A160" s="204" t="s">
+        <v>228</v>
+      </c>
+      <c r="B160" s="205">
+        <f>SUM(B157:B159)</f>
         <v>1506421.54</v>
       </c>
-      <c r="D155" s="48"/>
-    </row>
-    <row r="156" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D156" s="48"/>
-    </row>
-    <row r="157" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D157" s="48"/>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A158" s="253" t="s">
-        <v>125</v>
-      </c>
-      <c r="B158" s="253"/>
-      <c r="C158" s="253"/>
-      <c r="D158" s="48"/>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A159" s="253"/>
-      <c r="B159" s="253"/>
-      <c r="C159" s="253"/>
-      <c r="D159" s="48"/>
-    </row>
-    <row r="160" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="69"/>
-      <c r="B160" s="110"/>
-      <c r="C160" s="70"/>
-      <c r="D160" s="225"/>
-    </row>
-    <row r="161" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A161" s="69"/>
-      <c r="B161" s="110"/>
-      <c r="C161" s="70"/>
-      <c r="D161" s="225"/>
-    </row>
-    <row r="162" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="69"/>
-      <c r="B162" s="110"/>
-      <c r="C162" s="70"/>
-      <c r="D162" s="56"/>
-    </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A163" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="B163" s="72">
-        <f>SUM(B160:B162)</f>
-        <v>0</v>
-      </c>
-      <c r="C163" s="73"/>
-    </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M164" s="74"/>
+      <c r="D160" s="48"/>
+    </row>
+    <row r="161" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D161" s="48"/>
+    </row>
+    <row r="162" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D162" s="48"/>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A163" s="254" t="s">
+        <v>124</v>
+      </c>
+      <c r="B163" s="254"/>
+      <c r="C163" s="254"/>
+      <c r="D163" s="48"/>
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A164" s="254"/>
+      <c r="B164" s="254"/>
+      <c r="C164" s="254"/>
+      <c r="D164" s="48"/>
+    </row>
+    <row r="165" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="69"/>
+      <c r="B165" s="110"/>
+      <c r="C165" s="70"/>
+      <c r="D165" s="217"/>
+    </row>
+    <row r="166" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="69"/>
+      <c r="B166" s="110"/>
+      <c r="C166" s="70"/>
+      <c r="D166" s="217"/>
+    </row>
+    <row r="167" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="69"/>
+      <c r="B167" s="110"/>
+      <c r="C167" s="70"/>
+      <c r="D167" s="56"/>
+    </row>
+    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A168" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="B168" s="72">
+        <f>SUM(B165:B167)</f>
+        <v>0</v>
+      </c>
+      <c r="C168" s="73"/>
+    </row>
+    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M169" s="74"/>
     </row>
   </sheetData>
-  <mergeCells count="33">
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="D92:D93"/>
-    <mergeCell ref="E92:E93"/>
-    <mergeCell ref="A83:B83"/>
+  <mergeCells count="36">
+    <mergeCell ref="D90:D91"/>
+    <mergeCell ref="E90:E91"/>
+    <mergeCell ref="A81:B81"/>
     <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A92:B93"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A90:B91"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A80:B80"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A74:B74"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A68:B68"/>
     <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A67:B67"/>
     <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="A158:C159"/>
-    <mergeCell ref="A121:B123"/>
-    <mergeCell ref="A133:B135"/>
-    <mergeCell ref="A129:B131"/>
-    <mergeCell ref="A109:B111"/>
-    <mergeCell ref="A125:B127"/>
-    <mergeCell ref="A113:B115"/>
-    <mergeCell ref="A117:B119"/>
+    <mergeCell ref="A163:C164"/>
+    <mergeCell ref="A119:B121"/>
+    <mergeCell ref="A131:B133"/>
+    <mergeCell ref="A127:B129"/>
+    <mergeCell ref="A107:B109"/>
+    <mergeCell ref="A123:B125"/>
+    <mergeCell ref="A111:B113"/>
+    <mergeCell ref="A115:B117"/>
+    <mergeCell ref="A145:D151"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="90" orientation="portrait" r:id="rId1"/>
@@ -4342,59 +4385,59 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{533DB7A7-09F4-49CF-B824-70F15C1FF525}">
   <dimension ref="A1:Q135"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <col min="2" max="2" width="25.5546875" customWidth="1"/>
-    <col min="3" max="3" width="0.109375" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" customWidth="1"/>
-    <col min="8" max="8" width="9.5546875" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" customWidth="1"/>
-    <col min="10" max="11" width="16.33203125" customWidth="1"/>
-    <col min="12" max="12" width="12.33203125" customWidth="1"/>
-    <col min="13" max="13" width="16.109375" customWidth="1"/>
-    <col min="14" max="14" width="14.6640625" customWidth="1"/>
-    <col min="15" max="15" width="14.33203125" customWidth="1"/>
-    <col min="16" max="16" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="25.5703125" customWidth="1"/>
+    <col min="3" max="3" width="0.140625" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" customWidth="1"/>
+    <col min="10" max="11" width="16.28515625" customWidth="1"/>
+    <col min="12" max="12" width="12.28515625" customWidth="1"/>
+    <col min="13" max="13" width="16.140625" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" customWidth="1"/>
+    <col min="16" max="16" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="88"/>
       <c r="B1" s="89"/>
       <c r="C1" s="89"/>
-      <c r="D1" s="287"/>
-      <c r="E1" s="287"/>
-      <c r="F1" s="287"/>
-      <c r="G1" s="287"/>
-      <c r="H1" s="287"/>
-      <c r="I1" s="287"/>
-      <c r="J1" s="287"/>
-      <c r="K1" s="287"/>
-      <c r="L1" s="287"/>
-      <c r="M1" s="287"/>
-      <c r="N1" s="287"/>
+      <c r="D1" s="284"/>
+      <c r="E1" s="284"/>
+      <c r="F1" s="284"/>
+      <c r="G1" s="284"/>
+      <c r="H1" s="284"/>
+      <c r="I1" s="284"/>
+      <c r="J1" s="284"/>
+      <c r="K1" s="284"/>
+      <c r="L1" s="284"/>
+      <c r="M1" s="284"/>
+      <c r="N1" s="284"/>
       <c r="O1" s="90"/>
     </row>
-    <row r="2" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="91"/>
       <c r="B2" s="92"/>
       <c r="C2" s="93"/>
       <c r="D2" s="93" t="s">
-        <v>126</v>
-      </c>
-      <c r="E2" s="309">
+        <v>125</v>
+      </c>
+      <c r="E2" s="306">
         <v>4500000</v>
       </c>
-      <c r="F2" s="309"/>
+      <c r="F2" s="306"/>
       <c r="G2" s="93"/>
       <c r="H2" s="93"/>
       <c r="I2" s="93" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J2" s="94">
         <f>16000000-M2+1500000</f>
@@ -4402,7 +4445,7 @@
       </c>
       <c r="K2" s="94"/>
       <c r="L2" s="94" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="M2" s="94">
         <v>5805252.4400000004</v>
@@ -4414,7 +4457,7 @@
         <v>13312274.1</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="97"/>
       <c r="B3" s="98"/>
       <c r="C3" s="98"/>
@@ -4432,241 +4475,241 @@
       <c r="O3" s="101"/>
       <c r="P3" s="75"/>
     </row>
-    <row r="4" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="288" t="s">
-        <v>159</v>
-      </c>
-      <c r="B4" s="289"/>
-      <c r="C4" s="289"/>
-      <c r="D4" s="289"/>
-      <c r="E4" s="289"/>
-      <c r="F4" s="289"/>
-      <c r="G4" s="289"/>
-      <c r="H4" s="289"/>
-      <c r="I4" s="289"/>
-      <c r="J4" s="289"/>
-      <c r="K4" s="289"/>
-      <c r="L4" s="289"/>
-      <c r="M4" s="289"/>
-      <c r="N4" s="289"/>
-      <c r="O4" s="290"/>
+    <row r="4" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="285" t="s">
+        <v>158</v>
+      </c>
+      <c r="B4" s="286"/>
+      <c r="C4" s="286"/>
+      <c r="D4" s="286"/>
+      <c r="E4" s="286"/>
+      <c r="F4" s="286"/>
+      <c r="G4" s="286"/>
+      <c r="H4" s="286"/>
+      <c r="I4" s="286"/>
+      <c r="J4" s="286"/>
+      <c r="K4" s="286"/>
+      <c r="L4" s="286"/>
+      <c r="M4" s="286"/>
+      <c r="N4" s="286"/>
+      <c r="O4" s="287"/>
       <c r="P4" s="75"/>
     </row>
-    <row r="5" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="291"/>
-      <c r="B5" s="292"/>
-      <c r="C5" s="292"/>
-      <c r="D5" s="292"/>
-      <c r="E5" s="292"/>
-      <c r="F5" s="292"/>
-      <c r="G5" s="292"/>
-      <c r="H5" s="292"/>
-      <c r="I5" s="292"/>
-      <c r="J5" s="292"/>
-      <c r="K5" s="292"/>
-      <c r="L5" s="292"/>
-      <c r="M5" s="292"/>
-      <c r="N5" s="292"/>
-      <c r="O5" s="293"/>
+    <row r="5" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="288"/>
+      <c r="B5" s="289"/>
+      <c r="C5" s="289"/>
+      <c r="D5" s="289"/>
+      <c r="E5" s="289"/>
+      <c r="F5" s="289"/>
+      <c r="G5" s="289"/>
+      <c r="H5" s="289"/>
+      <c r="I5" s="289"/>
+      <c r="J5" s="289"/>
+      <c r="K5" s="289"/>
+      <c r="L5" s="289"/>
+      <c r="M5" s="289"/>
+      <c r="N5" s="289"/>
+      <c r="O5" s="290"/>
       <c r="P5" s="75"/>
     </row>
-    <row r="6" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="291"/>
-      <c r="B6" s="292"/>
-      <c r="C6" s="292"/>
-      <c r="D6" s="292"/>
-      <c r="E6" s="292"/>
-      <c r="F6" s="292"/>
-      <c r="G6" s="292"/>
-      <c r="H6" s="292"/>
-      <c r="I6" s="292"/>
-      <c r="J6" s="292"/>
-      <c r="K6" s="292"/>
-      <c r="L6" s="292"/>
-      <c r="M6" s="292"/>
-      <c r="N6" s="292"/>
-      <c r="O6" s="293"/>
+    <row r="6" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="288"/>
+      <c r="B6" s="289"/>
+      <c r="C6" s="289"/>
+      <c r="D6" s="289"/>
+      <c r="E6" s="289"/>
+      <c r="F6" s="289"/>
+      <c r="G6" s="289"/>
+      <c r="H6" s="289"/>
+      <c r="I6" s="289"/>
+      <c r="J6" s="289"/>
+      <c r="K6" s="289"/>
+      <c r="L6" s="289"/>
+      <c r="M6" s="289"/>
+      <c r="N6" s="289"/>
+      <c r="O6" s="290"/>
       <c r="P6" s="75"/>
     </row>
-    <row r="7" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="291"/>
-      <c r="B7" s="292"/>
-      <c r="C7" s="292"/>
-      <c r="D7" s="292"/>
-      <c r="E7" s="292"/>
-      <c r="F7" s="292"/>
-      <c r="G7" s="292"/>
-      <c r="H7" s="292"/>
-      <c r="I7" s="292"/>
-      <c r="J7" s="292"/>
-      <c r="K7" s="292"/>
-      <c r="L7" s="292"/>
-      <c r="M7" s="292"/>
-      <c r="N7" s="292"/>
-      <c r="O7" s="293"/>
+    <row r="7" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="288"/>
+      <c r="B7" s="289"/>
+      <c r="C7" s="289"/>
+      <c r="D7" s="289"/>
+      <c r="E7" s="289"/>
+      <c r="F7" s="289"/>
+      <c r="G7" s="289"/>
+      <c r="H7" s="289"/>
+      <c r="I7" s="289"/>
+      <c r="J7" s="289"/>
+      <c r="K7" s="289"/>
+      <c r="L7" s="289"/>
+      <c r="M7" s="289"/>
+      <c r="N7" s="289"/>
+      <c r="O7" s="290"/>
       <c r="P7" s="75"/>
     </row>
-    <row r="8" spans="1:17" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="294"/>
-      <c r="B8" s="295"/>
-      <c r="C8" s="295"/>
-      <c r="D8" s="295"/>
-      <c r="E8" s="295"/>
-      <c r="F8" s="295"/>
-      <c r="G8" s="295"/>
-      <c r="H8" s="295"/>
-      <c r="I8" s="295"/>
-      <c r="J8" s="295"/>
-      <c r="K8" s="295"/>
-      <c r="L8" s="295"/>
-      <c r="M8" s="295"/>
-      <c r="N8" s="295"/>
-      <c r="O8" s="296"/>
-    </row>
-    <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="303" t="s">
+    <row r="8" spans="1:17" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="291"/>
+      <c r="B8" s="292"/>
+      <c r="C8" s="292"/>
+      <c r="D8" s="292"/>
+      <c r="E8" s="292"/>
+      <c r="F8" s="292"/>
+      <c r="G8" s="292"/>
+      <c r="H8" s="292"/>
+      <c r="I8" s="292"/>
+      <c r="J8" s="292"/>
+      <c r="K8" s="292"/>
+      <c r="L8" s="292"/>
+      <c r="M8" s="292"/>
+      <c r="N8" s="292"/>
+      <c r="O8" s="293"/>
+    </row>
+    <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="300" t="s">
+        <v>156</v>
+      </c>
+      <c r="B9" s="301"/>
+      <c r="C9" s="301"/>
+      <c r="D9" s="301"/>
+      <c r="E9" s="301"/>
+      <c r="F9" s="301"/>
+      <c r="G9" s="301"/>
+      <c r="H9" s="301"/>
+      <c r="I9" s="301"/>
+      <c r="J9" s="301"/>
+      <c r="K9" s="301"/>
+      <c r="L9" s="301"/>
+      <c r="M9" s="301"/>
+      <c r="N9" s="301"/>
+      <c r="O9" s="302"/>
+    </row>
+    <row r="10" spans="1:17" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="273" t="s">
+        <v>210</v>
+      </c>
+      <c r="B10" s="274"/>
+      <c r="C10" s="274"/>
+      <c r="D10" s="274"/>
+      <c r="E10" s="274"/>
+      <c r="F10" s="274"/>
+      <c r="G10" s="274"/>
+      <c r="H10" s="274"/>
+      <c r="I10" s="274"/>
+      <c r="J10" s="274"/>
+      <c r="K10" s="274"/>
+      <c r="L10" s="274"/>
+      <c r="M10" s="274"/>
+      <c r="N10" s="274"/>
+      <c r="O10" s="275"/>
+    </row>
+    <row r="11" spans="1:17" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="276" t="s">
+        <v>211</v>
+      </c>
+      <c r="B11" s="277"/>
+      <c r="C11" s="277"/>
+      <c r="D11" s="277"/>
+      <c r="E11" s="277"/>
+      <c r="F11" s="277"/>
+      <c r="G11" s="277"/>
+      <c r="H11" s="277"/>
+      <c r="I11" s="277"/>
+      <c r="J11" s="277"/>
+      <c r="K11" s="277"/>
+      <c r="L11" s="277"/>
+      <c r="M11" s="277"/>
+      <c r="N11" s="277"/>
+      <c r="O11" s="278"/>
+    </row>
+    <row r="12" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="303" t="s">
         <v>157</v>
       </c>
-      <c r="B9" s="304"/>
-      <c r="C9" s="304"/>
-      <c r="D9" s="304"/>
-      <c r="E9" s="304"/>
-      <c r="F9" s="304"/>
-      <c r="G9" s="304"/>
-      <c r="H9" s="304"/>
-      <c r="I9" s="304"/>
-      <c r="J9" s="304"/>
-      <c r="K9" s="304"/>
-      <c r="L9" s="304"/>
-      <c r="M9" s="304"/>
-      <c r="N9" s="304"/>
-      <c r="O9" s="305"/>
-    </row>
-    <row r="10" spans="1:17" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="276" t="s">
-        <v>211</v>
-      </c>
-      <c r="B10" s="277"/>
-      <c r="C10" s="277"/>
-      <c r="D10" s="277"/>
-      <c r="E10" s="277"/>
-      <c r="F10" s="277"/>
-      <c r="G10" s="277"/>
-      <c r="H10" s="277"/>
-      <c r="I10" s="277"/>
-      <c r="J10" s="277"/>
-      <c r="K10" s="277"/>
-      <c r="L10" s="277"/>
-      <c r="M10" s="277"/>
-      <c r="N10" s="277"/>
-      <c r="O10" s="278"/>
-    </row>
-    <row r="11" spans="1:17" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="279" t="s">
-        <v>212</v>
-      </c>
-      <c r="B11" s="280"/>
-      <c r="C11" s="280"/>
-      <c r="D11" s="280"/>
-      <c r="E11" s="280"/>
-      <c r="F11" s="280"/>
-      <c r="G11" s="280"/>
-      <c r="H11" s="280"/>
-      <c r="I11" s="280"/>
-      <c r="J11" s="280"/>
-      <c r="K11" s="280"/>
-      <c r="L11" s="280"/>
-      <c r="M11" s="280"/>
-      <c r="N11" s="280"/>
-      <c r="O11" s="281"/>
-    </row>
-    <row r="12" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="306" t="s">
-        <v>158</v>
-      </c>
-      <c r="B12" s="307"/>
-      <c r="C12" s="307"/>
-      <c r="D12" s="307"/>
-      <c r="E12" s="307"/>
-      <c r="F12" s="307"/>
-      <c r="G12" s="307"/>
-      <c r="H12" s="307"/>
-      <c r="I12" s="307"/>
-      <c r="J12" s="307"/>
-      <c r="K12" s="307"/>
-      <c r="L12" s="307"/>
-      <c r="M12" s="307"/>
-      <c r="N12" s="307"/>
-      <c r="O12" s="308"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" s="297" t="s">
+      <c r="B12" s="304"/>
+      <c r="C12" s="304"/>
+      <c r="D12" s="304"/>
+      <c r="E12" s="304"/>
+      <c r="F12" s="304"/>
+      <c r="G12" s="304"/>
+      <c r="H12" s="304"/>
+      <c r="I12" s="304"/>
+      <c r="J12" s="304"/>
+      <c r="K12" s="304"/>
+      <c r="L12" s="304"/>
+      <c r="M12" s="304"/>
+      <c r="N12" s="304"/>
+      <c r="O12" s="305"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="294" t="s">
+        <v>127</v>
+      </c>
+      <c r="B13" s="296" t="s">
         <v>128</v>
       </c>
-      <c r="B13" s="299" t="s">
+      <c r="C13" s="296" t="s">
         <v>129</v>
       </c>
-      <c r="C13" s="299" t="s">
+      <c r="D13" s="296" t="s">
         <v>130</v>
       </c>
-      <c r="D13" s="299" t="s">
+      <c r="E13" s="271" t="s">
         <v>131</v>
       </c>
-      <c r="E13" s="274" t="s">
+      <c r="F13" s="296" t="s">
         <v>132</v>
       </c>
-      <c r="F13" s="299" t="s">
+      <c r="G13" s="298" t="s">
         <v>133</v>
       </c>
-      <c r="G13" s="301" t="s">
+      <c r="H13" s="271" t="s">
         <v>134</v>
       </c>
-      <c r="H13" s="274" t="s">
+      <c r="I13" s="271" t="s">
+        <v>126</v>
+      </c>
+      <c r="J13" s="271" t="s">
+        <v>125</v>
+      </c>
+      <c r="K13" s="281" t="s">
+        <v>217</v>
+      </c>
+      <c r="L13" s="307" t="s">
+        <v>173</v>
+      </c>
+      <c r="M13" s="269" t="s">
+        <v>179</v>
+      </c>
+      <c r="N13" s="138" t="s">
+        <v>206</v>
+      </c>
+      <c r="O13" s="279" t="s">
         <v>135</v>
       </c>
-      <c r="I13" s="274" t="s">
-        <v>127</v>
-      </c>
-      <c r="J13" s="274" t="s">
-        <v>126</v>
-      </c>
-      <c r="K13" s="284" t="s">
-        <v>219</v>
-      </c>
-      <c r="L13" s="310" t="s">
-        <v>174</v>
-      </c>
-      <c r="M13" s="272" t="s">
-        <v>180</v>
-      </c>
-      <c r="N13" s="138" t="s">
-        <v>207</v>
-      </c>
-      <c r="O13" s="282" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="298"/>
-      <c r="B14" s="300"/>
-      <c r="C14" s="300"/>
-      <c r="D14" s="300"/>
-      <c r="E14" s="275"/>
-      <c r="F14" s="300"/>
-      <c r="G14" s="302"/>
-      <c r="H14" s="275"/>
-      <c r="I14" s="275"/>
-      <c r="J14" s="275"/>
-      <c r="K14" s="285"/>
-      <c r="L14" s="311"/>
-      <c r="M14" s="273"/>
+    </row>
+    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="295"/>
+      <c r="B14" s="297"/>
+      <c r="C14" s="297"/>
+      <c r="D14" s="297"/>
+      <c r="E14" s="272"/>
+      <c r="F14" s="297"/>
+      <c r="G14" s="299"/>
+      <c r="H14" s="272"/>
+      <c r="I14" s="272"/>
+      <c r="J14" s="272"/>
+      <c r="K14" s="282"/>
+      <c r="L14" s="308"/>
+      <c r="M14" s="270"/>
       <c r="N14" s="139" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 16/10</v>
       </c>
-      <c r="O14" s="283"/>
-    </row>
-    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O14" s="280"/>
+    </row>
+    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="124">
         <v>1</v>
       </c>
@@ -4678,11 +4721,11 @@
         <v>1.37</v>
       </c>
       <c r="E15" s="78">
-        <v>287700.01</v>
-      </c>
-      <c r="F15" s="79">
+        <v>301400.01</v>
+      </c>
+      <c r="F15" s="315">
         <f>E15</f>
-        <v>287700.01</v>
+        <v>301400.01</v>
       </c>
       <c r="G15" s="80">
         <f t="shared" ref="G15:G78" si="0">E15-F15</f>
@@ -4718,76 +4761,76 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="179">
+    <row r="16" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="178">
         <v>2</v>
       </c>
-      <c r="B16" s="188" t="s">
+      <c r="B16" s="187" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="189"/>
-      <c r="D16" s="190">
+      <c r="C16" s="188"/>
+      <c r="D16" s="189">
         <v>1.18</v>
       </c>
-      <c r="E16" s="191">
-        <v>4186325.02</v>
-      </c>
-      <c r="F16" s="191"/>
-      <c r="G16" s="192">
+      <c r="E16" s="190">
+        <v>4571515.0199999996</v>
+      </c>
+      <c r="F16" s="190"/>
+      <c r="G16" s="191">
         <f t="shared" si="0"/>
-        <v>4186325.02</v>
-      </c>
-      <c r="H16" s="192">
+        <v>4571515.0199999996</v>
+      </c>
+      <c r="H16" s="191">
         <f t="shared" ref="H16:H79" si="3">IF(G16&gt;0,G16*3%,0)</f>
-        <v>125589.7506</v>
-      </c>
-      <c r="I16" s="193">
+        <v>137145.45059999998</v>
+      </c>
+      <c r="I16" s="192">
         <f t="shared" ref="I16:I46" si="4">J$2*D16/100</f>
         <v>137998.02120799999</v>
       </c>
-      <c r="J16" s="193">
+      <c r="J16" s="192">
         <f t="shared" si="1"/>
         <v>53100</v>
       </c>
-      <c r="K16" s="193">
+      <c r="K16" s="192">
         <f t="shared" ref="K16:K79" si="5">M$2*D16/100</f>
         <v>68501.978792000009</v>
       </c>
-      <c r="L16" s="193"/>
-      <c r="M16" s="194"/>
-      <c r="N16" s="195">
+      <c r="L16" s="192"/>
+      <c r="M16" s="193"/>
+      <c r="N16" s="194">
         <f>ROUND(SUM(G16:M16),0) + P16</f>
-        <v>4571515.0199999996</v>
-      </c>
-      <c r="O16" s="196">
+        <v>4968260.0199999996</v>
+      </c>
+      <c r="O16" s="195">
         <f t="shared" si="2"/>
-        <v>4708660.0199999996</v>
+        <v>5117308.0199999996</v>
       </c>
       <c r="P16" s="50">
         <f>P15+0.01</f>
         <v>0.02</v>
       </c>
       <c r="Q16" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="238">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="125">
         <v>3</v>
       </c>
-      <c r="B17" s="239" t="s">
+      <c r="B17" s="103" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="82"/>
-      <c r="D17" s="77">
+      <c r="C17" s="108"/>
+      <c r="D17" s="105">
         <v>0.74</v>
       </c>
       <c r="E17" s="78">
-        <v>155400.03</v>
-      </c>
-      <c r="F17" s="79">
-        <f>E17</f>
-        <v>155400.03</v>
+        <v>162800.03</v>
+      </c>
+      <c r="F17" s="315">
+        <f>162000+800.03</f>
+        <v>162800.03</v>
       </c>
       <c r="G17" s="80">
         <f t="shared" si="0"/>
@@ -4824,7 +4867,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="125">
         <v>4</v>
       </c>
@@ -4836,11 +4879,11 @@
         <v>1.47</v>
       </c>
       <c r="E18" s="79">
-        <v>308700.03999999998</v>
-      </c>
-      <c r="F18" s="79">
+        <v>323400.03999999998</v>
+      </c>
+      <c r="F18" s="315">
         <f>E18</f>
-        <v>308700.03999999998</v>
+        <v>323400.03999999998</v>
       </c>
       <c r="G18" s="106">
         <f t="shared" si="0"/>
@@ -4877,26 +4920,26 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="124">
+    <row r="19" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="125">
         <v>5</v>
       </c>
-      <c r="B19" s="76" t="s">
+      <c r="B19" s="103" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="76"/>
-      <c r="D19" s="77">
+      <c r="C19" s="103"/>
+      <c r="D19" s="105">
         <v>1.1200000000000001</v>
       </c>
       <c r="E19" s="79">
-        <v>229318.05</v>
-      </c>
-      <c r="F19" s="79">
-        <v>236198.05</v>
+        <v>239520.05</v>
+      </c>
+      <c r="F19" s="315">
+        <v>246706.05</v>
       </c>
       <c r="G19" s="80">
         <f t="shared" si="0"/>
-        <v>-6880</v>
+        <v>-7186</v>
       </c>
       <c r="H19" s="80">
         <f t="shared" si="3"/>
@@ -4918,37 +4961,37 @@
       <c r="M19" s="141"/>
       <c r="N19" s="81">
         <f t="shared" si="6"/>
-        <v>239520.05</v>
+        <v>239214.05</v>
       </c>
       <c r="O19" s="134">
         <f t="shared" si="2"/>
-        <v>246706.05</v>
+        <v>246390.05</v>
       </c>
       <c r="P19" s="50">
         <f t="shared" si="7"/>
         <v>0.05</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="245">
+    <row r="20" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="125">
         <v>6</v>
       </c>
-      <c r="B20" s="246" t="s">
+      <c r="B20" s="103" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="76"/>
-      <c r="D20" s="77">
+      <c r="C20" s="103"/>
+      <c r="D20" s="105">
         <v>1.35</v>
       </c>
       <c r="E20" s="78">
-        <v>283082.06</v>
-      </c>
-      <c r="F20" s="79">
-        <v>284000.06</v>
+        <v>296082.06</v>
+      </c>
+      <c r="F20" s="315">
+        <v>307000</v>
       </c>
       <c r="G20" s="80">
         <f t="shared" si="0"/>
-        <v>-918</v>
+        <v>-10917.940000000002</v>
       </c>
       <c r="H20" s="80">
         <f t="shared" si="3"/>
@@ -4970,34 +5013,34 @@
       <c r="M20" s="141"/>
       <c r="N20" s="81">
         <f t="shared" si="6"/>
-        <v>296082.06</v>
+        <v>286082.06</v>
       </c>
       <c r="O20" s="134">
         <f t="shared" si="2"/>
-        <v>304964.06</v>
+        <v>294664.06</v>
       </c>
       <c r="P20" s="50">
         <f t="shared" si="7"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="124">
+    <row r="21" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="125">
         <v>7</v>
       </c>
-      <c r="B21" s="76" t="s">
+      <c r="B21" s="103" t="s">
         <v>9</v>
       </c>
-      <c r="C21" s="76"/>
-      <c r="D21" s="77">
+      <c r="C21" s="103"/>
+      <c r="D21" s="105">
         <v>1.1200000000000001</v>
       </c>
       <c r="E21" s="78">
-        <v>235200.07</v>
-      </c>
-      <c r="F21" s="79">
+        <v>246400.07</v>
+      </c>
+      <c r="F21" s="315">
         <f>E21</f>
-        <v>235200.07</v>
+        <v>246400.07</v>
       </c>
       <c r="G21" s="80">
         <f t="shared" si="0"/>
@@ -5034,23 +5077,23 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="124">
+    <row r="22" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="125">
         <v>8</v>
       </c>
-      <c r="B22" s="76" t="s">
+      <c r="B22" s="103" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="82"/>
-      <c r="D22" s="77">
+      <c r="C22" s="108"/>
+      <c r="D22" s="105">
         <v>0.82</v>
       </c>
       <c r="E22" s="78">
-        <v>172200.08</v>
-      </c>
-      <c r="F22" s="79">
+        <v>180400.08</v>
+      </c>
+      <c r="F22" s="315">
         <f>E22</f>
-        <v>172200.08</v>
+        <v>180400.08</v>
       </c>
       <c r="G22" s="80">
         <f t="shared" si="0"/>
@@ -5087,7 +5130,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="124">
         <v>9</v>
       </c>
@@ -5099,14 +5142,14 @@
         <v>0.82</v>
       </c>
       <c r="E23" s="78">
-        <v>167890.09</v>
-      </c>
-      <c r="F23" s="79">
-        <v>172927.09</v>
+        <v>175363.09</v>
+      </c>
+      <c r="F23" s="315">
+        <v>180624.09</v>
       </c>
       <c r="G23" s="80">
         <f t="shared" si="0"/>
-        <v>-5037</v>
+        <v>-5261</v>
       </c>
       <c r="H23" s="80">
         <f t="shared" si="3"/>
@@ -5128,18 +5171,18 @@
       <c r="M23" s="141"/>
       <c r="N23" s="81">
         <f t="shared" si="6"/>
-        <v>175363.09</v>
+        <v>175139.09</v>
       </c>
       <c r="O23" s="134">
         <f t="shared" si="2"/>
-        <v>180624.09</v>
+        <v>180393.09</v>
       </c>
       <c r="P23" s="50">
         <f t="shared" si="7"/>
         <v>0.09</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="124">
         <v>10</v>
       </c>
@@ -5151,11 +5194,11 @@
         <v>1.34</v>
       </c>
       <c r="E24" s="78">
-        <v>288853.09999999998</v>
-      </c>
-      <c r="F24" s="79">
+        <v>294800.09999999998</v>
+      </c>
+      <c r="F24" s="315">
         <f>E24</f>
-        <v>288853.09999999998</v>
+        <v>294800.09999999998</v>
       </c>
       <c r="G24" s="80">
         <f t="shared" si="0"/>
@@ -5192,7 +5235,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="124">
         <v>11</v>
       </c>
@@ -5204,11 +5247,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E25" s="78">
-        <v>235200.11</v>
-      </c>
-      <c r="F25" s="79">
+        <v>246400.11</v>
+      </c>
+      <c r="F25" s="315">
         <f>E25</f>
-        <v>235200.11</v>
+        <v>246400.11</v>
       </c>
       <c r="G25" s="80">
         <f t="shared" si="0"/>
@@ -5245,59 +5288,59 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="179">
+    <row r="26" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="178">
         <v>12</v>
       </c>
-      <c r="B26" s="188" t="s">
+      <c r="B26" s="187" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="189"/>
-      <c r="D26" s="190">
+      <c r="C26" s="188"/>
+      <c r="D26" s="189">
         <v>1.17</v>
       </c>
-      <c r="E26" s="191">
-        <v>5209364.12</v>
-      </c>
-      <c r="F26" s="191">
-        <v>0</v>
-      </c>
-      <c r="G26" s="192">
+      <c r="E26" s="190">
+        <v>5623045.1200000001</v>
+      </c>
+      <c r="F26" s="190">
+        <v>0</v>
+      </c>
+      <c r="G26" s="191">
         <f t="shared" si="0"/>
-        <v>5209364.12</v>
-      </c>
-      <c r="H26" s="192">
+        <v>5623045.1200000001</v>
+      </c>
+      <c r="H26" s="191">
         <f t="shared" si="3"/>
-        <v>156280.92360000001</v>
-      </c>
-      <c r="I26" s="193">
+        <v>168691.3536</v>
+      </c>
+      <c r="I26" s="192">
         <f t="shared" si="4"/>
         <v>136828.54645199998</v>
       </c>
-      <c r="J26" s="193">
+      <c r="J26" s="192">
         <f t="shared" si="1"/>
         <v>52650</v>
       </c>
-      <c r="K26" s="193">
+      <c r="K26" s="192">
         <f t="shared" si="5"/>
         <v>67921.453548000005</v>
       </c>
-      <c r="L26" s="193"/>
-      <c r="M26" s="194"/>
-      <c r="N26" s="195">
+      <c r="L26" s="192"/>
+      <c r="M26" s="193"/>
+      <c r="N26" s="194">
         <f t="shared" si="6"/>
-        <v>5623045.1200000001</v>
-      </c>
-      <c r="O26" s="196">
+        <v>6049136.1200000001</v>
+      </c>
+      <c r="O26" s="195">
         <f t="shared" si="2"/>
-        <v>5791736.1200000001</v>
+        <v>6230610.1200000001</v>
       </c>
       <c r="P26" s="50">
         <f t="shared" si="7"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="124">
         <v>13</v>
       </c>
@@ -5309,11 +5352,11 @@
         <v>1.35</v>
       </c>
       <c r="E27" s="78">
-        <v>283500.13</v>
-      </c>
-      <c r="F27" s="79">
+        <v>297000.13</v>
+      </c>
+      <c r="F27" s="315">
         <f>E27</f>
-        <v>283500.13</v>
+        <v>297000.13</v>
       </c>
       <c r="G27" s="80">
         <f t="shared" si="0"/>
@@ -5350,7 +5393,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="124">
         <v>14</v>
       </c>
@@ -5362,16 +5405,16 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E28" s="78">
-        <v>844219.14</v>
+        <v>1115946.1399999999</v>
       </c>
       <c r="F28" s="79"/>
       <c r="G28" s="80">
         <f t="shared" si="0"/>
-        <v>844219.14</v>
+        <v>1115946.1399999999</v>
       </c>
       <c r="H28" s="80">
         <f t="shared" si="3"/>
-        <v>25326.574199999999</v>
+        <v>33478.384199999993</v>
       </c>
       <c r="I28" s="120">
         <f t="shared" si="4"/>
@@ -5389,18 +5432,18 @@
       <c r="M28" s="141"/>
       <c r="N28" s="81">
         <f t="shared" si="6"/>
-        <v>1115946.1399999999</v>
+        <v>1395825.14</v>
       </c>
       <c r="O28" s="134">
         <f t="shared" si="2"/>
-        <v>1149424.1399999999</v>
+        <v>1437700.14</v>
       </c>
       <c r="P28" s="50">
         <f t="shared" si="7"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="125">
         <v>15</v>
       </c>
@@ -5412,11 +5455,11 @@
         <v>0.82</v>
       </c>
       <c r="E29" s="79">
-        <v>172200.15</v>
-      </c>
-      <c r="F29" s="79">
+        <v>180400.15</v>
+      </c>
+      <c r="F29" s="315">
         <f>E29</f>
-        <v>172200.15</v>
+        <v>180400.15</v>
       </c>
       <c r="G29" s="80">
         <f t="shared" si="0"/>
@@ -5453,7 +5496,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="124">
         <v>16</v>
       </c>
@@ -5465,11 +5508,11 @@
         <v>0.82</v>
       </c>
       <c r="E30" s="78">
-        <v>172200.16</v>
-      </c>
-      <c r="F30" s="79">
+        <v>180400.16</v>
+      </c>
+      <c r="F30" s="315">
         <f>E30</f>
-        <v>172200.16</v>
+        <v>180400.16</v>
       </c>
       <c r="G30" s="80">
         <f t="shared" si="0"/>
@@ -5506,7 +5549,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="124">
         <v>17</v>
       </c>
@@ -5518,18 +5561,16 @@
         <v>1.34</v>
       </c>
       <c r="E31" s="78">
-        <v>281400.17</v>
-      </c>
-      <c r="F31" s="79">
-        <v>193374.17</v>
-      </c>
+        <v>385467.17</v>
+      </c>
+      <c r="F31" s="79"/>
       <c r="G31" s="80">
         <f t="shared" si="0"/>
-        <v>88025.999999999971</v>
+        <v>385467.17</v>
       </c>
       <c r="H31" s="80">
         <f t="shared" si="3"/>
-        <v>2640.7799999999988</v>
+        <v>11564.015099999999</v>
       </c>
       <c r="I31" s="120">
         <f t="shared" si="4"/>
@@ -5547,18 +5588,18 @@
       <c r="M31" s="141"/>
       <c r="N31" s="81">
         <f t="shared" si="6"/>
-        <v>385467.17</v>
+        <v>691831.17</v>
       </c>
       <c r="O31" s="134">
         <f t="shared" si="2"/>
-        <v>397031.17</v>
+        <v>712586.17</v>
       </c>
       <c r="P31" s="50">
         <f t="shared" si="7"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="125">
         <v>18</v>
       </c>
@@ -5570,11 +5611,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E32" s="79">
-        <v>235200.18</v>
-      </c>
-      <c r="F32" s="79">
+        <v>246400.18</v>
+      </c>
+      <c r="F32" s="315">
         <f>E32</f>
-        <v>235200.18</v>
+        <v>246400.18</v>
       </c>
       <c r="G32" s="106">
         <f t="shared" si="0"/>
@@ -5611,7 +5652,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="125">
         <v>19</v>
       </c>
@@ -5623,14 +5664,15 @@
         <v>1.17</v>
       </c>
       <c r="E33" s="78">
-        <v>211920.19</v>
-      </c>
-      <c r="F33" s="79">
-        <v>245700</v>
+        <v>223620.19</v>
+      </c>
+      <c r="F33" s="315">
+        <f>E33</f>
+        <v>223620.19</v>
       </c>
       <c r="G33" s="80">
         <f t="shared" si="0"/>
-        <v>-33779.81</v>
+        <v>0</v>
       </c>
       <c r="H33" s="80">
         <f t="shared" si="3"/>
@@ -5652,21 +5694,21 @@
       <c r="M33" s="141"/>
       <c r="N33" s="81">
         <f t="shared" si="6"/>
-        <v>223620.19</v>
+        <v>257400.19</v>
       </c>
       <c r="O33" s="134">
         <f t="shared" si="2"/>
-        <v>230329.19</v>
+        <v>265122.19</v>
       </c>
       <c r="P33" s="50">
         <f>P32+0.01</f>
         <v>0.19000000000000003</v>
       </c>
       <c r="Q33" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="126">
         <v>20</v>
       </c>
@@ -5678,14 +5720,14 @@
         <v>1.35</v>
       </c>
       <c r="E34" s="117">
-        <v>1199638.2</v>
-      </c>
-      <c r="F34" s="117">
-        <v>369300</v>
+        <v>1250638.2</v>
+      </c>
+      <c r="F34" s="317">
+        <v>366300</v>
       </c>
       <c r="G34" s="118">
         <f t="shared" si="0"/>
-        <v>830338.2</v>
+        <v>884338.2</v>
       </c>
       <c r="H34" s="118"/>
       <c r="I34" s="123">
@@ -5706,21 +5748,21 @@
       </c>
       <c r="N34" s="119">
         <f t="shared" si="6"/>
-        <v>1250638.2</v>
+        <v>1304638.2</v>
       </c>
       <c r="O34" s="136">
         <f t="shared" si="2"/>
-        <v>1288157.2</v>
+        <v>1343777.2</v>
       </c>
       <c r="P34" s="50">
         <f t="shared" ref="P34:P97" si="8">P33+0.01</f>
         <v>0.20000000000000004</v>
       </c>
       <c r="Q34" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="125">
         <v>21</v>
       </c>
@@ -5732,11 +5774,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E35" s="79">
-        <v>235200.21</v>
-      </c>
-      <c r="F35" s="79">
+        <v>246400.21</v>
+      </c>
+      <c r="F35" s="315">
         <f>E35</f>
-        <v>235200.21</v>
+        <v>246400.21</v>
       </c>
       <c r="G35" s="106">
         <f t="shared" si="0"/>
@@ -5773,24 +5815,24 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="125">
         <f>A35+1</f>
         <v>22</v>
       </c>
       <c r="B36" s="109" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C36" s="82"/>
       <c r="D36" s="77">
         <v>0.82</v>
       </c>
       <c r="E36" s="78">
-        <v>172200.22</v>
-      </c>
-      <c r="F36" s="79">
+        <v>180400.22</v>
+      </c>
+      <c r="F36" s="315">
         <f>E36</f>
-        <v>172200.22</v>
+        <v>180400.22</v>
       </c>
       <c r="G36" s="80">
         <f t="shared" si="0"/>
@@ -5827,7 +5869,7 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="124">
         <f t="shared" ref="A37:A100" si="10">A36+1</f>
         <v>23</v>
@@ -5840,11 +5882,11 @@
         <v>0.82</v>
       </c>
       <c r="E37" s="78">
-        <v>172200.23</v>
-      </c>
-      <c r="F37" s="79">
+        <v>180400.23</v>
+      </c>
+      <c r="F37" s="315">
         <f>E37</f>
-        <v>172200.23</v>
+        <v>180400.23</v>
       </c>
       <c r="G37" s="80">
         <f t="shared" si="0"/>
@@ -5881,7 +5923,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="124">
         <f t="shared" si="10"/>
         <v>24</v>
@@ -5894,10 +5936,11 @@
         <v>1.34</v>
       </c>
       <c r="E38" s="78">
-        <v>529836.24</v>
-      </c>
-      <c r="F38" s="79">
-        <v>529836.24</v>
+        <v>294800.24</v>
+      </c>
+      <c r="F38" s="315">
+        <f>E38</f>
+        <v>294800.24</v>
       </c>
       <c r="G38" s="80">
         <f t="shared" si="0"/>
@@ -5934,7 +5977,7 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="124">
         <f t="shared" si="10"/>
         <v>25</v>
@@ -5947,18 +5990,16 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E39" s="78">
-        <v>442848.25</v>
-      </c>
-      <c r="F39" s="79">
-        <v>207848.25</v>
-      </c>
+        <v>488450.25</v>
+      </c>
+      <c r="F39" s="79"/>
       <c r="G39" s="80">
         <f t="shared" si="0"/>
-        <v>235000</v>
+        <v>488450.25</v>
       </c>
       <c r="H39" s="80">
         <f t="shared" si="3"/>
-        <v>7050</v>
+        <v>14653.5075</v>
       </c>
       <c r="I39" s="120">
         <f t="shared" si="4"/>
@@ -5976,43 +6017,40 @@
       <c r="M39" s="141"/>
       <c r="N39" s="81">
         <f t="shared" si="6"/>
-        <v>488450.25</v>
+        <v>749504.25</v>
       </c>
       <c r="O39" s="134">
         <f t="shared" si="9"/>
-        <v>503104.25</v>
+        <v>771989.25</v>
       </c>
       <c r="P39" s="50">
         <f t="shared" si="8"/>
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A40" s="124">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A40" s="125">
         <f t="shared" si="10"/>
         <v>26</v>
       </c>
-      <c r="B40" s="83" t="s">
+      <c r="B40" s="109" t="s">
         <v>27</v>
       </c>
-      <c r="C40" s="82"/>
-      <c r="D40" s="77">
+      <c r="C40" s="108"/>
+      <c r="D40" s="105">
         <v>1.17</v>
       </c>
       <c r="E40" s="78">
-        <v>476497.26</v>
-      </c>
-      <c r="F40" s="79">
-        <f>216918.26+259579</f>
-        <v>476497.26</v>
-      </c>
+        <v>257400.26</v>
+      </c>
+      <c r="F40" s="79"/>
       <c r="G40" s="80">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>257400.26</v>
       </c>
       <c r="H40" s="80">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7722.0078000000003</v>
       </c>
       <c r="I40" s="120">
         <f t="shared" si="4"/>
@@ -6030,35 +6068,35 @@
       <c r="M40" s="141"/>
       <c r="N40" s="81">
         <f t="shared" si="6"/>
-        <v>257400.26</v>
+        <v>522522.26</v>
       </c>
       <c r="O40" s="134">
         <f t="shared" si="9"/>
-        <v>265122.26</v>
+        <v>538198.26</v>
       </c>
       <c r="P40" s="50">
         <f t="shared" si="8"/>
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A41" s="229">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A41" s="125">
         <f t="shared" si="10"/>
         <v>27</v>
       </c>
-      <c r="B41" s="230" t="s">
+      <c r="B41" s="109" t="s">
         <v>28</v>
       </c>
-      <c r="C41" s="82"/>
-      <c r="D41" s="77">
+      <c r="C41" s="108"/>
+      <c r="D41" s="105">
         <v>1.35</v>
       </c>
       <c r="E41" s="78">
-        <v>283500.27</v>
-      </c>
-      <c r="F41" s="79">
+        <v>297000.27</v>
+      </c>
+      <c r="F41" s="315">
         <f t="shared" ref="F41" si="11">E41</f>
-        <v>283500.27</v>
+        <v>297000.27</v>
       </c>
       <c r="G41" s="80">
         <f t="shared" si="0"/>
@@ -6095,31 +6133,32 @@
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A42" s="124">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A42" s="125">
         <f t="shared" si="10"/>
         <v>28</v>
       </c>
-      <c r="B42" s="83" t="s">
+      <c r="B42" s="109" t="s">
         <v>29</v>
       </c>
-      <c r="C42" s="82"/>
-      <c r="D42" s="77">
+      <c r="C42" s="108"/>
+      <c r="D42" s="105">
         <v>1.1200000000000001</v>
       </c>
       <c r="E42" s="78">
-        <v>1036322.28</v>
-      </c>
-      <c r="F42" s="79">
-        <v>507000</v>
+        <v>791602.28</v>
+      </c>
+      <c r="F42" s="315">
+        <f>791603</f>
+        <v>791603</v>
       </c>
       <c r="G42" s="80">
         <f t="shared" si="0"/>
-        <v>529322.28</v>
+        <v>-0.71999999997206032</v>
       </c>
       <c r="H42" s="80">
         <f t="shared" si="3"/>
-        <v>15879.6684</v>
+        <v>0</v>
       </c>
       <c r="I42" s="120">
         <f t="shared" si="4"/>
@@ -6137,21 +6176,21 @@
       <c r="M42" s="141"/>
       <c r="N42" s="81">
         <f t="shared" si="6"/>
-        <v>791602.28</v>
+        <v>246399.28</v>
       </c>
       <c r="O42" s="134">
         <f t="shared" si="9"/>
-        <v>815350.28</v>
+        <v>253791.28</v>
       </c>
       <c r="P42" s="50">
         <f t="shared" si="8"/>
         <v>0.28000000000000008</v>
       </c>
       <c r="Q42" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="125">
         <f t="shared" si="10"/>
         <v>29</v>
@@ -6164,11 +6203,11 @@
         <v>0.82</v>
       </c>
       <c r="E43" s="79">
-        <v>167897.29</v>
-      </c>
-      <c r="F43" s="79">
+        <v>180400.29</v>
+      </c>
+      <c r="F43" s="315">
         <f t="shared" ref="F43" si="12">E43</f>
-        <v>167897.29</v>
+        <v>180400.29</v>
       </c>
       <c r="G43" s="106">
         <f t="shared" si="0"/>
@@ -6205,10 +6244,10 @@
         <v>0.29000000000000009</v>
       </c>
       <c r="Q43" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="125">
         <f t="shared" si="10"/>
         <v>30</v>
@@ -6221,11 +6260,11 @@
         <v>0.82</v>
       </c>
       <c r="E44" s="79">
-        <v>172200.3</v>
-      </c>
-      <c r="F44" s="79">
+        <v>180400.3</v>
+      </c>
+      <c r="F44" s="315">
         <f>E44</f>
-        <v>172200.3</v>
+        <v>180400.3</v>
       </c>
       <c r="G44" s="106">
         <f t="shared" si="0"/>
@@ -6262,7 +6301,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="124">
         <f t="shared" si="10"/>
         <v>31</v>
@@ -6275,11 +6314,11 @@
         <v>1.34</v>
       </c>
       <c r="E45" s="78">
-        <v>281400.31</v>
-      </c>
-      <c r="F45" s="79">
+        <v>294800.31</v>
+      </c>
+      <c r="F45" s="315">
         <f>E45</f>
-        <v>281400.31</v>
+        <v>294800.31</v>
       </c>
       <c r="G45" s="80">
         <f t="shared" si="0"/>
@@ -6316,7 +6355,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="124">
         <f t="shared" si="10"/>
         <v>32</v>
@@ -6329,15 +6368,15 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E46" s="78">
-        <v>372170.32</v>
-      </c>
-      <c r="F46" s="79">
-        <f>186085.3*2</f>
-        <v>372170.6</v>
+        <v>246400.32</v>
+      </c>
+      <c r="F46" s="315">
+        <f>46400.32+200000.32</f>
+        <v>246400.64000000001</v>
       </c>
       <c r="G46" s="80">
         <f t="shared" si="0"/>
-        <v>-0.27999999996973202</v>
+        <v>-0.32000000000698492</v>
       </c>
       <c r="H46" s="80">
         <f t="shared" si="3"/>
@@ -6370,7 +6409,7 @@
         <v>0.32000000000000012</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="126">
         <f t="shared" si="10"/>
         <v>33</v>
@@ -6383,11 +6422,11 @@
         <v>1.17</v>
       </c>
       <c r="E47" s="117">
-        <v>415700.33</v>
-      </c>
-      <c r="F47" s="117">
+        <v>427400.33</v>
+      </c>
+      <c r="F47" s="317">
         <f>E47</f>
-        <v>415700.33</v>
+        <v>427400.33</v>
       </c>
       <c r="G47" s="118">
         <f t="shared" si="0"/>
@@ -6423,10 +6462,10 @@
         <v>0.33000000000000013</v>
       </c>
       <c r="Q47" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="124">
         <f t="shared" si="10"/>
         <v>34</v>
@@ -6439,11 +6478,11 @@
         <v>1.35</v>
       </c>
       <c r="E48" s="78">
-        <v>283500.34000000003</v>
-      </c>
-      <c r="F48" s="79">
+        <v>297000.34000000003</v>
+      </c>
+      <c r="F48" s="315">
         <f>E48</f>
-        <v>283500.34000000003</v>
+        <v>297000.34000000003</v>
       </c>
       <c r="G48" s="80">
         <f t="shared" si="0"/>
@@ -6480,38 +6519,38 @@
         <v>0.34000000000000014</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A49" s="181">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A49" s="180">
         <f t="shared" si="10"/>
         <v>35</v>
       </c>
-      <c r="B49" s="182" t="s">
+      <c r="B49" s="181" t="s">
         <v>36</v>
       </c>
-      <c r="C49" s="183"/>
-      <c r="D49" s="184">
+      <c r="C49" s="182"/>
+      <c r="D49" s="183">
         <v>1.1200000000000001</v>
       </c>
       <c r="E49" s="79">
-        <v>235200.35</v>
-      </c>
-      <c r="F49" s="79">
+        <v>246400.35</v>
+      </c>
+      <c r="F49" s="315">
         <f>E49</f>
-        <v>235200.35</v>
-      </c>
-      <c r="G49" s="185">
+        <v>246400.35</v>
+      </c>
+      <c r="G49" s="184">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H49" s="185">
+      <c r="H49" s="184">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I49" s="186">
+      <c r="I49" s="185">
         <f t="shared" si="13"/>
         <v>130981.172672</v>
       </c>
-      <c r="J49" s="186">
+      <c r="J49" s="185">
         <f t="shared" si="14"/>
         <v>50400.000000000007</v>
       </c>
@@ -6519,8 +6558,8 @@
         <f t="shared" si="5"/>
         <v>65018.827328000014</v>
       </c>
-      <c r="L49" s="186"/>
-      <c r="M49" s="187"/>
+      <c r="L49" s="185"/>
+      <c r="M49" s="186"/>
       <c r="N49" s="107">
         <f t="shared" si="6"/>
         <v>246400.35</v>
@@ -6534,10 +6573,10 @@
         <v>0.35000000000000014</v>
       </c>
       <c r="Q49" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="124">
         <f t="shared" si="10"/>
         <v>36</v>
@@ -6550,11 +6589,11 @@
         <v>0.82</v>
       </c>
       <c r="E50" s="78">
-        <v>172200.36</v>
-      </c>
-      <c r="F50" s="79">
+        <v>180400.36</v>
+      </c>
+      <c r="F50" s="315">
         <f>E50</f>
-        <v>172200.36</v>
+        <v>180400.36</v>
       </c>
       <c r="G50" s="80">
         <f t="shared" si="0"/>
@@ -6591,10 +6630,10 @@
         <v>0.36000000000000015</v>
       </c>
       <c r="Q50" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="124">
         <f t="shared" si="10"/>
         <v>37</v>
@@ -6607,18 +6646,16 @@
         <v>0.82</v>
       </c>
       <c r="E51" s="79">
-        <v>176336.37</v>
-      </c>
-      <c r="F51" s="79">
-        <v>164000</v>
-      </c>
+        <v>193106.37</v>
+      </c>
+      <c r="F51" s="79"/>
       <c r="G51" s="80">
         <f t="shared" si="0"/>
-        <v>12336.369999999995</v>
+        <v>193106.37</v>
       </c>
       <c r="H51" s="80">
         <f t="shared" si="3"/>
-        <v>370.09109999999987</v>
+        <v>5793.1911</v>
       </c>
       <c r="I51" s="120">
         <f t="shared" si="13"/>
@@ -6636,21 +6673,21 @@
       <c r="M51" s="141"/>
       <c r="N51" s="81">
         <f t="shared" si="6"/>
-        <v>193106.37</v>
+        <v>379300.37</v>
       </c>
       <c r="O51" s="134">
         <f t="shared" si="9"/>
-        <v>198899.37</v>
+        <v>390679.37</v>
       </c>
       <c r="P51" s="50">
         <f t="shared" si="8"/>
         <v>0.37000000000000016</v>
       </c>
       <c r="Q51" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="126">
         <f t="shared" si="10"/>
         <v>38</v>
@@ -6663,14 +6700,14 @@
         <v>1.34</v>
       </c>
       <c r="E52" s="117">
-        <v>281400.38</v>
+        <v>766200.38</v>
       </c>
       <c r="F52" s="117">
         <v>0</v>
       </c>
       <c r="G52" s="118">
         <f t="shared" si="0"/>
-        <v>281400.38</v>
+        <v>766200.38</v>
       </c>
       <c r="H52" s="118">
         <v>0</v>
@@ -6693,21 +6730,21 @@
       </c>
       <c r="N52" s="119">
         <f t="shared" si="6"/>
-        <v>766200.38</v>
+        <v>1251000.3799999999</v>
       </c>
       <c r="O52" s="136">
         <f t="shared" si="9"/>
-        <v>789186.38</v>
+        <v>1288530.3799999999</v>
       </c>
       <c r="P52" s="50">
         <f t="shared" si="8"/>
         <v>0.38000000000000017</v>
       </c>
       <c r="Q52" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="124">
         <f t="shared" si="10"/>
         <v>39</v>
@@ -6720,18 +6757,19 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E53" s="78">
-        <v>235200.39</v>
-      </c>
-      <c r="F53" s="79">
-        <v>218400.39</v>
+        <v>263704.39</v>
+      </c>
+      <c r="F53" s="315">
+        <f>E53</f>
+        <v>263704.39</v>
       </c>
       <c r="G53" s="80">
         <f t="shared" si="0"/>
-        <v>16800</v>
+        <v>0</v>
       </c>
       <c r="H53" s="80">
         <f t="shared" si="3"/>
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="I53" s="120">
         <f t="shared" si="13"/>
@@ -6749,18 +6787,18 @@
       <c r="M53" s="141"/>
       <c r="N53" s="81">
         <f t="shared" si="6"/>
-        <v>263704.39</v>
+        <v>246400.39</v>
       </c>
       <c r="O53" s="134">
         <f t="shared" si="9"/>
-        <v>271615.39</v>
+        <v>253792.39</v>
       </c>
       <c r="P53" s="50">
         <f t="shared" si="8"/>
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="124">
         <f t="shared" si="10"/>
         <v>40</v>
@@ -6773,19 +6811,16 @@
         <v>1.17</v>
       </c>
       <c r="E54" s="78">
-        <v>245700.4</v>
-      </c>
-      <c r="F54" s="79">
-        <f>E54</f>
-        <v>245700.4</v>
-      </c>
+        <v>257400.4</v>
+      </c>
+      <c r="F54" s="79"/>
       <c r="G54" s="80">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>257400.4</v>
       </c>
       <c r="H54" s="80">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7722.0119999999997</v>
       </c>
       <c r="I54" s="120">
         <f t="shared" si="13"/>
@@ -6803,18 +6838,18 @@
       <c r="M54" s="141"/>
       <c r="N54" s="81">
         <f t="shared" si="6"/>
-        <v>257400.4</v>
+        <v>522522.4</v>
       </c>
       <c r="O54" s="134">
         <f t="shared" si="9"/>
-        <v>265122.40000000002</v>
+        <v>538198.4</v>
       </c>
       <c r="P54" s="50">
         <f t="shared" si="8"/>
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="124">
         <f t="shared" si="10"/>
         <v>41</v>
@@ -6827,11 +6862,11 @@
         <v>1.35</v>
       </c>
       <c r="E55" s="78">
-        <v>276127.40999999997</v>
-      </c>
-      <c r="F55" s="79">
+        <v>297000.40999999997</v>
+      </c>
+      <c r="F55" s="315">
         <f>E55</f>
-        <v>276127.40999999997</v>
+        <v>297000.40999999997</v>
       </c>
       <c r="G55" s="80">
         <f t="shared" si="0"/>
@@ -6868,7 +6903,7 @@
         <v>0.4100000000000002</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="126">
         <f t="shared" si="10"/>
         <v>42</v>
@@ -6881,10 +6916,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E56" s="117">
-        <v>266191.42</v>
-      </c>
-      <c r="F56" s="117">
-        <v>266191.42</v>
+        <v>279400.42</v>
+      </c>
+      <c r="F56" s="317">
+        <f>E56</f>
+        <v>279400.42</v>
       </c>
       <c r="G56" s="118">
         <f t="shared" si="0"/>
@@ -6923,10 +6959,10 @@
         <v>0.42000000000000021</v>
       </c>
       <c r="Q56" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="125">
         <f t="shared" si="10"/>
         <v>43</v>
@@ -6938,20 +6974,17 @@
       <c r="D57" s="105">
         <v>0.82</v>
       </c>
-      <c r="E57" s="204">
-        <v>790470.43</v>
-      </c>
-      <c r="F57" s="79">
-        <f>300000+472200.43+18270</f>
-        <v>790470.42999999993</v>
-      </c>
+      <c r="E57" s="203">
+        <v>180400.43</v>
+      </c>
+      <c r="F57" s="79"/>
       <c r="G57" s="106">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>180400.43</v>
       </c>
       <c r="H57" s="106">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>5412.0128999999997</v>
       </c>
       <c r="I57" s="121">
         <f t="shared" si="13"/>
@@ -6971,21 +7004,21 @@
       </c>
       <c r="N57" s="107">
         <f>ROUND(SUM(G57:M57),0) + P57</f>
-        <v>180400.43</v>
+        <v>366212.43</v>
       </c>
       <c r="O57" s="135">
         <f t="shared" si="9"/>
-        <v>185812.43</v>
+        <v>377198.43</v>
       </c>
       <c r="P57" s="50">
         <f t="shared" si="8"/>
         <v>0.43000000000000022</v>
       </c>
       <c r="Q57" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="125">
         <f t="shared" si="10"/>
         <v>44</v>
@@ -6998,15 +7031,15 @@
         <v>0.82</v>
       </c>
       <c r="E58" s="78">
-        <v>129113.44</v>
-      </c>
-      <c r="F58" s="79">
-        <f>E58+40669.71</f>
-        <v>169783.15</v>
+        <v>139730.44</v>
+      </c>
+      <c r="F58" s="315">
+        <f>E58</f>
+        <v>139730.44</v>
       </c>
       <c r="G58" s="80">
         <f t="shared" si="0"/>
-        <v>-40669.709999999992</v>
+        <v>0</v>
       </c>
       <c r="H58" s="80">
         <f t="shared" si="3"/>
@@ -7028,38 +7061,38 @@
       <c r="M58" s="141"/>
       <c r="N58" s="81">
         <f t="shared" si="6"/>
-        <v>139730.44</v>
+        <v>180400.44</v>
       </c>
       <c r="O58" s="134">
         <f t="shared" si="9"/>
-        <v>143922.44</v>
+        <v>185812.44</v>
       </c>
       <c r="P58" s="50">
         <f t="shared" si="8"/>
         <v>0.44000000000000022</v>
       </c>
       <c r="Q58" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="125">
         <f t="shared" si="10"/>
         <v>45</v>
       </c>
       <c r="B59" s="109" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C59" s="108"/>
       <c r="D59" s="105">
         <v>1.34</v>
       </c>
       <c r="E59" s="78">
-        <v>281400.45</v>
-      </c>
-      <c r="F59" s="79">
+        <v>294800.45</v>
+      </c>
+      <c r="F59" s="315">
         <f>E59</f>
-        <v>281400.45</v>
+        <v>294800.45</v>
       </c>
       <c r="G59" s="80">
         <f t="shared" si="0"/>
@@ -7096,12 +7129,12 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A60" s="247">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A60" s="125">
         <f t="shared" si="10"/>
         <v>46</v>
       </c>
-      <c r="B60" s="248" t="s">
+      <c r="B60" s="109" t="s">
         <v>45</v>
       </c>
       <c r="C60" s="108"/>
@@ -7109,18 +7142,18 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E60" s="78">
-        <v>243390.46</v>
-      </c>
-      <c r="F60" s="79">
-        <v>220000</v>
+        <v>270492.46000000002</v>
+      </c>
+      <c r="F60" s="315">
+        <v>250000</v>
       </c>
       <c r="G60" s="80">
         <f t="shared" si="0"/>
-        <v>23390.459999999992</v>
+        <v>20492.460000000021</v>
       </c>
       <c r="H60" s="80">
         <f t="shared" si="3"/>
-        <v>701.71379999999976</v>
+        <v>614.77380000000062</v>
       </c>
       <c r="I60" s="120">
         <f t="shared" si="13"/>
@@ -7138,21 +7171,21 @@
       <c r="M60" s="141"/>
       <c r="N60" s="81">
         <f t="shared" si="6"/>
-        <v>270492.46000000002</v>
+        <v>267507.46000000002</v>
       </c>
       <c r="O60" s="134">
         <f t="shared" si="9"/>
-        <v>278607.46000000002</v>
+        <v>275532.46000000002</v>
       </c>
       <c r="P60" s="50">
         <f t="shared" si="8"/>
         <v>0.46000000000000024</v>
       </c>
       <c r="Q60" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="126">
         <f t="shared" si="10"/>
         <v>47</v>
@@ -7165,14 +7198,14 @@
         <v>1.17</v>
       </c>
       <c r="E61" s="117">
-        <v>1115795.47</v>
+        <v>1508195.47</v>
       </c>
       <c r="F61" s="117">
         <v>0</v>
       </c>
       <c r="G61" s="118">
         <f t="shared" si="0"/>
-        <v>1115795.47</v>
+        <v>1508195.47</v>
       </c>
       <c r="H61" s="118"/>
       <c r="I61" s="123">
@@ -7193,21 +7226,21 @@
       </c>
       <c r="N61" s="119">
         <f t="shared" si="6"/>
-        <v>1508195.47</v>
+        <v>1900595.47</v>
       </c>
       <c r="O61" s="136">
         <f t="shared" si="9"/>
-        <v>1553441.47</v>
+        <v>1957613.47</v>
       </c>
       <c r="P61" s="50">
         <f t="shared" si="8"/>
         <v>0.47000000000000025</v>
       </c>
       <c r="Q61" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="125">
         <f t="shared" si="10"/>
         <v>48</v>
@@ -7220,19 +7253,16 @@
         <v>1.35</v>
       </c>
       <c r="E62" s="79">
-        <v>292005.48</v>
-      </c>
-      <c r="F62" s="79">
-        <f t="shared" ref="F62:F67" si="15">E62</f>
-        <v>292005.48</v>
-      </c>
+        <v>297000.48</v>
+      </c>
+      <c r="F62" s="79"/>
       <c r="G62" s="106">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>297000.48</v>
       </c>
       <c r="H62" s="106">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>8910.0143999999982</v>
       </c>
       <c r="I62" s="121">
         <f t="shared" si="13"/>
@@ -7250,21 +7280,21 @@
       <c r="M62" s="142"/>
       <c r="N62" s="107">
         <f t="shared" si="6"/>
-        <v>297000.48</v>
+        <v>602910.48</v>
       </c>
       <c r="O62" s="135">
         <f t="shared" si="9"/>
-        <v>305910.48</v>
+        <v>620997.48</v>
       </c>
       <c r="P62" s="50">
         <f t="shared" si="8"/>
         <v>0.48000000000000026</v>
       </c>
       <c r="Q62" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="125">
         <f t="shared" si="10"/>
         <v>49</v>
@@ -7277,11 +7307,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E63" s="78">
-        <v>235200.49</v>
-      </c>
-      <c r="F63" s="79">
+        <v>246400.49</v>
+      </c>
+      <c r="F63" s="315">
         <f>E63</f>
-        <v>235200.49</v>
+        <v>246400.49</v>
       </c>
       <c r="G63" s="80">
         <f t="shared" si="0"/>
@@ -7318,7 +7348,7 @@
         <v>0.49000000000000027</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="125">
         <f t="shared" si="10"/>
         <v>50</v>
@@ -7331,19 +7361,16 @@
         <v>0.82</v>
       </c>
       <c r="E64" s="78">
-        <v>324229.5</v>
-      </c>
-      <c r="F64" s="79">
-        <f>E64</f>
-        <v>324229.5</v>
-      </c>
+        <v>180400.5</v>
+      </c>
+      <c r="F64" s="79"/>
       <c r="G64" s="80">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>180400.5</v>
       </c>
       <c r="H64" s="80">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>5412.0149999999994</v>
       </c>
       <c r="I64" s="120">
         <f t="shared" si="13"/>
@@ -7361,18 +7388,18 @@
       <c r="M64" s="141"/>
       <c r="N64" s="81">
         <f t="shared" si="6"/>
-        <v>180400.5</v>
+        <v>366213.5</v>
       </c>
       <c r="O64" s="134">
         <f t="shared" si="9"/>
-        <v>185812.5</v>
+        <v>377199.5</v>
       </c>
       <c r="P64" s="50">
         <f t="shared" si="8"/>
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="125">
         <f t="shared" si="10"/>
         <v>51</v>
@@ -7385,11 +7412,11 @@
         <v>0.82</v>
       </c>
       <c r="E65" s="78">
-        <v>172200.51</v>
-      </c>
-      <c r="F65" s="79">
-        <f t="shared" si="15"/>
-        <v>172200.51</v>
+        <v>180400.51</v>
+      </c>
+      <c r="F65" s="315">
+        <f>E65</f>
+        <v>180400.51</v>
       </c>
       <c r="G65" s="80">
         <f t="shared" si="0"/>
@@ -7426,7 +7453,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="125">
         <f t="shared" si="10"/>
         <v>52</v>
@@ -7439,11 +7466,11 @@
         <v>1.34</v>
       </c>
       <c r="E66" s="78">
-        <v>281400.52</v>
-      </c>
-      <c r="F66" s="79">
-        <f t="shared" si="15"/>
-        <v>281400.52</v>
+        <v>294800.52</v>
+      </c>
+      <c r="F66" s="315">
+        <f t="shared" ref="F62:F67" si="15">E66</f>
+        <v>294800.52</v>
       </c>
       <c r="G66" s="80">
         <f t="shared" si="0"/>
@@ -7480,7 +7507,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="125">
         <f t="shared" si="10"/>
         <v>53</v>
@@ -7493,11 +7520,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E67" s="79">
-        <v>242256.53</v>
-      </c>
-      <c r="F67" s="79">
+        <v>253792.53</v>
+      </c>
+      <c r="F67" s="315">
         <f t="shared" si="15"/>
-        <v>242256.53</v>
+        <v>253792.53</v>
       </c>
       <c r="G67" s="80">
         <f t="shared" si="0"/>
@@ -7534,7 +7561,7 @@
         <v>0.53000000000000025</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="125">
         <f t="shared" si="10"/>
         <v>54</v>
@@ -7547,15 +7574,14 @@
         <v>1.17</v>
       </c>
       <c r="E68" s="78">
-        <v>239561.54</v>
-      </c>
-      <c r="F68" s="79">
-        <f>E68</f>
-        <v>239561.54</v>
+        <v>257400.54</v>
+      </c>
+      <c r="F68" s="315">
+        <v>265122.53999999998</v>
       </c>
       <c r="G68" s="80">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-7721.9999999999709</v>
       </c>
       <c r="H68" s="80">
         <f t="shared" si="3"/>
@@ -7577,18 +7603,18 @@
       <c r="M68" s="141"/>
       <c r="N68" s="81">
         <f t="shared" si="6"/>
-        <v>257400.54</v>
+        <v>249678.54</v>
       </c>
       <c r="O68" s="134">
         <f t="shared" si="9"/>
-        <v>265122.54000000004</v>
+        <v>257168.54</v>
       </c>
       <c r="P68" s="50">
         <f t="shared" si="8"/>
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="125">
         <f t="shared" si="10"/>
         <v>55</v>
@@ -7601,11 +7627,11 @@
         <v>1.35</v>
       </c>
       <c r="E69" s="78">
-        <v>283500.55</v>
-      </c>
-      <c r="F69" s="79">
+        <v>297000.55</v>
+      </c>
+      <c r="F69" s="315">
         <f>E69</f>
-        <v>283500.55</v>
+        <v>297000.55</v>
       </c>
       <c r="G69" s="80">
         <f t="shared" si="0"/>
@@ -7642,7 +7668,7 @@
         <v>0.55000000000000027</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="125">
         <f t="shared" si="10"/>
         <v>56</v>
@@ -7655,18 +7681,18 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E70" s="78">
-        <v>770329.56</v>
-      </c>
-      <c r="F70" s="79">
-        <v>243000.56</v>
+        <v>789549.56</v>
+      </c>
+      <c r="F70" s="315">
+        <v>253792.56</v>
       </c>
       <c r="G70" s="80">
         <f t="shared" si="0"/>
-        <v>527329</v>
+        <v>535757</v>
       </c>
       <c r="H70" s="80">
         <f t="shared" si="3"/>
-        <v>15819.869999999999</v>
+        <v>16072.71</v>
       </c>
       <c r="I70" s="120">
         <f t="shared" si="13"/>
@@ -7684,18 +7710,18 @@
       <c r="M70" s="141"/>
       <c r="N70" s="81">
         <f t="shared" si="6"/>
-        <v>789549.56</v>
+        <v>798230.56</v>
       </c>
       <c r="O70" s="134">
         <f t="shared" si="9"/>
-        <v>813235.56</v>
+        <v>822177.56</v>
       </c>
       <c r="P70" s="50">
         <f t="shared" si="8"/>
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="125">
         <f t="shared" si="10"/>
         <v>57</v>
@@ -7708,11 +7734,11 @@
         <v>0.82</v>
       </c>
       <c r="E71" s="78">
-        <v>172200.57</v>
-      </c>
-      <c r="F71" s="79">
+        <v>180400.57</v>
+      </c>
+      <c r="F71" s="315">
         <f>E71</f>
-        <v>172200.57</v>
+        <v>180400.57</v>
       </c>
       <c r="G71" s="80">
         <f t="shared" si="0"/>
@@ -7749,10 +7775,10 @@
         <v>0.57000000000000028</v>
       </c>
       <c r="Q71" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="125">
         <f t="shared" si="10"/>
         <v>58</v>
@@ -7765,11 +7791,11 @@
         <v>0.82</v>
       </c>
       <c r="E72" s="78">
-        <v>172200.58</v>
-      </c>
-      <c r="F72" s="79">
+        <v>180400.58</v>
+      </c>
+      <c r="F72" s="315">
         <f t="shared" ref="F72" si="16">E72</f>
-        <v>172200.58</v>
+        <v>180400.58</v>
       </c>
       <c r="G72" s="80">
         <f t="shared" si="0"/>
@@ -7806,10 +7832,10 @@
         <v>0.58000000000000029</v>
       </c>
       <c r="Q72" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="125">
         <f t="shared" si="10"/>
         <v>59</v>
@@ -7822,14 +7848,15 @@
         <v>1.34</v>
       </c>
       <c r="E73" s="79">
-        <v>274369.59000000003</v>
-      </c>
-      <c r="F73" s="79">
-        <v>282600.59000000003</v>
+        <v>286569.59000000003</v>
+      </c>
+      <c r="F73" s="315">
+        <f>339888.53</f>
+        <v>339888.53</v>
       </c>
       <c r="G73" s="106">
         <f t="shared" si="0"/>
-        <v>-8231</v>
+        <v>-53318.94</v>
       </c>
       <c r="H73" s="106">
         <f t="shared" si="3"/>
@@ -7851,18 +7878,18 @@
       <c r="M73" s="142"/>
       <c r="N73" s="81">
         <f t="shared" si="6"/>
-        <v>286569.59000000003</v>
+        <v>241481.59</v>
       </c>
       <c r="O73" s="135">
         <f t="shared" si="9"/>
-        <v>295166.59000000003</v>
+        <v>248725.59</v>
       </c>
       <c r="P73" s="50">
         <f t="shared" si="8"/>
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="125">
         <f t="shared" si="10"/>
         <v>60</v>
@@ -7875,14 +7902,15 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E74" s="78">
-        <v>229318.6</v>
-      </c>
-      <c r="F74" s="79">
-        <v>236198.6</v>
+        <v>239520.6</v>
+      </c>
+      <c r="F74" s="315">
+        <f>E74</f>
+        <v>239520.6</v>
       </c>
       <c r="G74" s="80">
         <f t="shared" si="0"/>
-        <v>-6880</v>
+        <v>0</v>
       </c>
       <c r="H74" s="80">
         <f t="shared" si="3"/>
@@ -7904,18 +7932,18 @@
       <c r="M74" s="141"/>
       <c r="N74" s="81">
         <f t="shared" si="6"/>
-        <v>239520.6</v>
+        <v>246400.6</v>
       </c>
       <c r="O74" s="134">
         <f t="shared" si="9"/>
-        <v>246706.6</v>
+        <v>253792.6</v>
       </c>
       <c r="P74" s="50">
         <f t="shared" si="8"/>
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="125">
         <f t="shared" si="10"/>
         <v>61</v>
@@ -7928,11 +7956,11 @@
         <v>1.17</v>
       </c>
       <c r="E75" s="78">
-        <v>245700.61</v>
-      </c>
-      <c r="F75" s="79">
+        <v>257400.61</v>
+      </c>
+      <c r="F75" s="315">
         <f>E75</f>
-        <v>245700.61</v>
+        <v>257400.61</v>
       </c>
       <c r="G75" s="80">
         <f t="shared" si="0"/>
@@ -7969,7 +7997,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="125">
         <f t="shared" si="10"/>
         <v>62</v>
@@ -7982,11 +8010,11 @@
         <v>1.35</v>
       </c>
       <c r="E76" s="78">
-        <v>283500.62</v>
-      </c>
-      <c r="F76" s="79">
+        <v>297000.62</v>
+      </c>
+      <c r="F76" s="315">
         <f>E76</f>
-        <v>283500.62</v>
+        <v>297000.62</v>
       </c>
       <c r="G76" s="80">
         <f t="shared" si="0"/>
@@ -8023,7 +8051,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="125">
         <f t="shared" si="10"/>
         <v>63</v>
@@ -8036,11 +8064,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E77" s="78">
-        <v>242256.63</v>
-      </c>
-      <c r="F77" s="79">
+        <v>246400.63</v>
+      </c>
+      <c r="F77" s="315">
         <f>E77</f>
-        <v>242256.63</v>
+        <v>246400.63</v>
       </c>
       <c r="G77" s="80">
         <f t="shared" si="0"/>
@@ -8077,10 +8105,10 @@
         <v>0.63000000000000034</v>
       </c>
       <c r="Q77" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="125">
         <f t="shared" si="10"/>
         <v>64</v>
@@ -8093,18 +8121,18 @@
         <v>0.82</v>
       </c>
       <c r="E78" s="78">
-        <v>167896.64</v>
-      </c>
-      <c r="F78" s="79">
-        <v>160264.64000000001</v>
+        <v>188261.64</v>
+      </c>
+      <c r="F78" s="315">
+        <v>193909.64</v>
       </c>
       <c r="G78" s="80">
         <f t="shared" si="0"/>
-        <v>7632</v>
+        <v>-5648</v>
       </c>
       <c r="H78" s="80">
         <f t="shared" si="3"/>
-        <v>228.95999999999998</v>
+        <v>0</v>
       </c>
       <c r="I78" s="120">
         <f t="shared" si="13"/>
@@ -8122,18 +8150,18 @@
       <c r="M78" s="141"/>
       <c r="N78" s="81">
         <f t="shared" si="6"/>
-        <v>188261.64</v>
+        <v>174752.64000000001</v>
       </c>
       <c r="O78" s="134">
         <f t="shared" si="9"/>
-        <v>193909.64</v>
+        <v>179995.64</v>
       </c>
       <c r="P78" s="50">
         <f t="shared" si="8"/>
         <v>0.64000000000000035</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="125">
         <f t="shared" si="10"/>
         <v>65</v>
@@ -8146,19 +8174,18 @@
         <v>0.82</v>
       </c>
       <c r="E79" s="79">
-        <v>735530.65</v>
-      </c>
-      <c r="F79" s="168">
-        <f>320000+172200+6808</f>
-        <v>499008</v>
+        <v>424018.65</v>
+      </c>
+      <c r="F79" s="318">
+        <v>280000.65000000002</v>
       </c>
       <c r="G79" s="106">
         <f t="shared" ref="G79:G117" si="17">E79-F79</f>
-        <v>236522.65000000002</v>
+        <v>144018</v>
       </c>
       <c r="H79" s="106">
         <f t="shared" si="3"/>
-        <v>7095.6795000000002</v>
+        <v>4320.54</v>
       </c>
       <c r="I79" s="121">
         <f t="shared" ref="I79:I110" si="18">J$2*D79/100</f>
@@ -8176,21 +8203,21 @@
       <c r="M79" s="142"/>
       <c r="N79" s="81">
         <f t="shared" si="6"/>
-        <v>424018.65</v>
+        <v>328739.65000000002</v>
       </c>
       <c r="O79" s="135">
         <f t="shared" si="9"/>
-        <v>436739.65</v>
+        <v>338601.65</v>
       </c>
       <c r="P79" s="50">
         <f t="shared" si="8"/>
         <v>0.65000000000000036</v>
       </c>
       <c r="Q79" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="125">
         <f t="shared" si="10"/>
         <v>66</v>
@@ -8203,18 +8230,18 @@
         <v>1.34</v>
       </c>
       <c r="E80" s="79">
-        <v>887549.66</v>
+        <v>1208976.6599999999</v>
       </c>
       <c r="F80" s="79">
         <v>0</v>
       </c>
       <c r="G80" s="106">
         <f t="shared" si="17"/>
-        <v>887549.66</v>
+        <v>1208976.6599999999</v>
       </c>
       <c r="H80" s="106">
         <f t="shared" ref="H80:H117" si="20">IF(G80&gt;0,G80*3%,0)</f>
-        <v>26626.489799999999</v>
+        <v>36269.299799999993</v>
       </c>
       <c r="I80" s="121">
         <f t="shared" si="18"/>
@@ -8232,42 +8259,43 @@
       <c r="M80" s="142"/>
       <c r="N80" s="107">
         <f t="shared" si="6"/>
-        <v>1208976.6599999999</v>
+        <v>1540046.66</v>
       </c>
       <c r="O80" s="135">
         <f t="shared" si="9"/>
-        <v>1245245.6599999999</v>
+        <v>1586247.66</v>
       </c>
       <c r="P80" s="50">
         <f t="shared" si="8"/>
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A81" s="322">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A81" s="125">
         <f t="shared" si="10"/>
         <v>67</v>
       </c>
-      <c r="B81" s="323" t="s">
+      <c r="B81" s="109" t="s">
         <v>66</v>
       </c>
-      <c r="C81" s="82"/>
-      <c r="D81" s="77">
+      <c r="C81" s="108"/>
+      <c r="D81" s="105">
         <v>1.1200000000000001</v>
       </c>
       <c r="E81" s="78">
-        <v>436973.67</v>
-      </c>
-      <c r="F81" s="79">
-        <v>235240.67</v>
+        <v>454185.67</v>
+      </c>
+      <c r="F81" s="315">
+        <f>200000+261811.67+5877</f>
+        <v>467688.67000000004</v>
       </c>
       <c r="G81" s="80">
         <f t="shared" si="17"/>
-        <v>201732.99999999997</v>
+        <v>-13503.000000000058</v>
       </c>
       <c r="H81" s="80">
         <f t="shared" si="20"/>
-        <v>6051.9899999999989</v>
+        <v>0</v>
       </c>
       <c r="I81" s="120">
         <f t="shared" si="18"/>
@@ -8285,93 +8313,93 @@
       <c r="M81" s="141"/>
       <c r="N81" s="81">
         <f t="shared" ref="N81:N117" si="22">ROUND(SUM(G81:M81),0) + P81</f>
-        <v>454185.67</v>
+        <v>232897.67</v>
       </c>
       <c r="O81" s="134">
         <f t="shared" si="9"/>
-        <v>467811.67</v>
+        <v>239884.67</v>
       </c>
       <c r="P81" s="50">
         <f t="shared" si="8"/>
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A82" s="179">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A82" s="178">
         <f t="shared" si="10"/>
         <v>68</v>
       </c>
-      <c r="B82" s="180" t="s">
+      <c r="B82" s="179" t="s">
         <v>67</v>
       </c>
-      <c r="C82" s="189"/>
-      <c r="D82" s="190">
+      <c r="C82" s="188"/>
+      <c r="D82" s="189">
         <v>1.17</v>
       </c>
-      <c r="E82" s="191">
-        <v>7899036.6799999997</v>
-      </c>
-      <c r="F82" s="191">
-        <v>0</v>
-      </c>
-      <c r="G82" s="192">
+      <c r="E82" s="190">
+        <v>8488408.6799999997</v>
+      </c>
+      <c r="F82" s="190">
+        <v>0</v>
+      </c>
+      <c r="G82" s="191">
         <f t="shared" si="17"/>
-        <v>7899036.6799999997</v>
-      </c>
-      <c r="H82" s="192">
+        <v>8488408.6799999997</v>
+      </c>
+      <c r="H82" s="191">
         <f t="shared" si="20"/>
-        <v>236971.1004</v>
-      </c>
-      <c r="I82" s="193">
+        <v>254652.26039999997</v>
+      </c>
+      <c r="I82" s="192">
         <f t="shared" si="18"/>
         <v>136828.54645199998</v>
       </c>
-      <c r="J82" s="193">
+      <c r="J82" s="192">
         <f t="shared" si="19"/>
         <v>52650</v>
       </c>
-      <c r="K82" s="193">
+      <c r="K82" s="192">
         <f t="shared" si="21"/>
         <v>67921.453548000005</v>
       </c>
-      <c r="L82" s="193">
+      <c r="L82" s="192">
         <v>95000</v>
       </c>
-      <c r="M82" s="194"/>
-      <c r="N82" s="195">
+      <c r="M82" s="193"/>
+      <c r="N82" s="194">
         <f t="shared" si="22"/>
-        <v>8488408.6799999997</v>
-      </c>
-      <c r="O82" s="196">
+        <v>9095461.6799999997</v>
+      </c>
+      <c r="O82" s="195">
         <f t="shared" si="9"/>
-        <v>8743060.6799999997</v>
+        <v>9368325.6799999997</v>
       </c>
       <c r="P82" s="50">
         <f t="shared" si="8"/>
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A83" s="227">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A83" s="125">
         <f t="shared" si="10"/>
         <v>69</v>
       </c>
-      <c r="B83" s="228" t="s">
+      <c r="B83" s="109" t="s">
         <v>68</v>
       </c>
-      <c r="C83" s="82"/>
-      <c r="D83" s="77">
+      <c r="C83" s="108"/>
+      <c r="D83" s="105">
         <v>1.35</v>
       </c>
       <c r="E83" s="78">
-        <v>283420.69</v>
-      </c>
-      <c r="F83" s="79">
-        <v>285000</v>
+        <v>295421.69</v>
+      </c>
+      <c r="F83" s="315">
+        <v>300000</v>
       </c>
       <c r="G83" s="80">
         <f t="shared" si="17"/>
-        <v>-1579.3099999999977</v>
+        <v>-4578.3099999999977</v>
       </c>
       <c r="H83" s="80">
         <f t="shared" si="20"/>
@@ -8390,23 +8418,23 @@
         <v>78370.907940000005</v>
       </c>
       <c r="L83" s="120" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M83" s="141"/>
       <c r="N83" s="81">
         <f t="shared" si="22"/>
-        <v>295421.69</v>
+        <v>292422.69</v>
       </c>
       <c r="O83" s="134">
         <f t="shared" si="9"/>
-        <v>304284.69</v>
+        <v>301195.69</v>
       </c>
       <c r="P83" s="50">
         <f t="shared" si="8"/>
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="125">
         <f t="shared" si="10"/>
         <v>70</v>
@@ -8419,18 +8447,16 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E84" s="79">
-        <v>442849.7</v>
-      </c>
-      <c r="F84" s="79">
-        <v>50400</v>
-      </c>
+        <v>650623.69999999995</v>
+      </c>
+      <c r="F84" s="79"/>
       <c r="G84" s="106">
         <f t="shared" si="17"/>
-        <v>392449.7</v>
+        <v>650623.69999999995</v>
       </c>
       <c r="H84" s="106">
         <f t="shared" si="20"/>
-        <v>11773.491</v>
+        <v>19518.710999999999</v>
       </c>
       <c r="I84" s="121">
         <f t="shared" si="18"/>
@@ -8448,21 +8474,21 @@
       <c r="M84" s="142"/>
       <c r="N84" s="81">
         <f t="shared" si="22"/>
-        <v>650623.69999999995</v>
+        <v>916542.7</v>
       </c>
       <c r="O84" s="135">
         <f t="shared" si="9"/>
-        <v>670142.69999999995</v>
+        <v>944038.7</v>
       </c>
       <c r="P84" s="50">
         <f t="shared" si="8"/>
         <v>0.7000000000000004</v>
       </c>
       <c r="Q84" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="125">
         <f t="shared" si="10"/>
         <v>71</v>
@@ -8470,16 +8496,16 @@
       <c r="B85" s="109" t="s">
         <v>70</v>
       </c>
-      <c r="C85" s="82"/>
-      <c r="D85" s="77">
+      <c r="C85" s="108"/>
+      <c r="D85" s="105">
         <v>0.82</v>
       </c>
       <c r="E85" s="78">
-        <v>172200.71</v>
-      </c>
-      <c r="F85" s="79">
+        <v>180400.71</v>
+      </c>
+      <c r="F85" s="315">
         <f>E85</f>
-        <v>172200.71</v>
+        <v>180400.71</v>
       </c>
       <c r="G85" s="80">
         <f t="shared" si="17"/>
@@ -8516,7 +8542,7 @@
         <v>0.71000000000000041</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="125">
         <f t="shared" si="10"/>
         <v>72</v>
@@ -8529,11 +8555,11 @@
         <v>0.82</v>
       </c>
       <c r="E86" s="78">
-        <v>172200.72</v>
-      </c>
-      <c r="F86" s="79">
+        <v>180400.72</v>
+      </c>
+      <c r="F86" s="315">
         <f>E86</f>
-        <v>172200.72</v>
+        <v>180400.72</v>
       </c>
       <c r="G86" s="80">
         <f t="shared" si="17"/>
@@ -8570,7 +8596,7 @@
         <v>0.72000000000000042</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="125">
         <f t="shared" si="10"/>
         <v>73</v>
@@ -8583,19 +8609,16 @@
         <v>1.34</v>
       </c>
       <c r="E87" s="78">
-        <v>281400.73</v>
-      </c>
-      <c r="F87" s="79">
-        <f>E87</f>
-        <v>281400.73</v>
-      </c>
+        <v>294800.73</v>
+      </c>
+      <c r="F87" s="79"/>
       <c r="G87" s="80">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>294800.73</v>
       </c>
       <c r="H87" s="80">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>8844.0218999999997</v>
       </c>
       <c r="I87" s="120">
         <f t="shared" si="18"/>
@@ -8613,18 +8636,18 @@
       <c r="M87" s="141"/>
       <c r="N87" s="81">
         <f t="shared" si="22"/>
-        <v>294800.73</v>
+        <v>598445.73</v>
       </c>
       <c r="O87" s="134">
         <f t="shared" si="9"/>
-        <v>303644.73</v>
+        <v>616398.73</v>
       </c>
       <c r="P87" s="50">
         <f t="shared" si="8"/>
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="126">
         <f t="shared" si="10"/>
         <v>74</v>
@@ -8637,10 +8660,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E88" s="117">
-        <v>365200.74</v>
-      </c>
-      <c r="F88" s="117">
-        <v>365200.74</v>
+        <v>376400.74</v>
+      </c>
+      <c r="F88" s="317">
+        <f>E88</f>
+        <v>376400.74</v>
       </c>
       <c r="G88" s="118">
         <f t="shared" si="17"/>
@@ -8678,10 +8702,10 @@
         <v>0.74000000000000044</v>
       </c>
       <c r="Q88" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="124">
         <f t="shared" si="10"/>
         <v>75</v>
@@ -8694,14 +8718,14 @@
         <v>1.17</v>
       </c>
       <c r="E89" s="78">
-        <v>239382.75</v>
-      </c>
-      <c r="F89" s="79">
-        <v>246563.75</v>
+        <v>250219.75</v>
+      </c>
+      <c r="F89" s="315">
+        <v>257726.75</v>
       </c>
       <c r="G89" s="80">
         <f t="shared" si="17"/>
-        <v>-7181</v>
+        <v>-7507</v>
       </c>
       <c r="H89" s="80">
         <f t="shared" si="20"/>
@@ -8723,18 +8747,18 @@
       <c r="M89" s="141"/>
       <c r="N89" s="81">
         <f t="shared" si="22"/>
-        <v>250219.75</v>
+        <v>249893.75</v>
       </c>
       <c r="O89" s="134">
         <f t="shared" si="9"/>
-        <v>257726.75</v>
+        <v>257390.75</v>
       </c>
       <c r="P89" s="50">
         <f t="shared" si="8"/>
         <v>0.75000000000000044</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="125">
         <f t="shared" si="10"/>
         <v>76</v>
@@ -8747,11 +8771,11 @@
         <v>1.35</v>
       </c>
       <c r="E90" s="79">
-        <v>291009.76</v>
-      </c>
-      <c r="F90" s="79">
+        <v>297000.76</v>
+      </c>
+      <c r="F90" s="315">
         <f>E90</f>
-        <v>291009.76</v>
+        <v>297000.76</v>
       </c>
       <c r="G90" s="106">
         <f t="shared" si="17"/>
@@ -8788,7 +8812,7 @@
         <v>0.76000000000000045</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="124">
         <f t="shared" si="10"/>
         <v>77</v>
@@ -8801,11 +8825,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E91" s="78">
-        <v>235200.77</v>
-      </c>
-      <c r="F91" s="79">
+        <v>246400.77</v>
+      </c>
+      <c r="F91" s="315">
         <f>E91</f>
-        <v>235200.77</v>
+        <v>246400.77</v>
       </c>
       <c r="G91" s="80">
         <f t="shared" si="17"/>
@@ -8842,7 +8866,7 @@
         <v>0.77000000000000046</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="126">
         <f t="shared" si="10"/>
         <v>78</v>
@@ -8855,11 +8879,11 @@
         <v>0.82</v>
       </c>
       <c r="E92" s="117">
-        <v>347316.78</v>
-      </c>
-      <c r="F92" s="117">
+        <v>355762.78</v>
+      </c>
+      <c r="F92" s="317">
         <f>E92</f>
-        <v>347316.78</v>
+        <v>355762.78</v>
       </c>
       <c r="G92" s="118">
         <f t="shared" si="17"/>
@@ -8895,34 +8919,35 @@
         <v>0.78000000000000047</v>
       </c>
       <c r="Q92" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="124">
         <f t="shared" si="10"/>
         <v>79</v>
       </c>
       <c r="B93" s="83" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C93" s="82"/>
       <c r="D93" s="77">
         <v>0.82</v>
       </c>
       <c r="E93" s="78">
-        <v>172200.79</v>
-      </c>
-      <c r="F93" s="79">
-        <v>159900.79</v>
+        <v>193069.79</v>
+      </c>
+      <c r="F93" s="315">
+        <f>E93</f>
+        <v>193069.79</v>
       </c>
       <c r="G93" s="80">
         <f t="shared" si="17"/>
-        <v>12300</v>
+        <v>0</v>
       </c>
       <c r="H93" s="80">
         <f t="shared" si="20"/>
-        <v>369</v>
+        <v>0</v>
       </c>
       <c r="I93" s="120">
         <f t="shared" si="18"/>
@@ -8940,21 +8965,21 @@
       <c r="M93" s="141"/>
       <c r="N93" s="81">
         <f t="shared" si="22"/>
-        <v>193069.79</v>
+        <v>180400.79</v>
       </c>
       <c r="O93" s="134">
         <f t="shared" si="9"/>
-        <v>198861.79</v>
+        <v>185812.79</v>
       </c>
       <c r="P93" s="50">
         <f t="shared" si="8"/>
         <v>0.79000000000000048</v>
       </c>
       <c r="Q93" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="125">
         <f t="shared" si="10"/>
         <v>80</v>
@@ -8967,11 +8992,11 @@
         <v>1.34</v>
       </c>
       <c r="E94" s="79">
-        <v>274162.8</v>
-      </c>
-      <c r="F94" s="79">
+        <v>294800.8</v>
+      </c>
+      <c r="F94" s="315">
         <f>E94</f>
-        <v>274162.8</v>
+        <v>294800.8</v>
       </c>
       <c r="G94" s="80">
         <f>E94-F94</f>
@@ -9008,7 +9033,7 @@
         <v>0.80000000000000049</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="125">
         <f t="shared" si="10"/>
         <v>81</v>
@@ -9021,11 +9046,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E95" s="79">
-        <v>235200.81</v>
-      </c>
-      <c r="F95" s="79">
+        <v>246400.81</v>
+      </c>
+      <c r="F95" s="315">
         <f>E95</f>
-        <v>235200.81</v>
+        <v>246400.81</v>
       </c>
       <c r="G95" s="106">
         <f t="shared" si="17"/>
@@ -9062,10 +9087,10 @@
         <v>0.8100000000000005</v>
       </c>
       <c r="Q95" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="125">
         <f t="shared" si="10"/>
         <v>82</v>
@@ -9078,18 +9103,19 @@
         <v>1.17</v>
       </c>
       <c r="E96" s="78">
-        <v>253071.82</v>
-      </c>
-      <c r="F96" s="79">
-        <v>234995.82</v>
+        <v>276018.82</v>
+      </c>
+      <c r="F96" s="315">
+        <f>E96</f>
+        <v>276018.82</v>
       </c>
       <c r="G96" s="80">
         <f t="shared" si="17"/>
-        <v>18076</v>
+        <v>0</v>
       </c>
       <c r="H96" s="80">
         <f t="shared" si="20"/>
-        <v>542.28</v>
+        <v>0</v>
       </c>
       <c r="I96" s="120">
         <f t="shared" si="18"/>
@@ -9107,18 +9133,18 @@
       <c r="M96" s="141"/>
       <c r="N96" s="81">
         <f t="shared" si="22"/>
-        <v>276018.82</v>
+        <v>257400.82</v>
       </c>
       <c r="O96" s="134">
         <f t="shared" si="9"/>
-        <v>284299.82</v>
+        <v>265122.82</v>
       </c>
       <c r="P96" s="50">
         <f t="shared" si="8"/>
         <v>0.82000000000000051</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="125">
         <f t="shared" si="10"/>
         <v>83</v>
@@ -9131,11 +9157,11 @@
         <v>1.35</v>
       </c>
       <c r="E97" s="79">
-        <v>283500.83</v>
-      </c>
-      <c r="F97" s="79">
+        <v>297000.83</v>
+      </c>
+      <c r="F97" s="315">
         <f t="shared" ref="F97:F104" si="23">E97</f>
-        <v>283500.83</v>
+        <v>297000.83</v>
       </c>
       <c r="G97" s="80">
         <f t="shared" si="17"/>
@@ -9172,7 +9198,7 @@
         <v>0.83000000000000052</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="125">
         <f t="shared" si="10"/>
         <v>84</v>
@@ -9185,19 +9211,16 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E98" s="79">
-        <v>178463.84</v>
-      </c>
-      <c r="F98" s="79">
-        <f t="shared" si="23"/>
-        <v>178463.84</v>
-      </c>
+        <v>246400.84</v>
+      </c>
+      <c r="F98" s="79"/>
       <c r="G98" s="80">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>246400.84</v>
       </c>
       <c r="H98" s="80">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>7392.0252</v>
       </c>
       <c r="I98" s="120">
         <f t="shared" si="18"/>
@@ -9215,18 +9238,18 @@
       <c r="M98" s="141"/>
       <c r="N98" s="81">
         <f t="shared" si="22"/>
-        <v>246400.84</v>
+        <v>500193.84</v>
       </c>
       <c r="O98" s="134">
         <f t="shared" si="9"/>
-        <v>253792.84</v>
+        <v>515199.84</v>
       </c>
       <c r="P98" s="50">
         <f t="shared" ref="P98:P117" si="24">P97+0.01</f>
         <v>0.84000000000000052</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="124">
         <f t="shared" si="10"/>
         <v>85</v>
@@ -9239,11 +9262,11 @@
         <v>0.82</v>
       </c>
       <c r="E99" s="78">
-        <v>172200.85</v>
-      </c>
-      <c r="F99" s="79">
+        <v>180400.85</v>
+      </c>
+      <c r="F99" s="315">
         <f t="shared" si="23"/>
-        <v>172200.85</v>
+        <v>180400.85</v>
       </c>
       <c r="G99" s="80">
         <f t="shared" si="17"/>
@@ -9280,7 +9303,7 @@
         <v>0.85000000000000053</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="125">
         <f t="shared" si="10"/>
         <v>86</v>
@@ -9293,11 +9316,11 @@
         <v>0.82</v>
       </c>
       <c r="E100" s="79">
-        <v>167772.86</v>
-      </c>
-      <c r="F100" s="79">
+        <v>180400.86</v>
+      </c>
+      <c r="F100" s="315">
         <f t="shared" si="23"/>
-        <v>167772.86</v>
+        <v>180400.86</v>
       </c>
       <c r="G100" s="106">
         <f t="shared" si="17"/>
@@ -9334,7 +9357,7 @@
         <v>0.86000000000000054</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="124">
         <f t="shared" ref="A101:A117" si="26">A100+1</f>
         <v>87</v>
@@ -9347,11 +9370,11 @@
         <v>1.34</v>
       </c>
       <c r="E101" s="78">
-        <v>281400.87</v>
-      </c>
-      <c r="F101" s="79">
+        <v>294800.87</v>
+      </c>
+      <c r="F101" s="315">
         <f t="shared" si="23"/>
-        <v>281400.87</v>
+        <v>294800.87</v>
       </c>
       <c r="G101" s="80">
         <f t="shared" si="17"/>
@@ -9388,7 +9411,7 @@
         <v>0.87000000000000055</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" s="124">
         <f t="shared" si="26"/>
         <v>88</v>
@@ -9401,11 +9424,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E102" s="78">
-        <v>235200.88</v>
-      </c>
-      <c r="F102" s="79">
+        <v>246400.88</v>
+      </c>
+      <c r="F102" s="315">
         <f t="shared" si="23"/>
-        <v>235200.88</v>
+        <v>246400.88</v>
       </c>
       <c r="G102" s="80">
         <f t="shared" si="17"/>
@@ -9442,7 +9465,7 @@
         <v>0.88000000000000056</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" s="124">
         <f t="shared" si="26"/>
         <v>89</v>
@@ -9455,11 +9478,11 @@
         <v>1.17</v>
       </c>
       <c r="E103" s="78">
-        <v>245700.89</v>
-      </c>
-      <c r="F103" s="79">
+        <v>257400.89</v>
+      </c>
+      <c r="F103" s="315">
         <f t="shared" si="23"/>
-        <v>245700.89</v>
+        <v>257400.89</v>
       </c>
       <c r="G103" s="80">
         <f t="shared" si="17"/>
@@ -9496,7 +9519,7 @@
         <v>0.89000000000000057</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="124">
         <f t="shared" si="26"/>
         <v>90</v>
@@ -9509,11 +9532,11 @@
         <v>0.1</v>
       </c>
       <c r="E104" s="78">
-        <v>21000.9</v>
-      </c>
-      <c r="F104" s="79">
+        <v>22000.9</v>
+      </c>
+      <c r="F104" s="315">
         <f t="shared" si="23"/>
-        <v>21000.9</v>
+        <v>22000.9</v>
       </c>
       <c r="G104" s="80">
         <f t="shared" si="17"/>
@@ -9550,7 +9573,7 @@
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" s="124">
         <f t="shared" si="26"/>
         <v>91</v>
@@ -9563,18 +9586,19 @@
         <v>0.1</v>
       </c>
       <c r="E105" s="78">
-        <v>22155.91</v>
-      </c>
-      <c r="F105" s="79">
-        <v>20610.91</v>
+        <v>23591.91</v>
+      </c>
+      <c r="F105" s="315">
+        <f>E105</f>
+        <v>23591.91</v>
       </c>
       <c r="G105" s="80">
         <f t="shared" si="17"/>
-        <v>1545</v>
+        <v>0</v>
       </c>
       <c r="H105" s="80">
         <f t="shared" si="20"/>
-        <v>46.35</v>
+        <v>0</v>
       </c>
       <c r="I105" s="120">
         <f t="shared" si="18"/>
@@ -9592,18 +9616,18 @@
       <c r="M105" s="141"/>
       <c r="N105" s="81">
         <f t="shared" si="22"/>
-        <v>23591.91</v>
+        <v>22000.91</v>
       </c>
       <c r="O105" s="134">
         <f t="shared" si="25"/>
-        <v>24299.91</v>
+        <v>22660.91</v>
       </c>
       <c r="P105" s="50">
         <f t="shared" si="24"/>
         <v>0.91000000000000059</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" s="124">
         <f t="shared" si="26"/>
         <v>92</v>
@@ -9616,14 +9640,14 @@
         <v>0.1</v>
       </c>
       <c r="E106" s="78">
-        <v>20475.919999999998</v>
-      </c>
-      <c r="F106" s="79">
-        <v>21081.919999999998</v>
+        <v>21394.92</v>
+      </c>
+      <c r="F106" s="315">
+        <v>22036.92</v>
       </c>
       <c r="G106" s="80">
         <f t="shared" si="17"/>
-        <v>-606</v>
+        <v>-642</v>
       </c>
       <c r="H106" s="80">
         <f t="shared" si="20"/>
@@ -9645,18 +9669,18 @@
       <c r="M106" s="141"/>
       <c r="N106" s="81">
         <f t="shared" si="22"/>
-        <v>21394.92</v>
+        <v>21358.92</v>
       </c>
       <c r="O106" s="134">
         <f t="shared" si="25"/>
-        <v>22036.92</v>
+        <v>21999.919999999998</v>
       </c>
       <c r="P106" s="50">
         <f t="shared" si="24"/>
         <v>0.9200000000000006</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" s="125">
         <f t="shared" si="26"/>
         <v>93</v>
@@ -9669,11 +9693,11 @@
         <v>0.1</v>
       </c>
       <c r="E107" s="79">
-        <v>20475.93</v>
-      </c>
-      <c r="F107" s="79">
+        <v>22000.93</v>
+      </c>
+      <c r="F107" s="315">
         <f>E107</f>
-        <v>20475.93</v>
+        <v>22000.93</v>
       </c>
       <c r="G107" s="106">
         <f t="shared" si="17"/>
@@ -9710,7 +9734,7 @@
         <v>0.9300000000000006</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" s="125">
         <f t="shared" si="26"/>
         <v>94</v>
@@ -9723,11 +9747,11 @@
         <v>0.1</v>
       </c>
       <c r="E108" s="79">
-        <v>21000.94</v>
-      </c>
-      <c r="F108" s="79">
+        <v>22000.94</v>
+      </c>
+      <c r="F108" s="315">
         <f t="shared" ref="F108:F113" si="27">E108</f>
-        <v>21000.94</v>
+        <v>22000.94</v>
       </c>
       <c r="G108" s="106">
         <f t="shared" si="17"/>
@@ -9764,24 +9788,24 @@
         <v>0.94000000000000061</v>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="125">
         <f t="shared" si="26"/>
         <v>95</v>
       </c>
       <c r="B109" s="109" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C109" s="108"/>
       <c r="D109" s="105">
         <v>0.1</v>
       </c>
       <c r="E109" s="79">
-        <v>21000.95</v>
-      </c>
-      <c r="F109" s="79">
+        <v>22000.95</v>
+      </c>
+      <c r="F109" s="315">
         <f t="shared" si="27"/>
-        <v>21000.95</v>
+        <v>22000.95</v>
       </c>
       <c r="G109" s="106">
         <f t="shared" si="17"/>
@@ -9818,7 +9842,7 @@
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" s="125">
         <f t="shared" si="26"/>
         <v>96</v>
@@ -9831,11 +9855,11 @@
         <v>0.1</v>
       </c>
       <c r="E110" s="79">
-        <v>21000.959999999999</v>
-      </c>
-      <c r="F110" s="79">
+        <v>22000.959999999999</v>
+      </c>
+      <c r="F110" s="315">
         <f>E110</f>
-        <v>21000.959999999999</v>
+        <v>22000.959999999999</v>
       </c>
       <c r="G110" s="106">
         <f t="shared" si="17"/>
@@ -9872,10 +9896,10 @@
         <v>0.96000000000000063</v>
       </c>
       <c r="Q110" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" s="125">
         <f t="shared" si="26"/>
         <v>97</v>
@@ -9888,11 +9912,11 @@
         <v>0.1</v>
       </c>
       <c r="E111" s="79">
-        <v>21000.97</v>
-      </c>
-      <c r="F111" s="79">
+        <v>22000.97</v>
+      </c>
+      <c r="F111" s="315">
         <f t="shared" si="27"/>
-        <v>21000.97</v>
+        <v>22000.97</v>
       </c>
       <c r="G111" s="106">
         <f t="shared" si="17"/>
@@ -9929,7 +9953,7 @@
         <v>0.97000000000000064</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" s="125">
         <f t="shared" si="26"/>
         <v>98</v>
@@ -9942,11 +9966,11 @@
         <v>0.1</v>
       </c>
       <c r="E112" s="79">
-        <v>21000.98</v>
-      </c>
-      <c r="F112" s="79">
+        <v>22000.98</v>
+      </c>
+      <c r="F112" s="315">
         <f>E112</f>
-        <v>21000.98</v>
+        <v>22000.98</v>
       </c>
       <c r="G112" s="106">
         <f t="shared" si="17"/>
@@ -9983,7 +10007,7 @@
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A113" s="125">
         <f t="shared" si="26"/>
         <v>99</v>
@@ -9996,11 +10020,11 @@
         <v>0.1</v>
       </c>
       <c r="E113" s="79">
-        <v>21000.99</v>
-      </c>
-      <c r="F113" s="79">
+        <v>22000.99</v>
+      </c>
+      <c r="F113" s="315">
         <f t="shared" si="27"/>
-        <v>21000.99</v>
+        <v>22000.99</v>
       </c>
       <c r="G113" s="106">
         <f t="shared" si="17"/>
@@ -10037,7 +10061,7 @@
         <v>0.99000000000000066</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A114" s="125">
         <f t="shared" si="26"/>
         <v>100</v>
@@ -10050,15 +10074,12 @@
         <v>0.1</v>
       </c>
       <c r="E114" s="79">
-        <v>6236</v>
-      </c>
-      <c r="F114" s="79">
-        <f>12043+21000</f>
-        <v>33043</v>
-      </c>
+        <v>-4806</v>
+      </c>
+      <c r="F114" s="79"/>
       <c r="G114" s="106">
         <f t="shared" si="17"/>
-        <v>-26807</v>
+        <v>-4806</v>
       </c>
       <c r="H114" s="106">
         <f t="shared" si="20"/>
@@ -10080,18 +10101,18 @@
       <c r="M114" s="142"/>
       <c r="N114" s="81">
         <f t="shared" si="22"/>
-        <v>-4806</v>
+        <v>17195</v>
       </c>
       <c r="O114" s="135">
         <f t="shared" si="25"/>
-        <v>-4950</v>
+        <v>17711</v>
       </c>
       <c r="P114" s="50">
         <f t="shared" si="24"/>
         <v>1.0000000000000007</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A115" s="125">
         <f t="shared" si="26"/>
         <v>101</v>
@@ -10104,11 +10125,11 @@
         <v>0.1</v>
       </c>
       <c r="E115" s="79">
-        <v>20476.009999999998</v>
-      </c>
-      <c r="F115" s="79">
+        <v>22001.01</v>
+      </c>
+      <c r="F115" s="315">
         <f>E115</f>
-        <v>20476.009999999998</v>
+        <v>22001.01</v>
       </c>
       <c r="G115" s="106">
         <f t="shared" si="17"/>
@@ -10145,7 +10166,7 @@
         <v>1.0100000000000007</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A116" s="125">
         <f t="shared" si="26"/>
         <v>102</v>
@@ -10158,11 +10179,11 @@
         <v>0.1</v>
       </c>
       <c r="E116" s="79">
-        <v>21001.02</v>
-      </c>
-      <c r="F116" s="79">
+        <v>22001.02</v>
+      </c>
+      <c r="F116" s="315">
         <f>E116</f>
-        <v>21001.02</v>
+        <v>22001.02</v>
       </c>
       <c r="G116" s="106">
         <f t="shared" si="17"/>
@@ -10199,24 +10220,24 @@
         <v>1.0200000000000007</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A117" s="125">
         <f t="shared" si="26"/>
         <v>103</v>
       </c>
       <c r="B117" s="109" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C117" s="108"/>
       <c r="D117" s="105">
         <v>0.1</v>
       </c>
       <c r="E117" s="79">
-        <v>21001.03</v>
-      </c>
-      <c r="F117" s="79">
+        <v>22001.03</v>
+      </c>
+      <c r="F117" s="315">
         <f>E117</f>
-        <v>21001.03</v>
+        <v>22001.03</v>
       </c>
       <c r="G117" s="106">
         <f t="shared" si="17"/>
@@ -10253,7 +10274,7 @@
         <v>1.0300000000000007</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A118" s="125"/>
       <c r="B118" s="103"/>
       <c r="C118" s="108"/>
@@ -10271,7 +10292,7 @@
       <c r="O118" s="135"/>
       <c r="P118" s="50"/>
     </row>
-    <row r="119" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="127"/>
       <c r="B119" s="128"/>
       <c r="C119" s="128"/>
@@ -10281,19 +10302,19 @@
       </c>
       <c r="E119" s="130">
         <f t="shared" si="30"/>
-        <v>44844620.56000001</v>
-      </c>
-      <c r="F119" s="226">
+        <v>47152096.559999995</v>
+      </c>
+      <c r="F119" s="218">
         <f>SUM(F15:F118)</f>
-        <v>21426698.540000003</v>
+        <v>18974843.529999997</v>
       </c>
       <c r="G119" s="131">
         <f t="shared" si="30"/>
-        <v>23417922.020000003</v>
+        <v>28177253.030000001</v>
       </c>
       <c r="H119" s="131">
         <f t="shared" si="30"/>
-        <v>639868.71240000008</v>
+        <v>754188.30630000005</v>
       </c>
       <c r="I119" s="132">
         <f t="shared" si="30"/>
@@ -10308,126 +10329,126 @@
       <c r="M119" s="144"/>
       <c r="N119" s="140">
         <f t="shared" si="30"/>
-        <v>47134342.559999995</v>
+        <v>52007993.560000002</v>
       </c>
       <c r="O119" s="137">
         <f t="shared" si="30"/>
-        <v>48548373.560000002</v>
-      </c>
-    </row>
-    <row r="120" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>53568230.560000002</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B120" s="84"/>
       <c r="C120" s="84"/>
     </row>
-    <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="122" spans="1:16" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B122" s="286" t="s">
+    <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="122" spans="1:16" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B122" s="283" t="s">
         <v>103</v>
       </c>
-      <c r="C122" s="286"/>
-      <c r="D122" s="286"/>
-      <c r="E122" s="286"/>
-      <c r="F122" s="286"/>
-      <c r="G122" s="286"/>
-      <c r="H122" s="286"/>
-      <c r="I122" s="286"/>
-      <c r="J122" s="286"/>
-      <c r="K122" s="286"/>
-      <c r="L122" s="286"/>
-      <c r="M122" s="286"/>
-      <c r="N122" s="286"/>
-    </row>
-    <row r="123" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B123" s="286"/>
-      <c r="C123" s="286"/>
-      <c r="D123" s="286"/>
-      <c r="E123" s="286"/>
-      <c r="F123" s="286"/>
-      <c r="G123" s="286"/>
-      <c r="H123" s="286"/>
-      <c r="I123" s="286"/>
-      <c r="J123" s="286"/>
-      <c r="K123" s="286"/>
-      <c r="L123" s="286"/>
-      <c r="M123" s="286"/>
-      <c r="N123" s="286"/>
-    </row>
-    <row r="124" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B124" s="286"/>
-      <c r="C124" s="286"/>
-      <c r="D124" s="286"/>
-      <c r="E124" s="286"/>
-      <c r="F124" s="286"/>
-      <c r="G124" s="286"/>
-      <c r="H124" s="286"/>
-      <c r="I124" s="286"/>
-      <c r="J124" s="286"/>
-      <c r="K124" s="286"/>
-      <c r="L124" s="286"/>
-      <c r="M124" s="286"/>
-      <c r="N124" s="286"/>
-    </row>
-    <row r="125" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B125" s="286"/>
-      <c r="C125" s="286"/>
-      <c r="D125" s="286"/>
-      <c r="E125" s="286"/>
-      <c r="F125" s="286"/>
-      <c r="G125" s="286"/>
-      <c r="H125" s="286"/>
-      <c r="I125" s="286"/>
-      <c r="J125" s="286"/>
-      <c r="K125" s="286"/>
-      <c r="L125" s="286"/>
-      <c r="M125" s="286"/>
-      <c r="N125" s="286"/>
-    </row>
-    <row r="126" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B126" s="286"/>
-      <c r="C126" s="286"/>
-      <c r="D126" s="286"/>
-      <c r="E126" s="286"/>
-      <c r="F126" s="286"/>
-      <c r="G126" s="286"/>
-      <c r="H126" s="286"/>
-      <c r="I126" s="286"/>
-      <c r="J126" s="286"/>
-      <c r="K126" s="286"/>
-      <c r="L126" s="286"/>
-      <c r="M126" s="286"/>
-      <c r="N126" s="286"/>
-    </row>
-    <row r="127" spans="1:16" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B127" s="286"/>
-      <c r="C127" s="286"/>
-      <c r="D127" s="286"/>
-      <c r="E127" s="286"/>
-      <c r="F127" s="286"/>
-      <c r="G127" s="286"/>
-      <c r="H127" s="286"/>
-      <c r="I127" s="286"/>
-      <c r="J127" s="286"/>
-      <c r="K127" s="286"/>
-      <c r="L127" s="286"/>
-      <c r="M127" s="286"/>
-      <c r="N127" s="286"/>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C122" s="283"/>
+      <c r="D122" s="283"/>
+      <c r="E122" s="283"/>
+      <c r="F122" s="283"/>
+      <c r="G122" s="283"/>
+      <c r="H122" s="283"/>
+      <c r="I122" s="283"/>
+      <c r="J122" s="283"/>
+      <c r="K122" s="283"/>
+      <c r="L122" s="283"/>
+      <c r="M122" s="283"/>
+      <c r="N122" s="283"/>
+    </row>
+    <row r="123" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B123" s="283"/>
+      <c r="C123" s="283"/>
+      <c r="D123" s="283"/>
+      <c r="E123" s="283"/>
+      <c r="F123" s="283"/>
+      <c r="G123" s="283"/>
+      <c r="H123" s="283"/>
+      <c r="I123" s="283"/>
+      <c r="J123" s="283"/>
+      <c r="K123" s="283"/>
+      <c r="L123" s="283"/>
+      <c r="M123" s="283"/>
+      <c r="N123" s="283"/>
+    </row>
+    <row r="124" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B124" s="283"/>
+      <c r="C124" s="283"/>
+      <c r="D124" s="283"/>
+      <c r="E124" s="283"/>
+      <c r="F124" s="283"/>
+      <c r="G124" s="283"/>
+      <c r="H124" s="283"/>
+      <c r="I124" s="283"/>
+      <c r="J124" s="283"/>
+      <c r="K124" s="283"/>
+      <c r="L124" s="283"/>
+      <c r="M124" s="283"/>
+      <c r="N124" s="283"/>
+    </row>
+    <row r="125" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B125" s="283"/>
+      <c r="C125" s="283"/>
+      <c r="D125" s="283"/>
+      <c r="E125" s="283"/>
+      <c r="F125" s="283"/>
+      <c r="G125" s="283"/>
+      <c r="H125" s="283"/>
+      <c r="I125" s="283"/>
+      <c r="J125" s="283"/>
+      <c r="K125" s="283"/>
+      <c r="L125" s="283"/>
+      <c r="M125" s="283"/>
+      <c r="N125" s="283"/>
+    </row>
+    <row r="126" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B126" s="283"/>
+      <c r="C126" s="283"/>
+      <c r="D126" s="283"/>
+      <c r="E126" s="283"/>
+      <c r="F126" s="283"/>
+      <c r="G126" s="283"/>
+      <c r="H126" s="283"/>
+      <c r="I126" s="283"/>
+      <c r="J126" s="283"/>
+      <c r="K126" s="283"/>
+      <c r="L126" s="283"/>
+      <c r="M126" s="283"/>
+      <c r="N126" s="283"/>
+    </row>
+    <row r="127" spans="1:16" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B127" s="283"/>
+      <c r="C127" s="283"/>
+      <c r="D127" s="283"/>
+      <c r="E127" s="283"/>
+      <c r="F127" s="283"/>
+      <c r="G127" s="283"/>
+      <c r="H127" s="283"/>
+      <c r="I127" s="283"/>
+      <c r="J127" s="283"/>
+      <c r="K127" s="283"/>
+      <c r="L127" s="283"/>
+      <c r="M127" s="283"/>
+      <c r="N127" s="283"/>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B130">
         <v>1631378.049999997</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>218</v>
-      </c>
-      <c r="B134" s="197">
+        <v>216</v>
+      </c>
+      <c r="B134" s="196">
         <v>-3942</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B135">
         <v>-132000</v>
@@ -10465,19 +10486,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56D35F41-74CB-4294-A7A2-EC3C67574818}">
-  <dimension ref="C3:N59"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="C3:N61"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C3" s="19"/>
     </row>
-    <row r="4" spans="3:14" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:14" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C4" s="164" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D4" s="165">
         <v>1</v>
@@ -10492,118 +10513,118 @@
       <c r="L4" s="19"/>
       <c r="M4" s="19"/>
     </row>
-    <row r="5" spans="3:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:14" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="166" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D5" s="167"/>
       <c r="E5" t="s">
+        <v>190</v>
+      </c>
+      <c r="G5" t="s">
         <v>191</v>
       </c>
-      <c r="G5" t="s">
-        <v>192</v>
-      </c>
       <c r="J5" s="163"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
+      <c r="K5" s="316"/>
+      <c r="L5" s="316"/>
       <c r="M5" s="19"/>
       <c r="N5" s="19"/>
     </row>
-    <row r="6" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C6" s="166" t="s">
+        <v>192</v>
+      </c>
+      <c r="D6" s="167" t="s">
         <v>193</v>
       </c>
-      <c r="D6" s="167" t="s">
+      <c r="E6" t="s">
         <v>194</v>
       </c>
-      <c r="E6" t="s">
-        <v>195</v>
-      </c>
       <c r="G6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="J6" s="163"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
+      <c r="K6" s="316"/>
+      <c r="L6" s="316"/>
       <c r="M6" s="19"/>
       <c r="N6" s="19"/>
     </row>
-    <row r="7" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C7" s="47" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J7" s="163"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
+      <c r="K7" s="316"/>
+      <c r="L7" s="316"/>
       <c r="M7" s="19"/>
       <c r="N7" s="19"/>
     </row>
-    <row r="8" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C8" s="312" t="s">
-        <v>257</v>
-      </c>
-      <c r="D8" s="313"/>
-      <c r="E8" s="313"/>
-      <c r="F8" s="313"/>
-      <c r="G8" s="313"/>
-      <c r="H8" s="313"/>
-      <c r="I8" s="313"/>
-      <c r="J8" s="314"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
+    <row r="8" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C8" s="309" t="s">
+        <v>230</v>
+      </c>
+      <c r="D8" s="310"/>
+      <c r="E8" s="310"/>
+      <c r="F8" s="310"/>
+      <c r="G8" s="310"/>
+      <c r="H8" s="310"/>
+      <c r="I8" s="310"/>
+      <c r="J8" s="311"/>
+      <c r="K8" s="316"/>
+      <c r="L8" s="316"/>
       <c r="M8" s="19"/>
       <c r="N8" s="19"/>
     </row>
-    <row r="9" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C9" s="315"/>
-      <c r="D9" s="316"/>
-      <c r="E9" s="316"/>
-      <c r="F9" s="316"/>
-      <c r="G9" s="316"/>
-      <c r="H9" s="316"/>
-      <c r="I9" s="316"/>
-      <c r="J9" s="317"/>
+    <row r="9" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="312"/>
+      <c r="D9" s="313"/>
+      <c r="E9" s="313"/>
+      <c r="F9" s="313"/>
+      <c r="G9" s="313"/>
+      <c r="H9" s="313"/>
+      <c r="I9" s="313"/>
+      <c r="J9" s="314"/>
       <c r="K9" s="19"/>
       <c r="L9" s="19"/>
       <c r="M9" s="19"/>
       <c r="N9" s="19"/>
     </row>
-    <row r="10" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C10" s="240"/>
-      <c r="D10" s="240"/>
-      <c r="E10" s="240"/>
-      <c r="F10" s="240"/>
-      <c r="G10" s="240"/>
-      <c r="H10" s="240"/>
-      <c r="I10" s="240"/>
-      <c r="J10" s="240"/>
+    <row r="10" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C10" s="226"/>
+      <c r="D10" s="226"/>
+      <c r="E10" s="226"/>
+      <c r="F10" s="226"/>
+      <c r="G10" s="226"/>
+      <c r="H10" s="226"/>
+      <c r="I10" s="226"/>
+      <c r="J10" s="226"/>
       <c r="K10" s="19"/>
       <c r="L10" s="19"/>
       <c r="M10" s="19"/>
       <c r="N10" s="19"/>
     </row>
-    <row r="11" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C11" s="240"/>
-      <c r="D11" s="240"/>
-      <c r="E11" s="240"/>
-      <c r="F11" s="240"/>
-      <c r="G11" s="240"/>
-      <c r="H11" s="240"/>
-      <c r="I11" s="240"/>
-      <c r="J11" s="240"/>
+    <row r="11" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C11" s="226"/>
+      <c r="D11" s="226"/>
+      <c r="E11" s="226"/>
+      <c r="F11" s="226"/>
+      <c r="G11" s="226"/>
+      <c r="H11" s="226"/>
+      <c r="I11" s="226"/>
+      <c r="J11" s="226"/>
       <c r="K11" s="19"/>
       <c r="L11" s="19"/>
       <c r="M11" s="19"/>
       <c r="N11" s="19"/>
     </row>
-    <row r="12" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C12" s="241" t="s">
-        <v>189</v>
-      </c>
-      <c r="D12" s="242">
+    <row r="12" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C12" s="227" t="s">
+        <v>188</v>
+      </c>
+      <c r="D12" s="228">
         <f>D4+1</f>
         <v>2</v>
       </c>
@@ -10613,92 +10634,92 @@
       <c r="H12" s="161"/>
       <c r="I12" s="161"/>
       <c r="J12" s="162"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
+      <c r="K12" s="316"/>
+      <c r="L12" s="316"/>
       <c r="M12" s="19"/>
       <c r="N12" s="19"/>
     </row>
-    <row r="13" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C13" s="243" t="s">
+    <row r="13" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C13" s="229" t="s">
+        <v>189</v>
+      </c>
+      <c r="D13" s="230"/>
+      <c r="E13" t="s">
         <v>190</v>
       </c>
-      <c r="D13" s="244"/>
-      <c r="E13" t="s">
+      <c r="G13" t="s">
         <v>191</v>
       </c>
-      <c r="G13" t="s">
-        <v>192</v>
-      </c>
       <c r="J13" s="163"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
+      <c r="K13" s="316"/>
+      <c r="L13" s="316"/>
       <c r="M13" s="19"/>
       <c r="N13" s="19"/>
     </row>
-    <row r="14" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C14" s="243" t="s">
+    <row r="14" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C14" s="229" t="s">
+        <v>192</v>
+      </c>
+      <c r="D14" s="230" t="s">
         <v>193</v>
       </c>
-      <c r="D14" s="244" t="s">
+      <c r="E14" t="s">
         <v>194</v>
       </c>
-      <c r="E14" t="s">
-        <v>195</v>
-      </c>
       <c r="G14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H14" t="s">
-        <v>263</v>
+        <v>236</v>
       </c>
       <c r="J14" s="163"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="19"/>
+      <c r="K14" s="316"/>
+      <c r="L14" s="316"/>
       <c r="M14" s="19"/>
       <c r="N14" s="19"/>
     </row>
-    <row r="15" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C15" s="47" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J15" s="163"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="19"/>
+      <c r="K15" s="316"/>
+      <c r="L15" s="316"/>
       <c r="M15" s="19"/>
       <c r="N15" s="19"/>
     </row>
-    <row r="16" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C16" s="312" t="s">
-        <v>262</v>
-      </c>
-      <c r="D16" s="313"/>
-      <c r="E16" s="313"/>
-      <c r="F16" s="313"/>
-      <c r="G16" s="313"/>
-      <c r="H16" s="313"/>
-      <c r="I16" s="313"/>
-      <c r="J16" s="314"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
+    <row r="16" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C16" s="309" t="s">
+        <v>235</v>
+      </c>
+      <c r="D16" s="310"/>
+      <c r="E16" s="310"/>
+      <c r="F16" s="310"/>
+      <c r="G16" s="310"/>
+      <c r="H16" s="310"/>
+      <c r="I16" s="310"/>
+      <c r="J16" s="311"/>
+      <c r="K16" s="316"/>
+      <c r="L16" s="316"/>
       <c r="M16" s="19"/>
       <c r="N16" s="19"/>
     </row>
-    <row r="17" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C17" s="315"/>
-      <c r="D17" s="316"/>
-      <c r="E17" s="316"/>
-      <c r="F17" s="316"/>
-      <c r="G17" s="316"/>
-      <c r="H17" s="316"/>
-      <c r="I17" s="316"/>
-      <c r="J17" s="317"/>
-    </row>
-    <row r="21" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C22" s="200" t="s">
-        <v>189</v>
-      </c>
-      <c r="D22" s="201">
+    <row r="17" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C17" s="312"/>
+      <c r="D17" s="313"/>
+      <c r="E17" s="313"/>
+      <c r="F17" s="313"/>
+      <c r="G17" s="313"/>
+      <c r="H17" s="313"/>
+      <c r="I17" s="313"/>
+      <c r="J17" s="314"/>
+    </row>
+    <row r="21" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C22" s="199" t="s">
+        <v>188</v>
+      </c>
+      <c r="D22" s="200">
         <f>D4+1</f>
         <v>2</v>
       </c>
@@ -10708,72 +10729,87 @@
       <c r="H22" s="161"/>
       <c r="I22" s="161"/>
       <c r="J22" s="162"/>
-    </row>
-    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C23" s="202" t="s">
+      <c r="K22" s="316"/>
+      <c r="L22" s="316"/>
+      <c r="M22" s="316"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C23" s="201" t="s">
+        <v>189</v>
+      </c>
+      <c r="D23" s="202"/>
+      <c r="E23" t="s">
         <v>190</v>
       </c>
-      <c r="D23" s="203"/>
-      <c r="E23" t="s">
+      <c r="G23" t="s">
         <v>191</v>
       </c>
-      <c r="G23" t="s">
+      <c r="J23" s="163"/>
+      <c r="K23" s="316"/>
+      <c r="L23" s="316"/>
+      <c r="M23" s="316"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C24" s="201" t="s">
         <v>192</v>
       </c>
-      <c r="J23" s="163"/>
-    </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C24" s="202" t="s">
+      <c r="D24" s="202" t="s">
         <v>193</v>
       </c>
-      <c r="D24" s="203" t="s">
+      <c r="E24" t="s">
         <v>194</v>
       </c>
-      <c r="E24" t="s">
+      <c r="G24" t="s">
+        <v>127</v>
+      </c>
+      <c r="J24" s="163"/>
+      <c r="K24" s="316"/>
+      <c r="L24" s="316"/>
+      <c r="M24" s="316"/>
+    </row>
+    <row r="25" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C25" s="47" t="s">
         <v>195</v>
       </c>
-      <c r="G24" t="s">
-        <v>128</v>
-      </c>
-      <c r="H24" t="s">
-        <v>221</v>
-      </c>
-      <c r="J24" s="163"/>
-    </row>
-    <row r="25" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C25" s="47" t="s">
-        <v>196</v>
-      </c>
       <c r="J25" s="163"/>
-    </row>
-    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C26" s="312" t="s">
-        <v>258</v>
-      </c>
-      <c r="D26" s="313"/>
-      <c r="E26" s="313"/>
-      <c r="F26" s="313"/>
-      <c r="G26" s="313"/>
-      <c r="H26" s="313"/>
-      <c r="I26" s="313"/>
-      <c r="J26" s="314"/>
-    </row>
-    <row r="27" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C27" s="315"/>
-      <c r="D27" s="316"/>
-      <c r="E27" s="316"/>
-      <c r="F27" s="316"/>
-      <c r="G27" s="316"/>
-      <c r="H27" s="316"/>
-      <c r="I27" s="316"/>
-      <c r="J27" s="317"/>
-    </row>
-    <row r="29" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C30" s="231" t="s">
-        <v>189</v>
-      </c>
-      <c r="D30" s="232">
+      <c r="K25" s="316"/>
+      <c r="L25" s="316"/>
+      <c r="M25" s="316"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C26" s="309" t="s">
+        <v>231</v>
+      </c>
+      <c r="D26" s="310"/>
+      <c r="E26" s="310"/>
+      <c r="F26" s="310"/>
+      <c r="G26" s="310"/>
+      <c r="H26" s="310"/>
+      <c r="I26" s="310"/>
+      <c r="J26" s="311"/>
+      <c r="K26" s="316"/>
+      <c r="L26" s="316"/>
+      <c r="M26" s="316"/>
+    </row>
+    <row r="27" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C27" s="312"/>
+      <c r="D27" s="313"/>
+      <c r="E27" s="313"/>
+      <c r="F27" s="313"/>
+      <c r="G27" s="313"/>
+      <c r="H27" s="313"/>
+      <c r="I27" s="313"/>
+      <c r="J27" s="314"/>
+      <c r="K27" s="316"/>
+      <c r="L27" s="316"/>
+      <c r="M27" s="316"/>
+    </row>
+    <row r="29" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C30" s="219" t="s">
+        <v>188</v>
+      </c>
+      <c r="D30" s="220">
         <f>D22+1</f>
         <v>3</v>
       </c>
@@ -10784,72 +10820,72 @@
       <c r="I30" s="161"/>
       <c r="J30" s="162"/>
     </row>
-    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C31" s="233" t="s">
-        <v>190</v>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C31" s="221" t="s">
+        <v>189</v>
       </c>
       <c r="D31" s="19"/>
       <c r="E31" t="s">
+        <v>190</v>
+      </c>
+      <c r="G31" t="s">
         <v>191</v>
       </c>
-      <c r="G31" t="s">
+      <c r="J31" s="163"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C32" s="221" t="s">
         <v>192</v>
       </c>
-      <c r="J31" s="163"/>
-    </row>
-    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C32" s="233" t="s">
+      <c r="D32" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="D32" s="19" t="s">
+      <c r="E32" t="s">
         <v>194</v>
       </c>
-      <c r="E32" t="s">
+      <c r="G32" t="s">
+        <v>127</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="J32" s="163"/>
+    </row>
+    <row r="33" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C33" s="221" t="s">
         <v>195</v>
-      </c>
-      <c r="G32" t="s">
-        <v>128</v>
-      </c>
-      <c r="H32">
-        <v>0</v>
-      </c>
-      <c r="J32" s="163"/>
-    </row>
-    <row r="33" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C33" s="233" t="s">
-        <v>196</v>
       </c>
       <c r="D33" s="19"/>
       <c r="J33" s="163"/>
     </row>
-    <row r="34" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C34" s="312" t="s">
-        <v>259</v>
-      </c>
-      <c r="D34" s="313"/>
-      <c r="E34" s="313"/>
-      <c r="F34" s="313"/>
-      <c r="G34" s="313"/>
-      <c r="H34" s="313"/>
-      <c r="I34" s="313"/>
-      <c r="J34" s="314"/>
-    </row>
-    <row r="35" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C35" s="315"/>
-      <c r="D35" s="316"/>
-      <c r="E35" s="316"/>
-      <c r="F35" s="316"/>
-      <c r="G35" s="316"/>
-      <c r="H35" s="316"/>
-      <c r="I35" s="316"/>
-      <c r="J35" s="317"/>
-    </row>
-    <row r="37" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="38" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C38" s="234" t="s">
-        <v>189</v>
-      </c>
-      <c r="D38" s="235">
+    <row r="34" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C34" s="309" t="s">
+        <v>232</v>
+      </c>
+      <c r="D34" s="310"/>
+      <c r="E34" s="310"/>
+      <c r="F34" s="310"/>
+      <c r="G34" s="310"/>
+      <c r="H34" s="310"/>
+      <c r="I34" s="310"/>
+      <c r="J34" s="311"/>
+    </row>
+    <row r="35" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C35" s="312"/>
+      <c r="D35" s="313"/>
+      <c r="E35" s="313"/>
+      <c r="F35" s="313"/>
+      <c r="G35" s="313"/>
+      <c r="H35" s="313"/>
+      <c r="I35" s="313"/>
+      <c r="J35" s="314"/>
+    </row>
+    <row r="37" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="38" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C38" s="222" t="s">
+        <v>188</v>
+      </c>
+      <c r="D38" s="223">
         <f>D30+1</f>
         <v>4</v>
       </c>
@@ -10860,72 +10896,87 @@
       <c r="I38" s="161"/>
       <c r="J38" s="162"/>
     </row>
-    <row r="39" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C39" s="236" t="s">
+    <row r="39" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C39" s="224" t="s">
+        <v>189</v>
+      </c>
+      <c r="D39" s="225"/>
+      <c r="E39" t="s">
         <v>190</v>
       </c>
-      <c r="D39" s="237"/>
-      <c r="E39" t="s">
+      <c r="G39" t="s">
         <v>191</v>
       </c>
-      <c r="G39" t="s">
+      <c r="J39" s="163"/>
+      <c r="K39" s="316"/>
+      <c r="L39" s="316"/>
+      <c r="M39" s="316"/>
+    </row>
+    <row r="40" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C40" s="224" t="s">
         <v>192</v>
       </c>
-      <c r="J39" s="163"/>
-    </row>
-    <row r="40" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C40" s="236" t="s">
+      <c r="D40" s="225" t="s">
         <v>193</v>
       </c>
-      <c r="D40" s="237" t="s">
+      <c r="E40" t="s">
         <v>194</v>
       </c>
-      <c r="E40" t="s">
+      <c r="G40" t="s">
+        <v>127</v>
+      </c>
+      <c r="H40" t="s">
+        <v>233</v>
+      </c>
+      <c r="J40" s="163"/>
+      <c r="K40" s="316"/>
+      <c r="L40" s="316"/>
+      <c r="M40" s="316"/>
+    </row>
+    <row r="41" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C41" s="221" t="s">
         <v>195</v>
-      </c>
-      <c r="G40" t="s">
-        <v>128</v>
-      </c>
-      <c r="H40" t="s">
-        <v>260</v>
-      </c>
-      <c r="J40" s="163"/>
-    </row>
-    <row r="41" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C41" s="233" t="s">
-        <v>196</v>
       </c>
       <c r="D41" s="19"/>
       <c r="J41" s="163"/>
-    </row>
-    <row r="42" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C42" s="312" t="s">
-        <v>261</v>
-      </c>
-      <c r="D42" s="313"/>
-      <c r="E42" s="313"/>
-      <c r="F42" s="313"/>
-      <c r="G42" s="313"/>
-      <c r="H42" s="313"/>
-      <c r="I42" s="313"/>
-      <c r="J42" s="314"/>
-    </row>
-    <row r="43" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C43" s="315"/>
-      <c r="D43" s="316"/>
-      <c r="E43" s="316"/>
-      <c r="F43" s="316"/>
-      <c r="G43" s="316"/>
-      <c r="H43" s="316"/>
-      <c r="I43" s="316"/>
-      <c r="J43" s="317"/>
-    </row>
-    <row r="45" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="46" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C46" s="249" t="s">
-        <v>189</v>
-      </c>
-      <c r="D46" s="250">
+      <c r="K41" s="316"/>
+      <c r="L41" s="316"/>
+      <c r="M41" s="316"/>
+    </row>
+    <row r="42" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C42" s="309" t="s">
+        <v>234</v>
+      </c>
+      <c r="D42" s="310"/>
+      <c r="E42" s="310"/>
+      <c r="F42" s="310"/>
+      <c r="G42" s="310"/>
+      <c r="H42" s="310"/>
+      <c r="I42" s="310"/>
+      <c r="J42" s="311"/>
+      <c r="K42" s="316"/>
+      <c r="L42" s="316"/>
+      <c r="M42" s="316"/>
+    </row>
+    <row r="43" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C43" s="312"/>
+      <c r="D43" s="313"/>
+      <c r="E43" s="313"/>
+      <c r="F43" s="313"/>
+      <c r="G43" s="313"/>
+      <c r="H43" s="313"/>
+      <c r="I43" s="313"/>
+      <c r="J43" s="314"/>
+      <c r="K43" s="316"/>
+      <c r="L43" s="316"/>
+      <c r="M43" s="316"/>
+    </row>
+    <row r="45" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="46" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C46" s="231" t="s">
+        <v>188</v>
+      </c>
+      <c r="D46" s="232">
         <f>D38+1</f>
         <v>5</v>
       </c>
@@ -10935,73 +10986,91 @@
       <c r="H46" s="161"/>
       <c r="I46" s="161"/>
       <c r="J46" s="162"/>
-    </row>
-    <row r="47" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C47" s="251" t="s">
+      <c r="K46" s="316"/>
+      <c r="L46" s="316"/>
+      <c r="M46" s="316"/>
+    </row>
+    <row r="47" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C47" s="233" t="s">
+        <v>189</v>
+      </c>
+      <c r="D47" s="234"/>
+      <c r="E47" t="s">
         <v>190</v>
       </c>
-      <c r="D47" s="252"/>
-      <c r="E47" t="s">
+      <c r="G47" t="s">
         <v>191</v>
       </c>
-      <c r="G47" t="s">
+      <c r="J47" s="163"/>
+      <c r="K47" s="316"/>
+      <c r="L47" s="316"/>
+      <c r="M47" s="316"/>
+    </row>
+    <row r="48" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C48" s="233" t="s">
         <v>192</v>
       </c>
-      <c r="J47" s="163"/>
-    </row>
-    <row r="48" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C48" s="251" t="s">
+      <c r="D48" s="234" t="s">
         <v>193</v>
       </c>
-      <c r="D48" s="252" t="s">
+      <c r="E48" t="s">
         <v>194</v>
       </c>
-      <c r="E48" t="s">
+      <c r="G48" t="s">
+        <v>127</v>
+      </c>
+      <c r="H48" t="s">
+        <v>237</v>
+      </c>
+      <c r="J48" s="163"/>
+      <c r="K48" s="316"/>
+      <c r="L48" s="316"/>
+      <c r="M48" s="316"/>
+    </row>
+    <row r="49" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C49" s="233" t="s">
         <v>195</v>
       </c>
-      <c r="G48" t="s">
-        <v>128</v>
-      </c>
-      <c r="H48" t="s">
-        <v>264</v>
-      </c>
-      <c r="J48" s="163"/>
-    </row>
-    <row r="49" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C49" s="251" t="s">
-        <v>196</v>
-      </c>
-      <c r="D49" s="252"/>
+      <c r="D49" s="234"/>
       <c r="J49" s="163"/>
-    </row>
-    <row r="50" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C50" s="312" t="s">
-        <v>265</v>
-      </c>
-      <c r="D50" s="313"/>
-      <c r="E50" s="313"/>
-      <c r="F50" s="313"/>
-      <c r="G50" s="313"/>
-      <c r="H50" s="313"/>
-      <c r="I50" s="313"/>
-      <c r="J50" s="314"/>
-    </row>
-    <row r="51" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C51" s="315"/>
-      <c r="D51" s="316"/>
-      <c r="E51" s="316"/>
-      <c r="F51" s="316"/>
-      <c r="G51" s="316"/>
-      <c r="H51" s="316"/>
-      <c r="I51" s="316"/>
-      <c r="J51" s="317"/>
-    </row>
-    <row r="53" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="54" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C54" s="324" t="s">
-        <v>189</v>
-      </c>
-      <c r="D54" s="325">
+      <c r="K49" s="316"/>
+      <c r="L49" s="316"/>
+      <c r="M49" s="316"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C50" s="309" t="s">
+        <v>238</v>
+      </c>
+      <c r="D50" s="310"/>
+      <c r="E50" s="310"/>
+      <c r="F50" s="310"/>
+      <c r="G50" s="310"/>
+      <c r="H50" s="310"/>
+      <c r="I50" s="310"/>
+      <c r="J50" s="311"/>
+      <c r="K50" s="316"/>
+      <c r="L50" s="316"/>
+      <c r="M50" s="316"/>
+    </row>
+    <row r="51" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C51" s="312"/>
+      <c r="D51" s="313"/>
+      <c r="E51" s="313"/>
+      <c r="F51" s="313"/>
+      <c r="G51" s="313"/>
+      <c r="H51" s="313"/>
+      <c r="I51" s="313"/>
+      <c r="J51" s="314"/>
+      <c r="K51" s="316"/>
+      <c r="L51" s="316"/>
+      <c r="M51" s="316"/>
+    </row>
+    <row r="53" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C54" s="237" t="s">
+        <v>188</v>
+      </c>
+      <c r="D54" s="238">
         <f>D46+1</f>
         <v>6</v>
       </c>
@@ -11011,66 +11080,102 @@
       <c r="H54" s="161"/>
       <c r="I54" s="161"/>
       <c r="J54" s="162"/>
-    </row>
-    <row r="55" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C55" s="326" t="s">
+      <c r="K54" s="316"/>
+      <c r="L54" s="316"/>
+      <c r="M54" s="316"/>
+      <c r="N54" s="316"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C55" s="239" t="s">
+        <v>189</v>
+      </c>
+      <c r="D55" s="240"/>
+      <c r="E55" t="s">
         <v>190</v>
       </c>
-      <c r="D55" s="327"/>
-      <c r="E55" t="s">
+      <c r="G55" t="s">
         <v>191</v>
       </c>
-      <c r="G55" t="s">
+      <c r="J55" s="163"/>
+      <c r="K55" s="316"/>
+      <c r="L55" s="316"/>
+      <c r="M55" s="316"/>
+      <c r="N55" s="316"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C56" s="239" t="s">
         <v>192</v>
       </c>
-      <c r="J55" s="163"/>
-    </row>
-    <row r="56" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C56" s="326" t="s">
+      <c r="D56" s="240" t="s">
         <v>193</v>
       </c>
-      <c r="D56" s="327" t="s">
+      <c r="E56" t="s">
         <v>194</v>
       </c>
-      <c r="E56" t="s">
+      <c r="G56" t="s">
+        <v>127</v>
+      </c>
+      <c r="H56" t="s">
+        <v>252</v>
+      </c>
+      <c r="J56" s="163"/>
+      <c r="K56" s="316"/>
+      <c r="L56" s="316"/>
+      <c r="M56" s="316"/>
+      <c r="N56" s="316"/>
+    </row>
+    <row r="57" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C57" s="239" t="s">
         <v>195</v>
       </c>
-      <c r="G56" t="s">
-        <v>128</v>
-      </c>
-      <c r="H56" t="s">
-        <v>282</v>
-      </c>
-      <c r="J56" s="163"/>
-    </row>
-    <row r="57" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C57" s="326" t="s">
-        <v>196</v>
-      </c>
-      <c r="D57" s="327"/>
+      <c r="D57" s="240"/>
       <c r="J57" s="163"/>
-    </row>
-    <row r="58" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C58" s="312" t="s">
-        <v>281</v>
-      </c>
-      <c r="D58" s="313"/>
-      <c r="E58" s="313"/>
-      <c r="F58" s="313"/>
-      <c r="G58" s="313"/>
-      <c r="H58" s="313"/>
-      <c r="I58" s="313"/>
-      <c r="J58" s="314"/>
-    </row>
-    <row r="59" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C59" s="315"/>
-      <c r="D59" s="316"/>
-      <c r="E59" s="316"/>
-      <c r="F59" s="316"/>
-      <c r="G59" s="316"/>
-      <c r="H59" s="316"/>
-      <c r="I59" s="316"/>
-      <c r="J59" s="317"/>
+      <c r="K57" s="316"/>
+      <c r="L57" s="316"/>
+      <c r="M57" s="316"/>
+      <c r="N57" s="316"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C58" s="309" t="s">
+        <v>251</v>
+      </c>
+      <c r="D58" s="310"/>
+      <c r="E58" s="310"/>
+      <c r="F58" s="310"/>
+      <c r="G58" s="310"/>
+      <c r="H58" s="310"/>
+      <c r="I58" s="310"/>
+      <c r="J58" s="311"/>
+      <c r="K58" s="316"/>
+      <c r="L58" s="316"/>
+      <c r="M58" s="316"/>
+      <c r="N58" s="316"/>
+    </row>
+    <row r="59" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C59" s="312"/>
+      <c r="D59" s="313"/>
+      <c r="E59" s="313"/>
+      <c r="F59" s="313"/>
+      <c r="G59" s="313"/>
+      <c r="H59" s="313"/>
+      <c r="I59" s="313"/>
+      <c r="J59" s="314"/>
+      <c r="K59" s="316"/>
+      <c r="L59" s="316"/>
+      <c r="M59" s="316"/>
+      <c r="N59" s="316"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="K60" s="316"/>
+      <c r="L60" s="316"/>
+      <c r="M60" s="316"/>
+      <c r="N60" s="316"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="K61" s="316"/>
+      <c r="L61" s="316"/>
+      <c r="M61" s="316"/>
+      <c r="N61" s="316"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/2026/ITALIA/Septiembre/Septiembre ITALIA.xlsx
+++ b/2026/ITALIA/Septiembre/Septiembre ITALIA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\ITALIA\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{561B60AD-3A1F-4CA4-B553-40D5EB757F8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4F1488B-2BF0-4369-90E0-A3C5C5A195D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$O$127</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$168</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$174</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="293">
   <si>
     <t>TOTAL</t>
   </si>
@@ -718,16 +718,7 @@
     <t>ARCA - Plan de pago - Cuota 47/60</t>
   </si>
   <si>
-    <t>Ramon Troncoso -  En septiembre debe pagar la 1er cuota de 6 - Consta de 6 cuotas mensuales de $190.000 + expensas en curso</t>
-  </si>
-  <si>
-    <t>Ingreso 25/08</t>
-  </si>
-  <si>
     <t>Intereses</t>
-  </si>
-  <si>
-    <t>SALDO FINAL AL 31/08</t>
   </si>
   <si>
     <t>FCI - SALDO INICIAL</t>
@@ -943,6 +934,33 @@
     <t>Se crea una caja destinada exclusivamente a la gestión de los fondos correspondientes al arreglo del techado de las cocheras.
 La misma contará mensualmente con el ingreso proveniente del alquiler o comodato de la portería. La caja se inicia con dicho ingreso, abonado en efectivo, quedando los fondos afectados exclusivamente a los gastos relacionados con la reparación y mantenimiento del techado de las cocheras.</t>
   </si>
+  <si>
+    <t>Cristian Marcelo Del Pezzo - CUIL 20-24184416-2</t>
+  </si>
+  <si>
+    <t>Cuello Natalia - Desobstruccion columna baño y de inodoro inodoro UF 4G</t>
+  </si>
+  <si>
+    <t>4G : Desobstruccion columna baño y de inodoro inodoro UF 4G</t>
+  </si>
+  <si>
+    <t>Destapaciones Roman -Destapación de cloaca desde cámara hacia la salida, y destapación de rejilla del baño de PB, correspondiente a la cámara cloacal. Servicio solicitado de urgencia el día domingo.</t>
+  </si>
+  <si>
+    <t>Transf 29/09</t>
+  </si>
+  <si>
+    <t>Ramon Troncoso -  En septiembre paga la 1er cuota de 6 - Consta de 6 cuotas mensuales de $190.000 + expensas en curso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARCA VEP </t>
+  </si>
+  <si>
+    <t>Transf 16/09</t>
+  </si>
+  <si>
+    <t>SALDO FINAL</t>
+  </si>
 </sst>
 </file>
 
@@ -958,7 +976,7 @@
     <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1143,8 +1161,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="22">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1265,12 +1290,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="43">
     <border>
@@ -1816,7 +1835,7 @@
     <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="320">
+  <cellXfs count="314">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2143,9 +2162,6 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="10" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2175,26 +2191,24 @@
     <xf numFmtId="0" fontId="0" fillId="19" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="44" fontId="7" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="7" fillId="21" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="21" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="21" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="8" fontId="7" fillId="21" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="8" fontId="7" fillId="21" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="21" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="21" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="10" fillId="4" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="44" fontId="10" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2207,50 +2221,125 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2258,12 +2347,6 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2294,84 +2377,6 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2390,14 +2395,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="22" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="22" fillId="13" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="22" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="12" fillId="7" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="25" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="17" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="44" fontId="10" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="8" fontId="10" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="8" fontId="10" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2804,7 +2815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E413A25D-5161-4141-BE0B-6E37A2A76CA5}">
-  <dimension ref="A1:M169"/>
+  <dimension ref="A1:M175"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.5703125" customWidth="1"/>
@@ -2812,8 +2823,7 @@
     <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="21.7109375" customWidth="1"/>
     <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.28515625" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
@@ -2822,12 +2832,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="256" t="s">
+      <c r="B1" s="250" t="s">
         <v>145</v>
       </c>
-      <c r="C1" s="256"/>
-      <c r="D1" s="256"/>
-      <c r="E1" s="257"/>
+      <c r="C1" s="250"/>
+      <c r="D1" s="250"/>
+      <c r="E1" s="251"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
@@ -2840,12 +2850,12 @@
     </row>
     <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
-      <c r="B3" s="260" t="s">
+      <c r="B3" s="254" t="s">
         <v>186</v>
       </c>
-      <c r="C3" s="260"/>
-      <c r="D3" s="260"/>
-      <c r="E3" s="261"/>
+      <c r="C3" s="254"/>
+      <c r="D3" s="254"/>
+      <c r="E3" s="255"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
@@ -2863,7 +2873,7 @@
         <v>146</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="3" t="s">
@@ -2884,24 +2894,24 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="48"/>
-      <c r="B8" s="262" t="s">
-        <v>239</v>
-      </c>
-      <c r="C8" s="262"/>
+      <c r="B8" s="256" t="s">
+        <v>236</v>
+      </c>
+      <c r="C8" s="256"/>
       <c r="D8" s="48"/>
       <c r="E8" s="48"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="48"/>
-      <c r="B9" s="262"/>
-      <c r="C9" s="262"/>
+      <c r="B9" s="256"/>
+      <c r="C9" s="256"/>
       <c r="D9" s="48"/>
       <c r="E9" s="48"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="48"/>
-      <c r="B10" s="262"/>
-      <c r="C10" s="262"/>
+      <c r="B10" s="256"/>
+      <c r="C10" s="256"/>
       <c r="D10" s="48"/>
       <c r="E10" s="48"/>
     </row>
@@ -2920,34 +2930,34 @@
       <c r="E12" s="48"/>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="263" t="s">
+      <c r="A13" s="257" t="s">
         <v>103</v>
       </c>
-      <c r="B13" s="263"/>
-      <c r="C13" s="263"/>
-      <c r="D13" s="263"/>
-      <c r="E13" s="263"/>
+      <c r="B13" s="257"/>
+      <c r="C13" s="257"/>
+      <c r="D13" s="257"/>
+      <c r="E13" s="257"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="263"/>
-      <c r="B14" s="263"/>
-      <c r="C14" s="263"/>
-      <c r="D14" s="263"/>
-      <c r="E14" s="263"/>
+      <c r="A14" s="257"/>
+      <c r="B14" s="257"/>
+      <c r="C14" s="257"/>
+      <c r="D14" s="257"/>
+      <c r="E14" s="257"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="263"/>
-      <c r="B15" s="263"/>
-      <c r="C15" s="263"/>
-      <c r="D15" s="263"/>
-      <c r="E15" s="263"/>
+      <c r="A15" s="257"/>
+      <c r="B15" s="257"/>
+      <c r="C15" s="257"/>
+      <c r="D15" s="257"/>
+      <c r="E15" s="257"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="263"/>
-      <c r="B16" s="263"/>
-      <c r="C16" s="263"/>
-      <c r="D16" s="263"/>
-      <c r="E16" s="263"/>
+      <c r="A16" s="257"/>
+      <c r="B16" s="257"/>
+      <c r="C16" s="257"/>
+      <c r="D16" s="257"/>
+      <c r="E16" s="257"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="48"/>
@@ -2989,34 +2999,34 @@
       <c r="E21" s="145"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="258" t="s">
+      <c r="A22" s="252" t="s">
         <v>160</v>
       </c>
-      <c r="B22" s="259"/>
+      <c r="B22" s="253"/>
       <c r="C22" s="172"/>
       <c r="D22" s="173">
-        <v>2415207.52</v>
+        <v>2427661.11</v>
       </c>
       <c r="E22" s="146"/>
       <c r="H22" s="19"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="258" t="s">
+      <c r="A23" s="252" t="s">
         <v>161</v>
       </c>
-      <c r="B23" s="259"/>
+      <c r="B23" s="253"/>
       <c r="C23" s="172"/>
       <c r="D23" s="173">
-        <v>-525307.52</v>
+        <v>-528016.11</v>
       </c>
       <c r="E23" s="20"/>
       <c r="H23" s="19"/>
     </row>
     <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="258" t="s">
+      <c r="A24" s="252" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="259"/>
+      <c r="B24" s="253"/>
       <c r="C24" s="172"/>
       <c r="D24" s="174">
         <v>0</v>
@@ -3025,1356 +3035,1457 @@
       <c r="F24" s="197"/>
       <c r="H24" s="19"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="175" t="s">
+    <row r="25" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="36" t="s">
+        <v>284</v>
+      </c>
+      <c r="B25" s="36"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="112">
+        <f>SUM(D22:D24)</f>
+        <v>1899645</v>
+      </c>
+      <c r="E25" s="145"/>
+      <c r="F25" s="197"/>
+      <c r="H25" s="19"/>
+    </row>
+    <row r="26" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="252" t="s">
+        <v>160</v>
+      </c>
+      <c r="B26" s="253"/>
+      <c r="C26" s="172"/>
+      <c r="D26" s="174">
+        <v>1136835.6499999999</v>
+      </c>
+      <c r="E26" s="20"/>
+      <c r="F26" s="197"/>
+      <c r="H26" s="19"/>
+    </row>
+    <row r="27" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="252" t="s">
+        <v>161</v>
+      </c>
+      <c r="B27" s="253"/>
+      <c r="C27" s="172"/>
+      <c r="D27" s="174">
+        <v>-281366.65000000002</v>
+      </c>
+      <c r="E27" s="20"/>
+      <c r="F27" s="197"/>
+      <c r="H27" s="19"/>
+    </row>
+    <row r="28" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="252" t="s">
+        <v>1</v>
+      </c>
+      <c r="B28" s="253"/>
+      <c r="C28" s="172"/>
+      <c r="D28" s="174">
+        <v>0</v>
+      </c>
+      <c r="E28" s="20"/>
+      <c r="F28" s="197"/>
+      <c r="H28" s="19"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="175" t="s">
         <v>105</v>
       </c>
-      <c r="B25" s="175"/>
-      <c r="C25" s="175"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="147">
-        <f>SUM(D22:D24)</f>
-        <v>1889900</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="175" t="s">
+      <c r="B29" s="175"/>
+      <c r="C29" s="175"/>
+      <c r="D29" s="307">
+        <f>SUM(D26:D28)</f>
+        <v>855468.99999999988</v>
+      </c>
+      <c r="E29" s="147">
+        <f>D25+D29</f>
+        <v>2755114</v>
+      </c>
+      <c r="G29" s="75"/>
+    </row>
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="175" t="s">
         <v>175</v>
       </c>
-      <c r="B26" s="175"/>
-      <c r="C26" s="175"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="148"/>
-    </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="172"/>
-      <c r="B27" s="172"/>
-      <c r="C27" s="172"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="160"/>
-    </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="172"/>
-      <c r="B28" s="172"/>
-      <c r="C28" s="172"/>
-      <c r="D28" s="35"/>
-      <c r="E28" s="160"/>
-    </row>
-    <row r="29" spans="1:8" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="172"/>
-      <c r="B29" s="172"/>
-      <c r="C29" s="172"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="160"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="247" t="s">
-        <v>262</v>
-      </c>
-      <c r="B30" s="172"/>
-      <c r="C30" s="172"/>
-      <c r="D30" s="242">
-        <v>237600</v>
-      </c>
-      <c r="E30" s="149" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="172" t="s">
-        <v>263</v>
-      </c>
+      <c r="B30" s="175"/>
+      <c r="C30" s="175"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="148"/>
+    </row>
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="172"/>
       <c r="B31" s="172"/>
       <c r="C31" s="172"/>
-      <c r="D31" s="242">
-        <v>13000</v>
-      </c>
-      <c r="E31" s="149" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D31" s="35"/>
+      <c r="E31" s="160"/>
+    </row>
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="172"/>
       <c r="B32" s="172"/>
       <c r="C32" s="172"/>
       <c r="D32" s="35"/>
-      <c r="E32" s="149"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="175" t="s">
-        <v>105</v>
-      </c>
-      <c r="B33" s="176"/>
-      <c r="C33" s="176"/>
-      <c r="D33" s="102"/>
-      <c r="E33" s="150">
-        <f>SUM(D29:D32)</f>
-        <v>250600</v>
-      </c>
+      <c r="E32" s="160"/>
+    </row>
+    <row r="33" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="172"/>
+      <c r="B33" s="172"/>
+      <c r="C33" s="172"/>
+      <c r="D33" s="35"/>
+      <c r="E33" s="160"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="36" t="s">
-        <v>138</v>
-      </c>
-      <c r="B34" s="175"/>
-      <c r="C34" s="175"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="148"/>
+      <c r="A34" s="239" t="s">
+        <v>259</v>
+      </c>
+      <c r="B34" s="172"/>
+      <c r="C34" s="172"/>
+      <c r="D34" s="35">
+        <v>237600</v>
+      </c>
+      <c r="E34" s="149" t="s">
+        <v>261</v>
+      </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="172" t="s">
-        <v>224</v>
-      </c>
-      <c r="B35" s="177"/>
-      <c r="C35" s="177"/>
-      <c r="D35" s="249">
-        <v>11886</v>
-      </c>
-      <c r="E35" s="149"/>
-      <c r="G35" s="66"/>
+        <v>260</v>
+      </c>
+      <c r="B35" s="172"/>
+      <c r="C35" s="172"/>
+      <c r="D35" s="35">
+        <v>13000</v>
+      </c>
+      <c r="E35" s="149" t="s">
+        <v>262</v>
+      </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="172" t="s">
-        <v>256</v>
-      </c>
-      <c r="B36" s="177"/>
-      <c r="C36" s="177"/>
-      <c r="D36" s="242">
-        <v>1061960.04</v>
-      </c>
-      <c r="E36" s="149" t="s">
-        <v>248</v>
-      </c>
-      <c r="G36" s="66"/>
+      <c r="A36" s="172"/>
+      <c r="B36" s="172"/>
+      <c r="C36" s="172"/>
+      <c r="D36" s="35"/>
+      <c r="E36" s="149"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="172"/>
-      <c r="B37" s="177"/>
-      <c r="C37" s="177"/>
-      <c r="D37" s="235">
-        <v>392020.44</v>
-      </c>
-      <c r="E37" s="149"/>
-      <c r="F37" s="235"/>
-      <c r="G37" s="66"/>
+      <c r="A37" s="175" t="s">
+        <v>105</v>
+      </c>
+      <c r="B37" s="176"/>
+      <c r="C37" s="176"/>
+      <c r="D37" s="102"/>
+      <c r="E37" s="150">
+        <f>SUM(D33:D36)</f>
+        <v>250600</v>
+      </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="172" t="s">
-        <v>257</v>
-      </c>
-      <c r="B38" s="177"/>
-      <c r="C38" s="177"/>
-      <c r="D38" s="242">
-        <v>506489.49</v>
-      </c>
-      <c r="E38" s="149"/>
-      <c r="G38" s="66"/>
+      <c r="A38" s="36" t="s">
+        <v>138</v>
+      </c>
+      <c r="B38" s="175"/>
+      <c r="C38" s="175"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="148"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="172" t="s">
-        <v>258</v>
+        <v>224</v>
       </c>
       <c r="B39" s="177"/>
       <c r="C39" s="177"/>
-      <c r="D39" s="242">
-        <v>115902.14</v>
-      </c>
-      <c r="E39" s="149"/>
+      <c r="D39" s="35">
+        <v>11886</v>
+      </c>
+      <c r="E39" s="149" t="s">
+        <v>291</v>
+      </c>
       <c r="G39" s="66"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="172" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B40" s="177"/>
       <c r="C40" s="177"/>
-      <c r="D40" s="242">
-        <v>61640.3</v>
-      </c>
-      <c r="E40" s="149"/>
+      <c r="D40" s="35">
+        <v>1061960.04</v>
+      </c>
+      <c r="E40" s="149" t="s">
+        <v>245</v>
+      </c>
       <c r="G40" s="66"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="172" t="s">
-        <v>140</v>
+        <v>290</v>
       </c>
       <c r="B41" s="177"/>
       <c r="C41" s="177"/>
-      <c r="D41" s="242">
-        <v>207318.45</v>
-      </c>
-      <c r="E41" s="149" t="s">
-        <v>261</v>
-      </c>
+      <c r="D41" s="35">
+        <v>392020.44</v>
+      </c>
+      <c r="E41" s="149"/>
+      <c r="F41" s="234"/>
       <c r="G41" s="66"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="172" t="s">
-        <v>142</v>
+        <v>254</v>
       </c>
       <c r="B42" s="177"/>
       <c r="C42" s="177"/>
-      <c r="D42" s="242">
-        <v>108684.32</v>
-      </c>
-      <c r="E42" s="149" t="str">
-        <f>E41</f>
-        <v>Debito 14/09</v>
-      </c>
-      <c r="G42" s="50"/>
+      <c r="D42" s="35">
+        <v>506489.49</v>
+      </c>
+      <c r="E42" s="149"/>
+      <c r="G42" s="66"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="172" t="s">
-        <v>141</v>
+        <v>255</v>
       </c>
       <c r="B43" s="177"/>
       <c r="C43" s="177"/>
-      <c r="D43" s="242">
-        <v>12076.04</v>
-      </c>
-      <c r="E43" s="149" t="str">
-        <f>E41</f>
-        <v>Debito 14/09</v>
-      </c>
+      <c r="D43" s="35">
+        <v>115902.14</v>
+      </c>
+      <c r="E43" s="149"/>
+      <c r="G43" s="66"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="172" t="s">
-        <v>148</v>
+        <v>255</v>
       </c>
       <c r="B44" s="177"/>
       <c r="C44" s="177"/>
-      <c r="D44" s="35"/>
+      <c r="D44" s="35">
+        <v>61640.3</v>
+      </c>
       <c r="E44" s="149"/>
-    </row>
-    <row r="45" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="175" t="s">
+      <c r="G44" s="66"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="172" t="s">
+        <v>140</v>
+      </c>
+      <c r="B45" s="177"/>
+      <c r="C45" s="177"/>
+      <c r="D45" s="35">
+        <v>207318.45</v>
+      </c>
+      <c r="E45" s="149" t="s">
+        <v>258</v>
+      </c>
+      <c r="G45" s="66"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="172" t="s">
+        <v>142</v>
+      </c>
+      <c r="B46" s="177"/>
+      <c r="C46" s="177"/>
+      <c r="D46" s="35">
+        <v>108684.32</v>
+      </c>
+      <c r="E46" s="149" t="str">
+        <f>E45</f>
+        <v>Debito 14/09</v>
+      </c>
+      <c r="G46" s="50"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="172" t="s">
+        <v>141</v>
+      </c>
+      <c r="B47" s="177"/>
+      <c r="C47" s="177"/>
+      <c r="D47" s="35">
+        <v>12076.04</v>
+      </c>
+      <c r="E47" s="149" t="str">
+        <f>E45</f>
+        <v>Debito 14/09</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="172" t="s">
+        <v>148</v>
+      </c>
+      <c r="B48" s="177"/>
+      <c r="C48" s="177"/>
+      <c r="D48" s="35"/>
+      <c r="E48" s="149"/>
+    </row>
+    <row r="49" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="175" t="s">
         <v>139</v>
       </c>
-      <c r="B45" s="175"/>
-      <c r="C45" s="175"/>
-      <c r="D45" s="22"/>
-      <c r="E45" s="41">
-        <f>SUM(D35:D44)</f>
+      <c r="B49" s="175"/>
+      <c r="C49" s="175"/>
+      <c r="D49" s="22"/>
+      <c r="E49" s="41">
+        <f>SUM(D39:D48)</f>
         <v>2477977.2199999997</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="14" t="s">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="14" t="s">
         <v>106</v>
-      </c>
-      <c r="B46" s="21"/>
-      <c r="C46" s="21"/>
-      <c r="D46" s="23"/>
-      <c r="E46" s="150"/>
-    </row>
-    <row r="47" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="250" t="s">
-        <v>182</v>
-      </c>
-      <c r="B47" s="251"/>
-      <c r="C47" s="26"/>
-      <c r="D47" s="246">
-        <v>7805</v>
-      </c>
-      <c r="E47" s="20" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="250" t="s">
-        <v>268</v>
-      </c>
-      <c r="B48" s="251"/>
-      <c r="C48" s="26"/>
-      <c r="D48" s="246">
-        <v>7129</v>
-      </c>
-      <c r="E48" s="20" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="250" t="s">
-        <v>184</v>
-      </c>
-      <c r="B49" s="251"/>
-      <c r="C49" s="26"/>
-      <c r="D49" s="246">
-        <v>213891</v>
-      </c>
-      <c r="E49" s="20" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="21" t="s">
-        <v>107</v>
       </c>
       <c r="B50" s="21"/>
       <c r="C50" s="21"/>
-      <c r="D50" s="22"/>
-      <c r="E50" s="41">
-        <f>SUM(D47:D49)</f>
+      <c r="D50" s="23"/>
+      <c r="E50" s="150"/>
+    </row>
+    <row r="51" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="245" t="s">
+        <v>182</v>
+      </c>
+      <c r="B51" s="246"/>
+      <c r="C51" s="26"/>
+      <c r="D51" s="310">
+        <v>7805</v>
+      </c>
+      <c r="E51" s="20" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="245" t="s">
+        <v>265</v>
+      </c>
+      <c r="B52" s="246"/>
+      <c r="C52" s="26"/>
+      <c r="D52" s="310">
+        <v>7129</v>
+      </c>
+      <c r="E52" s="20" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="245" t="s">
+        <v>184</v>
+      </c>
+      <c r="B53" s="246"/>
+      <c r="C53" s="26"/>
+      <c r="D53" s="310">
+        <v>213891</v>
+      </c>
+      <c r="E53" s="20" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="B54" s="21"/>
+      <c r="C54" s="21"/>
+      <c r="D54" s="22"/>
+      <c r="E54" s="41">
+        <f>SUM(D51:D53)</f>
         <v>228825</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="14" t="s">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="B51" s="27"/>
-      <c r="C51" s="27"/>
-      <c r="D51" s="28"/>
-      <c r="E51" s="151"/>
-    </row>
-    <row r="52" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="29" t="s">
+      <c r="B55" s="27"/>
+      <c r="C55" s="27"/>
+      <c r="D55" s="28"/>
+      <c r="E55" s="151"/>
+    </row>
+    <row r="56" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="B52" s="29" t="s">
+      <c r="B56" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="C52" s="29"/>
-      <c r="D52" s="241">
+      <c r="C56" s="29"/>
+      <c r="D56" s="30">
         <v>635896.65</v>
       </c>
-      <c r="E52" s="113" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="29" t="s">
+      <c r="E56" s="113" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="B53" s="29" t="s">
+      <c r="B57" s="29" t="s">
         <v>169</v>
       </c>
-      <c r="C53" s="29"/>
-      <c r="D53" s="241">
+      <c r="C57" s="29"/>
+      <c r="D57" s="30">
         <v>35000.639999999999</v>
       </c>
-      <c r="E53" s="113" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="29" t="s">
+      <c r="E57" s="113" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="29" t="s">
         <v>176</v>
       </c>
-      <c r="B54" s="29" t="s">
+      <c r="B58" s="29" t="s">
         <v>168</v>
       </c>
-      <c r="C54" s="29"/>
-      <c r="D54" s="30">
-        <v>0</v>
-      </c>
-      <c r="E54" s="20"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="29" t="s">
+      <c r="C58" s="29"/>
+      <c r="D58" s="30">
+        <v>0</v>
+      </c>
+      <c r="E58" s="20"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="29" t="s">
         <v>177</v>
       </c>
-      <c r="B55" s="31"/>
-      <c r="C55" s="29"/>
-      <c r="D55" s="30">
-        <v>0</v>
-      </c>
-      <c r="E55" s="20"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="252" t="s">
-        <v>285</v>
-      </c>
-      <c r="B56" s="253"/>
-      <c r="C56" s="29"/>
-      <c r="D56" s="241">
+      <c r="B59" s="31"/>
+      <c r="C59" s="29"/>
+      <c r="D59" s="30">
+        <v>0</v>
+      </c>
+      <c r="E59" s="20"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="247" t="s">
+        <v>282</v>
+      </c>
+      <c r="B60" s="248"/>
+      <c r="C60" s="29"/>
+      <c r="D60" s="30">
         <v>5778358.5099999998</v>
       </c>
-      <c r="E56" s="113" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="250" t="s">
-        <v>274</v>
-      </c>
-      <c r="B57" s="251"/>
-      <c r="C57" s="29"/>
-      <c r="D57" s="241">
+      <c r="E60" s="113" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="245" t="s">
+        <v>271</v>
+      </c>
+      <c r="B61" s="246"/>
+      <c r="C61" s="29"/>
+      <c r="D61" s="30">
         <v>4488639.75</v>
       </c>
-      <c r="E57" s="113" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="32" t="s">
+      <c r="E61" s="113" t="s">
+        <v>266</v>
+      </c>
+      <c r="F61" s="50"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="B58" s="25"/>
-      <c r="C58" s="29"/>
-      <c r="D58" s="30"/>
-      <c r="E58" s="20"/>
-    </row>
-    <row r="59" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="21" t="s">
+      <c r="B62" s="25"/>
+      <c r="C62" s="29"/>
+      <c r="D62" s="30"/>
+      <c r="E62" s="20"/>
+    </row>
+    <row r="63" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="B59" s="21"/>
-      <c r="C59" s="21"/>
-      <c r="D59" s="33"/>
-      <c r="E59" s="152">
-        <f>SUM(D52:D58)</f>
+      <c r="B63" s="21"/>
+      <c r="C63" s="21"/>
+      <c r="D63" s="33"/>
+      <c r="E63" s="152">
+        <f>SUM(D56:D62)</f>
         <v>10937895.550000001</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="14"/>
-      <c r="B60" s="21"/>
-      <c r="C60" s="21"/>
-      <c r="D60" s="22"/>
-      <c r="E60" s="153"/>
-    </row>
-    <row r="61" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="252" t="s">
+    <row r="64" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="14"/>
+      <c r="B64" s="21"/>
+      <c r="C64" s="21"/>
+      <c r="D64" s="22"/>
+      <c r="E64" s="153"/>
+    </row>
+    <row r="65" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="247" t="s">
         <v>163</v>
       </c>
-      <c r="B61" s="253"/>
-      <c r="C61" s="29"/>
-      <c r="D61" s="241">
+      <c r="B65" s="248"/>
+      <c r="C65" s="29"/>
+      <c r="D65" s="30">
         <v>285000</v>
       </c>
-      <c r="E61" s="159" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="252" t="s">
-        <v>255</v>
-      </c>
-      <c r="B62" s="253"/>
-      <c r="C62" s="29"/>
-      <c r="D62" s="241">
+      <c r="E65" s="159" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="247" t="s">
+        <v>252</v>
+      </c>
+      <c r="B66" s="248"/>
+      <c r="C66" s="29"/>
+      <c r="D66" s="30">
         <f>430000+430000*15%</f>
         <v>494500</v>
       </c>
-      <c r="E62" s="159" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="186.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="252" t="s">
-        <v>266</v>
-      </c>
-      <c r="B63" s="253"/>
-      <c r="C63" s="29"/>
-      <c r="D63" s="241">
+      <c r="E66" s="159" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="186.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="247" t="s">
+        <v>263</v>
+      </c>
+      <c r="B67" s="248"/>
+      <c r="C67" s="29"/>
+      <c r="D67" s="30">
         <v>2800000</v>
       </c>
-      <c r="E63" s="159" t="s">
-        <v>244</v>
-      </c>
-      <c r="F63" s="50"/>
-    </row>
-    <row r="64" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="16" t="s">
+      <c r="E67" s="159" t="s">
+        <v>241</v>
+      </c>
+      <c r="F67" s="50"/>
+    </row>
+    <row r="68" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="B64" s="17"/>
-      <c r="C64" s="29"/>
-      <c r="D64" s="241">
+      <c r="B68" s="17"/>
+      <c r="C68" s="29"/>
+      <c r="D68" s="30">
         <v>6990</v>
       </c>
-      <c r="E64" s="34"/>
-      <c r="F64" s="198"/>
-    </row>
-    <row r="65" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="252" t="s">
-        <v>273</v>
-      </c>
-      <c r="B65" s="253"/>
-      <c r="C65" s="29"/>
-      <c r="D65" s="241">
+      <c r="E68" s="34"/>
+      <c r="F68" s="198"/>
+    </row>
+    <row r="69" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="247" t="s">
+        <v>270</v>
+      </c>
+      <c r="B69" s="248"/>
+      <c r="C69" s="29"/>
+      <c r="D69" s="30">
         <v>140000</v>
       </c>
-      <c r="E65" s="34" t="s">
-        <v>271</v>
-      </c>
-      <c r="F65" s="50"/>
-    </row>
-    <row r="66" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="252" t="s">
-        <v>270</v>
-      </c>
-      <c r="B66" s="253"/>
-      <c r="C66" s="29"/>
-      <c r="D66" s="241">
-        <v>31400</v>
-      </c>
-      <c r="E66" s="34" t="s">
-        <v>271</v>
-      </c>
-      <c r="F66" s="50"/>
-    </row>
-    <row r="67" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="252" t="s">
-        <v>272</v>
-      </c>
-      <c r="B67" s="253"/>
-      <c r="C67" s="29"/>
-      <c r="D67" s="241">
-        <v>140000</v>
-      </c>
-      <c r="E67" s="34" t="s">
-        <v>271</v>
-      </c>
-      <c r="F67" s="50"/>
-    </row>
-    <row r="68" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="252" t="s">
-        <v>250</v>
-      </c>
-      <c r="B68" s="253"/>
-      <c r="C68" s="29"/>
-      <c r="D68" s="236">
-        <v>9000</v>
-      </c>
-      <c r="E68" s="159" t="s">
-        <v>265</v>
-      </c>
-      <c r="F68" s="50"/>
-    </row>
-    <row r="69" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="87" t="s">
-        <v>247</v>
-      </c>
-      <c r="B69" s="17"/>
-      <c r="C69" s="29"/>
-      <c r="D69" s="241">
-        <v>158400</v>
-      </c>
-      <c r="E69" s="159" t="s">
-        <v>246</v>
+      <c r="E69" s="34" t="s">
+        <v>268</v>
       </c>
       <c r="F69" s="50"/>
     </row>
-    <row r="70" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="87" t="s">
-        <v>198</v>
-      </c>
-      <c r="B70" s="17"/>
+    <row r="70" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="247" t="s">
+        <v>267</v>
+      </c>
+      <c r="B70" s="248"/>
       <c r="C70" s="29"/>
       <c r="D70" s="30">
-        <v>0</v>
-      </c>
-      <c r="E70" s="159"/>
+        <v>31400</v>
+      </c>
+      <c r="E70" s="34" t="s">
+        <v>268</v>
+      </c>
       <c r="F70" s="50"/>
     </row>
-    <row r="71" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="252" t="s">
-        <v>241</v>
-      </c>
-      <c r="B71" s="253"/>
+    <row r="71" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="247" t="s">
+        <v>269</v>
+      </c>
+      <c r="B71" s="248"/>
       <c r="C71" s="29"/>
       <c r="D71" s="30">
-        <v>0</v>
-      </c>
-      <c r="E71" s="159"/>
+        <v>140000</v>
+      </c>
+      <c r="E71" s="34" t="s">
+        <v>268</v>
+      </c>
       <c r="F71" s="50"/>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="B72" s="14"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="36"/>
-      <c r="E72" s="41">
-        <f>SUM(D61:D71)</f>
-        <v>4065290</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="B73" s="14"/>
-      <c r="C73" s="14"/>
-      <c r="D73" s="15"/>
-      <c r="E73" s="145"/>
-    </row>
-    <row r="74" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="252" t="s">
-        <v>242</v>
-      </c>
-      <c r="B74" s="253"/>
-      <c r="C74" s="18"/>
-      <c r="D74" s="244">
-        <v>781000</v>
+    <row r="72" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="247" t="s">
+        <v>285</v>
+      </c>
+      <c r="B72" s="248"/>
+      <c r="C72" s="29"/>
+      <c r="D72" s="30">
+        <v>42400</v>
+      </c>
+      <c r="E72" s="34" t="s">
+        <v>264</v>
+      </c>
+      <c r="F72" s="50"/>
+    </row>
+    <row r="73" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="247" t="s">
+        <v>247</v>
+      </c>
+      <c r="B73" s="248"/>
+      <c r="C73" s="29"/>
+      <c r="D73" s="30">
+        <v>9000</v>
+      </c>
+      <c r="E73" s="159" t="s">
+        <v>262</v>
+      </c>
+      <c r="F73" s="50"/>
+    </row>
+    <row r="74" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="87" t="s">
+        <v>244</v>
+      </c>
+      <c r="B74" s="17"/>
+      <c r="C74" s="29"/>
+      <c r="D74" s="30">
+        <v>158400</v>
       </c>
       <c r="E74" s="159" t="s">
-        <v>248</v>
-      </c>
-      <c r="G74" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="252" t="s">
-        <v>253</v>
-      </c>
-      <c r="B75" s="253"/>
-      <c r="C75" s="18"/>
-      <c r="D75" s="245">
-        <v>630000</v>
+        <v>243</v>
+      </c>
+      <c r="F74" s="50"/>
+    </row>
+    <row r="75" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="247" t="s">
+        <v>287</v>
+      </c>
+      <c r="B75" s="248"/>
+      <c r="C75" s="29"/>
+      <c r="D75" s="30">
+        <v>215000</v>
       </c>
       <c r="E75" s="159" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="16" t="s">
-        <v>162</v>
+        <v>288</v>
+      </c>
+      <c r="F75" s="50"/>
+    </row>
+    <row r="76" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="87" t="s">
+        <v>198</v>
       </c>
       <c r="B76" s="17"/>
-      <c r="C76" s="18"/>
-      <c r="D76" s="245">
-        <v>250000</v>
-      </c>
-      <c r="E76" s="159" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="87" t="s">
-        <v>243</v>
-      </c>
-      <c r="B77" s="17"/>
-      <c r="C77" s="18"/>
-      <c r="D77" s="245">
-        <v>50000</v>
-      </c>
-      <c r="E77" s="159" t="s">
-        <v>267</v>
-      </c>
+      <c r="C76" s="29"/>
+      <c r="D76" s="30">
+        <v>0</v>
+      </c>
+      <c r="E76" s="159"/>
+      <c r="F76" s="50"/>
+    </row>
+    <row r="77" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="247" t="s">
+        <v>238</v>
+      </c>
+      <c r="B77" s="248"/>
+      <c r="C77" s="29"/>
+      <c r="D77" s="30">
+        <v>0</v>
+      </c>
+      <c r="E77" s="159"/>
+      <c r="F77" s="50"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="B78" s="21"/>
-      <c r="C78" s="21"/>
-      <c r="D78" s="22"/>
-      <c r="E78" s="147">
-        <f>SUM(D74:D77)</f>
-        <v>1711000</v>
+        <v>0</v>
+      </c>
+      <c r="B78" s="14"/>
+      <c r="C78" s="14"/>
+      <c r="D78" s="36"/>
+      <c r="E78" s="41">
+        <f>SUM(D65:D77)</f>
+        <v>4322690</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="B79" s="14"/>
+      <c r="C79" s="14"/>
+      <c r="D79" s="15"/>
+      <c r="E79" s="145"/>
+    </row>
+    <row r="80" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="247" t="s">
+        <v>239</v>
+      </c>
+      <c r="B80" s="248"/>
+      <c r="C80" s="18"/>
+      <c r="D80" s="311">
+        <v>781000</v>
+      </c>
+      <c r="E80" s="159" t="s">
+        <v>245</v>
+      </c>
+      <c r="G80" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="247" t="s">
+        <v>250</v>
+      </c>
+      <c r="B81" s="248"/>
+      <c r="C81" s="18"/>
+      <c r="D81" s="312">
+        <v>630000</v>
+      </c>
+      <c r="E81" s="159" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="B82" s="17"/>
+      <c r="C82" s="18"/>
+      <c r="D82" s="312">
+        <v>250000</v>
+      </c>
+      <c r="E82" s="159" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="87" t="s">
+        <v>240</v>
+      </c>
+      <c r="B83" s="17"/>
+      <c r="C83" s="18"/>
+      <c r="D83" s="312">
+        <v>50000</v>
+      </c>
+      <c r="E83" s="159" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="B84" s="21"/>
+      <c r="C84" s="21"/>
+      <c r="D84" s="22"/>
+      <c r="E84" s="147">
+        <f>SUM(D80:D83)</f>
+        <v>1711000</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="B79" s="37"/>
-      <c r="C79" s="21"/>
-      <c r="D79" s="38"/>
-      <c r="E79" s="41"/>
-    </row>
-    <row r="80" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="250" t="s">
-        <v>275</v>
-      </c>
-      <c r="B80" s="251"/>
-      <c r="C80" s="86"/>
-      <c r="D80" s="248">
+      <c r="B85" s="37"/>
+      <c r="C85" s="21"/>
+      <c r="D85" s="38"/>
+      <c r="E85" s="41"/>
+    </row>
+    <row r="86" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="245" t="s">
+        <v>272</v>
+      </c>
+      <c r="B86" s="246"/>
+      <c r="C86" s="86"/>
+      <c r="D86" s="214">
         <f>65000+29590.38</f>
         <v>94590.38</v>
       </c>
-      <c r="E80" s="154"/>
-    </row>
-    <row r="81" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="250" t="s">
+      <c r="E86" s="154"/>
+    </row>
+    <row r="87" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="245" t="s">
         <v>213</v>
       </c>
-      <c r="B81" s="251"/>
-      <c r="C81" s="86"/>
-      <c r="D81" s="215">
-        <v>269207.65999999997</v>
-      </c>
-      <c r="E81" s="154"/>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="39" t="s">
+      <c r="B87" s="246"/>
+      <c r="C87" s="86"/>
+      <c r="D87" s="214">
+        <v>305996.14</v>
+      </c>
+      <c r="E87" s="154"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="B82" s="39"/>
-      <c r="C82" s="39"/>
-      <c r="D82" s="40"/>
-      <c r="E82" s="41">
-        <f>SUM(D80:D81)</f>
-        <v>363798.04</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="29"/>
-      <c r="B83" s="29"/>
-      <c r="C83" s="29"/>
-      <c r="D83" s="42"/>
-      <c r="E83" s="43"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="44" t="s">
+      <c r="B88" s="39"/>
+      <c r="C88" s="39"/>
+      <c r="D88" s="40"/>
+      <c r="E88" s="41">
+        <f>SUM(D86:D87)</f>
+        <v>400586.52</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="29"/>
+      <c r="B89" s="29"/>
+      <c r="C89" s="29"/>
+      <c r="D89" s="42"/>
+      <c r="E89" s="43"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="B84" s="44"/>
-      <c r="C84" s="44"/>
-      <c r="D84" s="45"/>
-      <c r="E84" s="46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="47"/>
-      <c r="D85" s="48"/>
-      <c r="E85" s="49"/>
-      <c r="F85" s="50"/>
-    </row>
-    <row r="86" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="51" t="s">
+      <c r="B90" s="44"/>
+      <c r="C90" s="44"/>
+      <c r="D90" s="45"/>
+      <c r="E90" s="46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="47"/>
+      <c r="D91" s="48"/>
+      <c r="E91" s="49"/>
+      <c r="F91" s="50"/>
+    </row>
+    <row r="92" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="51" t="s">
         <v>115</v>
       </c>
-      <c r="B86" s="52"/>
-      <c r="C86" s="53"/>
-      <c r="D86" s="54"/>
-      <c r="E86" s="55">
-        <f>(SUM(E21:E84))</f>
-        <v>21925285.809999999</v>
-      </c>
-      <c r="F86" s="56"/>
-      <c r="G86" s="50"/>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D87" s="48"/>
-      <c r="E87" s="48"/>
-    </row>
-    <row r="88" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D88" s="48"/>
-      <c r="E88" s="48"/>
-      <c r="H88" s="57"/>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="11" t="s">
+      <c r="B92" s="52"/>
+      <c r="C92" s="53"/>
+      <c r="D92" s="54"/>
+      <c r="E92" s="55">
+        <f>(SUM(E21:E90))</f>
+        <v>23084688.289999999</v>
+      </c>
+      <c r="F92" s="56">
+        <v>10266998.26</v>
+      </c>
+      <c r="G92" s="50">
+        <f>E92-F92</f>
+        <v>12817690.029999999</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D93" s="48"/>
+      <c r="E93" s="48"/>
+    </row>
+    <row r="94" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D94" s="48"/>
+      <c r="E94" s="48"/>
+      <c r="H94" s="57"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="B89" s="12"/>
-      <c r="C89" s="13"/>
-      <c r="D89" s="58"/>
-      <c r="E89" s="59"/>
-    </row>
-    <row r="90" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="268"/>
-      <c r="B90" s="268"/>
-      <c r="C90" s="31"/>
-      <c r="D90" s="264"/>
-      <c r="E90" s="266"/>
-    </row>
-    <row r="91" spans="1:8" ht="1.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="268"/>
-      <c r="B91" s="268"/>
-      <c r="C91" s="31"/>
-      <c r="D91" s="265"/>
-      <c r="E91" s="267"/>
-    </row>
-    <row r="92" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="29"/>
-      <c r="B92" s="29"/>
-      <c r="D92" s="42"/>
-      <c r="E92" s="42"/>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="24"/>
-      <c r="B93" s="61"/>
-      <c r="C93" s="29"/>
-      <c r="D93" s="35"/>
-      <c r="E93" s="60"/>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="62" t="s">
+      <c r="B95" s="12"/>
+      <c r="C95" s="13"/>
+      <c r="D95" s="58"/>
+      <c r="E95" s="59"/>
+    </row>
+    <row r="96" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="249"/>
+      <c r="B96" s="249"/>
+      <c r="C96" s="31"/>
+      <c r="D96" s="241"/>
+      <c r="E96" s="243"/>
+    </row>
+    <row r="97" spans="1:5" ht="1.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="249"/>
+      <c r="B97" s="249"/>
+      <c r="C97" s="31"/>
+      <c r="D97" s="242"/>
+      <c r="E97" s="244"/>
+    </row>
+    <row r="98" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="29"/>
+      <c r="B98" s="29"/>
+      <c r="D98" s="42"/>
+      <c r="E98" s="42"/>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="24"/>
+      <c r="B99" s="61"/>
+      <c r="C99" s="29"/>
+      <c r="D99" s="35"/>
+      <c r="E99" s="60"/>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="62" t="s">
         <v>144</v>
       </c>
-      <c r="B94" s="63"/>
-      <c r="C94" s="63"/>
-      <c r="D94" s="111"/>
-      <c r="E94" s="155">
-        <f>SUM(D90:D93)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D95" s="48"/>
-      <c r="E95" s="48"/>
-    </row>
-    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D96" s="48"/>
-      <c r="E96" s="48"/>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="44" t="s">
-        <v>117</v>
-      </c>
-      <c r="B97" s="44"/>
-      <c r="C97" s="44"/>
-      <c r="D97" s="45"/>
-      <c r="E97" s="158">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D98" s="48"/>
-      <c r="E98" s="48"/>
-    </row>
-    <row r="99" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="51" t="s">
-        <v>118</v>
-      </c>
-      <c r="B99" s="52"/>
-      <c r="C99" s="53"/>
-      <c r="D99" s="54"/>
-      <c r="E99" s="55">
-        <f>E94+E97</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D100" s="48"/>
-      <c r="E100" s="48"/>
-    </row>
-    <row r="101" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="64" t="s">
-        <v>119</v>
-      </c>
-      <c r="B101" s="65">
-        <f>E86</f>
-        <v>21925285.809999999</v>
-      </c>
+      <c r="B100" s="63"/>
+      <c r="C100" s="63"/>
+      <c r="D100" s="111"/>
+      <c r="E100" s="155">
+        <f>SUM(D96:D99)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D101" s="48"/>
       <c r="E101" s="48"/>
     </row>
-    <row r="102" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="64" t="s">
-        <v>120</v>
-      </c>
-      <c r="B102" s="65">
-        <f>E86-E84</f>
-        <v>21925285.809999999</v>
-      </c>
+    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="D102" s="48"/>
       <c r="E102" s="48"/>
     </row>
-    <row r="103" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="64" t="s">
-        <v>121</v>
-      </c>
-      <c r="B103" s="65">
-        <f>E99-E97</f>
-        <v>0</v>
-      </c>
-      <c r="D103" s="48"/>
-      <c r="E103" s="48"/>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="44" t="s">
+        <v>117</v>
+      </c>
+      <c r="B103" s="44"/>
+      <c r="C103" s="44"/>
+      <c r="D103" s="45"/>
+      <c r="E103" s="158">
+        <v>4500000</v>
+      </c>
     </row>
     <row r="104" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="64" t="s">
-        <v>122</v>
-      </c>
-      <c r="B104" s="65">
-        <f>E99</f>
-        <v>0</v>
-      </c>
       <c r="D104" s="48"/>
       <c r="E104" s="48"/>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D105" s="48"/>
-      <c r="E105" s="48"/>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="51" t="s">
+        <v>118</v>
+      </c>
+      <c r="B105" s="52"/>
+      <c r="C105" s="53"/>
+      <c r="D105" s="54"/>
+      <c r="E105" s="55">
+        <f>E100+E103</f>
+        <v>4500000</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D106" s="48"/>
       <c r="E106" s="48"/>
     </row>
-    <row r="107" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="255" t="s">
-        <v>171</v>
-      </c>
-      <c r="B107" s="255"/>
+    <row r="107" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="64" t="s">
+        <v>119</v>
+      </c>
+      <c r="B107" s="65">
+        <f>E92</f>
+        <v>23084688.289999999</v>
+      </c>
       <c r="D107" s="48"/>
       <c r="E107" s="48"/>
     </row>
-    <row r="108" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="255"/>
-      <c r="B108" s="255"/>
+    <row r="108" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="64" t="s">
+        <v>120</v>
+      </c>
+      <c r="B108" s="65">
+        <f>E92-E90</f>
+        <v>23084688.289999999</v>
+      </c>
       <c r="D108" s="48"/>
       <c r="E108" s="48"/>
     </row>
-    <row r="109" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="255"/>
-      <c r="B109" s="255"/>
+    <row r="109" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="64" t="s">
+        <v>121</v>
+      </c>
+      <c r="B109" s="65">
+        <f>E105-E103</f>
+        <v>0</v>
+      </c>
       <c r="D109" s="48"/>
       <c r="E109" s="48"/>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="64" t="s">
+        <v>122</v>
+      </c>
+      <c r="B110" s="65">
+        <f>E105</f>
+        <v>4500000</v>
+      </c>
       <c r="D110" s="48"/>
       <c r="E110" s="48"/>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="255" t="s">
-        <v>220</v>
-      </c>
-      <c r="B111" s="255"/>
       <c r="D111" s="48"/>
       <c r="E111" s="48"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" s="255"/>
-      <c r="B112" s="255"/>
       <c r="D112" s="48"/>
       <c r="E112" s="48"/>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A113" s="255"/>
-      <c r="B113" s="255"/>
+    <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="259" t="s">
+        <v>171</v>
+      </c>
+      <c r="B113" s="259"/>
       <c r="D113" s="48"/>
       <c r="E113" s="48"/>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="259"/>
+      <c r="B114" s="259"/>
       <c r="D114" s="48"/>
       <c r="E114" s="48"/>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A115" s="255" t="s">
-        <v>221</v>
-      </c>
-      <c r="B115" s="255"/>
+    <row r="115" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="259"/>
+      <c r="B115" s="259"/>
       <c r="D115" s="48"/>
       <c r="E115" s="48"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A116" s="255"/>
-      <c r="B116" s="255"/>
       <c r="D116" s="48"/>
       <c r="E116" s="48"/>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A117" s="255"/>
-      <c r="B117" s="255"/>
+      <c r="A117" s="259" t="s">
+        <v>220</v>
+      </c>
+      <c r="B117" s="259"/>
       <c r="D117" s="48"/>
       <c r="E117" s="48"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="259"/>
+      <c r="B118" s="259"/>
       <c r="D118" s="48"/>
       <c r="E118" s="48"/>
     </row>
-    <row r="119" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="255" t="s">
-        <v>197</v>
-      </c>
-      <c r="B119" s="255"/>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" s="259"/>
+      <c r="B119" s="259"/>
       <c r="D119" s="48"/>
       <c r="E119" s="48"/>
     </row>
-    <row r="120" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="255"/>
-      <c r="B120" s="255"/>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D120" s="48"/>
       <c r="E120" s="48"/>
     </row>
-    <row r="121" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="255"/>
-      <c r="B121" s="255"/>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" s="259" t="s">
+        <v>221</v>
+      </c>
+      <c r="B121" s="259"/>
       <c r="D121" s="48"/>
       <c r="E121" s="48"/>
     </row>
-    <row r="122" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" s="259"/>
+      <c r="B122" s="259"/>
       <c r="D122" s="48"/>
       <c r="E122" s="48"/>
-      <c r="F122" s="197"/>
-    </row>
-    <row r="123" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="255" t="s">
-        <v>178</v>
-      </c>
-      <c r="B123" s="255"/>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="259"/>
+      <c r="B123" s="259"/>
       <c r="D123" s="48"/>
       <c r="E123" s="48"/>
     </row>
-    <row r="124" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="255"/>
-      <c r="B124" s="255"/>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D124" s="48"/>
       <c r="E124" s="48"/>
     </row>
-    <row r="125" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="255"/>
-      <c r="B125" s="255"/>
+    <row r="125" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="259" t="s">
+        <v>197</v>
+      </c>
+      <c r="B125" s="259"/>
       <c r="D125" s="48"/>
       <c r="E125" s="48"/>
     </row>
-    <row r="126" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="259"/>
+      <c r="B126" s="259"/>
       <c r="D126" s="48"/>
       <c r="E126" s="48"/>
     </row>
-    <row r="127" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="255" t="s">
-        <v>181</v>
-      </c>
-      <c r="B127" s="255"/>
+    <row r="127" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="259"/>
+      <c r="B127" s="259"/>
       <c r="D127" s="48"/>
       <c r="E127" s="48"/>
     </row>
-    <row r="128" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="255"/>
-      <c r="B128" s="255"/>
+    <row r="128" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D128" s="48"/>
       <c r="E128" s="48"/>
-    </row>
-    <row r="129" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="255"/>
-      <c r="B129" s="255"/>
+      <c r="F128" s="197"/>
+    </row>
+    <row r="129" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="259" t="s">
+        <v>178</v>
+      </c>
+      <c r="B129" s="259"/>
       <c r="D129" s="48"/>
       <c r="E129" s="48"/>
     </row>
-    <row r="130" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="259"/>
+      <c r="B130" s="259"/>
       <c r="D130" s="48"/>
       <c r="E130" s="48"/>
     </row>
-    <row r="131" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="255" t="s">
-        <v>180</v>
-      </c>
-      <c r="B131" s="255"/>
+    <row r="131" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="259"/>
+      <c r="B131" s="259"/>
       <c r="D131" s="48"/>
       <c r="E131" s="48"/>
     </row>
     <row r="132" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="255"/>
-      <c r="B132" s="255"/>
       <c r="D132" s="48"/>
       <c r="E132" s="48"/>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A133" s="255"/>
-      <c r="B133" s="255"/>
+    <row r="133" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="259" t="s">
+        <v>181</v>
+      </c>
+      <c r="B133" s="259"/>
       <c r="D133" s="48"/>
       <c r="E133" s="48"/>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="259"/>
+      <c r="B134" s="259"/>
       <c r="D134" s="48"/>
       <c r="E134" s="48"/>
     </row>
-    <row r="135" spans="1:6" s="68" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A135"/>
-      <c r="B135" s="66"/>
-      <c r="C135" s="67"/>
-      <c r="D135" s="156"/>
-      <c r="E135" s="156"/>
-    </row>
-    <row r="136" spans="1:6" s="68" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="206" t="s">
-        <v>187</v>
-      </c>
-      <c r="B136" s="207">
-        <v>1157299.74</v>
-      </c>
-      <c r="C136" s="67"/>
-      <c r="D136" s="157"/>
-      <c r="E136" s="157"/>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A137" s="208" t="s">
-        <v>143</v>
-      </c>
-      <c r="B137" s="209">
-        <f>-B102-B103</f>
-        <v>-21925285.809999999</v>
-      </c>
+    <row r="135" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="259"/>
+      <c r="B135" s="259"/>
+      <c r="D135" s="48"/>
+      <c r="E135" s="48"/>
+    </row>
+    <row r="136" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D136" s="48"/>
+      <c r="E136" s="48"/>
+    </row>
+    <row r="137" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="259" t="s">
+        <v>180</v>
+      </c>
+      <c r="B137" s="259"/>
       <c r="D137" s="48"/>
       <c r="E137" s="48"/>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A138" s="208" t="s">
-        <v>123</v>
-      </c>
-      <c r="B138" s="210">
-        <f>B168</f>
-        <v>0</v>
-      </c>
+    <row r="138" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="259"/>
+      <c r="B138" s="259"/>
       <c r="D138" s="48"/>
       <c r="E138" s="48"/>
-      <c r="F138" s="66"/>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A139" s="208" t="s">
-        <v>2</v>
-      </c>
-      <c r="B139" s="211">
-        <f>PRORRATEO!F119</f>
-        <v>18974843.529999997</v>
-      </c>
+      <c r="A139" s="259"/>
+      <c r="B139" s="259"/>
       <c r="D139" s="48"/>
       <c r="E139" s="48"/>
-      <c r="F139" s="66"/>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A140" s="208" t="s">
-        <v>259</v>
-      </c>
-      <c r="B140" s="243">
-        <v>-24000</v>
-      </c>
       <c r="D140" s="48"/>
       <c r="E140" s="48"/>
-      <c r="F140" s="66"/>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A141" s="208" t="s">
+    </row>
+    <row r="141" spans="1:6" s="68" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A141"/>
+      <c r="B141" s="66"/>
+      <c r="C141" s="67"/>
+      <c r="D141" s="156"/>
+      <c r="E141" s="156"/>
+    </row>
+    <row r="142" spans="1:6" s="68" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="206" t="s">
+        <v>187</v>
+      </c>
+      <c r="B142" s="308">
+        <v>1544535.81</v>
+      </c>
+      <c r="C142" s="67"/>
+      <c r="D142" s="157"/>
+      <c r="E142" s="157"/>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" s="208" t="s">
+        <v>143</v>
+      </c>
+      <c r="B143" s="209">
+        <f>-B108-B109</f>
+        <v>-23084688.289999999</v>
+      </c>
+      <c r="D143" s="48"/>
+      <c r="E143" s="48"/>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" s="208" t="s">
+        <v>123</v>
+      </c>
+      <c r="B144" s="210">
+        <f>B174</f>
+        <v>0</v>
+      </c>
+      <c r="D144" s="48"/>
+      <c r="E144" s="48"/>
+      <c r="F144" s="66"/>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" s="208" t="s">
+        <v>2</v>
+      </c>
+      <c r="B145" s="211">
+        <f>PRORRATEO!F119</f>
+        <v>20030676.670000002</v>
+      </c>
+      <c r="D145" s="48"/>
+      <c r="E145" s="48"/>
+      <c r="F145" s="66"/>
+    </row>
+    <row r="146" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A146" s="208" t="s">
+        <v>286</v>
+      </c>
+      <c r="B146" s="313">
+        <v>-140000</v>
+      </c>
+      <c r="D146" s="48"/>
+      <c r="E146" s="48"/>
+      <c r="F146" s="66"/>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" s="208" t="s">
+        <v>256</v>
+      </c>
+      <c r="B147" s="313">
+        <v>-24000</v>
+      </c>
+      <c r="D147" s="48"/>
+      <c r="E147" s="48"/>
+      <c r="F147" s="66"/>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A148" s="208" t="s">
+        <v>276</v>
+      </c>
+      <c r="B148" s="313">
+        <v>-200000</v>
+      </c>
+      <c r="D148" s="48"/>
+      <c r="E148" s="48"/>
+      <c r="F148" s="66"/>
+    </row>
+    <row r="149" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A149" s="208" t="s">
+        <v>216</v>
+      </c>
+      <c r="B149" s="313">
+        <v>-5877</v>
+      </c>
+      <c r="D149" s="48"/>
+      <c r="E149" s="48"/>
+      <c r="F149" s="66"/>
+    </row>
+    <row r="150" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="204" t="s">
+        <v>159</v>
+      </c>
+      <c r="B150" s="205">
+        <f>SUM(B142:C149)</f>
+        <v>-1879352.8099999987</v>
+      </c>
+      <c r="D150" s="215"/>
+      <c r="E150" s="50"/>
+      <c r="F150" s="50"/>
+    </row>
+    <row r="151" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D151" s="48"/>
+    </row>
+    <row r="152" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="260" t="s">
+        <v>283</v>
+      </c>
+      <c r="B152" s="260"/>
+      <c r="C152" s="260"/>
+      <c r="D152" s="260"/>
+    </row>
+    <row r="153" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="260"/>
+      <c r="B153" s="260"/>
+      <c r="C153" s="260"/>
+      <c r="D153" s="260"/>
+    </row>
+    <row r="154" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="260"/>
+      <c r="B154" s="260"/>
+      <c r="C154" s="260"/>
+      <c r="D154" s="260"/>
+    </row>
+    <row r="155" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="260"/>
+      <c r="B155" s="260"/>
+      <c r="C155" s="260"/>
+      <c r="D155" s="260"/>
+    </row>
+    <row r="156" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="260"/>
+      <c r="B156" s="260"/>
+      <c r="C156" s="260"/>
+      <c r="D156" s="260"/>
+    </row>
+    <row r="157" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="260"/>
+      <c r="B157" s="260"/>
+      <c r="C157" s="260"/>
+      <c r="D157" s="260"/>
+    </row>
+    <row r="158" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="260"/>
+      <c r="B158" s="260"/>
+      <c r="C158" s="260"/>
+      <c r="D158" s="260"/>
+    </row>
+    <row r="159" spans="1:6" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D159" s="48"/>
+    </row>
+    <row r="160" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="206" t="s">
         <v>279</v>
       </c>
-      <c r="B141" s="243">
-        <v>-200000</v>
-      </c>
-      <c r="D141" s="48"/>
-      <c r="E141" s="48"/>
-      <c r="F141" s="66"/>
-    </row>
-    <row r="142" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="208" t="s">
-        <v>216</v>
-      </c>
-      <c r="B142" s="243">
-        <v>-5877</v>
-      </c>
-      <c r="D142" s="48"/>
-      <c r="E142" s="48"/>
-      <c r="F142" s="66"/>
-    </row>
-    <row r="143" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="204" t="s">
-        <v>159</v>
-      </c>
-      <c r="B143" s="205">
-        <f>SUM(B136:C142)</f>
-        <v>-2023019.5400000028</v>
-      </c>
-      <c r="D143" s="216"/>
-      <c r="E143" s="50"/>
-      <c r="F143" s="50"/>
-    </row>
-    <row r="144" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D144" s="48"/>
-    </row>
-    <row r="145" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="319" t="s">
-        <v>286</v>
-      </c>
-      <c r="B145" s="319"/>
-      <c r="C145" s="319"/>
-      <c r="D145" s="319"/>
-    </row>
-    <row r="146" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="319"/>
-      <c r="B146" s="319"/>
-      <c r="C146" s="319"/>
-      <c r="D146" s="319"/>
-    </row>
-    <row r="147" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="319"/>
-      <c r="B147" s="319"/>
-      <c r="C147" s="319"/>
-      <c r="D147" s="319"/>
-    </row>
-    <row r="148" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="319"/>
-      <c r="B148" s="319"/>
-      <c r="C148" s="319"/>
-      <c r="D148" s="319"/>
-    </row>
-    <row r="149" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="319"/>
-      <c r="B149" s="319"/>
-      <c r="C149" s="319"/>
-      <c r="D149" s="319"/>
-    </row>
-    <row r="150" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="319"/>
-      <c r="B150" s="319"/>
-      <c r="C150" s="319"/>
-      <c r="D150" s="319"/>
-    </row>
-    <row r="151" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="319"/>
-      <c r="B151" s="319"/>
-      <c r="C151" s="319"/>
-      <c r="D151" s="319"/>
-    </row>
-    <row r="152" spans="1:4" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D152" s="48"/>
-    </row>
-    <row r="153" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="206" t="s">
-        <v>282</v>
-      </c>
-      <c r="B153" s="207">
-        <v>0</v>
-      </c>
-      <c r="D153" s="48"/>
-    </row>
-    <row r="154" spans="1:4" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="208" t="s">
-        <v>284</v>
-      </c>
-      <c r="B154" s="211">
+      <c r="B160" s="207">
+        <v>0</v>
+      </c>
+      <c r="D160" s="48"/>
+    </row>
+    <row r="161" spans="1:13" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A161" s="208" t="s">
+        <v>281</v>
+      </c>
+      <c r="B161" s="211">
         <v>320000</v>
       </c>
-      <c r="D154" s="48"/>
-    </row>
-    <row r="155" spans="1:4" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="204" t="s">
-        <v>283</v>
-      </c>
-      <c r="B155" s="205">
-        <f>SUM(B153:C154)</f>
+      <c r="D161" s="48"/>
+    </row>
+    <row r="162" spans="1:13" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A162" s="204" t="s">
+        <v>280</v>
+      </c>
+      <c r="B162" s="205">
+        <f>SUM(B160:C161)</f>
         <v>320000</v>
       </c>
-      <c r="D155" s="48"/>
-    </row>
-    <row r="156" spans="1:4" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D156" s="48"/>
-    </row>
-    <row r="157" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="206" t="s">
-        <v>229</v>
-      </c>
-      <c r="B157" s="207">
-        <v>0</v>
-      </c>
-      <c r="D157" s="48"/>
-    </row>
-    <row r="158" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="208" t="s">
+      <c r="D162" s="48"/>
+    </row>
+    <row r="163" spans="1:13" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D163" s="48"/>
+    </row>
+    <row r="164" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="206" t="s">
         <v>226</v>
       </c>
-      <c r="B158" s="212">
-        <v>1500000</v>
-      </c>
-      <c r="D158" s="48"/>
-    </row>
-    <row r="159" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="213" t="s">
-        <v>227</v>
-      </c>
-      <c r="B159" s="214">
-        <f>1506421.54-B158</f>
-        <v>6421.5400000000373</v>
-      </c>
-      <c r="D159" s="48"/>
-    </row>
-    <row r="160" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="204" t="s">
-        <v>228</v>
-      </c>
-      <c r="B160" s="205">
-        <f>SUM(B157:B159)</f>
+      <c r="B164" s="308">
         <v>1506421.54</v>
       </c>
-      <c r="D160" s="48"/>
-    </row>
-    <row r="161" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D161" s="48"/>
-    </row>
-    <row r="162" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D162" s="48"/>
-    </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A163" s="254" t="s">
+      <c r="D164" s="48"/>
+    </row>
+    <row r="165" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A165" s="212" t="s">
+        <v>225</v>
+      </c>
+      <c r="B165" s="213">
+        <f>B166-B164</f>
+        <v>23256.959999999963</v>
+      </c>
+      <c r="D165" s="48"/>
+    </row>
+    <row r="166" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A166" s="204" t="s">
+        <v>292</v>
+      </c>
+      <c r="B166" s="205">
+        <v>1529678.5</v>
+      </c>
+      <c r="D166" s="48"/>
+    </row>
+    <row r="167" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D167" s="48"/>
+    </row>
+    <row r="168" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D168" s="48"/>
+    </row>
+    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A169" s="258" t="s">
         <v>124</v>
       </c>
-      <c r="B163" s="254"/>
-      <c r="C163" s="254"/>
-      <c r="D163" s="48"/>
-    </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A164" s="254"/>
-      <c r="B164" s="254"/>
-      <c r="C164" s="254"/>
-      <c r="D164" s="48"/>
-    </row>
-    <row r="165" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="69"/>
-      <c r="B165" s="110"/>
-      <c r="C165" s="70"/>
-      <c r="D165" s="217"/>
-    </row>
-    <row r="166" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="69"/>
-      <c r="B166" s="110"/>
-      <c r="C166" s="70"/>
-      <c r="D166" s="217"/>
-    </row>
-    <row r="167" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="69"/>
-      <c r="B167" s="110"/>
-      <c r="C167" s="70"/>
-      <c r="D167" s="56"/>
-    </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A168" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="B168" s="72">
-        <f>SUM(B165:B167)</f>
-        <v>0</v>
-      </c>
-      <c r="C168" s="73"/>
-    </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M169" s="74"/>
+      <c r="B169" s="258"/>
+      <c r="C169" s="258"/>
+      <c r="D169" s="48"/>
+    </row>
+    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A170" s="258"/>
+      <c r="B170" s="258"/>
+      <c r="C170" s="258"/>
+      <c r="D170" s="48"/>
+    </row>
+    <row r="171" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="69"/>
+      <c r="B171" s="110"/>
+      <c r="C171" s="70"/>
+      <c r="D171" s="216"/>
+    </row>
+    <row r="172" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A172" s="69"/>
+      <c r="B172" s="110"/>
+      <c r="C172" s="70"/>
+      <c r="D172" s="216"/>
+    </row>
+    <row r="173" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A173" s="69"/>
+      <c r="B173" s="110"/>
+      <c r="C173" s="70"/>
+      <c r="D173" s="56"/>
+    </row>
+    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A174" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="B174" s="72">
+        <f>SUM(B171:B173)</f>
+        <v>0</v>
+      </c>
+      <c r="C174" s="73"/>
+    </row>
+    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M175" s="74"/>
     </row>
   </sheetData>
-  <mergeCells count="36">
-    <mergeCell ref="D90:D91"/>
-    <mergeCell ref="E90:E91"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="A66:B66"/>
+  <mergeCells count="41">
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A61:B61"/>
     <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A90:B91"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A169:C170"/>
+    <mergeCell ref="A125:B127"/>
+    <mergeCell ref="A137:B139"/>
+    <mergeCell ref="A133:B135"/>
+    <mergeCell ref="A113:B115"/>
+    <mergeCell ref="A129:B131"/>
+    <mergeCell ref="A117:B119"/>
+    <mergeCell ref="A121:B123"/>
+    <mergeCell ref="A152:D158"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A80:B80"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A65:B65"/>
     <mergeCell ref="A67:B67"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A163:C164"/>
-    <mergeCell ref="A119:B121"/>
-    <mergeCell ref="A131:B133"/>
-    <mergeCell ref="A127:B129"/>
-    <mergeCell ref="A107:B109"/>
-    <mergeCell ref="A123:B125"/>
-    <mergeCell ref="A111:B113"/>
-    <mergeCell ref="A115:B117"/>
-    <mergeCell ref="A145:D151"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="D96:D97"/>
+    <mergeCell ref="E96:E97"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A96:B97"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="A86:B86"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="90" orientation="portrait" r:id="rId1"/>
@@ -4410,17 +4521,17 @@
       <c r="A1" s="88"/>
       <c r="B1" s="89"/>
       <c r="C1" s="89"/>
-      <c r="D1" s="284"/>
-      <c r="E1" s="284"/>
-      <c r="F1" s="284"/>
-      <c r="G1" s="284"/>
-      <c r="H1" s="284"/>
-      <c r="I1" s="284"/>
-      <c r="J1" s="284"/>
-      <c r="K1" s="284"/>
-      <c r="L1" s="284"/>
-      <c r="M1" s="284"/>
-      <c r="N1" s="284"/>
+      <c r="D1" s="262"/>
+      <c r="E1" s="262"/>
+      <c r="F1" s="262"/>
+      <c r="G1" s="262"/>
+      <c r="H1" s="262"/>
+      <c r="I1" s="262"/>
+      <c r="J1" s="262"/>
+      <c r="K1" s="262"/>
+      <c r="L1" s="262"/>
+      <c r="M1" s="262"/>
+      <c r="N1" s="262"/>
       <c r="O1" s="90"/>
     </row>
     <row r="2" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4430,25 +4541,24 @@
       <c r="D2" s="93" t="s">
         <v>125</v>
       </c>
-      <c r="E2" s="306">
+      <c r="E2" s="286">
         <v>4500000</v>
       </c>
-      <c r="F2" s="306"/>
+      <c r="F2" s="286"/>
       <c r="G2" s="93"/>
       <c r="H2" s="93"/>
       <c r="I2" s="93" t="s">
         <v>126</v>
       </c>
       <c r="J2" s="94">
-        <f>16000000-M2+1500000</f>
-        <v>11694747.559999999</v>
+        <v>9000000</v>
       </c>
       <c r="K2" s="94"/>
       <c r="L2" s="94" t="s">
         <v>218</v>
       </c>
       <c r="M2" s="94">
-        <v>5805252.4400000004</v>
+        <v>10266998.26</v>
       </c>
       <c r="N2" s="95"/>
       <c r="O2" s="96"/>
@@ -4476,238 +4586,238 @@
       <c r="P3" s="75"/>
     </row>
     <row r="4" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="285" t="s">
+      <c r="A4" s="263" t="s">
         <v>158</v>
       </c>
-      <c r="B4" s="286"/>
-      <c r="C4" s="286"/>
-      <c r="D4" s="286"/>
-      <c r="E4" s="286"/>
-      <c r="F4" s="286"/>
-      <c r="G4" s="286"/>
-      <c r="H4" s="286"/>
-      <c r="I4" s="286"/>
-      <c r="J4" s="286"/>
-      <c r="K4" s="286"/>
-      <c r="L4" s="286"/>
-      <c r="M4" s="286"/>
-      <c r="N4" s="286"/>
-      <c r="O4" s="287"/>
+      <c r="B4" s="264"/>
+      <c r="C4" s="264"/>
+      <c r="D4" s="264"/>
+      <c r="E4" s="264"/>
+      <c r="F4" s="264"/>
+      <c r="G4" s="264"/>
+      <c r="H4" s="264"/>
+      <c r="I4" s="264"/>
+      <c r="J4" s="264"/>
+      <c r="K4" s="264"/>
+      <c r="L4" s="264"/>
+      <c r="M4" s="264"/>
+      <c r="N4" s="264"/>
+      <c r="O4" s="265"/>
       <c r="P4" s="75"/>
     </row>
     <row r="5" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="288"/>
-      <c r="B5" s="289"/>
-      <c r="C5" s="289"/>
-      <c r="D5" s="289"/>
-      <c r="E5" s="289"/>
-      <c r="F5" s="289"/>
-      <c r="G5" s="289"/>
-      <c r="H5" s="289"/>
-      <c r="I5" s="289"/>
-      <c r="J5" s="289"/>
-      <c r="K5" s="289"/>
-      <c r="L5" s="289"/>
-      <c r="M5" s="289"/>
-      <c r="N5" s="289"/>
-      <c r="O5" s="290"/>
+      <c r="A5" s="266"/>
+      <c r="B5" s="267"/>
+      <c r="C5" s="267"/>
+      <c r="D5" s="267"/>
+      <c r="E5" s="267"/>
+      <c r="F5" s="267"/>
+      <c r="G5" s="267"/>
+      <c r="H5" s="267"/>
+      <c r="I5" s="267"/>
+      <c r="J5" s="267"/>
+      <c r="K5" s="267"/>
+      <c r="L5" s="267"/>
+      <c r="M5" s="267"/>
+      <c r="N5" s="267"/>
+      <c r="O5" s="268"/>
       <c r="P5" s="75"/>
     </row>
     <row r="6" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="288"/>
-      <c r="B6" s="289"/>
-      <c r="C6" s="289"/>
-      <c r="D6" s="289"/>
-      <c r="E6" s="289"/>
-      <c r="F6" s="289"/>
-      <c r="G6" s="289"/>
-      <c r="H6" s="289"/>
-      <c r="I6" s="289"/>
-      <c r="J6" s="289"/>
-      <c r="K6" s="289"/>
-      <c r="L6" s="289"/>
-      <c r="M6" s="289"/>
-      <c r="N6" s="289"/>
-      <c r="O6" s="290"/>
+      <c r="A6" s="266"/>
+      <c r="B6" s="267"/>
+      <c r="C6" s="267"/>
+      <c r="D6" s="267"/>
+      <c r="E6" s="267"/>
+      <c r="F6" s="267"/>
+      <c r="G6" s="267"/>
+      <c r="H6" s="267"/>
+      <c r="I6" s="267"/>
+      <c r="J6" s="267"/>
+      <c r="K6" s="267"/>
+      <c r="L6" s="267"/>
+      <c r="M6" s="267"/>
+      <c r="N6" s="267"/>
+      <c r="O6" s="268"/>
       <c r="P6" s="75"/>
     </row>
     <row r="7" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="288"/>
-      <c r="B7" s="289"/>
-      <c r="C7" s="289"/>
-      <c r="D7" s="289"/>
-      <c r="E7" s="289"/>
-      <c r="F7" s="289"/>
-      <c r="G7" s="289"/>
-      <c r="H7" s="289"/>
-      <c r="I7" s="289"/>
-      <c r="J7" s="289"/>
-      <c r="K7" s="289"/>
-      <c r="L7" s="289"/>
-      <c r="M7" s="289"/>
-      <c r="N7" s="289"/>
-      <c r="O7" s="290"/>
+      <c r="A7" s="266"/>
+      <c r="B7" s="267"/>
+      <c r="C7" s="267"/>
+      <c r="D7" s="267"/>
+      <c r="E7" s="267"/>
+      <c r="F7" s="267"/>
+      <c r="G7" s="267"/>
+      <c r="H7" s="267"/>
+      <c r="I7" s="267"/>
+      <c r="J7" s="267"/>
+      <c r="K7" s="267"/>
+      <c r="L7" s="267"/>
+      <c r="M7" s="267"/>
+      <c r="N7" s="267"/>
+      <c r="O7" s="268"/>
       <c r="P7" s="75"/>
     </row>
     <row r="8" spans="1:17" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="291"/>
-      <c r="B8" s="292"/>
-      <c r="C8" s="292"/>
-      <c r="D8" s="292"/>
-      <c r="E8" s="292"/>
-      <c r="F8" s="292"/>
-      <c r="G8" s="292"/>
-      <c r="H8" s="292"/>
-      <c r="I8" s="292"/>
-      <c r="J8" s="292"/>
-      <c r="K8" s="292"/>
-      <c r="L8" s="292"/>
-      <c r="M8" s="292"/>
-      <c r="N8" s="292"/>
-      <c r="O8" s="293"/>
+      <c r="A8" s="269"/>
+      <c r="B8" s="270"/>
+      <c r="C8" s="270"/>
+      <c r="D8" s="270"/>
+      <c r="E8" s="270"/>
+      <c r="F8" s="270"/>
+      <c r="G8" s="270"/>
+      <c r="H8" s="270"/>
+      <c r="I8" s="270"/>
+      <c r="J8" s="270"/>
+      <c r="K8" s="270"/>
+      <c r="L8" s="270"/>
+      <c r="M8" s="270"/>
+      <c r="N8" s="270"/>
+      <c r="O8" s="271"/>
     </row>
     <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="300" t="s">
+      <c r="A9" s="280" t="s">
         <v>156</v>
       </c>
-      <c r="B9" s="301"/>
-      <c r="C9" s="301"/>
-      <c r="D9" s="301"/>
-      <c r="E9" s="301"/>
-      <c r="F9" s="301"/>
-      <c r="G9" s="301"/>
-      <c r="H9" s="301"/>
-      <c r="I9" s="301"/>
-      <c r="J9" s="301"/>
-      <c r="K9" s="301"/>
-      <c r="L9" s="301"/>
-      <c r="M9" s="301"/>
-      <c r="N9" s="301"/>
-      <c r="O9" s="302"/>
+      <c r="B9" s="281"/>
+      <c r="C9" s="281"/>
+      <c r="D9" s="281"/>
+      <c r="E9" s="281"/>
+      <c r="F9" s="281"/>
+      <c r="G9" s="281"/>
+      <c r="H9" s="281"/>
+      <c r="I9" s="281"/>
+      <c r="J9" s="281"/>
+      <c r="K9" s="281"/>
+      <c r="L9" s="281"/>
+      <c r="M9" s="281"/>
+      <c r="N9" s="281"/>
+      <c r="O9" s="282"/>
     </row>
     <row r="10" spans="1:17" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="273" t="s">
+      <c r="A10" s="291" t="s">
         <v>210</v>
       </c>
-      <c r="B10" s="274"/>
-      <c r="C10" s="274"/>
-      <c r="D10" s="274"/>
-      <c r="E10" s="274"/>
-      <c r="F10" s="274"/>
-      <c r="G10" s="274"/>
-      <c r="H10" s="274"/>
-      <c r="I10" s="274"/>
-      <c r="J10" s="274"/>
-      <c r="K10" s="274"/>
-      <c r="L10" s="274"/>
-      <c r="M10" s="274"/>
-      <c r="N10" s="274"/>
-      <c r="O10" s="275"/>
+      <c r="B10" s="292"/>
+      <c r="C10" s="292"/>
+      <c r="D10" s="292"/>
+      <c r="E10" s="292"/>
+      <c r="F10" s="292"/>
+      <c r="G10" s="292"/>
+      <c r="H10" s="292"/>
+      <c r="I10" s="292"/>
+      <c r="J10" s="292"/>
+      <c r="K10" s="292"/>
+      <c r="L10" s="292"/>
+      <c r="M10" s="292"/>
+      <c r="N10" s="292"/>
+      <c r="O10" s="293"/>
     </row>
     <row r="11" spans="1:17" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="276" t="s">
+      <c r="A11" s="294" t="s">
         <v>211</v>
       </c>
-      <c r="B11" s="277"/>
-      <c r="C11" s="277"/>
-      <c r="D11" s="277"/>
-      <c r="E11" s="277"/>
-      <c r="F11" s="277"/>
-      <c r="G11" s="277"/>
-      <c r="H11" s="277"/>
-      <c r="I11" s="277"/>
-      <c r="J11" s="277"/>
-      <c r="K11" s="277"/>
-      <c r="L11" s="277"/>
-      <c r="M11" s="277"/>
-      <c r="N11" s="277"/>
-      <c r="O11" s="278"/>
+      <c r="B11" s="295"/>
+      <c r="C11" s="295"/>
+      <c r="D11" s="295"/>
+      <c r="E11" s="295"/>
+      <c r="F11" s="295"/>
+      <c r="G11" s="295"/>
+      <c r="H11" s="295"/>
+      <c r="I11" s="295"/>
+      <c r="J11" s="295"/>
+      <c r="K11" s="295"/>
+      <c r="L11" s="295"/>
+      <c r="M11" s="295"/>
+      <c r="N11" s="295"/>
+      <c r="O11" s="296"/>
     </row>
     <row r="12" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="303" t="s">
+      <c r="A12" s="283" t="s">
         <v>157</v>
       </c>
-      <c r="B12" s="304"/>
-      <c r="C12" s="304"/>
-      <c r="D12" s="304"/>
-      <c r="E12" s="304"/>
-      <c r="F12" s="304"/>
-      <c r="G12" s="304"/>
-      <c r="H12" s="304"/>
-      <c r="I12" s="304"/>
-      <c r="J12" s="304"/>
-      <c r="K12" s="304"/>
-      <c r="L12" s="304"/>
-      <c r="M12" s="304"/>
-      <c r="N12" s="304"/>
-      <c r="O12" s="305"/>
+      <c r="B12" s="284"/>
+      <c r="C12" s="284"/>
+      <c r="D12" s="284"/>
+      <c r="E12" s="284"/>
+      <c r="F12" s="284"/>
+      <c r="G12" s="284"/>
+      <c r="H12" s="284"/>
+      <c r="I12" s="284"/>
+      <c r="J12" s="284"/>
+      <c r="K12" s="284"/>
+      <c r="L12" s="284"/>
+      <c r="M12" s="284"/>
+      <c r="N12" s="284"/>
+      <c r="O12" s="285"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="294" t="s">
+      <c r="A13" s="272" t="s">
         <v>127</v>
       </c>
-      <c r="B13" s="296" t="s">
+      <c r="B13" s="274" t="s">
         <v>128</v>
       </c>
-      <c r="C13" s="296" t="s">
+      <c r="C13" s="274" t="s">
         <v>129</v>
       </c>
-      <c r="D13" s="296" t="s">
+      <c r="D13" s="274" t="s">
         <v>130</v>
       </c>
-      <c r="E13" s="271" t="s">
+      <c r="E13" s="276" t="s">
         <v>131</v>
       </c>
-      <c r="F13" s="296" t="s">
+      <c r="F13" s="274" t="s">
         <v>132</v>
       </c>
-      <c r="G13" s="298" t="s">
+      <c r="G13" s="278" t="s">
         <v>133</v>
       </c>
-      <c r="H13" s="271" t="s">
+      <c r="H13" s="276" t="s">
         <v>134</v>
       </c>
-      <c r="I13" s="271" t="s">
+      <c r="I13" s="276" t="s">
         <v>126</v>
       </c>
-      <c r="J13" s="271" t="s">
+      <c r="J13" s="276" t="s">
         <v>125</v>
       </c>
-      <c r="K13" s="281" t="s">
+      <c r="K13" s="299" t="s">
         <v>217</v>
       </c>
-      <c r="L13" s="307" t="s">
+      <c r="L13" s="287" t="s">
         <v>173</v>
       </c>
-      <c r="M13" s="269" t="s">
+      <c r="M13" s="289" t="s">
         <v>179</v>
       </c>
       <c r="N13" s="138" t="s">
         <v>206</v>
       </c>
-      <c r="O13" s="279" t="s">
+      <c r="O13" s="297" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="295"/>
-      <c r="B14" s="297"/>
-      <c r="C14" s="297"/>
-      <c r="D14" s="297"/>
-      <c r="E14" s="272"/>
-      <c r="F14" s="297"/>
-      <c r="G14" s="299"/>
-      <c r="H14" s="272"/>
-      <c r="I14" s="272"/>
-      <c r="J14" s="272"/>
-      <c r="K14" s="282"/>
-      <c r="L14" s="308"/>
-      <c r="M14" s="270"/>
+      <c r="A14" s="273"/>
+      <c r="B14" s="275"/>
+      <c r="C14" s="275"/>
+      <c r="D14" s="275"/>
+      <c r="E14" s="277"/>
+      <c r="F14" s="275"/>
+      <c r="G14" s="279"/>
+      <c r="H14" s="277"/>
+      <c r="I14" s="277"/>
+      <c r="J14" s="277"/>
+      <c r="K14" s="300"/>
+      <c r="L14" s="288"/>
+      <c r="M14" s="290"/>
       <c r="N14" s="139" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 16/10</v>
       </c>
-      <c r="O14" s="280"/>
+      <c r="O14" s="298"/>
     </row>
     <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="124">
@@ -4723,7 +4833,7 @@
       <c r="E15" s="78">
         <v>301400.01</v>
       </c>
-      <c r="F15" s="315">
+      <c r="F15" s="79">
         <f>E15</f>
         <v>301400.01</v>
       </c>
@@ -4737,7 +4847,7 @@
       </c>
       <c r="I15" s="120">
         <f>J$2*D15/100</f>
-        <v>160218.04157199999</v>
+        <v>123300.00000000001</v>
       </c>
       <c r="J15" s="120">
         <f t="shared" ref="J15:J46" si="1">E$2*D15/100</f>
@@ -4745,17 +4855,17 @@
       </c>
       <c r="K15" s="120">
         <f>M$2*D15/100</f>
-        <v>79531.958428000013</v>
+        <v>140657.876162</v>
       </c>
       <c r="L15" s="120"/>
       <c r="M15" s="141"/>
       <c r="N15" s="81">
         <f>ROUND(SUM(G15:M15),0) + P15</f>
-        <v>301400.01</v>
+        <v>325608.01</v>
       </c>
       <c r="O15" s="134">
         <f t="shared" ref="O15:O35" si="2">ROUND(N15*3%,0) + N15</f>
-        <v>310442.01</v>
+        <v>335376.01</v>
       </c>
       <c r="P15" s="50">
         <v>0.01</v>
@@ -4786,7 +4896,7 @@
       </c>
       <c r="I16" s="192">
         <f t="shared" ref="I16:I46" si="4">J$2*D16/100</f>
-        <v>137998.02120799999</v>
+        <v>106200</v>
       </c>
       <c r="J16" s="192">
         <f t="shared" si="1"/>
@@ -4794,17 +4904,17 @@
       </c>
       <c r="K16" s="192">
         <f t="shared" ref="K16:K79" si="5">M$2*D16/100</f>
-        <v>68501.978792000009</v>
+        <v>121150.579468</v>
       </c>
       <c r="L16" s="192"/>
       <c r="M16" s="193"/>
       <c r="N16" s="194">
         <f>ROUND(SUM(G16:M16),0) + P16</f>
-        <v>4968260.0199999996</v>
+        <v>4989111.0199999996</v>
       </c>
       <c r="O16" s="195">
         <f t="shared" si="2"/>
-        <v>5117308.0199999996</v>
+        <v>5138784.0199999996</v>
       </c>
       <c r="P16" s="50">
         <f>P15+0.01</f>
@@ -4828,7 +4938,7 @@
       <c r="E17" s="78">
         <v>162800.03</v>
       </c>
-      <c r="F17" s="315">
+      <c r="F17" s="79">
         <f>162000+800.03</f>
         <v>162800.03</v>
       </c>
@@ -4842,7 +4952,7 @@
       </c>
       <c r="I17" s="120">
         <f t="shared" si="4"/>
-        <v>86541.131943999993</v>
+        <v>66600</v>
       </c>
       <c r="J17" s="120">
         <f t="shared" si="1"/>
@@ -4850,17 +4960,17 @@
       </c>
       <c r="K17" s="120">
         <f t="shared" si="5"/>
-        <v>42958.868056000007</v>
+        <v>75975.787123999995</v>
       </c>
       <c r="L17" s="120"/>
       <c r="M17" s="141"/>
       <c r="N17" s="81">
         <f t="shared" ref="N17:N80" si="6">ROUND(SUM(G17:M17),0) + P17</f>
-        <v>162800.03</v>
+        <v>175876.03</v>
       </c>
       <c r="O17" s="134">
         <f t="shared" si="2"/>
-        <v>167684.03</v>
+        <v>181152.03</v>
       </c>
       <c r="P17" s="50">
         <f t="shared" ref="P17:P32" si="7">P16+0.01</f>
@@ -4881,7 +4991,7 @@
       <c r="E18" s="79">
         <v>323400.03999999998</v>
       </c>
-      <c r="F18" s="315">
+      <c r="F18" s="79">
         <f>E18</f>
         <v>323400.03999999998</v>
       </c>
@@ -4895,7 +5005,7 @@
       </c>
       <c r="I18" s="121">
         <f t="shared" si="4"/>
-        <v>171912.78913199998</v>
+        <v>132300</v>
       </c>
       <c r="J18" s="121">
         <f t="shared" si="1"/>
@@ -4903,17 +5013,17 @@
       </c>
       <c r="K18" s="120">
         <f t="shared" si="5"/>
-        <v>85337.210867999995</v>
+        <v>150924.87442199999</v>
       </c>
       <c r="L18" s="121"/>
       <c r="M18" s="142"/>
       <c r="N18" s="81">
         <f t="shared" si="6"/>
-        <v>323400.03999999998</v>
+        <v>349375.04</v>
       </c>
       <c r="O18" s="135">
         <f t="shared" si="2"/>
-        <v>333102.03999999998</v>
+        <v>359856.04</v>
       </c>
       <c r="P18" s="50">
         <f t="shared" si="7"/>
@@ -4934,7 +5044,7 @@
       <c r="E19" s="79">
         <v>239520.05</v>
       </c>
-      <c r="F19" s="315">
+      <c r="F19" s="79">
         <v>246706.05</v>
       </c>
       <c r="G19" s="80">
@@ -4947,7 +5057,7 @@
       </c>
       <c r="I19" s="120">
         <f t="shared" si="4"/>
-        <v>130981.172672</v>
+        <v>100800.00000000001</v>
       </c>
       <c r="J19" s="120">
         <f t="shared" si="1"/>
@@ -4955,17 +5065,17 @@
       </c>
       <c r="K19" s="120">
         <f t="shared" si="5"/>
-        <v>65018.827328000014</v>
+        <v>114990.380512</v>
       </c>
       <c r="L19" s="120"/>
       <c r="M19" s="141"/>
       <c r="N19" s="81">
         <f t="shared" si="6"/>
-        <v>239214.05</v>
+        <v>259004.05</v>
       </c>
       <c r="O19" s="134">
         <f t="shared" si="2"/>
-        <v>246390.05</v>
+        <v>266774.05</v>
       </c>
       <c r="P19" s="50">
         <f t="shared" si="7"/>
@@ -4986,7 +5096,7 @@
       <c r="E20" s="78">
         <v>296082.06</v>
       </c>
-      <c r="F20" s="315">
+      <c r="F20" s="79">
         <v>307000</v>
       </c>
       <c r="G20" s="80">
@@ -4999,7 +5109,7 @@
       </c>
       <c r="I20" s="120">
         <f t="shared" si="4"/>
-        <v>157879.09206</v>
+        <v>121500</v>
       </c>
       <c r="J20" s="120">
         <f t="shared" si="1"/>
@@ -5007,17 +5117,17 @@
       </c>
       <c r="K20" s="120">
         <f t="shared" si="5"/>
-        <v>78370.907940000005</v>
+        <v>138604.47651000001</v>
       </c>
       <c r="L20" s="120"/>
       <c r="M20" s="141"/>
       <c r="N20" s="81">
         <f t="shared" si="6"/>
-        <v>286082.06</v>
+        <v>309937.06</v>
       </c>
       <c r="O20" s="134">
         <f t="shared" si="2"/>
-        <v>294664.06</v>
+        <v>319235.06</v>
       </c>
       <c r="P20" s="50">
         <f t="shared" si="7"/>
@@ -5038,7 +5148,7 @@
       <c r="E21" s="78">
         <v>246400.07</v>
       </c>
-      <c r="F21" s="315">
+      <c r="F21" s="79">
         <f>E21</f>
         <v>246400.07</v>
       </c>
@@ -5052,7 +5162,7 @@
       </c>
       <c r="I21" s="120">
         <f t="shared" si="4"/>
-        <v>130981.172672</v>
+        <v>100800.00000000001</v>
       </c>
       <c r="J21" s="120">
         <f t="shared" si="1"/>
@@ -5060,17 +5170,17 @@
       </c>
       <c r="K21" s="120">
         <f t="shared" si="5"/>
-        <v>65018.827328000014</v>
+        <v>114990.380512</v>
       </c>
       <c r="L21" s="120"/>
       <c r="M21" s="141"/>
       <c r="N21" s="81">
         <f t="shared" si="6"/>
-        <v>246400.07</v>
+        <v>266190.07</v>
       </c>
       <c r="O21" s="134">
         <f t="shared" si="2"/>
-        <v>253792.07</v>
+        <v>274176.07</v>
       </c>
       <c r="P21" s="50">
         <f t="shared" si="7"/>
@@ -5091,7 +5201,7 @@
       <c r="E22" s="78">
         <v>180400.08</v>
       </c>
-      <c r="F22" s="315">
+      <c r="F22" s="79">
         <f>E22</f>
         <v>180400.08</v>
       </c>
@@ -5105,7 +5215,7 @@
       </c>
       <c r="I22" s="120">
         <f t="shared" si="4"/>
-        <v>95896.929991999976</v>
+        <v>73800</v>
       </c>
       <c r="J22" s="120">
         <f t="shared" si="1"/>
@@ -5113,17 +5223,17 @@
       </c>
       <c r="K22" s="120">
         <f t="shared" si="5"/>
-        <v>47603.070008000002</v>
+        <v>84189.385731999981</v>
       </c>
       <c r="L22" s="120"/>
       <c r="M22" s="141"/>
       <c r="N22" s="81">
         <f t="shared" si="6"/>
-        <v>180400.08</v>
+        <v>194889.08</v>
       </c>
       <c r="O22" s="134">
         <f t="shared" si="2"/>
-        <v>185812.08</v>
+        <v>200736.08</v>
       </c>
       <c r="P22" s="50">
         <f t="shared" si="7"/>
@@ -5144,7 +5254,7 @@
       <c r="E23" s="78">
         <v>175363.09</v>
       </c>
-      <c r="F23" s="315">
+      <c r="F23" s="79">
         <v>180624.09</v>
       </c>
       <c r="G23" s="80">
@@ -5157,7 +5267,7 @@
       </c>
       <c r="I23" s="120">
         <f t="shared" si="4"/>
-        <v>95896.929991999976</v>
+        <v>73800</v>
       </c>
       <c r="J23" s="120">
         <f t="shared" si="1"/>
@@ -5165,17 +5275,17 @@
       </c>
       <c r="K23" s="120">
         <f t="shared" si="5"/>
-        <v>47603.070008000002</v>
+        <v>84189.385731999981</v>
       </c>
       <c r="L23" s="120"/>
       <c r="M23" s="141"/>
       <c r="N23" s="81">
         <f t="shared" si="6"/>
-        <v>175139.09</v>
+        <v>189628.09</v>
       </c>
       <c r="O23" s="134">
         <f t="shared" si="2"/>
-        <v>180393.09</v>
+        <v>195317.09</v>
       </c>
       <c r="P23" s="50">
         <f t="shared" si="7"/>
@@ -5196,7 +5306,7 @@
       <c r="E24" s="78">
         <v>294800.09999999998</v>
       </c>
-      <c r="F24" s="315">
+      <c r="F24" s="79">
         <f>E24</f>
         <v>294800.09999999998</v>
       </c>
@@ -5210,7 +5320,7 @@
       </c>
       <c r="I24" s="120">
         <f t="shared" si="4"/>
-        <v>156709.61730399998</v>
+        <v>120600</v>
       </c>
       <c r="J24" s="120">
         <f t="shared" si="1"/>
@@ -5218,17 +5328,17 @@
       </c>
       <c r="K24" s="120">
         <f t="shared" si="5"/>
-        <v>77790.382696000015</v>
+        <v>137577.77668400001</v>
       </c>
       <c r="L24" s="120"/>
       <c r="M24" s="141"/>
       <c r="N24" s="81">
         <f t="shared" si="6"/>
-        <v>294800.09999999998</v>
+        <v>318478.09999999998</v>
       </c>
       <c r="O24" s="134">
         <f t="shared" si="2"/>
-        <v>303644.09999999998</v>
+        <v>328032.09999999998</v>
       </c>
       <c r="P24" s="50">
         <f t="shared" si="7"/>
@@ -5249,7 +5359,7 @@
       <c r="E25" s="78">
         <v>246400.11</v>
       </c>
-      <c r="F25" s="315">
+      <c r="F25" s="79">
         <f>E25</f>
         <v>246400.11</v>
       </c>
@@ -5263,7 +5373,7 @@
       </c>
       <c r="I25" s="120">
         <f t="shared" si="4"/>
-        <v>130981.172672</v>
+        <v>100800.00000000001</v>
       </c>
       <c r="J25" s="120">
         <f t="shared" si="1"/>
@@ -5271,17 +5381,17 @@
       </c>
       <c r="K25" s="120">
         <f t="shared" si="5"/>
-        <v>65018.827328000014</v>
+        <v>114990.380512</v>
       </c>
       <c r="L25" s="120"/>
       <c r="M25" s="141"/>
       <c r="N25" s="81">
         <f t="shared" si="6"/>
-        <v>246400.11</v>
+        <v>266190.11</v>
       </c>
       <c r="O25" s="134">
         <f t="shared" si="2"/>
-        <v>253792.11</v>
+        <v>274176.11</v>
       </c>
       <c r="P25" s="50">
         <f t="shared" si="7"/>
@@ -5315,7 +5425,7 @@
       </c>
       <c r="I26" s="192">
         <f t="shared" si="4"/>
-        <v>136828.54645199998</v>
+        <v>105300</v>
       </c>
       <c r="J26" s="192">
         <f t="shared" si="1"/>
@@ -5323,17 +5433,17 @@
       </c>
       <c r="K26" s="192">
         <f t="shared" si="5"/>
-        <v>67921.453548000005</v>
+        <v>120123.879642</v>
       </c>
       <c r="L26" s="192"/>
       <c r="M26" s="193"/>
       <c r="N26" s="194">
         <f t="shared" si="6"/>
-        <v>6049136.1200000001</v>
+        <v>6069810.1200000001</v>
       </c>
       <c r="O26" s="195">
         <f t="shared" si="2"/>
-        <v>6230610.1200000001</v>
+        <v>6251904.1200000001</v>
       </c>
       <c r="P26" s="50">
         <f t="shared" si="7"/>
@@ -5354,7 +5464,7 @@
       <c r="E27" s="78">
         <v>297000.13</v>
       </c>
-      <c r="F27" s="315">
+      <c r="F27" s="79">
         <f>E27</f>
         <v>297000.13</v>
       </c>
@@ -5368,7 +5478,7 @@
       </c>
       <c r="I27" s="120">
         <f t="shared" si="4"/>
-        <v>157879.09206</v>
+        <v>121500</v>
       </c>
       <c r="J27" s="120">
         <f t="shared" si="1"/>
@@ -5376,17 +5486,17 @@
       </c>
       <c r="K27" s="120">
         <f t="shared" si="5"/>
-        <v>78370.907940000005</v>
+        <v>138604.47651000001</v>
       </c>
       <c r="L27" s="120"/>
       <c r="M27" s="141"/>
       <c r="N27" s="81">
         <f t="shared" si="6"/>
-        <v>297000.13</v>
+        <v>320854.13</v>
       </c>
       <c r="O27" s="134">
         <f t="shared" si="2"/>
-        <v>305910.13</v>
+        <v>330480.13</v>
       </c>
       <c r="P27" s="50">
         <f t="shared" si="7"/>
@@ -5418,7 +5528,7 @@
       </c>
       <c r="I28" s="120">
         <f t="shared" si="4"/>
-        <v>130981.172672</v>
+        <v>100800.00000000001</v>
       </c>
       <c r="J28" s="120">
         <f t="shared" si="1"/>
@@ -5426,17 +5536,17 @@
       </c>
       <c r="K28" s="120">
         <f t="shared" si="5"/>
-        <v>65018.827328000014</v>
+        <v>114990.380512</v>
       </c>
       <c r="L28" s="120"/>
       <c r="M28" s="141"/>
       <c r="N28" s="81">
         <f t="shared" si="6"/>
-        <v>1395825.14</v>
+        <v>1415615.14</v>
       </c>
       <c r="O28" s="134">
         <f t="shared" si="2"/>
-        <v>1437700.14</v>
+        <v>1458083.14</v>
       </c>
       <c r="P28" s="50">
         <f t="shared" si="7"/>
@@ -5457,7 +5567,7 @@
       <c r="E29" s="79">
         <v>180400.15</v>
       </c>
-      <c r="F29" s="315">
+      <c r="F29" s="79">
         <f>E29</f>
         <v>180400.15</v>
       </c>
@@ -5471,7 +5581,7 @@
       </c>
       <c r="I29" s="120">
         <f t="shared" si="4"/>
-        <v>95896.929991999976</v>
+        <v>73800</v>
       </c>
       <c r="J29" s="120">
         <f t="shared" si="1"/>
@@ -5479,17 +5589,17 @@
       </c>
       <c r="K29" s="120">
         <f t="shared" si="5"/>
-        <v>47603.070008000002</v>
+        <v>84189.385731999981</v>
       </c>
       <c r="L29" s="120"/>
       <c r="M29" s="141"/>
       <c r="N29" s="81">
         <f t="shared" si="6"/>
-        <v>180400.15</v>
+        <v>194889.15</v>
       </c>
       <c r="O29" s="134">
         <f t="shared" si="2"/>
-        <v>185812.15</v>
+        <v>200736.15</v>
       </c>
       <c r="P29" s="50">
         <f t="shared" si="7"/>
@@ -5510,7 +5620,7 @@
       <c r="E30" s="78">
         <v>180400.16</v>
       </c>
-      <c r="F30" s="315">
+      <c r="F30" s="79">
         <f>E30</f>
         <v>180400.16</v>
       </c>
@@ -5524,7 +5634,7 @@
       </c>
       <c r="I30" s="120">
         <f t="shared" si="4"/>
-        <v>95896.929991999976</v>
+        <v>73800</v>
       </c>
       <c r="J30" s="120">
         <f t="shared" si="1"/>
@@ -5532,17 +5642,17 @@
       </c>
       <c r="K30" s="120">
         <f t="shared" si="5"/>
-        <v>47603.070008000002</v>
+        <v>84189.385731999981</v>
       </c>
       <c r="L30" s="120"/>
       <c r="M30" s="141"/>
       <c r="N30" s="81">
         <f t="shared" si="6"/>
-        <v>180400.16</v>
+        <v>194889.16</v>
       </c>
       <c r="O30" s="134">
         <f t="shared" si="2"/>
-        <v>185812.16</v>
+        <v>200736.16</v>
       </c>
       <c r="P30" s="50">
         <f t="shared" si="7"/>
@@ -5574,7 +5684,7 @@
       </c>
       <c r="I31" s="120">
         <f t="shared" si="4"/>
-        <v>156709.61730399998</v>
+        <v>120600</v>
       </c>
       <c r="J31" s="120">
         <f t="shared" si="1"/>
@@ -5582,17 +5692,17 @@
       </c>
       <c r="K31" s="120">
         <f t="shared" si="5"/>
-        <v>77790.382696000015</v>
+        <v>137577.77668400001</v>
       </c>
       <c r="L31" s="120"/>
       <c r="M31" s="141"/>
       <c r="N31" s="81">
         <f t="shared" si="6"/>
-        <v>691831.17</v>
+        <v>715509.17</v>
       </c>
       <c r="O31" s="134">
         <f t="shared" si="2"/>
-        <v>712586.17</v>
+        <v>736974.17</v>
       </c>
       <c r="P31" s="50">
         <f t="shared" si="7"/>
@@ -5613,7 +5723,7 @@
       <c r="E32" s="79">
         <v>246400.18</v>
       </c>
-      <c r="F32" s="315">
+      <c r="F32" s="79">
         <f>E32</f>
         <v>246400.18</v>
       </c>
@@ -5627,7 +5737,7 @@
       </c>
       <c r="I32" s="121">
         <f t="shared" si="4"/>
-        <v>130981.172672</v>
+        <v>100800.00000000001</v>
       </c>
       <c r="J32" s="121">
         <f t="shared" si="1"/>
@@ -5635,17 +5745,17 @@
       </c>
       <c r="K32" s="120">
         <f t="shared" si="5"/>
-        <v>65018.827328000014</v>
+        <v>114990.380512</v>
       </c>
       <c r="L32" s="121"/>
       <c r="M32" s="142"/>
       <c r="N32" s="81">
         <f t="shared" si="6"/>
-        <v>246400.18</v>
+        <v>266190.18</v>
       </c>
       <c r="O32" s="135">
         <f t="shared" si="2"/>
-        <v>253792.18</v>
+        <v>274176.18</v>
       </c>
       <c r="P32" s="50">
         <f t="shared" si="7"/>
@@ -5666,7 +5776,7 @@
       <c r="E33" s="78">
         <v>223620.19</v>
       </c>
-      <c r="F33" s="315">
+      <c r="F33" s="79">
         <f>E33</f>
         <v>223620.19</v>
       </c>
@@ -5680,7 +5790,7 @@
       </c>
       <c r="I33" s="120">
         <f t="shared" si="4"/>
-        <v>136828.54645199998</v>
+        <v>105300</v>
       </c>
       <c r="J33" s="120">
         <f t="shared" si="1"/>
@@ -5688,17 +5798,17 @@
       </c>
       <c r="K33" s="120">
         <f t="shared" si="5"/>
-        <v>67921.453548000005</v>
+        <v>120123.879642</v>
       </c>
       <c r="L33" s="120"/>
       <c r="M33" s="141"/>
       <c r="N33" s="81">
         <f t="shared" si="6"/>
-        <v>257400.19</v>
+        <v>278074.19</v>
       </c>
       <c r="O33" s="134">
         <f t="shared" si="2"/>
-        <v>265122.19</v>
+        <v>286416.19</v>
       </c>
       <c r="P33" s="50">
         <f>P32+0.01</f>
@@ -5722,7 +5832,7 @@
       <c r="E34" s="117">
         <v>1250638.2</v>
       </c>
-      <c r="F34" s="317">
+      <c r="F34" s="117">
         <v>366300</v>
       </c>
       <c r="G34" s="118">
@@ -5732,7 +5842,7 @@
       <c r="H34" s="118"/>
       <c r="I34" s="123">
         <f t="shared" si="4"/>
-        <v>157879.09206</v>
+        <v>121500</v>
       </c>
       <c r="J34" s="123">
         <f t="shared" si="1"/>
@@ -5740,7 +5850,7 @@
       </c>
       <c r="K34" s="123">
         <f t="shared" si="5"/>
-        <v>78370.907940000005</v>
+        <v>138604.47651000001</v>
       </c>
       <c r="L34" s="123"/>
       <c r="M34" s="143">
@@ -5748,18 +5858,18 @@
       </c>
       <c r="N34" s="119">
         <f t="shared" si="6"/>
-        <v>1304638.2</v>
+        <v>1328493.2</v>
       </c>
       <c r="O34" s="136">
         <f t="shared" si="2"/>
-        <v>1343777.2</v>
+        <v>1368348.2</v>
       </c>
       <c r="P34" s="50">
         <f t="shared" ref="P34:P97" si="8">P33+0.01</f>
         <v>0.20000000000000004</v>
       </c>
       <c r="Q34" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -5776,7 +5886,7 @@
       <c r="E35" s="79">
         <v>246400.21</v>
       </c>
-      <c r="F35" s="315">
+      <c r="F35" s="79">
         <f>E35</f>
         <v>246400.21</v>
       </c>
@@ -5790,7 +5900,7 @@
       </c>
       <c r="I35" s="121">
         <f t="shared" si="4"/>
-        <v>130981.172672</v>
+        <v>100800.00000000001</v>
       </c>
       <c r="J35" s="121">
         <f t="shared" si="1"/>
@@ -5798,17 +5908,17 @@
       </c>
       <c r="K35" s="120">
         <f t="shared" si="5"/>
-        <v>65018.827328000014</v>
+        <v>114990.380512</v>
       </c>
       <c r="L35" s="121"/>
       <c r="M35" s="142"/>
       <c r="N35" s="81">
         <f t="shared" si="6"/>
-        <v>246400.21</v>
+        <v>266190.21000000002</v>
       </c>
       <c r="O35" s="135">
         <f t="shared" si="2"/>
-        <v>253792.21</v>
+        <v>274176.21000000002</v>
       </c>
       <c r="P35" s="50">
         <f t="shared" si="8"/>
@@ -5830,7 +5940,7 @@
       <c r="E36" s="78">
         <v>180400.22</v>
       </c>
-      <c r="F36" s="315">
+      <c r="F36" s="79">
         <f>E36</f>
         <v>180400.22</v>
       </c>
@@ -5844,7 +5954,7 @@
       </c>
       <c r="I36" s="120">
         <f t="shared" si="4"/>
-        <v>95896.929991999976</v>
+        <v>73800</v>
       </c>
       <c r="J36" s="120">
         <f t="shared" si="1"/>
@@ -5852,17 +5962,17 @@
       </c>
       <c r="K36" s="120">
         <f t="shared" si="5"/>
-        <v>47603.070008000002</v>
+        <v>84189.385731999981</v>
       </c>
       <c r="L36" s="120"/>
       <c r="M36" s="141"/>
       <c r="N36" s="81">
         <f t="shared" si="6"/>
-        <v>180400.22</v>
+        <v>194889.22</v>
       </c>
       <c r="O36" s="134">
         <f t="shared" ref="O36:O99" si="9">ROUND(N36*3%,0) + N36</f>
-        <v>185812.22</v>
+        <v>200736.22</v>
       </c>
       <c r="P36" s="50">
         <f t="shared" si="8"/>
@@ -5884,7 +5994,7 @@
       <c r="E37" s="78">
         <v>180400.23</v>
       </c>
-      <c r="F37" s="315">
+      <c r="F37" s="79">
         <f>E37</f>
         <v>180400.23</v>
       </c>
@@ -5898,7 +6008,7 @@
       </c>
       <c r="I37" s="120">
         <f t="shared" si="4"/>
-        <v>95896.929991999976</v>
+        <v>73800</v>
       </c>
       <c r="J37" s="120">
         <f t="shared" si="1"/>
@@ -5906,17 +6016,17 @@
       </c>
       <c r="K37" s="120">
         <f t="shared" si="5"/>
-        <v>47603.070008000002</v>
+        <v>84189.385731999981</v>
       </c>
       <c r="L37" s="120"/>
       <c r="M37" s="141"/>
       <c r="N37" s="81">
         <f t="shared" si="6"/>
-        <v>180400.23</v>
+        <v>194889.23</v>
       </c>
       <c r="O37" s="134">
         <f t="shared" si="9"/>
-        <v>185812.23</v>
+        <v>200736.23</v>
       </c>
       <c r="P37" s="50">
         <f t="shared" si="8"/>
@@ -5938,7 +6048,7 @@
       <c r="E38" s="78">
         <v>294800.24</v>
       </c>
-      <c r="F38" s="315">
+      <c r="F38" s="79">
         <f>E38</f>
         <v>294800.24</v>
       </c>
@@ -5952,7 +6062,7 @@
       </c>
       <c r="I38" s="120">
         <f t="shared" si="4"/>
-        <v>156709.61730399998</v>
+        <v>120600</v>
       </c>
       <c r="J38" s="120">
         <f t="shared" si="1"/>
@@ -5960,17 +6070,17 @@
       </c>
       <c r="K38" s="120">
         <f t="shared" si="5"/>
-        <v>77790.382696000015</v>
+        <v>137577.77668400001</v>
       </c>
       <c r="L38" s="120"/>
       <c r="M38" s="141"/>
       <c r="N38" s="81">
         <f t="shared" si="6"/>
-        <v>294800.24</v>
+        <v>318478.24</v>
       </c>
       <c r="O38" s="134">
         <f t="shared" si="9"/>
-        <v>303644.24</v>
+        <v>328032.24</v>
       </c>
       <c r="P38" s="50">
         <f t="shared" si="8"/>
@@ -6003,7 +6113,7 @@
       </c>
       <c r="I39" s="120">
         <f t="shared" si="4"/>
-        <v>130981.172672</v>
+        <v>100800.00000000001</v>
       </c>
       <c r="J39" s="120">
         <f t="shared" si="1"/>
@@ -6011,17 +6121,17 @@
       </c>
       <c r="K39" s="120">
         <f t="shared" si="5"/>
-        <v>65018.827328000014</v>
+        <v>114990.380512</v>
       </c>
       <c r="L39" s="120"/>
       <c r="M39" s="141"/>
       <c r="N39" s="81">
         <f t="shared" si="6"/>
-        <v>749504.25</v>
+        <v>769294.25</v>
       </c>
       <c r="O39" s="134">
         <f t="shared" si="9"/>
-        <v>771989.25</v>
+        <v>792373.25</v>
       </c>
       <c r="P39" s="50">
         <f t="shared" si="8"/>
@@ -6041,20 +6151,23 @@
         <v>1.17</v>
       </c>
       <c r="E40" s="78">
-        <v>257400.26</v>
-      </c>
-      <c r="F40" s="79"/>
+        <v>265122.65999999997</v>
+      </c>
+      <c r="F40" s="79">
+        <f>E40</f>
+        <v>265122.65999999997</v>
+      </c>
       <c r="G40" s="80">
         <f t="shared" si="0"/>
-        <v>257400.26</v>
+        <v>0</v>
       </c>
       <c r="H40" s="80">
         <f t="shared" si="3"/>
-        <v>7722.0078000000003</v>
+        <v>0</v>
       </c>
       <c r="I40" s="120">
         <f t="shared" si="4"/>
-        <v>136828.54645199998</v>
+        <v>105300</v>
       </c>
       <c r="J40" s="120">
         <f t="shared" si="1"/>
@@ -6062,17 +6175,17 @@
       </c>
       <c r="K40" s="120">
         <f t="shared" si="5"/>
-        <v>67921.453548000005</v>
+        <v>120123.879642</v>
       </c>
       <c r="L40" s="120"/>
       <c r="M40" s="141"/>
       <c r="N40" s="81">
         <f t="shared" si="6"/>
-        <v>522522.26</v>
+        <v>278074.26</v>
       </c>
       <c r="O40" s="134">
         <f t="shared" si="9"/>
-        <v>538198.26</v>
+        <v>286416.26</v>
       </c>
       <c r="P40" s="50">
         <f t="shared" si="8"/>
@@ -6094,7 +6207,7 @@
       <c r="E41" s="78">
         <v>297000.27</v>
       </c>
-      <c r="F41" s="315">
+      <c r="F41" s="79">
         <f t="shared" ref="F41" si="11">E41</f>
         <v>297000.27</v>
       </c>
@@ -6108,7 +6221,7 @@
       </c>
       <c r="I41" s="120">
         <f t="shared" si="4"/>
-        <v>157879.09206</v>
+        <v>121500</v>
       </c>
       <c r="J41" s="120">
         <f t="shared" si="1"/>
@@ -6116,17 +6229,17 @@
       </c>
       <c r="K41" s="120">
         <f t="shared" si="5"/>
-        <v>78370.907940000005</v>
+        <v>138604.47651000001</v>
       </c>
       <c r="L41" s="120"/>
       <c r="M41" s="141"/>
       <c r="N41" s="81">
         <f t="shared" si="6"/>
-        <v>297000.27</v>
+        <v>320854.27</v>
       </c>
       <c r="O41" s="134">
         <f t="shared" si="9"/>
-        <v>305910.27</v>
+        <v>330480.27</v>
       </c>
       <c r="P41" s="50">
         <f t="shared" si="8"/>
@@ -6148,7 +6261,7 @@
       <c r="E42" s="78">
         <v>791602.28</v>
       </c>
-      <c r="F42" s="315">
+      <c r="F42" s="79">
         <f>791603</f>
         <v>791603</v>
       </c>
@@ -6162,7 +6275,7 @@
       </c>
       <c r="I42" s="120">
         <f t="shared" si="4"/>
-        <v>130981.172672</v>
+        <v>100800.00000000001</v>
       </c>
       <c r="J42" s="120">
         <f t="shared" si="1"/>
@@ -6170,17 +6283,17 @@
       </c>
       <c r="K42" s="120">
         <f t="shared" si="5"/>
-        <v>65018.827328000014</v>
+        <v>114990.380512</v>
       </c>
       <c r="L42" s="120"/>
       <c r="M42" s="141"/>
       <c r="N42" s="81">
         <f t="shared" si="6"/>
-        <v>246399.28</v>
+        <v>266190.28000000003</v>
       </c>
       <c r="O42" s="134">
         <f t="shared" si="9"/>
-        <v>253791.28</v>
+        <v>274176.28000000003</v>
       </c>
       <c r="P42" s="50">
         <f t="shared" si="8"/>
@@ -6205,7 +6318,7 @@
       <c r="E43" s="79">
         <v>180400.29</v>
       </c>
-      <c r="F43" s="315">
+      <c r="F43" s="79">
         <f t="shared" ref="F43" si="12">E43</f>
         <v>180400.29</v>
       </c>
@@ -6219,7 +6332,7 @@
       </c>
       <c r="I43" s="121">
         <f t="shared" si="4"/>
-        <v>95896.929991999976</v>
+        <v>73800</v>
       </c>
       <c r="J43" s="121">
         <f t="shared" si="1"/>
@@ -6227,17 +6340,17 @@
       </c>
       <c r="K43" s="120">
         <f t="shared" si="5"/>
-        <v>47603.070008000002</v>
+        <v>84189.385731999981</v>
       </c>
       <c r="L43" s="121"/>
       <c r="M43" s="142"/>
       <c r="N43" s="81">
         <f t="shared" si="6"/>
-        <v>180400.29</v>
+        <v>194889.29</v>
       </c>
       <c r="O43" s="135">
         <f t="shared" si="9"/>
-        <v>185812.29</v>
+        <v>200736.29</v>
       </c>
       <c r="P43" s="50">
         <f t="shared" si="8"/>
@@ -6262,7 +6375,7 @@
       <c r="E44" s="79">
         <v>180400.3</v>
       </c>
-      <c r="F44" s="315">
+      <c r="F44" s="79">
         <f>E44</f>
         <v>180400.3</v>
       </c>
@@ -6276,7 +6389,7 @@
       </c>
       <c r="I44" s="121">
         <f t="shared" si="4"/>
-        <v>95896.929991999976</v>
+        <v>73800</v>
       </c>
       <c r="J44" s="121">
         <f t="shared" si="1"/>
@@ -6284,17 +6397,17 @@
       </c>
       <c r="K44" s="120">
         <f t="shared" si="5"/>
-        <v>47603.070008000002</v>
+        <v>84189.385731999981</v>
       </c>
       <c r="L44" s="121"/>
       <c r="M44" s="142"/>
       <c r="N44" s="107">
         <f t="shared" si="6"/>
-        <v>180400.3</v>
+        <v>194889.3</v>
       </c>
       <c r="O44" s="135">
         <f t="shared" si="9"/>
-        <v>185812.3</v>
+        <v>200736.3</v>
       </c>
       <c r="P44" s="50">
         <f t="shared" si="8"/>
@@ -6316,7 +6429,7 @@
       <c r="E45" s="78">
         <v>294800.31</v>
       </c>
-      <c r="F45" s="315">
+      <c r="F45" s="79">
         <f>E45</f>
         <v>294800.31</v>
       </c>
@@ -6330,7 +6443,7 @@
       </c>
       <c r="I45" s="120">
         <f t="shared" si="4"/>
-        <v>156709.61730399998</v>
+        <v>120600</v>
       </c>
       <c r="J45" s="120">
         <f t="shared" si="1"/>
@@ -6338,17 +6451,17 @@
       </c>
       <c r="K45" s="120">
         <f t="shared" si="5"/>
-        <v>77790.382696000015</v>
+        <v>137577.77668400001</v>
       </c>
       <c r="L45" s="120"/>
       <c r="M45" s="141"/>
       <c r="N45" s="81">
         <f t="shared" si="6"/>
-        <v>294800.31</v>
+        <v>318478.31</v>
       </c>
       <c r="O45" s="134">
         <f t="shared" si="9"/>
-        <v>303644.31</v>
+        <v>328032.31</v>
       </c>
       <c r="P45" s="50">
         <f t="shared" si="8"/>
@@ -6370,7 +6483,7 @@
       <c r="E46" s="78">
         <v>246400.32</v>
       </c>
-      <c r="F46" s="315">
+      <c r="F46" s="79">
         <f>46400.32+200000.32</f>
         <v>246400.64000000001</v>
       </c>
@@ -6384,7 +6497,7 @@
       </c>
       <c r="I46" s="120">
         <f t="shared" si="4"/>
-        <v>130981.172672</v>
+        <v>100800.00000000001</v>
       </c>
       <c r="J46" s="120">
         <f t="shared" si="1"/>
@@ -6392,17 +6505,17 @@
       </c>
       <c r="K46" s="120">
         <f t="shared" si="5"/>
-        <v>65018.827328000014</v>
+        <v>114990.380512</v>
       </c>
       <c r="L46" s="120"/>
       <c r="M46" s="141"/>
       <c r="N46" s="81">
         <f t="shared" si="6"/>
-        <v>246400.32</v>
+        <v>266190.32</v>
       </c>
       <c r="O46" s="134">
         <f t="shared" si="9"/>
-        <v>253792.32</v>
+        <v>274176.32</v>
       </c>
       <c r="P46" s="50">
         <f t="shared" si="8"/>
@@ -6424,7 +6537,7 @@
       <c r="E47" s="117">
         <v>427400.33</v>
       </c>
-      <c r="F47" s="317">
+      <c r="F47" s="117">
         <f>E47</f>
         <v>427400.33</v>
       </c>
@@ -6435,7 +6548,7 @@
       <c r="H47" s="118"/>
       <c r="I47" s="123">
         <f t="shared" ref="I47:I78" si="13">J$2*D47/100</f>
-        <v>136828.54645199998</v>
+        <v>105300</v>
       </c>
       <c r="J47" s="123">
         <f t="shared" ref="J47:J78" si="14">E$2*D47/100</f>
@@ -6443,26 +6556,28 @@
       </c>
       <c r="K47" s="123">
         <f t="shared" si="5"/>
-        <v>67921.453548000005</v>
-      </c>
-      <c r="L47" s="123"/>
+        <v>120123.879642</v>
+      </c>
+      <c r="L47" s="123">
+        <v>140000</v>
+      </c>
       <c r="M47" s="143">
         <v>170000</v>
       </c>
       <c r="N47" s="119">
         <f t="shared" si="6"/>
-        <v>427400.33</v>
+        <v>588074.32999999996</v>
       </c>
       <c r="O47" s="136">
         <f t="shared" si="9"/>
-        <v>440222.33</v>
+        <v>605716.32999999996</v>
       </c>
       <c r="P47" s="50">
         <f t="shared" si="8"/>
         <v>0.33000000000000013</v>
       </c>
       <c r="Q47" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
@@ -6480,7 +6595,7 @@
       <c r="E48" s="78">
         <v>297000.34000000003</v>
       </c>
-      <c r="F48" s="315">
+      <c r="F48" s="79">
         <f>E48</f>
         <v>297000.34000000003</v>
       </c>
@@ -6494,7 +6609,7 @@
       </c>
       <c r="I48" s="120">
         <f t="shared" si="13"/>
-        <v>157879.09206</v>
+        <v>121500</v>
       </c>
       <c r="J48" s="120">
         <f t="shared" si="14"/>
@@ -6502,17 +6617,17 @@
       </c>
       <c r="K48" s="120">
         <f t="shared" si="5"/>
-        <v>78370.907940000005</v>
+        <v>138604.47651000001</v>
       </c>
       <c r="L48" s="120"/>
       <c r="M48" s="141"/>
       <c r="N48" s="81">
         <f t="shared" si="6"/>
-        <v>297000.34000000003</v>
+        <v>320854.34000000003</v>
       </c>
       <c r="O48" s="134">
         <f t="shared" si="9"/>
-        <v>305910.34000000003</v>
+        <v>330480.34000000003</v>
       </c>
       <c r="P48" s="50">
         <f t="shared" si="8"/>
@@ -6534,7 +6649,7 @@
       <c r="E49" s="79">
         <v>246400.35</v>
       </c>
-      <c r="F49" s="315">
+      <c r="F49" s="79">
         <f>E49</f>
         <v>246400.35</v>
       </c>
@@ -6548,7 +6663,7 @@
       </c>
       <c r="I49" s="185">
         <f t="shared" si="13"/>
-        <v>130981.172672</v>
+        <v>100800.00000000001</v>
       </c>
       <c r="J49" s="185">
         <f t="shared" si="14"/>
@@ -6556,17 +6671,17 @@
       </c>
       <c r="K49" s="120">
         <f t="shared" si="5"/>
-        <v>65018.827328000014</v>
+        <v>114990.380512</v>
       </c>
       <c r="L49" s="185"/>
       <c r="M49" s="186"/>
       <c r="N49" s="107">
         <f t="shared" si="6"/>
-        <v>246400.35</v>
+        <v>266190.34999999998</v>
       </c>
       <c r="O49" s="135">
         <f t="shared" si="9"/>
-        <v>253792.35</v>
+        <v>274176.34999999998</v>
       </c>
       <c r="P49" s="50">
         <f t="shared" si="8"/>
@@ -6591,7 +6706,7 @@
       <c r="E50" s="78">
         <v>180400.36</v>
       </c>
-      <c r="F50" s="315">
+      <c r="F50" s="79">
         <f>E50</f>
         <v>180400.36</v>
       </c>
@@ -6605,7 +6720,7 @@
       </c>
       <c r="I50" s="120">
         <f t="shared" si="13"/>
-        <v>95896.929991999976</v>
+        <v>73800</v>
       </c>
       <c r="J50" s="120">
         <f t="shared" si="14"/>
@@ -6613,17 +6728,17 @@
       </c>
       <c r="K50" s="120">
         <f t="shared" si="5"/>
-        <v>47603.070008000002</v>
+        <v>84189.385731999981</v>
       </c>
       <c r="L50" s="120"/>
       <c r="M50" s="141"/>
       <c r="N50" s="81">
         <f t="shared" si="6"/>
-        <v>180400.36</v>
+        <v>194889.36</v>
       </c>
       <c r="O50" s="134">
         <f t="shared" si="9"/>
-        <v>185812.36</v>
+        <v>200736.36</v>
       </c>
       <c r="P50" s="50">
         <f t="shared" si="8"/>
@@ -6659,7 +6774,7 @@
       </c>
       <c r="I51" s="120">
         <f t="shared" si="13"/>
-        <v>95896.929991999976</v>
+        <v>73800</v>
       </c>
       <c r="J51" s="120">
         <f t="shared" si="14"/>
@@ -6667,17 +6782,17 @@
       </c>
       <c r="K51" s="120">
         <f t="shared" si="5"/>
-        <v>47603.070008000002</v>
+        <v>84189.385731999981</v>
       </c>
       <c r="L51" s="120"/>
       <c r="M51" s="141"/>
       <c r="N51" s="81">
         <f t="shared" si="6"/>
-        <v>379300.37</v>
+        <v>393789.37</v>
       </c>
       <c r="O51" s="134">
         <f t="shared" si="9"/>
-        <v>390679.37</v>
+        <v>405603.37</v>
       </c>
       <c r="P51" s="50">
         <f t="shared" si="8"/>
@@ -6703,18 +6818,18 @@
         <v>766200.38</v>
       </c>
       <c r="F52" s="117">
-        <v>0</v>
+        <v>484800</v>
       </c>
       <c r="G52" s="118">
         <f t="shared" si="0"/>
-        <v>766200.38</v>
+        <v>281400.38</v>
       </c>
       <c r="H52" s="118">
         <v>0</v>
       </c>
       <c r="I52" s="123">
         <f t="shared" si="13"/>
-        <v>156709.61730399998</v>
+        <v>120600</v>
       </c>
       <c r="J52" s="123">
         <f t="shared" si="14"/>
@@ -6722,7 +6837,7 @@
       </c>
       <c r="K52" s="123">
         <f t="shared" si="5"/>
-        <v>77790.382696000015</v>
+        <v>137577.77668400001</v>
       </c>
       <c r="L52" s="123"/>
       <c r="M52" s="143">
@@ -6730,18 +6845,18 @@
       </c>
       <c r="N52" s="119">
         <f t="shared" si="6"/>
-        <v>1251000.3799999999</v>
+        <v>789878.38</v>
       </c>
       <c r="O52" s="136">
         <f t="shared" si="9"/>
-        <v>1288530.3799999999</v>
+        <v>813574.38</v>
       </c>
       <c r="P52" s="50">
         <f t="shared" si="8"/>
         <v>0.38000000000000017</v>
       </c>
       <c r="Q52" t="s">
-        <v>225</v>
+        <v>289</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
@@ -6759,7 +6874,7 @@
       <c r="E53" s="78">
         <v>263704.39</v>
       </c>
-      <c r="F53" s="315">
+      <c r="F53" s="79">
         <f>E53</f>
         <v>263704.39</v>
       </c>
@@ -6773,7 +6888,7 @@
       </c>
       <c r="I53" s="120">
         <f t="shared" si="13"/>
-        <v>130981.172672</v>
+        <v>100800.00000000001</v>
       </c>
       <c r="J53" s="120">
         <f t="shared" si="14"/>
@@ -6781,17 +6896,17 @@
       </c>
       <c r="K53" s="120">
         <f t="shared" si="5"/>
-        <v>65018.827328000014</v>
+        <v>114990.380512</v>
       </c>
       <c r="L53" s="120"/>
       <c r="M53" s="141"/>
       <c r="N53" s="81">
         <f t="shared" si="6"/>
-        <v>246400.39</v>
+        <v>266190.39</v>
       </c>
       <c r="O53" s="134">
         <f t="shared" si="9"/>
-        <v>253792.39</v>
+        <v>274176.39</v>
       </c>
       <c r="P53" s="50">
         <f t="shared" si="8"/>
@@ -6824,7 +6939,7 @@
       </c>
       <c r="I54" s="120">
         <f t="shared" si="13"/>
-        <v>136828.54645199998</v>
+        <v>105300</v>
       </c>
       <c r="J54" s="120">
         <f t="shared" si="14"/>
@@ -6832,17 +6947,17 @@
       </c>
       <c r="K54" s="120">
         <f t="shared" si="5"/>
-        <v>67921.453548000005</v>
+        <v>120123.879642</v>
       </c>
       <c r="L54" s="120"/>
       <c r="M54" s="141"/>
       <c r="N54" s="81">
         <f t="shared" si="6"/>
-        <v>522522.4</v>
+        <v>543196.4</v>
       </c>
       <c r="O54" s="134">
         <f t="shared" si="9"/>
-        <v>538198.4</v>
+        <v>559492.4</v>
       </c>
       <c r="P54" s="50">
         <f t="shared" si="8"/>
@@ -6864,7 +6979,7 @@
       <c r="E55" s="78">
         <v>297000.40999999997</v>
       </c>
-      <c r="F55" s="315">
+      <c r="F55" s="79">
         <f>E55</f>
         <v>297000.40999999997</v>
       </c>
@@ -6878,7 +6993,7 @@
       </c>
       <c r="I55" s="120">
         <f t="shared" si="13"/>
-        <v>157879.09206</v>
+        <v>121500</v>
       </c>
       <c r="J55" s="120">
         <f t="shared" si="14"/>
@@ -6886,17 +7001,17 @@
       </c>
       <c r="K55" s="120">
         <f t="shared" si="5"/>
-        <v>78370.907940000005</v>
+        <v>138604.47651000001</v>
       </c>
       <c r="L55" s="120"/>
       <c r="M55" s="141"/>
       <c r="N55" s="81">
         <f t="shared" si="6"/>
-        <v>297000.40999999997</v>
+        <v>320854.40999999997</v>
       </c>
       <c r="O55" s="134">
         <f t="shared" si="9"/>
-        <v>305910.40999999997</v>
+        <v>330480.40999999997</v>
       </c>
       <c r="P55" s="50">
         <f t="shared" si="8"/>
@@ -6918,7 +7033,7 @@
       <c r="E56" s="117">
         <v>279400.42</v>
       </c>
-      <c r="F56" s="317">
+      <c r="F56" s="117">
         <f>E56</f>
         <v>279400.42</v>
       </c>
@@ -6932,7 +7047,7 @@
       </c>
       <c r="I56" s="123">
         <f t="shared" si="13"/>
-        <v>130981.172672</v>
+        <v>100800.00000000001</v>
       </c>
       <c r="J56" s="123">
         <f t="shared" si="14"/>
@@ -6940,7 +7055,7 @@
       </c>
       <c r="K56" s="123">
         <f t="shared" si="5"/>
-        <v>65018.827328000014</v>
+        <v>114990.380512</v>
       </c>
       <c r="L56" s="123"/>
       <c r="M56" s="143">
@@ -6948,18 +7063,18 @@
       </c>
       <c r="N56" s="119">
         <f t="shared" si="6"/>
-        <v>279400.42</v>
+        <v>299190.42</v>
       </c>
       <c r="O56" s="136">
         <f t="shared" si="9"/>
-        <v>287782.42</v>
+        <v>308166.42</v>
       </c>
       <c r="P56" s="50">
         <f t="shared" si="8"/>
         <v>0.42000000000000021</v>
       </c>
       <c r="Q56" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
@@ -6988,7 +7103,7 @@
       </c>
       <c r="I57" s="121">
         <f t="shared" si="13"/>
-        <v>95896.929991999976</v>
+        <v>73800</v>
       </c>
       <c r="J57" s="121">
         <f t="shared" si="14"/>
@@ -6996,7 +7111,7 @@
       </c>
       <c r="K57" s="121">
         <f t="shared" si="5"/>
-        <v>47603.070008000002</v>
+        <v>84189.385731999981</v>
       </c>
       <c r="L57" s="121"/>
       <c r="M57" s="142">
@@ -7004,11 +7119,11 @@
       </c>
       <c r="N57" s="107">
         <f>ROUND(SUM(G57:M57),0) + P57</f>
-        <v>366212.43</v>
+        <v>380702.43</v>
       </c>
       <c r="O57" s="135">
         <f t="shared" si="9"/>
-        <v>377198.43</v>
+        <v>392123.43</v>
       </c>
       <c r="P57" s="50">
         <f t="shared" si="8"/>
@@ -7033,7 +7148,7 @@
       <c r="E58" s="78">
         <v>139730.44</v>
       </c>
-      <c r="F58" s="315">
+      <c r="F58" s="79">
         <f>E58</f>
         <v>139730.44</v>
       </c>
@@ -7047,7 +7162,7 @@
       </c>
       <c r="I58" s="120">
         <f t="shared" si="13"/>
-        <v>95896.929991999976</v>
+        <v>73800</v>
       </c>
       <c r="J58" s="120">
         <f t="shared" si="14"/>
@@ -7055,17 +7170,17 @@
       </c>
       <c r="K58" s="120">
         <f t="shared" si="5"/>
-        <v>47603.070008000002</v>
+        <v>84189.385731999981</v>
       </c>
       <c r="L58" s="120"/>
       <c r="M58" s="141"/>
       <c r="N58" s="81">
         <f t="shared" si="6"/>
-        <v>180400.44</v>
+        <v>194889.44</v>
       </c>
       <c r="O58" s="134">
         <f t="shared" si="9"/>
-        <v>185812.44</v>
+        <v>200736.44</v>
       </c>
       <c r="P58" s="50">
         <f t="shared" si="8"/>
@@ -7090,7 +7205,7 @@
       <c r="E59" s="78">
         <v>294800.45</v>
       </c>
-      <c r="F59" s="315">
+      <c r="F59" s="79">
         <f>E59</f>
         <v>294800.45</v>
       </c>
@@ -7104,7 +7219,7 @@
       </c>
       <c r="I59" s="120">
         <f t="shared" si="13"/>
-        <v>156709.61730399998</v>
+        <v>120600</v>
       </c>
       <c r="J59" s="120">
         <f t="shared" si="14"/>
@@ -7112,17 +7227,17 @@
       </c>
       <c r="K59" s="120">
         <f t="shared" si="5"/>
-        <v>77790.382696000015</v>
+        <v>137577.77668400001</v>
       </c>
       <c r="L59" s="120"/>
       <c r="M59" s="141"/>
       <c r="N59" s="81">
         <f t="shared" si="6"/>
-        <v>294800.45</v>
+        <v>318478.45</v>
       </c>
       <c r="O59" s="134">
         <f t="shared" si="9"/>
-        <v>303644.45</v>
+        <v>328032.45</v>
       </c>
       <c r="P59" s="50">
         <f t="shared" si="8"/>
@@ -7144,7 +7259,7 @@
       <c r="E60" s="78">
         <v>270492.46000000002</v>
       </c>
-      <c r="F60" s="315">
+      <c r="F60" s="79">
         <v>250000</v>
       </c>
       <c r="G60" s="80">
@@ -7157,7 +7272,7 @@
       </c>
       <c r="I60" s="120">
         <f t="shared" si="13"/>
-        <v>130981.172672</v>
+        <v>100800.00000000001</v>
       </c>
       <c r="J60" s="120">
         <f t="shared" si="14"/>
@@ -7165,17 +7280,17 @@
       </c>
       <c r="K60" s="120">
         <f t="shared" si="5"/>
-        <v>65018.827328000014</v>
+        <v>114990.380512</v>
       </c>
       <c r="L60" s="120"/>
       <c r="M60" s="141"/>
       <c r="N60" s="81">
         <f t="shared" si="6"/>
-        <v>267507.46000000002</v>
+        <v>287298.46000000002</v>
       </c>
       <c r="O60" s="134">
         <f t="shared" si="9"/>
-        <v>275532.46000000002</v>
+        <v>295917.46000000002</v>
       </c>
       <c r="P60" s="50">
         <f t="shared" si="8"/>
@@ -7210,7 +7325,7 @@
       <c r="H61" s="118"/>
       <c r="I61" s="123">
         <f t="shared" si="13"/>
-        <v>136828.54645199998</v>
+        <v>105300</v>
       </c>
       <c r="J61" s="123">
         <f t="shared" si="14"/>
@@ -7218,7 +7333,7 @@
       </c>
       <c r="K61" s="123">
         <f t="shared" si="5"/>
-        <v>67921.453548000005</v>
+        <v>120123.879642</v>
       </c>
       <c r="L61" s="123"/>
       <c r="M61" s="143">
@@ -7226,11 +7341,11 @@
       </c>
       <c r="N61" s="119">
         <f t="shared" si="6"/>
-        <v>1900595.47</v>
+        <v>1921269.47</v>
       </c>
       <c r="O61" s="136">
         <f t="shared" si="9"/>
-        <v>1957613.47</v>
+        <v>1978907.47</v>
       </c>
       <c r="P61" s="50">
         <f t="shared" si="8"/>
@@ -7253,20 +7368,23 @@
         <v>1.35</v>
       </c>
       <c r="E62" s="79">
-        <v>297000.48</v>
-      </c>
-      <c r="F62" s="79"/>
+        <v>305910.48</v>
+      </c>
+      <c r="F62" s="79">
+        <f>E62</f>
+        <v>305910.48</v>
+      </c>
       <c r="G62" s="106">
         <f t="shared" si="0"/>
-        <v>297000.48</v>
+        <v>0</v>
       </c>
       <c r="H62" s="106">
         <f t="shared" si="3"/>
-        <v>8910.0143999999982</v>
+        <v>0</v>
       </c>
       <c r="I62" s="121">
         <f t="shared" si="13"/>
-        <v>157879.09206</v>
+        <v>121500</v>
       </c>
       <c r="J62" s="121">
         <f t="shared" si="14"/>
@@ -7274,17 +7392,17 @@
       </c>
       <c r="K62" s="121">
         <f t="shared" si="5"/>
-        <v>78370.907940000005</v>
+        <v>138604.47651000001</v>
       </c>
       <c r="L62" s="121"/>
       <c r="M62" s="142"/>
       <c r="N62" s="107">
         <f t="shared" si="6"/>
-        <v>602910.48</v>
+        <v>320854.48</v>
       </c>
       <c r="O62" s="135">
         <f t="shared" si="9"/>
-        <v>620997.48</v>
+        <v>330480.48</v>
       </c>
       <c r="P62" s="50">
         <f t="shared" si="8"/>
@@ -7309,7 +7427,7 @@
       <c r="E63" s="78">
         <v>246400.49</v>
       </c>
-      <c r="F63" s="315">
+      <c r="F63" s="79">
         <f>E63</f>
         <v>246400.49</v>
       </c>
@@ -7323,7 +7441,7 @@
       </c>
       <c r="I63" s="120">
         <f t="shared" si="13"/>
-        <v>130981.172672</v>
+        <v>100800.00000000001</v>
       </c>
       <c r="J63" s="120">
         <f t="shared" si="14"/>
@@ -7331,17 +7449,17 @@
       </c>
       <c r="K63" s="120">
         <f t="shared" si="5"/>
-        <v>65018.827328000014</v>
+        <v>114990.380512</v>
       </c>
       <c r="L63" s="120"/>
       <c r="M63" s="141"/>
       <c r="N63" s="81">
         <f t="shared" si="6"/>
-        <v>246400.49</v>
+        <v>266190.49</v>
       </c>
       <c r="O63" s="134">
         <f t="shared" si="9"/>
-        <v>253792.49</v>
+        <v>274176.49</v>
       </c>
       <c r="P63" s="50">
         <f t="shared" si="8"/>
@@ -7374,7 +7492,7 @@
       </c>
       <c r="I64" s="120">
         <f t="shared" si="13"/>
-        <v>95896.929991999976</v>
+        <v>73800</v>
       </c>
       <c r="J64" s="120">
         <f t="shared" si="14"/>
@@ -7382,17 +7500,17 @@
       </c>
       <c r="K64" s="120">
         <f t="shared" si="5"/>
-        <v>47603.070008000002</v>
+        <v>84189.385731999981</v>
       </c>
       <c r="L64" s="120"/>
       <c r="M64" s="141"/>
       <c r="N64" s="81">
         <f t="shared" si="6"/>
-        <v>366213.5</v>
+        <v>380702.5</v>
       </c>
       <c r="O64" s="134">
         <f t="shared" si="9"/>
-        <v>377199.5</v>
+        <v>392123.5</v>
       </c>
       <c r="P64" s="50">
         <f t="shared" si="8"/>
@@ -7414,7 +7532,7 @@
       <c r="E65" s="78">
         <v>180400.51</v>
       </c>
-      <c r="F65" s="315">
+      <c r="F65" s="79">
         <f>E65</f>
         <v>180400.51</v>
       </c>
@@ -7428,7 +7546,7 @@
       </c>
       <c r="I65" s="120">
         <f t="shared" si="13"/>
-        <v>95896.929991999976</v>
+        <v>73800</v>
       </c>
       <c r="J65" s="120">
         <f t="shared" si="14"/>
@@ -7436,17 +7554,17 @@
       </c>
       <c r="K65" s="120">
         <f t="shared" si="5"/>
-        <v>47603.070008000002</v>
+        <v>84189.385731999981</v>
       </c>
       <c r="L65" s="120"/>
       <c r="M65" s="141"/>
       <c r="N65" s="81">
         <f t="shared" si="6"/>
-        <v>180400.51</v>
+        <v>194889.51</v>
       </c>
       <c r="O65" s="134">
         <f t="shared" si="9"/>
-        <v>185812.51</v>
+        <v>200736.51</v>
       </c>
       <c r="P65" s="50">
         <f t="shared" si="8"/>
@@ -7468,8 +7586,8 @@
       <c r="E66" s="78">
         <v>294800.52</v>
       </c>
-      <c r="F66" s="315">
-        <f t="shared" ref="F62:F67" si="15">E66</f>
+      <c r="F66" s="79">
+        <f t="shared" ref="F66:F67" si="15">E66</f>
         <v>294800.52</v>
       </c>
       <c r="G66" s="80">
@@ -7482,7 +7600,7 @@
       </c>
       <c r="I66" s="120">
         <f t="shared" si="13"/>
-        <v>156709.61730399998</v>
+        <v>120600</v>
       </c>
       <c r="J66" s="120">
         <f t="shared" si="14"/>
@@ -7490,17 +7608,17 @@
       </c>
       <c r="K66" s="120">
         <f t="shared" si="5"/>
-        <v>77790.382696000015</v>
+        <v>137577.77668400001</v>
       </c>
       <c r="L66" s="120"/>
       <c r="M66" s="141"/>
       <c r="N66" s="81">
         <f t="shared" si="6"/>
-        <v>294800.52</v>
+        <v>318478.52</v>
       </c>
       <c r="O66" s="134">
         <f t="shared" si="9"/>
-        <v>303644.52</v>
+        <v>328032.52</v>
       </c>
       <c r="P66" s="50">
         <f t="shared" si="8"/>
@@ -7522,7 +7640,7 @@
       <c r="E67" s="79">
         <v>253792.53</v>
       </c>
-      <c r="F67" s="315">
+      <c r="F67" s="79">
         <f t="shared" si="15"/>
         <v>253792.53</v>
       </c>
@@ -7536,7 +7654,7 @@
       </c>
       <c r="I67" s="120">
         <f t="shared" si="13"/>
-        <v>130981.172672</v>
+        <v>100800.00000000001</v>
       </c>
       <c r="J67" s="120">
         <f t="shared" si="14"/>
@@ -7544,17 +7662,17 @@
       </c>
       <c r="K67" s="120">
         <f t="shared" si="5"/>
-        <v>65018.827328000014</v>
+        <v>114990.380512</v>
       </c>
       <c r="L67" s="120"/>
       <c r="M67" s="141"/>
       <c r="N67" s="81">
         <f t="shared" si="6"/>
-        <v>246400.53</v>
+        <v>266190.53000000003</v>
       </c>
       <c r="O67" s="134">
         <f t="shared" si="9"/>
-        <v>253792.53</v>
+        <v>274176.53000000003</v>
       </c>
       <c r="P67" s="50">
         <f t="shared" si="8"/>
@@ -7576,7 +7694,7 @@
       <c r="E68" s="78">
         <v>257400.54</v>
       </c>
-      <c r="F68" s="315">
+      <c r="F68" s="79">
         <v>265122.53999999998</v>
       </c>
       <c r="G68" s="80">
@@ -7589,7 +7707,7 @@
       </c>
       <c r="I68" s="120">
         <f t="shared" si="13"/>
-        <v>136828.54645199998</v>
+        <v>105300</v>
       </c>
       <c r="J68" s="120">
         <f t="shared" si="14"/>
@@ -7597,17 +7715,17 @@
       </c>
       <c r="K68" s="120">
         <f t="shared" si="5"/>
-        <v>67921.453548000005</v>
+        <v>120123.879642</v>
       </c>
       <c r="L68" s="120"/>
       <c r="M68" s="141"/>
       <c r="N68" s="81">
         <f t="shared" si="6"/>
-        <v>249678.54</v>
+        <v>270352.53999999998</v>
       </c>
       <c r="O68" s="134">
         <f t="shared" si="9"/>
-        <v>257168.54</v>
+        <v>278463.53999999998</v>
       </c>
       <c r="P68" s="50">
         <f t="shared" si="8"/>
@@ -7629,7 +7747,7 @@
       <c r="E69" s="78">
         <v>297000.55</v>
       </c>
-      <c r="F69" s="315">
+      <c r="F69" s="79">
         <f>E69</f>
         <v>297000.55</v>
       </c>
@@ -7643,7 +7761,7 @@
       </c>
       <c r="I69" s="120">
         <f t="shared" si="13"/>
-        <v>157879.09206</v>
+        <v>121500</v>
       </c>
       <c r="J69" s="120">
         <f t="shared" si="14"/>
@@ -7651,17 +7769,17 @@
       </c>
       <c r="K69" s="120">
         <f t="shared" si="5"/>
-        <v>78370.907940000005</v>
+        <v>138604.47651000001</v>
       </c>
       <c r="L69" s="120"/>
       <c r="M69" s="141"/>
       <c r="N69" s="81">
         <f t="shared" si="6"/>
-        <v>297000.55</v>
+        <v>320854.55</v>
       </c>
       <c r="O69" s="134">
         <f t="shared" si="9"/>
-        <v>305910.55</v>
+        <v>330480.55</v>
       </c>
       <c r="P69" s="50">
         <f t="shared" si="8"/>
@@ -7683,7 +7801,7 @@
       <c r="E70" s="78">
         <v>789549.56</v>
       </c>
-      <c r="F70" s="315">
+      <c r="F70" s="79">
         <v>253792.56</v>
       </c>
       <c r="G70" s="80">
@@ -7696,7 +7814,7 @@
       </c>
       <c r="I70" s="120">
         <f t="shared" si="13"/>
-        <v>130981.172672</v>
+        <v>100800.00000000001</v>
       </c>
       <c r="J70" s="120">
         <f t="shared" si="14"/>
@@ -7704,17 +7822,17 @@
       </c>
       <c r="K70" s="120">
         <f t="shared" si="5"/>
-        <v>65018.827328000014</v>
+        <v>114990.380512</v>
       </c>
       <c r="L70" s="120"/>
       <c r="M70" s="141"/>
       <c r="N70" s="81">
         <f t="shared" si="6"/>
-        <v>798230.56</v>
+        <v>818020.56</v>
       </c>
       <c r="O70" s="134">
         <f t="shared" si="9"/>
-        <v>822177.56</v>
+        <v>842561.56</v>
       </c>
       <c r="P70" s="50">
         <f t="shared" si="8"/>
@@ -7736,7 +7854,7 @@
       <c r="E71" s="78">
         <v>180400.57</v>
       </c>
-      <c r="F71" s="315">
+      <c r="F71" s="79">
         <f>E71</f>
         <v>180400.57</v>
       </c>
@@ -7750,7 +7868,7 @@
       </c>
       <c r="I71" s="120">
         <f t="shared" si="13"/>
-        <v>95896.929991999976</v>
+        <v>73800</v>
       </c>
       <c r="J71" s="120">
         <f t="shared" si="14"/>
@@ -7758,17 +7876,17 @@
       </c>
       <c r="K71" s="120">
         <f t="shared" si="5"/>
-        <v>47603.070008000002</v>
+        <v>84189.385731999981</v>
       </c>
       <c r="L71" s="120"/>
       <c r="M71" s="141"/>
       <c r="N71" s="81">
         <f t="shared" si="6"/>
-        <v>180400.57</v>
+        <v>194889.57</v>
       </c>
       <c r="O71" s="134">
         <f t="shared" si="9"/>
-        <v>185812.57</v>
+        <v>200736.57</v>
       </c>
       <c r="P71" s="50">
         <f t="shared" si="8"/>
@@ -7793,7 +7911,7 @@
       <c r="E72" s="78">
         <v>180400.58</v>
       </c>
-      <c r="F72" s="315">
+      <c r="F72" s="79">
         <f t="shared" ref="F72" si="16">E72</f>
         <v>180400.58</v>
       </c>
@@ -7807,7 +7925,7 @@
       </c>
       <c r="I72" s="120">
         <f t="shared" si="13"/>
-        <v>95896.929991999976</v>
+        <v>73800</v>
       </c>
       <c r="J72" s="120">
         <f t="shared" si="14"/>
@@ -7815,17 +7933,17 @@
       </c>
       <c r="K72" s="120">
         <f t="shared" si="5"/>
-        <v>47603.070008000002</v>
+        <v>84189.385731999981</v>
       </c>
       <c r="L72" s="120"/>
       <c r="M72" s="141"/>
       <c r="N72" s="81">
         <f t="shared" si="6"/>
-        <v>180400.58</v>
+        <v>194889.58</v>
       </c>
       <c r="O72" s="134">
         <f t="shared" si="9"/>
-        <v>185812.58</v>
+        <v>200736.58</v>
       </c>
       <c r="P72" s="50">
         <f t="shared" si="8"/>
@@ -7850,7 +7968,7 @@
       <c r="E73" s="79">
         <v>286569.59000000003</v>
       </c>
-      <c r="F73" s="315">
+      <c r="F73" s="79">
         <f>339888.53</f>
         <v>339888.53</v>
       </c>
@@ -7864,7 +7982,7 @@
       </c>
       <c r="I73" s="121">
         <f t="shared" si="13"/>
-        <v>156709.61730399998</v>
+        <v>120600</v>
       </c>
       <c r="J73" s="121">
         <f t="shared" si="14"/>
@@ -7872,17 +7990,17 @@
       </c>
       <c r="K73" s="120">
         <f t="shared" si="5"/>
-        <v>77790.382696000015</v>
+        <v>137577.77668400001</v>
       </c>
       <c r="L73" s="121"/>
       <c r="M73" s="142"/>
       <c r="N73" s="81">
         <f t="shared" si="6"/>
-        <v>241481.59</v>
+        <v>265159.59000000003</v>
       </c>
       <c r="O73" s="135">
         <f t="shared" si="9"/>
-        <v>248725.59</v>
+        <v>273114.59000000003</v>
       </c>
       <c r="P73" s="50">
         <f t="shared" si="8"/>
@@ -7904,7 +8022,7 @@
       <c r="E74" s="78">
         <v>239520.6</v>
       </c>
-      <c r="F74" s="315">
+      <c r="F74" s="79">
         <f>E74</f>
         <v>239520.6</v>
       </c>
@@ -7918,7 +8036,7 @@
       </c>
       <c r="I74" s="120">
         <f t="shared" si="13"/>
-        <v>130981.172672</v>
+        <v>100800.00000000001</v>
       </c>
       <c r="J74" s="120">
         <f t="shared" si="14"/>
@@ -7926,17 +8044,17 @@
       </c>
       <c r="K74" s="120">
         <f t="shared" si="5"/>
-        <v>65018.827328000014</v>
+        <v>114990.380512</v>
       </c>
       <c r="L74" s="120"/>
       <c r="M74" s="141"/>
       <c r="N74" s="81">
         <f t="shared" si="6"/>
-        <v>246400.6</v>
+        <v>266190.59999999998</v>
       </c>
       <c r="O74" s="134">
         <f t="shared" si="9"/>
-        <v>253792.6</v>
+        <v>274176.59999999998</v>
       </c>
       <c r="P74" s="50">
         <f t="shared" si="8"/>
@@ -7958,7 +8076,7 @@
       <c r="E75" s="78">
         <v>257400.61</v>
       </c>
-      <c r="F75" s="315">
+      <c r="F75" s="79">
         <f>E75</f>
         <v>257400.61</v>
       </c>
@@ -7972,7 +8090,7 @@
       </c>
       <c r="I75" s="120">
         <f t="shared" si="13"/>
-        <v>136828.54645199998</v>
+        <v>105300</v>
       </c>
       <c r="J75" s="120">
         <f t="shared" si="14"/>
@@ -7980,17 +8098,17 @@
       </c>
       <c r="K75" s="120">
         <f t="shared" si="5"/>
-        <v>67921.453548000005</v>
+        <v>120123.879642</v>
       </c>
       <c r="L75" s="120"/>
       <c r="M75" s="141"/>
       <c r="N75" s="81">
         <f t="shared" si="6"/>
-        <v>257400.61</v>
+        <v>278074.61</v>
       </c>
       <c r="O75" s="134">
         <f t="shared" si="9"/>
-        <v>265122.61</v>
+        <v>286416.61</v>
       </c>
       <c r="P75" s="50">
         <f t="shared" si="8"/>
@@ -8012,7 +8130,7 @@
       <c r="E76" s="78">
         <v>297000.62</v>
       </c>
-      <c r="F76" s="315">
+      <c r="F76" s="79">
         <f>E76</f>
         <v>297000.62</v>
       </c>
@@ -8026,7 +8144,7 @@
       </c>
       <c r="I76" s="120">
         <f t="shared" si="13"/>
-        <v>157879.09206</v>
+        <v>121500</v>
       </c>
       <c r="J76" s="120">
         <f t="shared" si="14"/>
@@ -8034,17 +8152,17 @@
       </c>
       <c r="K76" s="120">
         <f t="shared" si="5"/>
-        <v>78370.907940000005</v>
+        <v>138604.47651000001</v>
       </c>
       <c r="L76" s="120"/>
       <c r="M76" s="141"/>
       <c r="N76" s="81">
         <f t="shared" si="6"/>
-        <v>297000.62</v>
+        <v>320854.62</v>
       </c>
       <c r="O76" s="134">
         <f t="shared" si="9"/>
-        <v>305910.62</v>
+        <v>330480.62</v>
       </c>
       <c r="P76" s="50">
         <f t="shared" si="8"/>
@@ -8066,7 +8184,7 @@
       <c r="E77" s="78">
         <v>246400.63</v>
       </c>
-      <c r="F77" s="315">
+      <c r="F77" s="79">
         <f>E77</f>
         <v>246400.63</v>
       </c>
@@ -8080,7 +8198,7 @@
       </c>
       <c r="I77" s="120">
         <f t="shared" si="13"/>
-        <v>130981.172672</v>
+        <v>100800.00000000001</v>
       </c>
       <c r="J77" s="120">
         <f t="shared" si="14"/>
@@ -8088,17 +8206,17 @@
       </c>
       <c r="K77" s="120">
         <f t="shared" si="5"/>
-        <v>65018.827328000014</v>
+        <v>114990.380512</v>
       </c>
       <c r="L77" s="120"/>
       <c r="M77" s="141"/>
       <c r="N77" s="81">
         <f t="shared" si="6"/>
-        <v>246400.63</v>
+        <v>266190.63</v>
       </c>
       <c r="O77" s="134">
         <f t="shared" si="9"/>
-        <v>253792.63</v>
+        <v>274176.63</v>
       </c>
       <c r="P77" s="50">
         <f t="shared" si="8"/>
@@ -8123,7 +8241,7 @@
       <c r="E78" s="78">
         <v>188261.64</v>
       </c>
-      <c r="F78" s="315">
+      <c r="F78" s="79">
         <v>193909.64</v>
       </c>
       <c r="G78" s="80">
@@ -8136,7 +8254,7 @@
       </c>
       <c r="I78" s="120">
         <f t="shared" si="13"/>
-        <v>95896.929991999976</v>
+        <v>73800</v>
       </c>
       <c r="J78" s="120">
         <f t="shared" si="14"/>
@@ -8144,17 +8262,17 @@
       </c>
       <c r="K78" s="120">
         <f t="shared" si="5"/>
-        <v>47603.070008000002</v>
+        <v>84189.385731999981</v>
       </c>
       <c r="L78" s="120"/>
       <c r="M78" s="141"/>
       <c r="N78" s="81">
         <f t="shared" si="6"/>
-        <v>174752.64000000001</v>
+        <v>189241.64</v>
       </c>
       <c r="O78" s="134">
         <f t="shared" si="9"/>
-        <v>179995.64</v>
+        <v>194918.64</v>
       </c>
       <c r="P78" s="50">
         <f t="shared" si="8"/>
@@ -8176,7 +8294,7 @@
       <c r="E79" s="79">
         <v>424018.65</v>
       </c>
-      <c r="F79" s="318">
+      <c r="F79" s="309">
         <v>280000.65000000002</v>
       </c>
       <c r="G79" s="106">
@@ -8189,7 +8307,7 @@
       </c>
       <c r="I79" s="121">
         <f t="shared" ref="I79:I110" si="18">J$2*D79/100</f>
-        <v>95896.929991999976</v>
+        <v>73800</v>
       </c>
       <c r="J79" s="121">
         <f t="shared" ref="J79:J110" si="19">E$2*D79/100</f>
@@ -8197,17 +8315,17 @@
       </c>
       <c r="K79" s="120">
         <f t="shared" si="5"/>
-        <v>47603.070008000002</v>
+        <v>84189.385731999981</v>
       </c>
       <c r="L79" s="121"/>
       <c r="M79" s="142"/>
       <c r="N79" s="81">
         <f t="shared" si="6"/>
-        <v>328739.65000000002</v>
+        <v>343228.65</v>
       </c>
       <c r="O79" s="135">
         <f t="shared" si="9"/>
-        <v>338601.65</v>
+        <v>353525.65</v>
       </c>
       <c r="P79" s="50">
         <f t="shared" si="8"/>
@@ -8245,7 +8363,7 @@
       </c>
       <c r="I80" s="121">
         <f t="shared" si="18"/>
-        <v>156709.61730399998</v>
+        <v>120600</v>
       </c>
       <c r="J80" s="121">
         <f t="shared" si="19"/>
@@ -8253,17 +8371,17 @@
       </c>
       <c r="K80" s="120">
         <f t="shared" ref="K80:K117" si="21">M$2*D80/100</f>
-        <v>77790.382696000015</v>
+        <v>137577.77668400001</v>
       </c>
       <c r="L80" s="121"/>
       <c r="M80" s="142"/>
       <c r="N80" s="107">
         <f t="shared" si="6"/>
-        <v>1540046.66</v>
+        <v>1563724.66</v>
       </c>
       <c r="O80" s="135">
         <f t="shared" si="9"/>
-        <v>1586247.66</v>
+        <v>1610636.66</v>
       </c>
       <c r="P80" s="50">
         <f t="shared" si="8"/>
@@ -8285,7 +8403,7 @@
       <c r="E81" s="78">
         <v>454185.67</v>
       </c>
-      <c r="F81" s="315">
+      <c r="F81" s="79">
         <f>200000+261811.67+5877</f>
         <v>467688.67000000004</v>
       </c>
@@ -8299,7 +8417,7 @@
       </c>
       <c r="I81" s="120">
         <f t="shared" si="18"/>
-        <v>130981.172672</v>
+        <v>100800.00000000001</v>
       </c>
       <c r="J81" s="120">
         <f t="shared" si="19"/>
@@ -8307,17 +8425,17 @@
       </c>
       <c r="K81" s="120">
         <f t="shared" si="21"/>
-        <v>65018.827328000014</v>
+        <v>114990.380512</v>
       </c>
       <c r="L81" s="120"/>
       <c r="M81" s="141"/>
       <c r="N81" s="81">
         <f t="shared" ref="N81:N117" si="22">ROUND(SUM(G81:M81),0) + P81</f>
-        <v>232897.67</v>
+        <v>252687.67</v>
       </c>
       <c r="O81" s="134">
         <f t="shared" si="9"/>
-        <v>239884.67</v>
+        <v>260268.67</v>
       </c>
       <c r="P81" s="50">
         <f t="shared" si="8"/>
@@ -8352,7 +8470,7 @@
       </c>
       <c r="I82" s="192">
         <f t="shared" si="18"/>
-        <v>136828.54645199998</v>
+        <v>105300</v>
       </c>
       <c r="J82" s="192">
         <f t="shared" si="19"/>
@@ -8360,7 +8478,7 @@
       </c>
       <c r="K82" s="192">
         <f t="shared" si="21"/>
-        <v>67921.453548000005</v>
+        <v>120123.879642</v>
       </c>
       <c r="L82" s="192">
         <v>95000</v>
@@ -8368,11 +8486,11 @@
       <c r="M82" s="193"/>
       <c r="N82" s="194">
         <f t="shared" si="22"/>
-        <v>9095461.6799999997</v>
+        <v>9116135.6799999997</v>
       </c>
       <c r="O82" s="195">
         <f t="shared" si="9"/>
-        <v>9368325.6799999997</v>
+        <v>9389619.6799999997</v>
       </c>
       <c r="P82" s="50">
         <f t="shared" si="8"/>
@@ -8394,7 +8512,7 @@
       <c r="E83" s="78">
         <v>295421.69</v>
       </c>
-      <c r="F83" s="315">
+      <c r="F83" s="79">
         <v>300000</v>
       </c>
       <c r="G83" s="80">
@@ -8407,7 +8525,7 @@
       </c>
       <c r="I83" s="120">
         <f t="shared" si="18"/>
-        <v>157879.09206</v>
+        <v>121500</v>
       </c>
       <c r="J83" s="120">
         <f t="shared" si="19"/>
@@ -8415,7 +8533,7 @@
       </c>
       <c r="K83" s="120">
         <f t="shared" si="21"/>
-        <v>78370.907940000005</v>
+        <v>138604.47651000001</v>
       </c>
       <c r="L83" s="120" t="s">
         <v>199</v>
@@ -8423,11 +8541,11 @@
       <c r="M83" s="141"/>
       <c r="N83" s="81">
         <f t="shared" si="22"/>
-        <v>292422.69</v>
+        <v>316276.69</v>
       </c>
       <c r="O83" s="134">
         <f t="shared" si="9"/>
-        <v>301195.69</v>
+        <v>325764.69</v>
       </c>
       <c r="P83" s="50">
         <f t="shared" si="8"/>
@@ -8460,7 +8578,7 @@
       </c>
       <c r="I84" s="121">
         <f t="shared" si="18"/>
-        <v>130981.172672</v>
+        <v>100800.00000000001</v>
       </c>
       <c r="J84" s="121">
         <f t="shared" si="19"/>
@@ -8468,17 +8586,17 @@
       </c>
       <c r="K84" s="120">
         <f t="shared" si="21"/>
-        <v>65018.827328000014</v>
+        <v>114990.380512</v>
       </c>
       <c r="L84" s="121"/>
       <c r="M84" s="142"/>
       <c r="N84" s="81">
         <f t="shared" si="22"/>
-        <v>916542.7</v>
+        <v>936333.7</v>
       </c>
       <c r="O84" s="135">
         <f t="shared" si="9"/>
-        <v>944038.7</v>
+        <v>964423.7</v>
       </c>
       <c r="P84" s="50">
         <f t="shared" si="8"/>
@@ -8503,7 +8621,7 @@
       <c r="E85" s="78">
         <v>180400.71</v>
       </c>
-      <c r="F85" s="315">
+      <c r="F85" s="79">
         <f>E85</f>
         <v>180400.71</v>
       </c>
@@ -8517,7 +8635,7 @@
       </c>
       <c r="I85" s="120">
         <f t="shared" si="18"/>
-        <v>95896.929991999976</v>
+        <v>73800</v>
       </c>
       <c r="J85" s="120">
         <f t="shared" si="19"/>
@@ -8525,17 +8643,17 @@
       </c>
       <c r="K85" s="120">
         <f t="shared" si="21"/>
-        <v>47603.070008000002</v>
+        <v>84189.385731999981</v>
       </c>
       <c r="L85" s="120"/>
       <c r="M85" s="141"/>
       <c r="N85" s="81">
         <f t="shared" si="22"/>
-        <v>180400.71</v>
+        <v>194889.71</v>
       </c>
       <c r="O85" s="134">
         <f t="shared" si="9"/>
-        <v>185812.71</v>
+        <v>200736.71</v>
       </c>
       <c r="P85" s="50">
         <f t="shared" si="8"/>
@@ -8557,7 +8675,7 @@
       <c r="E86" s="78">
         <v>180400.72</v>
       </c>
-      <c r="F86" s="315">
+      <c r="F86" s="79">
         <f>E86</f>
         <v>180400.72</v>
       </c>
@@ -8571,7 +8689,7 @@
       </c>
       <c r="I86" s="120">
         <f t="shared" si="18"/>
-        <v>95896.929991999976</v>
+        <v>73800</v>
       </c>
       <c r="J86" s="120">
         <f t="shared" si="19"/>
@@ -8579,17 +8697,17 @@
       </c>
       <c r="K86" s="120">
         <f t="shared" si="21"/>
-        <v>47603.070008000002</v>
+        <v>84189.385731999981</v>
       </c>
       <c r="L86" s="120"/>
       <c r="M86" s="141"/>
       <c r="N86" s="81">
         <f t="shared" si="22"/>
-        <v>180400.72</v>
+        <v>194889.72</v>
       </c>
       <c r="O86" s="134">
         <f t="shared" si="9"/>
-        <v>185812.72</v>
+        <v>200736.72</v>
       </c>
       <c r="P86" s="50">
         <f t="shared" si="8"/>
@@ -8622,7 +8740,7 @@
       </c>
       <c r="I87" s="120">
         <f t="shared" si="18"/>
-        <v>156709.61730399998</v>
+        <v>120600</v>
       </c>
       <c r="J87" s="120">
         <f t="shared" si="19"/>
@@ -8630,17 +8748,17 @@
       </c>
       <c r="K87" s="120">
         <f t="shared" si="21"/>
-        <v>77790.382696000015</v>
+        <v>137577.77668400001</v>
       </c>
       <c r="L87" s="120"/>
       <c r="M87" s="141"/>
       <c r="N87" s="81">
         <f t="shared" si="22"/>
-        <v>598445.73</v>
+        <v>622123.73</v>
       </c>
       <c r="O87" s="134">
         <f t="shared" si="9"/>
-        <v>616398.73</v>
+        <v>640787.73</v>
       </c>
       <c r="P87" s="50">
         <f t="shared" si="8"/>
@@ -8662,7 +8780,7 @@
       <c r="E88" s="117">
         <v>376400.74</v>
       </c>
-      <c r="F88" s="317">
+      <c r="F88" s="117">
         <f>E88</f>
         <v>376400.74</v>
       </c>
@@ -8675,7 +8793,7 @@
       </c>
       <c r="I88" s="123">
         <f t="shared" si="18"/>
-        <v>130981.172672</v>
+        <v>100800.00000000001</v>
       </c>
       <c r="J88" s="123">
         <f t="shared" si="19"/>
@@ -8683,7 +8801,7 @@
       </c>
       <c r="K88" s="123">
         <f t="shared" si="21"/>
-        <v>65018.827328000014</v>
+        <v>114990.380512</v>
       </c>
       <c r="L88" s="123"/>
       <c r="M88" s="143">
@@ -8691,18 +8809,18 @@
       </c>
       <c r="N88" s="119">
         <f t="shared" si="22"/>
-        <v>376400.74</v>
+        <v>396190.74</v>
       </c>
       <c r="O88" s="136">
         <f t="shared" si="9"/>
-        <v>387692.74</v>
+        <v>408076.74</v>
       </c>
       <c r="P88" s="50">
         <f t="shared" si="8"/>
         <v>0.74000000000000044</v>
       </c>
       <c r="Q88" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
@@ -8720,7 +8838,7 @@
       <c r="E89" s="78">
         <v>250219.75</v>
       </c>
-      <c r="F89" s="315">
+      <c r="F89" s="79">
         <v>257726.75</v>
       </c>
       <c r="G89" s="80">
@@ -8733,7 +8851,7 @@
       </c>
       <c r="I89" s="120">
         <f t="shared" si="18"/>
-        <v>136828.54645199998</v>
+        <v>105300</v>
       </c>
       <c r="J89" s="120">
         <f t="shared" si="19"/>
@@ -8741,17 +8859,17 @@
       </c>
       <c r="K89" s="120">
         <f t="shared" si="21"/>
-        <v>67921.453548000005</v>
+        <v>120123.879642</v>
       </c>
       <c r="L89" s="120"/>
       <c r="M89" s="141"/>
       <c r="N89" s="81">
         <f t="shared" si="22"/>
-        <v>249893.75</v>
+        <v>270567.75</v>
       </c>
       <c r="O89" s="134">
         <f t="shared" si="9"/>
-        <v>257390.75</v>
+        <v>278684.75</v>
       </c>
       <c r="P89" s="50">
         <f t="shared" si="8"/>
@@ -8773,8 +8891,8 @@
       <c r="E90" s="79">
         <v>297000.76</v>
       </c>
-      <c r="F90" s="315">
-        <f>E90</f>
+      <c r="F90" s="79">
+        <f t="shared" ref="F90:F96" si="23">E90</f>
         <v>297000.76</v>
       </c>
       <c r="G90" s="106">
@@ -8787,7 +8905,7 @@
       </c>
       <c r="I90" s="121">
         <f t="shared" si="18"/>
-        <v>157879.09206</v>
+        <v>121500</v>
       </c>
       <c r="J90" s="121">
         <f t="shared" si="19"/>
@@ -8795,17 +8913,17 @@
       </c>
       <c r="K90" s="121">
         <f t="shared" si="21"/>
-        <v>78370.907940000005</v>
+        <v>138604.47651000001</v>
       </c>
       <c r="L90" s="121"/>
       <c r="M90" s="142"/>
       <c r="N90" s="107">
         <f t="shared" si="22"/>
-        <v>297000.76</v>
+        <v>320854.76</v>
       </c>
       <c r="O90" s="135">
         <f t="shared" si="9"/>
-        <v>305910.76</v>
+        <v>330480.76</v>
       </c>
       <c r="P90" s="50">
         <f t="shared" si="8"/>
@@ -8827,8 +8945,8 @@
       <c r="E91" s="78">
         <v>246400.77</v>
       </c>
-      <c r="F91" s="315">
-        <f>E91</f>
+      <c r="F91" s="79">
+        <f t="shared" si="23"/>
         <v>246400.77</v>
       </c>
       <c r="G91" s="80">
@@ -8841,7 +8959,7 @@
       </c>
       <c r="I91" s="120">
         <f t="shared" si="18"/>
-        <v>130981.172672</v>
+        <v>100800.00000000001</v>
       </c>
       <c r="J91" s="120">
         <f t="shared" si="19"/>
@@ -8849,17 +8967,17 @@
       </c>
       <c r="K91" s="120">
         <f t="shared" si="21"/>
-        <v>65018.827328000014</v>
+        <v>114990.380512</v>
       </c>
       <c r="L91" s="120"/>
       <c r="M91" s="141"/>
       <c r="N91" s="81">
         <f t="shared" si="22"/>
-        <v>246400.77</v>
+        <v>266190.77</v>
       </c>
       <c r="O91" s="134">
         <f t="shared" si="9"/>
-        <v>253792.77</v>
+        <v>274176.77</v>
       </c>
       <c r="P91" s="50">
         <f t="shared" si="8"/>
@@ -8881,8 +8999,8 @@
       <c r="E92" s="117">
         <v>355762.78</v>
       </c>
-      <c r="F92" s="317">
-        <f>E92</f>
+      <c r="F92" s="117">
+        <f t="shared" si="23"/>
         <v>355762.78</v>
       </c>
       <c r="G92" s="118">
@@ -8892,7 +9010,7 @@
       <c r="H92" s="118"/>
       <c r="I92" s="123">
         <f t="shared" si="18"/>
-        <v>95896.929991999976</v>
+        <v>73800</v>
       </c>
       <c r="J92" s="123">
         <f t="shared" si="19"/>
@@ -8900,7 +9018,7 @@
       </c>
       <c r="K92" s="123">
         <f t="shared" si="21"/>
-        <v>47603.070008000002</v>
+        <v>84189.385731999981</v>
       </c>
       <c r="L92" s="123"/>
       <c r="M92" s="143">
@@ -8908,18 +9026,18 @@
       </c>
       <c r="N92" s="119">
         <f t="shared" si="22"/>
-        <v>345400.78</v>
+        <v>359889.78</v>
       </c>
       <c r="O92" s="136">
         <f t="shared" si="9"/>
-        <v>355762.78</v>
+        <v>370686.78</v>
       </c>
       <c r="P92" s="50">
         <f t="shared" si="8"/>
         <v>0.78000000000000047</v>
       </c>
       <c r="Q92" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
@@ -8937,8 +9055,8 @@
       <c r="E93" s="78">
         <v>193069.79</v>
       </c>
-      <c r="F93" s="315">
-        <f>E93</f>
+      <c r="F93" s="79">
+        <f t="shared" si="23"/>
         <v>193069.79</v>
       </c>
       <c r="G93" s="80">
@@ -8951,7 +9069,7 @@
       </c>
       <c r="I93" s="120">
         <f t="shared" si="18"/>
-        <v>95896.929991999976</v>
+        <v>73800</v>
       </c>
       <c r="J93" s="120">
         <f t="shared" si="19"/>
@@ -8959,17 +9077,17 @@
       </c>
       <c r="K93" s="120">
         <f t="shared" si="21"/>
-        <v>47603.070008000002</v>
+        <v>84189.385731999981</v>
       </c>
       <c r="L93" s="120"/>
       <c r="M93" s="141"/>
       <c r="N93" s="81">
         <f t="shared" si="22"/>
-        <v>180400.79</v>
+        <v>194889.79</v>
       </c>
       <c r="O93" s="134">
         <f t="shared" si="9"/>
-        <v>185812.79</v>
+        <v>200736.79</v>
       </c>
       <c r="P93" s="50">
         <f t="shared" si="8"/>
@@ -8994,8 +9112,8 @@
       <c r="E94" s="79">
         <v>294800.8</v>
       </c>
-      <c r="F94" s="315">
-        <f>E94</f>
+      <c r="F94" s="79">
+        <f t="shared" si="23"/>
         <v>294800.8</v>
       </c>
       <c r="G94" s="80">
@@ -9008,7 +9126,7 @@
       </c>
       <c r="I94" s="120">
         <f t="shared" si="18"/>
-        <v>156709.61730399998</v>
+        <v>120600</v>
       </c>
       <c r="J94" s="120">
         <f t="shared" si="19"/>
@@ -9016,17 +9134,17 @@
       </c>
       <c r="K94" s="120">
         <f t="shared" si="21"/>
-        <v>77790.382696000015</v>
+        <v>137577.77668400001</v>
       </c>
       <c r="L94" s="120"/>
       <c r="M94" s="141"/>
       <c r="N94" s="81">
         <f t="shared" si="22"/>
-        <v>294800.8</v>
+        <v>318478.8</v>
       </c>
       <c r="O94" s="134">
         <f t="shared" si="9"/>
-        <v>303644.79999999999</v>
+        <v>328032.8</v>
       </c>
       <c r="P94" s="50">
         <f t="shared" si="8"/>
@@ -9048,8 +9166,8 @@
       <c r="E95" s="79">
         <v>246400.81</v>
       </c>
-      <c r="F95" s="315">
-        <f>E95</f>
+      <c r="F95" s="79">
+        <f t="shared" si="23"/>
         <v>246400.81</v>
       </c>
       <c r="G95" s="106">
@@ -9062,7 +9180,7 @@
       </c>
       <c r="I95" s="121">
         <f t="shared" si="18"/>
-        <v>130981.172672</v>
+        <v>100800.00000000001</v>
       </c>
       <c r="J95" s="121">
         <f t="shared" si="19"/>
@@ -9070,17 +9188,17 @@
       </c>
       <c r="K95" s="120">
         <f t="shared" si="21"/>
-        <v>65018.827328000014</v>
+        <v>114990.380512</v>
       </c>
       <c r="L95" s="121"/>
       <c r="M95" s="142"/>
       <c r="N95" s="107">
         <f t="shared" si="22"/>
-        <v>246400.81</v>
+        <v>266190.81</v>
       </c>
       <c r="O95" s="135">
         <f t="shared" si="9"/>
-        <v>253792.81</v>
+        <v>274176.81</v>
       </c>
       <c r="P95" s="50">
         <f t="shared" si="8"/>
@@ -9105,8 +9223,8 @@
       <c r="E96" s="78">
         <v>276018.82</v>
       </c>
-      <c r="F96" s="315">
-        <f>E96</f>
+      <c r="F96" s="79">
+        <f t="shared" si="23"/>
         <v>276018.82</v>
       </c>
       <c r="G96" s="80">
@@ -9119,7 +9237,7 @@
       </c>
       <c r="I96" s="120">
         <f t="shared" si="18"/>
-        <v>136828.54645199998</v>
+        <v>105300</v>
       </c>
       <c r="J96" s="120">
         <f t="shared" si="19"/>
@@ -9127,17 +9245,17 @@
       </c>
       <c r="K96" s="120">
         <f t="shared" si="21"/>
-        <v>67921.453548000005</v>
+        <v>120123.879642</v>
       </c>
       <c r="L96" s="120"/>
       <c r="M96" s="141"/>
       <c r="N96" s="81">
         <f t="shared" si="22"/>
-        <v>257400.82</v>
+        <v>278074.82</v>
       </c>
       <c r="O96" s="134">
         <f t="shared" si="9"/>
-        <v>265122.82</v>
+        <v>286416.82</v>
       </c>
       <c r="P96" s="50">
         <f t="shared" si="8"/>
@@ -9159,8 +9277,8 @@
       <c r="E97" s="79">
         <v>297000.83</v>
       </c>
-      <c r="F97" s="315">
-        <f t="shared" ref="F97:F104" si="23">E97</f>
+      <c r="F97" s="79">
+        <f t="shared" ref="F97:F104" si="24">E97</f>
         <v>297000.83</v>
       </c>
       <c r="G97" s="80">
@@ -9173,7 +9291,7 @@
       </c>
       <c r="I97" s="120">
         <f t="shared" si="18"/>
-        <v>157879.09206</v>
+        <v>121500</v>
       </c>
       <c r="J97" s="120">
         <f t="shared" si="19"/>
@@ -9181,17 +9299,17 @@
       </c>
       <c r="K97" s="120">
         <f t="shared" si="21"/>
-        <v>78370.907940000005</v>
+        <v>138604.47651000001</v>
       </c>
       <c r="L97" s="120"/>
       <c r="M97" s="141"/>
       <c r="N97" s="81">
         <f t="shared" si="22"/>
-        <v>297000.83</v>
+        <v>320854.83</v>
       </c>
       <c r="O97" s="134">
         <f t="shared" si="9"/>
-        <v>305910.83</v>
+        <v>330480.83</v>
       </c>
       <c r="P97" s="50">
         <f t="shared" si="8"/>
@@ -9224,7 +9342,7 @@
       </c>
       <c r="I98" s="120">
         <f t="shared" si="18"/>
-        <v>130981.172672</v>
+        <v>100800.00000000001</v>
       </c>
       <c r="J98" s="120">
         <f t="shared" si="19"/>
@@ -9232,20 +9350,20 @@
       </c>
       <c r="K98" s="120">
         <f t="shared" si="21"/>
-        <v>65018.827328000014</v>
+        <v>114990.380512</v>
       </c>
       <c r="L98" s="120"/>
       <c r="M98" s="141"/>
       <c r="N98" s="81">
         <f t="shared" si="22"/>
-        <v>500193.84</v>
+        <v>519983.84</v>
       </c>
       <c r="O98" s="134">
         <f t="shared" si="9"/>
-        <v>515199.84</v>
+        <v>535583.84000000008</v>
       </c>
       <c r="P98" s="50">
-        <f t="shared" ref="P98:P117" si="24">P97+0.01</f>
+        <f t="shared" ref="P98:P117" si="25">P97+0.01</f>
         <v>0.84000000000000052</v>
       </c>
     </row>
@@ -9264,8 +9382,8 @@
       <c r="E99" s="78">
         <v>180400.85</v>
       </c>
-      <c r="F99" s="315">
-        <f t="shared" si="23"/>
+      <c r="F99" s="79">
+        <f t="shared" si="24"/>
         <v>180400.85</v>
       </c>
       <c r="G99" s="80">
@@ -9278,7 +9396,7 @@
       </c>
       <c r="I99" s="120">
         <f t="shared" si="18"/>
-        <v>95896.929991999976</v>
+        <v>73800</v>
       </c>
       <c r="J99" s="120">
         <f t="shared" si="19"/>
@@ -9286,20 +9404,20 @@
       </c>
       <c r="K99" s="120">
         <f t="shared" si="21"/>
-        <v>47603.070008000002</v>
+        <v>84189.385731999981</v>
       </c>
       <c r="L99" s="120"/>
       <c r="M99" s="141"/>
       <c r="N99" s="81">
         <f t="shared" si="22"/>
-        <v>180400.85</v>
+        <v>194889.85</v>
       </c>
       <c r="O99" s="134">
         <f t="shared" si="9"/>
-        <v>185812.85</v>
+        <v>200736.85</v>
       </c>
       <c r="P99" s="50">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.85000000000000053</v>
       </c>
     </row>
@@ -9318,8 +9436,8 @@
       <c r="E100" s="79">
         <v>180400.86</v>
       </c>
-      <c r="F100" s="315">
-        <f t="shared" si="23"/>
+      <c r="F100" s="79">
+        <f t="shared" si="24"/>
         <v>180400.86</v>
       </c>
       <c r="G100" s="106">
@@ -9332,7 +9450,7 @@
       </c>
       <c r="I100" s="121">
         <f t="shared" si="18"/>
-        <v>95896.929991999976</v>
+        <v>73800</v>
       </c>
       <c r="J100" s="121">
         <f t="shared" si="19"/>
@@ -9340,26 +9458,26 @@
       </c>
       <c r="K100" s="120">
         <f t="shared" si="21"/>
-        <v>47603.070008000002</v>
+        <v>84189.385731999981</v>
       </c>
       <c r="L100" s="121"/>
       <c r="M100" s="142"/>
       <c r="N100" s="107">
         <f t="shared" si="22"/>
-        <v>180400.86</v>
+        <v>194889.86</v>
       </c>
       <c r="O100" s="135">
-        <f t="shared" ref="O100:O117" si="25">ROUND(N100*3%,0) + N100</f>
-        <v>185812.86</v>
+        <f t="shared" ref="O100:O117" si="26">ROUND(N100*3%,0) + N100</f>
+        <v>200736.86</v>
       </c>
       <c r="P100" s="50">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.86000000000000054</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="124">
-        <f t="shared" ref="A101:A117" si="26">A100+1</f>
+        <f t="shared" ref="A101:A117" si="27">A100+1</f>
         <v>87</v>
       </c>
       <c r="B101" s="83" t="s">
@@ -9372,8 +9490,8 @@
       <c r="E101" s="78">
         <v>294800.87</v>
       </c>
-      <c r="F101" s="315">
-        <f t="shared" si="23"/>
+      <c r="F101" s="79">
+        <f t="shared" si="24"/>
         <v>294800.87</v>
       </c>
       <c r="G101" s="80">
@@ -9386,7 +9504,7 @@
       </c>
       <c r="I101" s="120">
         <f t="shared" si="18"/>
-        <v>156709.61730399998</v>
+        <v>120600</v>
       </c>
       <c r="J101" s="120">
         <f t="shared" si="19"/>
@@ -9394,26 +9512,26 @@
       </c>
       <c r="K101" s="120">
         <f t="shared" si="21"/>
-        <v>77790.382696000015</v>
+        <v>137577.77668400001</v>
       </c>
       <c r="L101" s="120"/>
       <c r="M101" s="141"/>
       <c r="N101" s="81">
         <f t="shared" si="22"/>
-        <v>294800.87</v>
+        <v>318478.87</v>
       </c>
       <c r="O101" s="134">
+        <f t="shared" si="26"/>
+        <v>328032.87</v>
+      </c>
+      <c r="P101" s="50">
         <f t="shared" si="25"/>
-        <v>303644.87</v>
-      </c>
-      <c r="P101" s="50">
-        <f t="shared" si="24"/>
         <v>0.87000000000000055</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" s="124">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>88</v>
       </c>
       <c r="B102" s="83" t="s">
@@ -9426,8 +9544,8 @@
       <c r="E102" s="78">
         <v>246400.88</v>
       </c>
-      <c r="F102" s="315">
-        <f t="shared" si="23"/>
+      <c r="F102" s="79">
+        <f t="shared" si="24"/>
         <v>246400.88</v>
       </c>
       <c r="G102" s="80">
@@ -9440,7 +9558,7 @@
       </c>
       <c r="I102" s="120">
         <f t="shared" si="18"/>
-        <v>130981.172672</v>
+        <v>100800.00000000001</v>
       </c>
       <c r="J102" s="120">
         <f t="shared" si="19"/>
@@ -9448,26 +9566,26 @@
       </c>
       <c r="K102" s="120">
         <f t="shared" si="21"/>
-        <v>65018.827328000014</v>
+        <v>114990.380512</v>
       </c>
       <c r="L102" s="120"/>
       <c r="M102" s="141"/>
       <c r="N102" s="81">
         <f t="shared" si="22"/>
-        <v>246400.88</v>
+        <v>266190.88</v>
       </c>
       <c r="O102" s="134">
+        <f t="shared" si="26"/>
+        <v>274176.88</v>
+      </c>
+      <c r="P102" s="50">
         <f t="shared" si="25"/>
-        <v>253792.88</v>
-      </c>
-      <c r="P102" s="50">
-        <f t="shared" si="24"/>
         <v>0.88000000000000056</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" s="124">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>89</v>
       </c>
       <c r="B103" s="83" t="s">
@@ -9480,8 +9598,8 @@
       <c r="E103" s="78">
         <v>257400.89</v>
       </c>
-      <c r="F103" s="315">
-        <f t="shared" si="23"/>
+      <c r="F103" s="79">
+        <f t="shared" si="24"/>
         <v>257400.89</v>
       </c>
       <c r="G103" s="80">
@@ -9494,7 +9612,7 @@
       </c>
       <c r="I103" s="120">
         <f t="shared" si="18"/>
-        <v>136828.54645199998</v>
+        <v>105300</v>
       </c>
       <c r="J103" s="120">
         <f t="shared" si="19"/>
@@ -9502,26 +9620,26 @@
       </c>
       <c r="K103" s="120">
         <f t="shared" si="21"/>
-        <v>67921.453548000005</v>
+        <v>120123.879642</v>
       </c>
       <c r="L103" s="120"/>
       <c r="M103" s="141"/>
       <c r="N103" s="81">
         <f t="shared" si="22"/>
-        <v>257400.89</v>
+        <v>278074.89</v>
       </c>
       <c r="O103" s="134">
+        <f t="shared" si="26"/>
+        <v>286416.89</v>
+      </c>
+      <c r="P103" s="50">
         <f t="shared" si="25"/>
-        <v>265122.89</v>
-      </c>
-      <c r="P103" s="50">
-        <f t="shared" si="24"/>
         <v>0.89000000000000057</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="124">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>90</v>
       </c>
       <c r="B104" s="83" t="s">
@@ -9534,8 +9652,8 @@
       <c r="E104" s="78">
         <v>22000.9</v>
       </c>
-      <c r="F104" s="315">
-        <f t="shared" si="23"/>
+      <c r="F104" s="79">
+        <f t="shared" si="24"/>
         <v>22000.9</v>
       </c>
       <c r="G104" s="80">
@@ -9548,7 +9666,7 @@
       </c>
       <c r="I104" s="120">
         <f t="shared" si="18"/>
-        <v>11694.747559999998</v>
+        <v>9000</v>
       </c>
       <c r="J104" s="120">
         <f t="shared" si="19"/>
@@ -9556,26 +9674,26 @@
       </c>
       <c r="K104" s="120">
         <f t="shared" si="21"/>
-        <v>5805.2524400000002</v>
+        <v>10266.99826</v>
       </c>
       <c r="L104" s="120"/>
       <c r="M104" s="141"/>
       <c r="N104" s="81">
         <f t="shared" si="22"/>
-        <v>22000.9</v>
+        <v>23767.9</v>
       </c>
       <c r="O104" s="134">
+        <f t="shared" si="26"/>
+        <v>24480.9</v>
+      </c>
+      <c r="P104" s="50">
         <f t="shared" si="25"/>
-        <v>22660.9</v>
-      </c>
-      <c r="P104" s="50">
-        <f t="shared" si="24"/>
         <v>0.90000000000000058</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" s="124">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>91</v>
       </c>
       <c r="B105" s="83" t="s">
@@ -9588,7 +9706,7 @@
       <c r="E105" s="78">
         <v>23591.91</v>
       </c>
-      <c r="F105" s="315">
+      <c r="F105" s="79">
         <f>E105</f>
         <v>23591.91</v>
       </c>
@@ -9602,7 +9720,7 @@
       </c>
       <c r="I105" s="120">
         <f t="shared" si="18"/>
-        <v>11694.747559999998</v>
+        <v>9000</v>
       </c>
       <c r="J105" s="120">
         <f t="shared" si="19"/>
@@ -9610,26 +9728,26 @@
       </c>
       <c r="K105" s="120">
         <f t="shared" si="21"/>
-        <v>5805.2524400000002</v>
+        <v>10266.99826</v>
       </c>
       <c r="L105" s="120"/>
       <c r="M105" s="141"/>
       <c r="N105" s="81">
         <f t="shared" si="22"/>
-        <v>22000.91</v>
+        <v>23767.91</v>
       </c>
       <c r="O105" s="134">
+        <f t="shared" si="26"/>
+        <v>24480.91</v>
+      </c>
+      <c r="P105" s="50">
         <f t="shared" si="25"/>
-        <v>22660.91</v>
-      </c>
-      <c r="P105" s="50">
-        <f t="shared" si="24"/>
         <v>0.91000000000000059</v>
       </c>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" s="124">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>92</v>
       </c>
       <c r="B106" s="83" t="s">
@@ -9642,7 +9760,7 @@
       <c r="E106" s="78">
         <v>21394.92</v>
       </c>
-      <c r="F106" s="315">
+      <c r="F106" s="79">
         <v>22036.92</v>
       </c>
       <c r="G106" s="80">
@@ -9655,7 +9773,7 @@
       </c>
       <c r="I106" s="120">
         <f t="shared" si="18"/>
-        <v>11694.747559999998</v>
+        <v>9000</v>
       </c>
       <c r="J106" s="120">
         <f t="shared" si="19"/>
@@ -9663,26 +9781,26 @@
       </c>
       <c r="K106" s="120">
         <f t="shared" si="21"/>
-        <v>5805.2524400000002</v>
+        <v>10266.99826</v>
       </c>
       <c r="L106" s="120"/>
       <c r="M106" s="141"/>
       <c r="N106" s="81">
         <f t="shared" si="22"/>
-        <v>21358.92</v>
+        <v>23125.919999999998</v>
       </c>
       <c r="O106" s="134">
+        <f t="shared" si="26"/>
+        <v>23819.919999999998</v>
+      </c>
+      <c r="P106" s="50">
         <f t="shared" si="25"/>
-        <v>21999.919999999998</v>
-      </c>
-      <c r="P106" s="50">
-        <f t="shared" si="24"/>
         <v>0.9200000000000006</v>
       </c>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" s="125">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>93</v>
       </c>
       <c r="B107" s="109" t="s">
@@ -9695,7 +9813,7 @@
       <c r="E107" s="79">
         <v>22000.93</v>
       </c>
-      <c r="F107" s="315">
+      <c r="F107" s="79">
         <f>E107</f>
         <v>22000.93</v>
       </c>
@@ -9709,7 +9827,7 @@
       </c>
       <c r="I107" s="121">
         <f t="shared" si="18"/>
-        <v>11694.747559999998</v>
+        <v>9000</v>
       </c>
       <c r="J107" s="121">
         <f t="shared" si="19"/>
@@ -9717,26 +9835,26 @@
       </c>
       <c r="K107" s="120">
         <f t="shared" si="21"/>
-        <v>5805.2524400000002</v>
+        <v>10266.99826</v>
       </c>
       <c r="L107" s="121"/>
       <c r="M107" s="142"/>
       <c r="N107" s="81">
         <f t="shared" si="22"/>
-        <v>22000.93</v>
+        <v>23767.93</v>
       </c>
       <c r="O107" s="135">
+        <f t="shared" si="26"/>
+        <v>24480.93</v>
+      </c>
+      <c r="P107" s="50">
         <f t="shared" si="25"/>
-        <v>22660.93</v>
-      </c>
-      <c r="P107" s="50">
-        <f t="shared" si="24"/>
         <v>0.9300000000000006</v>
       </c>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" s="125">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>94</v>
       </c>
       <c r="B108" s="109" t="s">
@@ -9749,8 +9867,8 @@
       <c r="E108" s="79">
         <v>22000.94</v>
       </c>
-      <c r="F108" s="315">
-        <f t="shared" ref="F108:F113" si="27">E108</f>
+      <c r="F108" s="79">
+        <f t="shared" ref="F108:F113" si="28">E108</f>
         <v>22000.94</v>
       </c>
       <c r="G108" s="106">
@@ -9763,7 +9881,7 @@
       </c>
       <c r="I108" s="121">
         <f>J$2*D108/100</f>
-        <v>11694.747559999998</v>
+        <v>9000</v>
       </c>
       <c r="J108" s="121">
         <f t="shared" si="19"/>
@@ -9771,26 +9889,26 @@
       </c>
       <c r="K108" s="120">
         <f t="shared" si="21"/>
-        <v>5805.2524400000002</v>
+        <v>10266.99826</v>
       </c>
       <c r="L108" s="121"/>
       <c r="M108" s="142"/>
       <c r="N108" s="81">
         <f t="shared" si="22"/>
-        <v>22000.94</v>
+        <v>23767.94</v>
       </c>
       <c r="O108" s="135">
+        <f t="shared" si="26"/>
+        <v>24480.94</v>
+      </c>
+      <c r="P108" s="50">
         <f t="shared" si="25"/>
-        <v>22660.94</v>
-      </c>
-      <c r="P108" s="50">
-        <f t="shared" si="24"/>
         <v>0.94000000000000061</v>
       </c>
     </row>
     <row r="109" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="125">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>95</v>
       </c>
       <c r="B109" s="109" t="s">
@@ -9803,8 +9921,8 @@
       <c r="E109" s="79">
         <v>22000.95</v>
       </c>
-      <c r="F109" s="315">
-        <f t="shared" si="27"/>
+      <c r="F109" s="79">
+        <f t="shared" si="28"/>
         <v>22000.95</v>
       </c>
       <c r="G109" s="106">
@@ -9817,7 +9935,7 @@
       </c>
       <c r="I109" s="121">
         <f t="shared" si="18"/>
-        <v>11694.747559999998</v>
+        <v>9000</v>
       </c>
       <c r="J109" s="121">
         <f t="shared" si="19"/>
@@ -9825,26 +9943,26 @@
       </c>
       <c r="K109" s="120">
         <f t="shared" si="21"/>
-        <v>5805.2524400000002</v>
+        <v>10266.99826</v>
       </c>
       <c r="L109" s="121"/>
       <c r="M109" s="142"/>
       <c r="N109" s="81">
         <f t="shared" si="22"/>
-        <v>22000.95</v>
+        <v>23767.95</v>
       </c>
       <c r="O109" s="135">
+        <f t="shared" si="26"/>
+        <v>24480.95</v>
+      </c>
+      <c r="P109" s="50">
         <f t="shared" si="25"/>
-        <v>22660.95</v>
-      </c>
-      <c r="P109" s="50">
-        <f t="shared" si="24"/>
         <v>0.95000000000000062</v>
       </c>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" s="125">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>96</v>
       </c>
       <c r="B110" s="109" t="s">
@@ -9857,7 +9975,7 @@
       <c r="E110" s="79">
         <v>22000.959999999999</v>
       </c>
-      <c r="F110" s="315">
+      <c r="F110" s="79">
         <f>E110</f>
         <v>22000.959999999999</v>
       </c>
@@ -9871,7 +9989,7 @@
       </c>
       <c r="I110" s="121">
         <f t="shared" si="18"/>
-        <v>11694.747559999998</v>
+        <v>9000</v>
       </c>
       <c r="J110" s="121">
         <f t="shared" si="19"/>
@@ -9879,20 +9997,20 @@
       </c>
       <c r="K110" s="120">
         <f t="shared" si="21"/>
-        <v>5805.2524400000002</v>
+        <v>10266.99826</v>
       </c>
       <c r="L110" s="121"/>
       <c r="M110" s="142"/>
       <c r="N110" s="81">
         <f t="shared" si="22"/>
-        <v>22000.959999999999</v>
+        <v>23767.96</v>
       </c>
       <c r="O110" s="135">
+        <f t="shared" si="26"/>
+        <v>24480.959999999999</v>
+      </c>
+      <c r="P110" s="50">
         <f t="shared" si="25"/>
-        <v>22660.959999999999</v>
-      </c>
-      <c r="P110" s="50">
-        <f t="shared" si="24"/>
         <v>0.96000000000000063</v>
       </c>
       <c r="Q110" t="s">
@@ -9901,7 +10019,7 @@
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" s="125">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>97</v>
       </c>
       <c r="B111" s="109" t="s">
@@ -9914,8 +10032,8 @@
       <c r="E111" s="79">
         <v>22000.97</v>
       </c>
-      <c r="F111" s="315">
-        <f t="shared" si="27"/>
+      <c r="F111" s="79">
+        <f t="shared" si="28"/>
         <v>22000.97</v>
       </c>
       <c r="G111" s="106">
@@ -9927,35 +10045,35 @@
         <v>0</v>
       </c>
       <c r="I111" s="121">
-        <f t="shared" ref="I111:I117" si="28">J$2*D111/100</f>
-        <v>11694.747559999998</v>
+        <f t="shared" ref="I111:I117" si="29">J$2*D111/100</f>
+        <v>9000</v>
       </c>
       <c r="J111" s="121">
-        <f t="shared" ref="J111:J117" si="29">E$2*D111/100</f>
+        <f t="shared" ref="J111:J117" si="30">E$2*D111/100</f>
         <v>4500</v>
       </c>
       <c r="K111" s="120">
         <f t="shared" si="21"/>
-        <v>5805.2524400000002</v>
+        <v>10266.99826</v>
       </c>
       <c r="L111" s="121"/>
       <c r="M111" s="142"/>
       <c r="N111" s="81">
         <f t="shared" si="22"/>
-        <v>22000.97</v>
+        <v>23767.97</v>
       </c>
       <c r="O111" s="135">
+        <f t="shared" si="26"/>
+        <v>24480.97</v>
+      </c>
+      <c r="P111" s="50">
         <f t="shared" si="25"/>
-        <v>22660.97</v>
-      </c>
-      <c r="P111" s="50">
-        <f t="shared" si="24"/>
         <v>0.97000000000000064</v>
       </c>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" s="125">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>98</v>
       </c>
       <c r="B112" s="109" t="s">
@@ -9968,7 +10086,7 @@
       <c r="E112" s="79">
         <v>22000.98</v>
       </c>
-      <c r="F112" s="315">
+      <c r="F112" s="79">
         <f>E112</f>
         <v>22000.98</v>
       </c>
@@ -9981,35 +10099,35 @@
         <v>0</v>
       </c>
       <c r="I112" s="121">
-        <f t="shared" si="28"/>
-        <v>11694.747559999998</v>
+        <f t="shared" si="29"/>
+        <v>9000</v>
       </c>
       <c r="J112" s="121">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>4500</v>
       </c>
       <c r="K112" s="120">
         <f t="shared" si="21"/>
-        <v>5805.2524400000002</v>
+        <v>10266.99826</v>
       </c>
       <c r="L112" s="121"/>
       <c r="M112" s="142"/>
       <c r="N112" s="81">
         <f t="shared" si="22"/>
-        <v>22000.98</v>
+        <v>23767.98</v>
       </c>
       <c r="O112" s="135">
+        <f t="shared" si="26"/>
+        <v>24480.98</v>
+      </c>
+      <c r="P112" s="50">
         <f t="shared" si="25"/>
-        <v>22660.98</v>
-      </c>
-      <c r="P112" s="50">
-        <f t="shared" si="24"/>
         <v>0.98000000000000065</v>
       </c>
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A113" s="125">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>99</v>
       </c>
       <c r="B113" s="109" t="s">
@@ -10022,8 +10140,8 @@
       <c r="E113" s="79">
         <v>22000.99</v>
       </c>
-      <c r="F113" s="315">
-        <f t="shared" si="27"/>
+      <c r="F113" s="79">
+        <f t="shared" si="28"/>
         <v>22000.99</v>
       </c>
       <c r="G113" s="106">
@@ -10035,35 +10153,35 @@
         <v>0</v>
       </c>
       <c r="I113" s="121">
-        <f t="shared" si="28"/>
-        <v>11694.747559999998</v>
+        <f t="shared" si="29"/>
+        <v>9000</v>
       </c>
       <c r="J113" s="121">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>4500</v>
       </c>
       <c r="K113" s="120">
         <f t="shared" si="21"/>
-        <v>5805.2524400000002</v>
+        <v>10266.99826</v>
       </c>
       <c r="L113" s="121"/>
       <c r="M113" s="142"/>
       <c r="N113" s="81">
         <f t="shared" si="22"/>
-        <v>22000.99</v>
+        <v>23767.99</v>
       </c>
       <c r="O113" s="135">
+        <f t="shared" si="26"/>
+        <v>24480.99</v>
+      </c>
+      <c r="P113" s="50">
         <f t="shared" si="25"/>
-        <v>22660.99</v>
-      </c>
-      <c r="P113" s="50">
-        <f t="shared" si="24"/>
         <v>0.99000000000000066</v>
       </c>
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A114" s="125">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>100</v>
       </c>
       <c r="B114" s="109" t="s">
@@ -10086,35 +10204,35 @@
         <v>0</v>
       </c>
       <c r="I114" s="121">
-        <f t="shared" si="28"/>
-        <v>11694.747559999998</v>
+        <f t="shared" si="29"/>
+        <v>9000</v>
       </c>
       <c r="J114" s="121">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>4500</v>
       </c>
       <c r="K114" s="120">
         <f t="shared" si="21"/>
-        <v>5805.2524400000002</v>
+        <v>10266.99826</v>
       </c>
       <c r="L114" s="121"/>
       <c r="M114" s="142"/>
       <c r="N114" s="81">
         <f t="shared" si="22"/>
-        <v>17195</v>
+        <v>18962</v>
       </c>
       <c r="O114" s="135">
+        <f t="shared" si="26"/>
+        <v>19531</v>
+      </c>
+      <c r="P114" s="50">
         <f t="shared" si="25"/>
-        <v>17711</v>
-      </c>
-      <c r="P114" s="50">
-        <f t="shared" si="24"/>
         <v>1.0000000000000007</v>
       </c>
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A115" s="125">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>101</v>
       </c>
       <c r="B115" s="103" t="s">
@@ -10127,7 +10245,7 @@
       <c r="E115" s="79">
         <v>22001.01</v>
       </c>
-      <c r="F115" s="315">
+      <c r="F115" s="79">
         <f>E115</f>
         <v>22001.01</v>
       </c>
@@ -10140,35 +10258,35 @@
         <v>0</v>
       </c>
       <c r="I115" s="121">
-        <f t="shared" si="28"/>
-        <v>11694.747559999998</v>
+        <f t="shared" si="29"/>
+        <v>9000</v>
       </c>
       <c r="J115" s="121">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>4500</v>
       </c>
       <c r="K115" s="120">
         <f t="shared" si="21"/>
-        <v>5805.2524400000002</v>
+        <v>10266.99826</v>
       </c>
       <c r="L115" s="121"/>
       <c r="M115" s="142"/>
       <c r="N115" s="81">
         <f t="shared" si="22"/>
-        <v>22001.01</v>
+        <v>23768.01</v>
       </c>
       <c r="O115" s="135">
+        <f t="shared" si="26"/>
+        <v>24481.01</v>
+      </c>
+      <c r="P115" s="50">
         <f t="shared" si="25"/>
-        <v>22661.01</v>
-      </c>
-      <c r="P115" s="50">
-        <f t="shared" si="24"/>
         <v>1.0100000000000007</v>
       </c>
     </row>
     <row r="116" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A116" s="125">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>102</v>
       </c>
       <c r="B116" s="103" t="s">
@@ -10181,7 +10299,7 @@
       <c r="E116" s="79">
         <v>22001.02</v>
       </c>
-      <c r="F116" s="315">
+      <c r="F116" s="79">
         <f>E116</f>
         <v>22001.02</v>
       </c>
@@ -10194,35 +10312,35 @@
         <v>0</v>
       </c>
       <c r="I116" s="121">
-        <f t="shared" si="28"/>
-        <v>11694.747559999998</v>
+        <f t="shared" si="29"/>
+        <v>9000</v>
       </c>
       <c r="J116" s="121">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>4500</v>
       </c>
       <c r="K116" s="120">
         <f t="shared" si="21"/>
-        <v>5805.2524400000002</v>
+        <v>10266.99826</v>
       </c>
       <c r="L116" s="121"/>
       <c r="M116" s="142"/>
       <c r="N116" s="81">
         <f t="shared" si="22"/>
-        <v>22001.02</v>
+        <v>23768.02</v>
       </c>
       <c r="O116" s="135">
+        <f t="shared" si="26"/>
+        <v>24481.02</v>
+      </c>
+      <c r="P116" s="50">
         <f t="shared" si="25"/>
-        <v>22661.02</v>
-      </c>
-      <c r="P116" s="50">
-        <f t="shared" si="24"/>
         <v>1.0200000000000007</v>
       </c>
     </row>
     <row r="117" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A117" s="125">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>103</v>
       </c>
       <c r="B117" s="109" t="s">
@@ -10235,7 +10353,7 @@
       <c r="E117" s="79">
         <v>22001.03</v>
       </c>
-      <c r="F117" s="315">
+      <c r="F117" s="79">
         <f>E117</f>
         <v>22001.03</v>
       </c>
@@ -10248,29 +10366,29 @@
         <v>0</v>
       </c>
       <c r="I117" s="121">
-        <f t="shared" si="28"/>
-        <v>11694.747559999998</v>
+        <f t="shared" si="29"/>
+        <v>9000</v>
       </c>
       <c r="J117" s="121">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>4500</v>
       </c>
       <c r="K117" s="120">
         <f t="shared" si="21"/>
-        <v>5805.2524400000002</v>
+        <v>10266.99826</v>
       </c>
       <c r="L117" s="121"/>
       <c r="M117" s="142"/>
       <c r="N117" s="81">
         <f t="shared" si="22"/>
-        <v>22001.03</v>
+        <v>23768.03</v>
       </c>
       <c r="O117" s="135">
+        <f t="shared" si="26"/>
+        <v>24481.03</v>
+      </c>
+      <c r="P117" s="50">
         <f t="shared" si="25"/>
-        <v>22661.03</v>
-      </c>
-      <c r="P117" s="50">
-        <f t="shared" si="24"/>
         <v>1.0300000000000007</v>
       </c>
     </row>
@@ -10297,43 +10415,43 @@
       <c r="B119" s="128"/>
       <c r="C119" s="128"/>
       <c r="D119" s="129">
-        <f t="shared" ref="D119:O119" si="30">SUM(D15:D118)</f>
+        <f t="shared" ref="D119:O119" si="31">SUM(D15:D118)</f>
         <v>100.15999999999993</v>
       </c>
       <c r="E119" s="130">
-        <f t="shared" si="30"/>
-        <v>47152096.559999995</v>
-      </c>
-      <c r="F119" s="218">
+        <f t="shared" si="31"/>
+        <v>47168728.960000001</v>
+      </c>
+      <c r="F119" s="217">
         <f>SUM(F15:F118)</f>
-        <v>18974843.529999997</v>
+        <v>20030676.670000002</v>
       </c>
       <c r="G119" s="131">
-        <f t="shared" si="30"/>
-        <v>28177253.030000001</v>
+        <f t="shared" si="31"/>
+        <v>27138052.289999999</v>
       </c>
       <c r="H119" s="131">
-        <f t="shared" si="30"/>
-        <v>754188.30630000005</v>
+        <f t="shared" si="31"/>
+        <v>737556.28410000005</v>
       </c>
       <c r="I119" s="132">
-        <f t="shared" si="30"/>
-        <v>11713459.156095987</v>
+        <f t="shared" si="31"/>
+        <v>9014400</v>
       </c>
       <c r="J119" s="131">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>4507200</v>
       </c>
       <c r="K119" s="133"/>
       <c r="L119" s="133"/>
       <c r="M119" s="144"/>
       <c r="N119" s="140">
-        <f t="shared" si="30"/>
-        <v>52007993.560000002</v>
+        <f t="shared" si="31"/>
+        <v>52861973.560000002</v>
       </c>
       <c r="O119" s="137">
-        <f t="shared" si="30"/>
-        <v>53568230.560000002</v>
+        <f t="shared" si="31"/>
+        <v>54447842.560000002</v>
       </c>
     </row>
     <row r="120" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10342,96 +10460,96 @@
     </row>
     <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="122" spans="1:16" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B122" s="283" t="s">
+      <c r="B122" s="261" t="s">
         <v>103</v>
       </c>
-      <c r="C122" s="283"/>
-      <c r="D122" s="283"/>
-      <c r="E122" s="283"/>
-      <c r="F122" s="283"/>
-      <c r="G122" s="283"/>
-      <c r="H122" s="283"/>
-      <c r="I122" s="283"/>
-      <c r="J122" s="283"/>
-      <c r="K122" s="283"/>
-      <c r="L122" s="283"/>
-      <c r="M122" s="283"/>
-      <c r="N122" s="283"/>
+      <c r="C122" s="261"/>
+      <c r="D122" s="261"/>
+      <c r="E122" s="261"/>
+      <c r="F122" s="261"/>
+      <c r="G122" s="261"/>
+      <c r="H122" s="261"/>
+      <c r="I122" s="261"/>
+      <c r="J122" s="261"/>
+      <c r="K122" s="261"/>
+      <c r="L122" s="261"/>
+      <c r="M122" s="261"/>
+      <c r="N122" s="261"/>
     </row>
     <row r="123" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B123" s="283"/>
-      <c r="C123" s="283"/>
-      <c r="D123" s="283"/>
-      <c r="E123" s="283"/>
-      <c r="F123" s="283"/>
-      <c r="G123" s="283"/>
-      <c r="H123" s="283"/>
-      <c r="I123" s="283"/>
-      <c r="J123" s="283"/>
-      <c r="K123" s="283"/>
-      <c r="L123" s="283"/>
-      <c r="M123" s="283"/>
-      <c r="N123" s="283"/>
+      <c r="B123" s="261"/>
+      <c r="C123" s="261"/>
+      <c r="D123" s="261"/>
+      <c r="E123" s="261"/>
+      <c r="F123" s="261"/>
+      <c r="G123" s="261"/>
+      <c r="H123" s="261"/>
+      <c r="I123" s="261"/>
+      <c r="J123" s="261"/>
+      <c r="K123" s="261"/>
+      <c r="L123" s="261"/>
+      <c r="M123" s="261"/>
+      <c r="N123" s="261"/>
     </row>
     <row r="124" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B124" s="283"/>
-      <c r="C124" s="283"/>
-      <c r="D124" s="283"/>
-      <c r="E124" s="283"/>
-      <c r="F124" s="283"/>
-      <c r="G124" s="283"/>
-      <c r="H124" s="283"/>
-      <c r="I124" s="283"/>
-      <c r="J124" s="283"/>
-      <c r="K124" s="283"/>
-      <c r="L124" s="283"/>
-      <c r="M124" s="283"/>
-      <c r="N124" s="283"/>
+      <c r="B124" s="261"/>
+      <c r="C124" s="261"/>
+      <c r="D124" s="261"/>
+      <c r="E124" s="261"/>
+      <c r="F124" s="261"/>
+      <c r="G124" s="261"/>
+      <c r="H124" s="261"/>
+      <c r="I124" s="261"/>
+      <c r="J124" s="261"/>
+      <c r="K124" s="261"/>
+      <c r="L124" s="261"/>
+      <c r="M124" s="261"/>
+      <c r="N124" s="261"/>
     </row>
     <row r="125" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B125" s="283"/>
-      <c r="C125" s="283"/>
-      <c r="D125" s="283"/>
-      <c r="E125" s="283"/>
-      <c r="F125" s="283"/>
-      <c r="G125" s="283"/>
-      <c r="H125" s="283"/>
-      <c r="I125" s="283"/>
-      <c r="J125" s="283"/>
-      <c r="K125" s="283"/>
-      <c r="L125" s="283"/>
-      <c r="M125" s="283"/>
-      <c r="N125" s="283"/>
+      <c r="B125" s="261"/>
+      <c r="C125" s="261"/>
+      <c r="D125" s="261"/>
+      <c r="E125" s="261"/>
+      <c r="F125" s="261"/>
+      <c r="G125" s="261"/>
+      <c r="H125" s="261"/>
+      <c r="I125" s="261"/>
+      <c r="J125" s="261"/>
+      <c r="K125" s="261"/>
+      <c r="L125" s="261"/>
+      <c r="M125" s="261"/>
+      <c r="N125" s="261"/>
     </row>
     <row r="126" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B126" s="283"/>
-      <c r="C126" s="283"/>
-      <c r="D126" s="283"/>
-      <c r="E126" s="283"/>
-      <c r="F126" s="283"/>
-      <c r="G126" s="283"/>
-      <c r="H126" s="283"/>
-      <c r="I126" s="283"/>
-      <c r="J126" s="283"/>
-      <c r="K126" s="283"/>
-      <c r="L126" s="283"/>
-      <c r="M126" s="283"/>
-      <c r="N126" s="283"/>
+      <c r="B126" s="261"/>
+      <c r="C126" s="261"/>
+      <c r="D126" s="261"/>
+      <c r="E126" s="261"/>
+      <c r="F126" s="261"/>
+      <c r="G126" s="261"/>
+      <c r="H126" s="261"/>
+      <c r="I126" s="261"/>
+      <c r="J126" s="261"/>
+      <c r="K126" s="261"/>
+      <c r="L126" s="261"/>
+      <c r="M126" s="261"/>
+      <c r="N126" s="261"/>
     </row>
     <row r="127" spans="1:16" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B127" s="283"/>
-      <c r="C127" s="283"/>
-      <c r="D127" s="283"/>
-      <c r="E127" s="283"/>
-      <c r="F127" s="283"/>
-      <c r="G127" s="283"/>
-      <c r="H127" s="283"/>
-      <c r="I127" s="283"/>
-      <c r="J127" s="283"/>
-      <c r="K127" s="283"/>
-      <c r="L127" s="283"/>
-      <c r="M127" s="283"/>
-      <c r="N127" s="283"/>
+      <c r="B127" s="261"/>
+      <c r="C127" s="261"/>
+      <c r="D127" s="261"/>
+      <c r="E127" s="261"/>
+      <c r="F127" s="261"/>
+      <c r="G127" s="261"/>
+      <c r="H127" s="261"/>
+      <c r="I127" s="261"/>
+      <c r="J127" s="261"/>
+      <c r="K127" s="261"/>
+      <c r="L127" s="261"/>
+      <c r="M127" s="261"/>
+      <c r="N127" s="261"/>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B130">
@@ -10456,6 +10574,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A11:O11"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="K13:K14"/>
     <mergeCell ref="B122:N127"/>
     <mergeCell ref="D1:N1"/>
     <mergeCell ref="A4:O8"/>
@@ -10472,12 +10596,6 @@
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="I13:I14"/>
     <mergeCell ref="L13:L14"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="A10:O10"/>
-    <mergeCell ref="A11:O11"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="K13:K14"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="70" orientation="landscape" r:id="rId1"/>
@@ -10525,8 +10643,8 @@
         <v>191</v>
       </c>
       <c r="J5" s="163"/>
-      <c r="K5" s="316"/>
-      <c r="L5" s="316"/>
+      <c r="K5" s="240"/>
+      <c r="L5" s="240"/>
       <c r="M5" s="19"/>
       <c r="N5" s="19"/>
     </row>
@@ -10547,8 +10665,8 @@
         <v>219</v>
       </c>
       <c r="J6" s="163"/>
-      <c r="K6" s="316"/>
-      <c r="L6" s="316"/>
+      <c r="K6" s="240"/>
+      <c r="L6" s="240"/>
       <c r="M6" s="19"/>
       <c r="N6" s="19"/>
     </row>
@@ -10557,74 +10675,74 @@
         <v>195</v>
       </c>
       <c r="J7" s="163"/>
-      <c r="K7" s="316"/>
-      <c r="L7" s="316"/>
+      <c r="K7" s="240"/>
+      <c r="L7" s="240"/>
       <c r="M7" s="19"/>
       <c r="N7" s="19"/>
     </row>
     <row r="8" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C8" s="309" t="s">
-        <v>230</v>
-      </c>
-      <c r="D8" s="310"/>
-      <c r="E8" s="310"/>
-      <c r="F8" s="310"/>
-      <c r="G8" s="310"/>
-      <c r="H8" s="310"/>
-      <c r="I8" s="310"/>
-      <c r="J8" s="311"/>
-      <c r="K8" s="316"/>
-      <c r="L8" s="316"/>
+      <c r="C8" s="301" t="s">
+        <v>227</v>
+      </c>
+      <c r="D8" s="302"/>
+      <c r="E8" s="302"/>
+      <c r="F8" s="302"/>
+      <c r="G8" s="302"/>
+      <c r="H8" s="302"/>
+      <c r="I8" s="302"/>
+      <c r="J8" s="303"/>
+      <c r="K8" s="240"/>
+      <c r="L8" s="240"/>
       <c r="M8" s="19"/>
       <c r="N8" s="19"/>
     </row>
     <row r="9" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="312"/>
-      <c r="D9" s="313"/>
-      <c r="E9" s="313"/>
-      <c r="F9" s="313"/>
-      <c r="G9" s="313"/>
-      <c r="H9" s="313"/>
-      <c r="I9" s="313"/>
-      <c r="J9" s="314"/>
+      <c r="C9" s="304"/>
+      <c r="D9" s="305"/>
+      <c r="E9" s="305"/>
+      <c r="F9" s="305"/>
+      <c r="G9" s="305"/>
+      <c r="H9" s="305"/>
+      <c r="I9" s="305"/>
+      <c r="J9" s="306"/>
       <c r="K9" s="19"/>
       <c r="L9" s="19"/>
       <c r="M9" s="19"/>
       <c r="N9" s="19"/>
     </row>
     <row r="10" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C10" s="226"/>
-      <c r="D10" s="226"/>
-      <c r="E10" s="226"/>
-      <c r="F10" s="226"/>
-      <c r="G10" s="226"/>
-      <c r="H10" s="226"/>
-      <c r="I10" s="226"/>
-      <c r="J10" s="226"/>
+      <c r="C10" s="225"/>
+      <c r="D10" s="225"/>
+      <c r="E10" s="225"/>
+      <c r="F10" s="225"/>
+      <c r="G10" s="225"/>
+      <c r="H10" s="225"/>
+      <c r="I10" s="225"/>
+      <c r="J10" s="225"/>
       <c r="K10" s="19"/>
       <c r="L10" s="19"/>
       <c r="M10" s="19"/>
       <c r="N10" s="19"/>
     </row>
     <row r="11" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C11" s="226"/>
-      <c r="D11" s="226"/>
-      <c r="E11" s="226"/>
-      <c r="F11" s="226"/>
-      <c r="G11" s="226"/>
-      <c r="H11" s="226"/>
-      <c r="I11" s="226"/>
-      <c r="J11" s="226"/>
+      <c r="C11" s="225"/>
+      <c r="D11" s="225"/>
+      <c r="E11" s="225"/>
+      <c r="F11" s="225"/>
+      <c r="G11" s="225"/>
+      <c r="H11" s="225"/>
+      <c r="I11" s="225"/>
+      <c r="J11" s="225"/>
       <c r="K11" s="19"/>
       <c r="L11" s="19"/>
       <c r="M11" s="19"/>
       <c r="N11" s="19"/>
     </row>
     <row r="12" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C12" s="227" t="s">
+      <c r="C12" s="226" t="s">
         <v>188</v>
       </c>
-      <c r="D12" s="228">
+      <c r="D12" s="227">
         <f>D4+1</f>
         <v>2</v>
       </c>
@@ -10634,16 +10752,16 @@
       <c r="H12" s="161"/>
       <c r="I12" s="161"/>
       <c r="J12" s="162"/>
-      <c r="K12" s="316"/>
-      <c r="L12" s="316"/>
+      <c r="K12" s="240"/>
+      <c r="L12" s="240"/>
       <c r="M12" s="19"/>
       <c r="N12" s="19"/>
     </row>
     <row r="13" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C13" s="229" t="s">
+      <c r="C13" s="228" t="s">
         <v>189</v>
       </c>
-      <c r="D13" s="230"/>
+      <c r="D13" s="229"/>
       <c r="E13" t="s">
         <v>190</v>
       </c>
@@ -10651,16 +10769,16 @@
         <v>191</v>
       </c>
       <c r="J13" s="163"/>
-      <c r="K13" s="316"/>
-      <c r="L13" s="316"/>
+      <c r="K13" s="240"/>
+      <c r="L13" s="240"/>
       <c r="M13" s="19"/>
       <c r="N13" s="19"/>
     </row>
     <row r="14" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C14" s="229" t="s">
+      <c r="C14" s="228" t="s">
         <v>192</v>
       </c>
-      <c r="D14" s="230" t="s">
+      <c r="D14" s="229" t="s">
         <v>193</v>
       </c>
       <c r="E14" t="s">
@@ -10670,11 +10788,11 @@
         <v>127</v>
       </c>
       <c r="H14" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="J14" s="163"/>
-      <c r="K14" s="316"/>
-      <c r="L14" s="316"/>
+      <c r="K14" s="240"/>
+      <c r="L14" s="240"/>
       <c r="M14" s="19"/>
       <c r="N14" s="19"/>
     </row>
@@ -10683,36 +10801,36 @@
         <v>195</v>
       </c>
       <c r="J15" s="163"/>
-      <c r="K15" s="316"/>
-      <c r="L15" s="316"/>
+      <c r="K15" s="240"/>
+      <c r="L15" s="240"/>
       <c r="M15" s="19"/>
       <c r="N15" s="19"/>
     </row>
     <row r="16" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C16" s="309" t="s">
-        <v>235</v>
-      </c>
-      <c r="D16" s="310"/>
-      <c r="E16" s="310"/>
-      <c r="F16" s="310"/>
-      <c r="G16" s="310"/>
-      <c r="H16" s="310"/>
-      <c r="I16" s="310"/>
-      <c r="J16" s="311"/>
-      <c r="K16" s="316"/>
-      <c r="L16" s="316"/>
+      <c r="C16" s="301" t="s">
+        <v>232</v>
+      </c>
+      <c r="D16" s="302"/>
+      <c r="E16" s="302"/>
+      <c r="F16" s="302"/>
+      <c r="G16" s="302"/>
+      <c r="H16" s="302"/>
+      <c r="I16" s="302"/>
+      <c r="J16" s="303"/>
+      <c r="K16" s="240"/>
+      <c r="L16" s="240"/>
       <c r="M16" s="19"/>
       <c r="N16" s="19"/>
     </row>
     <row r="17" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="312"/>
-      <c r="D17" s="313"/>
-      <c r="E17" s="313"/>
-      <c r="F17" s="313"/>
-      <c r="G17" s="313"/>
-      <c r="H17" s="313"/>
-      <c r="I17" s="313"/>
-      <c r="J17" s="314"/>
+      <c r="C17" s="304"/>
+      <c r="D17" s="305"/>
+      <c r="E17" s="305"/>
+      <c r="F17" s="305"/>
+      <c r="G17" s="305"/>
+      <c r="H17" s="305"/>
+      <c r="I17" s="305"/>
+      <c r="J17" s="306"/>
     </row>
     <row r="21" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="22" spans="3:13" x14ac:dyDescent="0.25">
@@ -10729,9 +10847,9 @@
       <c r="H22" s="161"/>
       <c r="I22" s="161"/>
       <c r="J22" s="162"/>
-      <c r="K22" s="316"/>
-      <c r="L22" s="316"/>
-      <c r="M22" s="316"/>
+      <c r="K22" s="240"/>
+      <c r="L22" s="240"/>
+      <c r="M22" s="240"/>
     </row>
     <row r="23" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C23" s="201" t="s">
@@ -10745,9 +10863,9 @@
         <v>191</v>
       </c>
       <c r="J23" s="163"/>
-      <c r="K23" s="316"/>
-      <c r="L23" s="316"/>
-      <c r="M23" s="316"/>
+      <c r="K23" s="240"/>
+      <c r="L23" s="240"/>
+      <c r="M23" s="240"/>
     </row>
     <row r="24" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C24" s="201" t="s">
@@ -10763,53 +10881,53 @@
         <v>127</v>
       </c>
       <c r="J24" s="163"/>
-      <c r="K24" s="316"/>
-      <c r="L24" s="316"/>
-      <c r="M24" s="316"/>
+      <c r="K24" s="240"/>
+      <c r="L24" s="240"/>
+      <c r="M24" s="240"/>
     </row>
     <row r="25" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C25" s="47" t="s">
         <v>195</v>
       </c>
       <c r="J25" s="163"/>
-      <c r="K25" s="316"/>
-      <c r="L25" s="316"/>
-      <c r="M25" s="316"/>
+      <c r="K25" s="240"/>
+      <c r="L25" s="240"/>
+      <c r="M25" s="240"/>
     </row>
     <row r="26" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C26" s="309" t="s">
-        <v>231</v>
-      </c>
-      <c r="D26" s="310"/>
-      <c r="E26" s="310"/>
-      <c r="F26" s="310"/>
-      <c r="G26" s="310"/>
-      <c r="H26" s="310"/>
-      <c r="I26" s="310"/>
-      <c r="J26" s="311"/>
-      <c r="K26" s="316"/>
-      <c r="L26" s="316"/>
-      <c r="M26" s="316"/>
+      <c r="C26" s="301" t="s">
+        <v>228</v>
+      </c>
+      <c r="D26" s="302"/>
+      <c r="E26" s="302"/>
+      <c r="F26" s="302"/>
+      <c r="G26" s="302"/>
+      <c r="H26" s="302"/>
+      <c r="I26" s="302"/>
+      <c r="J26" s="303"/>
+      <c r="K26" s="240"/>
+      <c r="L26" s="240"/>
+      <c r="M26" s="240"/>
     </row>
     <row r="27" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C27" s="312"/>
-      <c r="D27" s="313"/>
-      <c r="E27" s="313"/>
-      <c r="F27" s="313"/>
-      <c r="G27" s="313"/>
-      <c r="H27" s="313"/>
-      <c r="I27" s="313"/>
-      <c r="J27" s="314"/>
-      <c r="K27" s="316"/>
-      <c r="L27" s="316"/>
-      <c r="M27" s="316"/>
+      <c r="C27" s="304"/>
+      <c r="D27" s="305"/>
+      <c r="E27" s="305"/>
+      <c r="F27" s="305"/>
+      <c r="G27" s="305"/>
+      <c r="H27" s="305"/>
+      <c r="I27" s="305"/>
+      <c r="J27" s="306"/>
+      <c r="K27" s="240"/>
+      <c r="L27" s="240"/>
+      <c r="M27" s="240"/>
     </row>
     <row r="29" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="30" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C30" s="219" t="s">
+      <c r="C30" s="218" t="s">
         <v>188</v>
       </c>
-      <c r="D30" s="220">
+      <c r="D30" s="219">
         <f>D22+1</f>
         <v>3</v>
       </c>
@@ -10821,7 +10939,7 @@
       <c r="J30" s="162"/>
     </row>
     <row r="31" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C31" s="221" t="s">
+      <c r="C31" s="220" t="s">
         <v>189</v>
       </c>
       <c r="D31" s="19"/>
@@ -10834,7 +10952,7 @@
       <c r="J31" s="163"/>
     </row>
     <row r="32" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C32" s="221" t="s">
+      <c r="C32" s="220" t="s">
         <v>192</v>
       </c>
       <c r="D32" s="19" t="s">
@@ -10852,40 +10970,40 @@
       <c r="J32" s="163"/>
     </row>
     <row r="33" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C33" s="221" t="s">
+      <c r="C33" s="220" t="s">
         <v>195</v>
       </c>
       <c r="D33" s="19"/>
       <c r="J33" s="163"/>
     </row>
     <row r="34" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C34" s="309" t="s">
-        <v>232</v>
-      </c>
-      <c r="D34" s="310"/>
-      <c r="E34" s="310"/>
-      <c r="F34" s="310"/>
-      <c r="G34" s="310"/>
-      <c r="H34" s="310"/>
-      <c r="I34" s="310"/>
-      <c r="J34" s="311"/>
+      <c r="C34" s="301" t="s">
+        <v>229</v>
+      </c>
+      <c r="D34" s="302"/>
+      <c r="E34" s="302"/>
+      <c r="F34" s="302"/>
+      <c r="G34" s="302"/>
+      <c r="H34" s="302"/>
+      <c r="I34" s="302"/>
+      <c r="J34" s="303"/>
     </row>
     <row r="35" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C35" s="312"/>
-      <c r="D35" s="313"/>
-      <c r="E35" s="313"/>
-      <c r="F35" s="313"/>
-      <c r="G35" s="313"/>
-      <c r="H35" s="313"/>
-      <c r="I35" s="313"/>
-      <c r="J35" s="314"/>
+      <c r="C35" s="304"/>
+      <c r="D35" s="305"/>
+      <c r="E35" s="305"/>
+      <c r="F35" s="305"/>
+      <c r="G35" s="305"/>
+      <c r="H35" s="305"/>
+      <c r="I35" s="305"/>
+      <c r="J35" s="306"/>
     </row>
     <row r="37" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="38" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C38" s="222" t="s">
+      <c r="C38" s="221" t="s">
         <v>188</v>
       </c>
-      <c r="D38" s="223">
+      <c r="D38" s="222">
         <f>D30+1</f>
         <v>4</v>
       </c>
@@ -10897,10 +11015,10 @@
       <c r="J38" s="162"/>
     </row>
     <row r="39" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C39" s="224" t="s">
+      <c r="C39" s="223" t="s">
         <v>189</v>
       </c>
-      <c r="D39" s="225"/>
+      <c r="D39" s="224"/>
       <c r="E39" t="s">
         <v>190</v>
       </c>
@@ -10908,15 +11026,15 @@
         <v>191</v>
       </c>
       <c r="J39" s="163"/>
-      <c r="K39" s="316"/>
-      <c r="L39" s="316"/>
-      <c r="M39" s="316"/>
+      <c r="K39" s="240"/>
+      <c r="L39" s="240"/>
+      <c r="M39" s="240"/>
     </row>
     <row r="40" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C40" s="224" t="s">
+      <c r="C40" s="223" t="s">
         <v>192</v>
       </c>
-      <c r="D40" s="225" t="s">
+      <c r="D40" s="224" t="s">
         <v>193</v>
       </c>
       <c r="E40" t="s">
@@ -10926,57 +11044,57 @@
         <v>127</v>
       </c>
       <c r="H40" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="J40" s="163"/>
-      <c r="K40" s="316"/>
-      <c r="L40" s="316"/>
-      <c r="M40" s="316"/>
+      <c r="K40" s="240"/>
+      <c r="L40" s="240"/>
+      <c r="M40" s="240"/>
     </row>
     <row r="41" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="221" t="s">
+      <c r="C41" s="220" t="s">
         <v>195</v>
       </c>
       <c r="D41" s="19"/>
       <c r="J41" s="163"/>
-      <c r="K41" s="316"/>
-      <c r="L41" s="316"/>
-      <c r="M41" s="316"/>
+      <c r="K41" s="240"/>
+      <c r="L41" s="240"/>
+      <c r="M41" s="240"/>
     </row>
     <row r="42" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C42" s="309" t="s">
-        <v>234</v>
-      </c>
-      <c r="D42" s="310"/>
-      <c r="E42" s="310"/>
-      <c r="F42" s="310"/>
-      <c r="G42" s="310"/>
-      <c r="H42" s="310"/>
-      <c r="I42" s="310"/>
-      <c r="J42" s="311"/>
-      <c r="K42" s="316"/>
-      <c r="L42" s="316"/>
-      <c r="M42" s="316"/>
+      <c r="C42" s="301" t="s">
+        <v>231</v>
+      </c>
+      <c r="D42" s="302"/>
+      <c r="E42" s="302"/>
+      <c r="F42" s="302"/>
+      <c r="G42" s="302"/>
+      <c r="H42" s="302"/>
+      <c r="I42" s="302"/>
+      <c r="J42" s="303"/>
+      <c r="K42" s="240"/>
+      <c r="L42" s="240"/>
+      <c r="M42" s="240"/>
     </row>
     <row r="43" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C43" s="312"/>
-      <c r="D43" s="313"/>
-      <c r="E43" s="313"/>
-      <c r="F43" s="313"/>
-      <c r="G43" s="313"/>
-      <c r="H43" s="313"/>
-      <c r="I43" s="313"/>
-      <c r="J43" s="314"/>
-      <c r="K43" s="316"/>
-      <c r="L43" s="316"/>
-      <c r="M43" s="316"/>
+      <c r="C43" s="304"/>
+      <c r="D43" s="305"/>
+      <c r="E43" s="305"/>
+      <c r="F43" s="305"/>
+      <c r="G43" s="305"/>
+      <c r="H43" s="305"/>
+      <c r="I43" s="305"/>
+      <c r="J43" s="306"/>
+      <c r="K43" s="240"/>
+      <c r="L43" s="240"/>
+      <c r="M43" s="240"/>
     </row>
     <row r="45" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="46" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C46" s="231" t="s">
+      <c r="C46" s="230" t="s">
         <v>188</v>
       </c>
-      <c r="D46" s="232">
+      <c r="D46" s="231">
         <f>D38+1</f>
         <v>5</v>
       </c>
@@ -10986,15 +11104,15 @@
       <c r="H46" s="161"/>
       <c r="I46" s="161"/>
       <c r="J46" s="162"/>
-      <c r="K46" s="316"/>
-      <c r="L46" s="316"/>
-      <c r="M46" s="316"/>
+      <c r="K46" s="240"/>
+      <c r="L46" s="240"/>
+      <c r="M46" s="240"/>
     </row>
     <row r="47" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C47" s="233" t="s">
+      <c r="C47" s="232" t="s">
         <v>189</v>
       </c>
-      <c r="D47" s="234"/>
+      <c r="D47" s="233"/>
       <c r="E47" t="s">
         <v>190</v>
       </c>
@@ -11002,15 +11120,15 @@
         <v>191</v>
       </c>
       <c r="J47" s="163"/>
-      <c r="K47" s="316"/>
-      <c r="L47" s="316"/>
-      <c r="M47" s="316"/>
+      <c r="K47" s="240"/>
+      <c r="L47" s="240"/>
+      <c r="M47" s="240"/>
     </row>
     <row r="48" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C48" s="233" t="s">
+      <c r="C48" s="232" t="s">
         <v>192</v>
       </c>
-      <c r="D48" s="234" t="s">
+      <c r="D48" s="233" t="s">
         <v>193</v>
       </c>
       <c r="E48" t="s">
@@ -11020,57 +11138,57 @@
         <v>127</v>
       </c>
       <c r="H48" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="J48" s="163"/>
-      <c r="K48" s="316"/>
-      <c r="L48" s="316"/>
-      <c r="M48" s="316"/>
+      <c r="K48" s="240"/>
+      <c r="L48" s="240"/>
+      <c r="M48" s="240"/>
     </row>
     <row r="49" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C49" s="233" t="s">
+      <c r="C49" s="232" t="s">
         <v>195</v>
       </c>
-      <c r="D49" s="234"/>
+      <c r="D49" s="233"/>
       <c r="J49" s="163"/>
-      <c r="K49" s="316"/>
-      <c r="L49" s="316"/>
-      <c r="M49" s="316"/>
+      <c r="K49" s="240"/>
+      <c r="L49" s="240"/>
+      <c r="M49" s="240"/>
     </row>
     <row r="50" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C50" s="309" t="s">
-        <v>238</v>
-      </c>
-      <c r="D50" s="310"/>
-      <c r="E50" s="310"/>
-      <c r="F50" s="310"/>
-      <c r="G50" s="310"/>
-      <c r="H50" s="310"/>
-      <c r="I50" s="310"/>
-      <c r="J50" s="311"/>
-      <c r="K50" s="316"/>
-      <c r="L50" s="316"/>
-      <c r="M50" s="316"/>
+      <c r="C50" s="301" t="s">
+        <v>235</v>
+      </c>
+      <c r="D50" s="302"/>
+      <c r="E50" s="302"/>
+      <c r="F50" s="302"/>
+      <c r="G50" s="302"/>
+      <c r="H50" s="302"/>
+      <c r="I50" s="302"/>
+      <c r="J50" s="303"/>
+      <c r="K50" s="240"/>
+      <c r="L50" s="240"/>
+      <c r="M50" s="240"/>
     </row>
     <row r="51" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C51" s="312"/>
-      <c r="D51" s="313"/>
-      <c r="E51" s="313"/>
-      <c r="F51" s="313"/>
-      <c r="G51" s="313"/>
-      <c r="H51" s="313"/>
-      <c r="I51" s="313"/>
-      <c r="J51" s="314"/>
-      <c r="K51" s="316"/>
-      <c r="L51" s="316"/>
-      <c r="M51" s="316"/>
+      <c r="C51" s="304"/>
+      <c r="D51" s="305"/>
+      <c r="E51" s="305"/>
+      <c r="F51" s="305"/>
+      <c r="G51" s="305"/>
+      <c r="H51" s="305"/>
+      <c r="I51" s="305"/>
+      <c r="J51" s="306"/>
+      <c r="K51" s="240"/>
+      <c r="L51" s="240"/>
+      <c r="M51" s="240"/>
     </row>
     <row r="53" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="54" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C54" s="237" t="s">
+      <c r="C54" s="235" t="s">
         <v>188</v>
       </c>
-      <c r="D54" s="238">
+      <c r="D54" s="236">
         <f>D46+1</f>
         <v>6</v>
       </c>
@@ -11080,16 +11198,16 @@
       <c r="H54" s="161"/>
       <c r="I54" s="161"/>
       <c r="J54" s="162"/>
-      <c r="K54" s="316"/>
-      <c r="L54" s="316"/>
-      <c r="M54" s="316"/>
-      <c r="N54" s="316"/>
+      <c r="K54" s="240"/>
+      <c r="L54" s="240"/>
+      <c r="M54" s="240"/>
+      <c r="N54" s="240"/>
     </row>
     <row r="55" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C55" s="239" t="s">
+      <c r="C55" s="237" t="s">
         <v>189</v>
       </c>
-      <c r="D55" s="240"/>
+      <c r="D55" s="238"/>
       <c r="E55" t="s">
         <v>190</v>
       </c>
@@ -11097,16 +11215,16 @@
         <v>191</v>
       </c>
       <c r="J55" s="163"/>
-      <c r="K55" s="316"/>
-      <c r="L55" s="316"/>
-      <c r="M55" s="316"/>
-      <c r="N55" s="316"/>
+      <c r="K55" s="240"/>
+      <c r="L55" s="240"/>
+      <c r="M55" s="240"/>
+      <c r="N55" s="240"/>
     </row>
     <row r="56" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C56" s="239" t="s">
+      <c r="C56" s="237" t="s">
         <v>192</v>
       </c>
-      <c r="D56" s="240" t="s">
+      <c r="D56" s="238" t="s">
         <v>193</v>
       </c>
       <c r="E56" t="s">
@@ -11116,66 +11234,66 @@
         <v>127</v>
       </c>
       <c r="H56" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="J56" s="163"/>
-      <c r="K56" s="316"/>
-      <c r="L56" s="316"/>
-      <c r="M56" s="316"/>
-      <c r="N56" s="316"/>
+      <c r="K56" s="240"/>
+      <c r="L56" s="240"/>
+      <c r="M56" s="240"/>
+      <c r="N56" s="240"/>
     </row>
     <row r="57" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C57" s="239" t="s">
+      <c r="C57" s="237" t="s">
         <v>195</v>
       </c>
-      <c r="D57" s="240"/>
+      <c r="D57" s="238"/>
       <c r="J57" s="163"/>
-      <c r="K57" s="316"/>
-      <c r="L57" s="316"/>
-      <c r="M57" s="316"/>
-      <c r="N57" s="316"/>
+      <c r="K57" s="240"/>
+      <c r="L57" s="240"/>
+      <c r="M57" s="240"/>
+      <c r="N57" s="240"/>
     </row>
     <row r="58" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C58" s="309" t="s">
-        <v>251</v>
-      </c>
-      <c r="D58" s="310"/>
-      <c r="E58" s="310"/>
-      <c r="F58" s="310"/>
-      <c r="G58" s="310"/>
-      <c r="H58" s="310"/>
-      <c r="I58" s="310"/>
-      <c r="J58" s="311"/>
-      <c r="K58" s="316"/>
-      <c r="L58" s="316"/>
-      <c r="M58" s="316"/>
-      <c r="N58" s="316"/>
+      <c r="C58" s="301" t="s">
+        <v>248</v>
+      </c>
+      <c r="D58" s="302"/>
+      <c r="E58" s="302"/>
+      <c r="F58" s="302"/>
+      <c r="G58" s="302"/>
+      <c r="H58" s="302"/>
+      <c r="I58" s="302"/>
+      <c r="J58" s="303"/>
+      <c r="K58" s="240"/>
+      <c r="L58" s="240"/>
+      <c r="M58" s="240"/>
+      <c r="N58" s="240"/>
     </row>
     <row r="59" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C59" s="312"/>
-      <c r="D59" s="313"/>
-      <c r="E59" s="313"/>
-      <c r="F59" s="313"/>
-      <c r="G59" s="313"/>
-      <c r="H59" s="313"/>
-      <c r="I59" s="313"/>
-      <c r="J59" s="314"/>
-      <c r="K59" s="316"/>
-      <c r="L59" s="316"/>
-      <c r="M59" s="316"/>
-      <c r="N59" s="316"/>
+      <c r="C59" s="304"/>
+      <c r="D59" s="305"/>
+      <c r="E59" s="305"/>
+      <c r="F59" s="305"/>
+      <c r="G59" s="305"/>
+      <c r="H59" s="305"/>
+      <c r="I59" s="305"/>
+      <c r="J59" s="306"/>
+      <c r="K59" s="240"/>
+      <c r="L59" s="240"/>
+      <c r="M59" s="240"/>
+      <c r="N59" s="240"/>
     </row>
     <row r="60" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="K60" s="316"/>
-      <c r="L60" s="316"/>
-      <c r="M60" s="316"/>
-      <c r="N60" s="316"/>
+      <c r="K60" s="240"/>
+      <c r="L60" s="240"/>
+      <c r="M60" s="240"/>
+      <c r="N60" s="240"/>
     </row>
     <row r="61" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="K61" s="316"/>
-      <c r="L61" s="316"/>
-      <c r="M61" s="316"/>
-      <c r="N61" s="316"/>
+      <c r="K61" s="240"/>
+      <c r="L61" s="240"/>
+      <c r="M61" s="240"/>
+      <c r="N61" s="240"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/2026/ITALIA/Septiembre/Septiembre ITALIA.xlsx
+++ b/2026/ITALIA/Septiembre/Septiembre ITALIA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\ITALIA\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ITALIA\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4F1488B-2BF0-4369-90E0-A3C5C5A195D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32E69BBF-0E95-427C-A90D-65BCBDEB77EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
@@ -22,16 +22,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$174</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="292">
   <si>
     <t>TOTAL</t>
   </si>
@@ -700,9 +695,6 @@
     <t>AYSA:</t>
   </si>
   <si>
-    <t>10A</t>
-  </si>
-  <si>
     <t>Plan de pago 5E: Consta de 6 cuotas mensuales de $190.000 + expensas en curso</t>
   </si>
   <si>
@@ -724,35 +716,6 @@
     <t>FCI - SALDO INICIAL</t>
   </si>
   <si>
-    <t xml:space="preserve">10A deposito $300.000 el 08/09
-</t>
-  </si>
-  <si>
-    <t>4A pago $297.000,02 el 09/08 LE ERRO A LOS CENTAVOS</t>
-  </si>
-  <si>
-    <t>Agregar a panchomorena27@gmail.com a la cadena de mail</t>
-  </si>
-  <si>
-    <t>03 - PB C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deposito $162.000 14/09 y se transfirió saldo $800,03.
-</t>
-  </si>
-  <si>
-    <t>Ricardo Vega transfirio $307.000 el 04/09</t>
-  </si>
-  <si>
-    <t>1A</t>
-  </si>
-  <si>
-    <t>6F - UF 46</t>
-  </si>
-  <si>
-    <t>Deposito 17/09 $250.000</t>
-  </si>
-  <si>
     <t>VTO 16/10</t>
   </si>
   <si>
@@ -787,12 +750,6 @@
   </si>
   <si>
     <t>Grafica Tauge - Fotocopias Byn</t>
-  </si>
-  <si>
-    <t>El deposito no identificado de $200000 7/7 es del 9F</t>
-  </si>
-  <si>
-    <t>9F</t>
   </si>
   <si>
     <t>Bayeto Gabriela Paola - Aporte notarial sellos, protocolo, testimonio e impresión de fotografias - Honorarios de acta de constatacion</t>
@@ -960,6 +917,39 @@
   </si>
   <si>
     <t>SALDO FINAL</t>
+  </si>
+  <si>
+    <t>UF 43</t>
+  </si>
+  <si>
+    <t>UF 43 Transfirio 194.389,43 (12/10 o habil siguiente)  + 186.313  el 14/10</t>
+  </si>
+  <si>
+    <t>11C</t>
+  </si>
+  <si>
+    <t>Jeremy Naguel</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Jeremy Nahuel: Imputarle $255.000 a favor, correspondientes al excedente abonado en las cuotas del plan de pago de abril, mayo y junio ($85.000 por mes). Aplicar el descuento sobre los $359.889,78 de octubre, dejando un saldo de $104.889,78. El propietario ya fue notificado.</t>
+  </si>
+  <si>
+    <t>8B</t>
+  </si>
+  <si>
+    <t>El 8B dice que esta al dia y que "hablo con romina"</t>
+  </si>
+  <si>
+    <t>10A</t>
+  </si>
+  <si>
+    <t>Deposito 316.500 el 09/10 UF 10A</t>
+  </si>
+  <si>
+    <t>4D</t>
+  </si>
+  <si>
+    <t>Transfirio $4.689 el 17/10</t>
   </si>
 </sst>
 </file>
@@ -1169,7 +1159,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1250,12 +1240,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1268,25 +1252,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3"/>
+        <fgColor rgb="FF00FF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF74FA84"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF0070C0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1835,7 +1813,7 @@
     <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="314">
+  <cellXfs count="315">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2084,10 +2062,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2102,8 +2076,8 @@
     <xf numFmtId="0" fontId="12" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2119,26 +2093,26 @@
     <xf numFmtId="167" fontId="17" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="17" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="17" fillId="2" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="17" fillId="15" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="15" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="15" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="15" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="15" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="14" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="14" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="14" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="14" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="14" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="14" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="44" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="43" fontId="17" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2172,244 +2146,257 @@
     <xf numFmtId="44" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="43" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="17" fillId="7" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="12" fillId="7" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="25" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="17" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="8" fontId="10" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="8" fontId="10" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="8" fontId="12" fillId="7" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="25" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="17" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="8" fontId="10" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="8" fontId="10" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -2420,8 +2407,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF00FF00"/>
       <color rgb="FF74FA84"/>
-      <color rgb="FF00FF00"/>
       <color rgb="FFCCCCFF"/>
     </mruColors>
   </colors>
@@ -2495,9 +2482,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2535,9 +2522,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2570,26 +2557,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2622,26 +2592,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2816,30 +2769,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E413A25D-5161-4141-BE0B-6E37A2A76CA5}">
   <dimension ref="A1:M175"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="7" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="7" width="15.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.28515625" customWidth="1"/>
+    <col min="10" max="10" width="16.33203125" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="250" t="s">
+      <c r="B1" s="252" t="s">
         <v>145</v>
       </c>
-      <c r="C1" s="250"/>
-      <c r="D1" s="250"/>
-      <c r="E1" s="251"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C1" s="252"/>
+      <c r="D1" s="252"/>
+      <c r="E1" s="253"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="9" t="s">
         <v>147</v>
@@ -2848,7 +2801,7 @@
       <c r="D2" s="3"/>
       <c r="E2" s="4"/>
     </row>
-    <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2"/>
       <c r="B3" s="254" t="s">
         <v>186</v>
@@ -2857,7 +2810,7 @@
       <c r="D3" s="254"/>
       <c r="E3" s="255"/>
     </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>100</v>
       </c>
@@ -2868,12 +2821,12 @@
       <c r="D4" s="7"/>
       <c r="E4" s="8"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>146</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="3" t="s">
@@ -2881,7 +2834,7 @@
       </c>
       <c r="E5" s="10"/>
     </row>
-    <row r="6" spans="1:5" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="85" t="s">
         <v>136</v>
       </c>
@@ -2892,44 +2845,44 @@
       </c>
       <c r="E6" s="8"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="48"/>
       <c r="B8" s="256" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="C8" s="256"/>
       <c r="D8" s="48"/>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="48"/>
       <c r="B9" s="256"/>
       <c r="C9" s="256"/>
       <c r="D9" s="48"/>
       <c r="E9" s="48"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="48"/>
       <c r="B10" s="256"/>
       <c r="C10" s="256"/>
       <c r="D10" s="48"/>
       <c r="E10" s="48"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="48"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
       <c r="E11" s="48"/>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="48"/>
       <c r="B12" s="48"/>
       <c r="C12" s="48"/>
       <c r="D12" s="48"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="257" t="s">
         <v>103</v>
       </c>
@@ -2938,58 +2891,58 @@
       <c r="D13" s="257"/>
       <c r="E13" s="257"/>
     </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="257"/>
       <c r="B14" s="257"/>
       <c r="C14" s="257"/>
       <c r="D14" s="257"/>
       <c r="E14" s="257"/>
     </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="257"/>
       <c r="B15" s="257"/>
       <c r="C15" s="257"/>
       <c r="D15" s="257"/>
       <c r="E15" s="257"/>
     </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="257"/>
       <c r="B16" s="257"/>
       <c r="C16" s="257"/>
       <c r="D16" s="257"/>
       <c r="E16" s="257"/>
     </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="48"/>
       <c r="B17" s="48"/>
       <c r="C17" s="48"/>
       <c r="D17" s="48"/>
       <c r="E17" s="48"/>
     </row>
-    <row r="18" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="168"/>
+    <row r="18" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="164"/>
       <c r="B18" s="48"/>
       <c r="C18" s="48"/>
       <c r="D18" s="48"/>
       <c r="E18" s="48"/>
     </row>
-    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="48"/>
       <c r="B19" s="48"/>
       <c r="C19" s="48"/>
       <c r="D19" s="48"/>
       <c r="E19" s="48"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="169" t="s">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="165" t="s">
         <v>104</v>
       </c>
-      <c r="B20" s="170"/>
-      <c r="C20" s="171"/>
+      <c r="B20" s="166"/>
+      <c r="C20" s="167"/>
       <c r="D20" s="58"/>
       <c r="E20" s="59"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="36" t="s">
         <v>137</v>
       </c>
@@ -2998,46 +2951,46 @@
       <c r="D21" s="112"/>
       <c r="E21" s="145"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="252" t="s">
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="243" t="s">
         <v>160</v>
       </c>
-      <c r="B22" s="253"/>
-      <c r="C22" s="172"/>
-      <c r="D22" s="173">
+      <c r="B22" s="244"/>
+      <c r="C22" s="168"/>
+      <c r="D22" s="169">
         <v>2427661.11</v>
       </c>
       <c r="E22" s="146"/>
       <c r="H22" s="19"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="252" t="s">
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="243" t="s">
         <v>161</v>
       </c>
-      <c r="B23" s="253"/>
-      <c r="C23" s="172"/>
-      <c r="D23" s="173">
+      <c r="B23" s="244"/>
+      <c r="C23" s="168"/>
+      <c r="D23" s="169">
         <v>-528016.11</v>
       </c>
       <c r="E23" s="20"/>
       <c r="H23" s="19"/>
     </row>
-    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="252" t="s">
+    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="243" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="253"/>
-      <c r="C24" s="172"/>
-      <c r="D24" s="174">
+      <c r="B24" s="244"/>
+      <c r="C24" s="168"/>
+      <c r="D24" s="170">
         <v>0</v>
       </c>
       <c r="E24" s="20"/>
-      <c r="F24" s="197"/>
+      <c r="F24" s="193"/>
       <c r="H24" s="19"/>
     </row>
-    <row r="25" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="36" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="B25" s="36"/>
       <c r="C25" s="36"/>
@@ -3046,55 +2999,55 @@
         <v>1899645</v>
       </c>
       <c r="E25" s="145"/>
-      <c r="F25" s="197"/>
+      <c r="F25" s="193"/>
       <c r="H25" s="19"/>
     </row>
-    <row r="26" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="252" t="s">
+    <row r="26" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="243" t="s">
         <v>160</v>
       </c>
-      <c r="B26" s="253"/>
-      <c r="C26" s="172"/>
-      <c r="D26" s="174">
+      <c r="B26" s="244"/>
+      <c r="C26" s="168"/>
+      <c r="D26" s="170">
         <v>1136835.6499999999</v>
       </c>
       <c r="E26" s="20"/>
-      <c r="F26" s="197"/>
+      <c r="F26" s="193"/>
       <c r="H26" s="19"/>
     </row>
-    <row r="27" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="252" t="s">
+    <row r="27" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="243" t="s">
         <v>161</v>
       </c>
-      <c r="B27" s="253"/>
-      <c r="C27" s="172"/>
-      <c r="D27" s="174">
+      <c r="B27" s="244"/>
+      <c r="C27" s="168"/>
+      <c r="D27" s="170">
         <v>-281366.65000000002</v>
       </c>
       <c r="E27" s="20"/>
-      <c r="F27" s="197"/>
+      <c r="F27" s="193"/>
       <c r="H27" s="19"/>
     </row>
-    <row r="28" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="252" t="s">
+    <row r="28" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="243" t="s">
         <v>1</v>
       </c>
-      <c r="B28" s="253"/>
-      <c r="C28" s="172"/>
-      <c r="D28" s="174">
+      <c r="B28" s="244"/>
+      <c r="C28" s="168"/>
+      <c r="D28" s="170">
         <v>0</v>
       </c>
       <c r="E28" s="20"/>
-      <c r="F28" s="197"/>
+      <c r="F28" s="193"/>
       <c r="H28" s="19"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="175" t="s">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="171" t="s">
         <v>105</v>
       </c>
-      <c r="B29" s="175"/>
-      <c r="C29" s="175"/>
-      <c r="D29" s="307">
+      <c r="B29" s="171"/>
+      <c r="C29" s="171"/>
+      <c r="D29" s="216">
         <f>SUM(D26:D28)</f>
         <v>855468.99999999988</v>
       </c>
@@ -3104,187 +3057,187 @@
       </c>
       <c r="G29" s="75"/>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="175" t="s">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="171" t="s">
         <v>175</v>
       </c>
-      <c r="B30" s="175"/>
-      <c r="C30" s="175"/>
+      <c r="B30" s="171"/>
+      <c r="C30" s="171"/>
       <c r="D30" s="22"/>
       <c r="E30" s="148"/>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="172"/>
-      <c r="B31" s="172"/>
-      <c r="C31" s="172"/>
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="168"/>
+      <c r="B31" s="168"/>
+      <c r="C31" s="168"/>
       <c r="D31" s="35"/>
       <c r="E31" s="160"/>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="172"/>
-      <c r="B32" s="172"/>
-      <c r="C32" s="172"/>
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="168"/>
+      <c r="B32" s="168"/>
+      <c r="C32" s="168"/>
       <c r="D32" s="35"/>
       <c r="E32" s="160"/>
     </row>
-    <row r="33" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="172"/>
-      <c r="B33" s="172"/>
-      <c r="C33" s="172"/>
+    <row r="33" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="168"/>
+      <c r="B33" s="168"/>
+      <c r="C33" s="168"/>
       <c r="D33" s="35"/>
       <c r="E33" s="160"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="239" t="s">
-        <v>259</v>
-      </c>
-      <c r="B34" s="172"/>
-      <c r="C34" s="172"/>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="215" t="s">
+        <v>247</v>
+      </c>
+      <c r="B34" s="168"/>
+      <c r="C34" s="168"/>
       <c r="D34" s="35">
         <v>237600</v>
       </c>
       <c r="E34" s="149" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="172" t="s">
-        <v>260</v>
-      </c>
-      <c r="B35" s="172"/>
-      <c r="C35" s="172"/>
+        <v>249</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="168" t="s">
+        <v>248</v>
+      </c>
+      <c r="B35" s="168"/>
+      <c r="C35" s="168"/>
       <c r="D35" s="35">
         <v>13000</v>
       </c>
       <c r="E35" s="149" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="172"/>
-      <c r="B36" s="172"/>
-      <c r="C36" s="172"/>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="168"/>
+      <c r="B36" s="168"/>
+      <c r="C36" s="168"/>
       <c r="D36" s="35"/>
       <c r="E36" s="149"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="175" t="s">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="171" t="s">
         <v>105</v>
       </c>
-      <c r="B37" s="176"/>
-      <c r="C37" s="176"/>
+      <c r="B37" s="172"/>
+      <c r="C37" s="172"/>
       <c r="D37" s="102"/>
       <c r="E37" s="150">
         <f>SUM(D33:D36)</f>
         <v>250600</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="36" t="s">
         <v>138</v>
       </c>
-      <c r="B38" s="175"/>
-      <c r="C38" s="175"/>
+      <c r="B38" s="171"/>
+      <c r="C38" s="171"/>
       <c r="D38" s="22"/>
       <c r="E38" s="148"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="172" t="s">
-        <v>224</v>
-      </c>
-      <c r="B39" s="177"/>
-      <c r="C39" s="177"/>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="168" t="s">
+        <v>223</v>
+      </c>
+      <c r="B39" s="173"/>
+      <c r="C39" s="173"/>
       <c r="D39" s="35">
         <v>11886</v>
       </c>
       <c r="E39" s="149" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="G39" s="66"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="172" t="s">
-        <v>253</v>
-      </c>
-      <c r="B40" s="177"/>
-      <c r="C40" s="177"/>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="168" t="s">
+        <v>241</v>
+      </c>
+      <c r="B40" s="173"/>
+      <c r="C40" s="173"/>
       <c r="D40" s="35">
         <v>1061960.04</v>
       </c>
       <c r="E40" s="149" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="G40" s="66"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="172" t="s">
-        <v>290</v>
-      </c>
-      <c r="B41" s="177"/>
-      <c r="C41" s="177"/>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="168" t="s">
+        <v>278</v>
+      </c>
+      <c r="B41" s="173"/>
+      <c r="C41" s="173"/>
       <c r="D41" s="35">
         <v>392020.44</v>
       </c>
       <c r="E41" s="149"/>
-      <c r="F41" s="234"/>
+      <c r="F41" s="214"/>
       <c r="G41" s="66"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="172" t="s">
-        <v>254</v>
-      </c>
-      <c r="B42" s="177"/>
-      <c r="C42" s="177"/>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="168" t="s">
+        <v>242</v>
+      </c>
+      <c r="B42" s="173"/>
+      <c r="C42" s="173"/>
       <c r="D42" s="35">
         <v>506489.49</v>
       </c>
       <c r="E42" s="149"/>
       <c r="G42" s="66"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="172" t="s">
-        <v>255</v>
-      </c>
-      <c r="B43" s="177"/>
-      <c r="C43" s="177"/>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="168" t="s">
+        <v>243</v>
+      </c>
+      <c r="B43" s="173"/>
+      <c r="C43" s="173"/>
       <c r="D43" s="35">
         <v>115902.14</v>
       </c>
       <c r="E43" s="149"/>
       <c r="G43" s="66"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="172" t="s">
-        <v>255</v>
-      </c>
-      <c r="B44" s="177"/>
-      <c r="C44" s="177"/>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="168" t="s">
+        <v>243</v>
+      </c>
+      <c r="B44" s="173"/>
+      <c r="C44" s="173"/>
       <c r="D44" s="35">
         <v>61640.3</v>
       </c>
       <c r="E44" s="149"/>
       <c r="G44" s="66"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="172" t="s">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" s="168" t="s">
         <v>140</v>
       </c>
-      <c r="B45" s="177"/>
-      <c r="C45" s="177"/>
+      <c r="B45" s="173"/>
+      <c r="C45" s="173"/>
       <c r="D45" s="35">
         <v>207318.45</v>
       </c>
       <c r="E45" s="149" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="G45" s="66"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="172" t="s">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="168" t="s">
         <v>142</v>
       </c>
-      <c r="B46" s="177"/>
-      <c r="C46" s="177"/>
+      <c r="B46" s="173"/>
+      <c r="C46" s="173"/>
       <c r="D46" s="35">
         <v>108684.32</v>
       </c>
@@ -3294,12 +3247,12 @@
       </c>
       <c r="G46" s="50"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="172" t="s">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="168" t="s">
         <v>141</v>
       </c>
-      <c r="B47" s="177"/>
-      <c r="C47" s="177"/>
+      <c r="B47" s="173"/>
+      <c r="C47" s="173"/>
       <c r="D47" s="35">
         <v>12076.04</v>
       </c>
@@ -3308,28 +3261,28 @@
         <v>Debito 14/09</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="172" t="s">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" s="168" t="s">
         <v>148</v>
       </c>
-      <c r="B48" s="177"/>
-      <c r="C48" s="177"/>
+      <c r="B48" s="173"/>
+      <c r="C48" s="173"/>
       <c r="D48" s="35"/>
       <c r="E48" s="149"/>
     </row>
-    <row r="49" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="175" t="s">
+    <row r="49" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="171" t="s">
         <v>139</v>
       </c>
-      <c r="B49" s="175"/>
-      <c r="C49" s="175"/>
+      <c r="B49" s="171"/>
+      <c r="C49" s="171"/>
       <c r="D49" s="22"/>
       <c r="E49" s="41">
         <f>SUM(D39:D48)</f>
         <v>2477977.2199999997</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="14" t="s">
         <v>106</v>
       </c>
@@ -3338,46 +3291,46 @@
       <c r="D50" s="23"/>
       <c r="E50" s="150"/>
     </row>
-    <row r="51" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="245" t="s">
+    <row r="51" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="247" t="s">
         <v>182</v>
       </c>
-      <c r="B51" s="246"/>
+      <c r="B51" s="248"/>
       <c r="C51" s="26"/>
-      <c r="D51" s="310">
+      <c r="D51" s="219">
         <v>7805</v>
       </c>
       <c r="E51" s="20" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="245" t="s">
-        <v>265</v>
-      </c>
-      <c r="B52" s="246"/>
+    <row r="52" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="247" t="s">
+        <v>253</v>
+      </c>
+      <c r="B52" s="248"/>
       <c r="C52" s="26"/>
-      <c r="D52" s="310">
+      <c r="D52" s="219">
         <v>7129</v>
       </c>
       <c r="E52" s="20" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="245" t="s">
+    <row r="53" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="247" t="s">
         <v>184</v>
       </c>
-      <c r="B53" s="246"/>
+      <c r="B53" s="248"/>
       <c r="C53" s="26"/>
-      <c r="D53" s="310">
+      <c r="D53" s="219">
         <v>213891</v>
       </c>
       <c r="E53" s="20" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="21" t="s">
         <v>107</v>
       </c>
@@ -3389,7 +3342,7 @@
         <v>228825</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="14" t="s">
         <v>108</v>
       </c>
@@ -3398,7 +3351,7 @@
       <c r="D55" s="28"/>
       <c r="E55" s="151"/>
     </row>
-    <row r="56" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="29" t="s">
         <v>109</v>
       </c>
@@ -3410,10 +3363,10 @@
         <v>635896.65</v>
       </c>
       <c r="E56" s="113" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="29" t="s">
         <v>109</v>
       </c>
@@ -3425,10 +3378,10 @@
         <v>35000.639999999999</v>
       </c>
       <c r="E57" s="113" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="29" t="s">
         <v>176</v>
       </c>
@@ -3441,7 +3394,7 @@
       </c>
       <c r="E58" s="20"/>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="29" t="s">
         <v>177</v>
       </c>
@@ -3452,34 +3405,34 @@
       </c>
       <c r="E59" s="20"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="247" t="s">
-        <v>282</v>
-      </c>
-      <c r="B60" s="248"/>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="245" t="s">
+        <v>270</v>
+      </c>
+      <c r="B60" s="246"/>
       <c r="C60" s="29"/>
       <c r="D60" s="30">
         <v>5778358.5099999998</v>
       </c>
       <c r="E60" s="113" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="245" t="s">
-        <v>271</v>
-      </c>
-      <c r="B61" s="246"/>
+        <v>245</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" s="247" t="s">
+        <v>259</v>
+      </c>
+      <c r="B61" s="248"/>
       <c r="C61" s="29"/>
       <c r="D61" s="30">
         <v>4488639.75</v>
       </c>
       <c r="E61" s="113" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="F61" s="50"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="32" t="s">
         <v>110</v>
       </c>
@@ -3488,7 +3441,7 @@
       <c r="D62" s="30"/>
       <c r="E62" s="20"/>
     </row>
-    <row r="63" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="21" t="s">
         <v>111</v>
       </c>
@@ -3500,55 +3453,55 @@
         <v>10937895.550000001</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="14"/>
       <c r="B64" s="21"/>
       <c r="C64" s="21"/>
       <c r="D64" s="22"/>
       <c r="E64" s="153"/>
     </row>
-    <row r="65" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="247" t="s">
+    <row r="65" spans="1:7" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="245" t="s">
         <v>163</v>
       </c>
-      <c r="B65" s="248"/>
+      <c r="B65" s="246"/>
       <c r="C65" s="29"/>
       <c r="D65" s="30">
         <v>285000</v>
       </c>
       <c r="E65" s="159" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="247" t="s">
-        <v>252</v>
-      </c>
-      <c r="B66" s="248"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="245" t="s">
+        <v>240</v>
+      </c>
+      <c r="B66" s="246"/>
       <c r="C66" s="29"/>
       <c r="D66" s="30">
         <f>430000+430000*15%</f>
         <v>494500</v>
       </c>
       <c r="E66" s="159" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="186.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="247" t="s">
-        <v>263</v>
-      </c>
-      <c r="B67" s="248"/>
+        <v>232</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="186.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="245" t="s">
+        <v>251</v>
+      </c>
+      <c r="B67" s="246"/>
       <c r="C67" s="29"/>
       <c r="D67" s="30">
         <v>2800000</v>
       </c>
       <c r="E67" s="159" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="F67" s="50"/>
     </row>
-    <row r="68" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="16" t="s">
         <v>209</v>
       </c>
@@ -3558,81 +3511,81 @@
         <v>6990</v>
       </c>
       <c r="E68" s="34"/>
-      <c r="F68" s="198"/>
-    </row>
-    <row r="69" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="247" t="s">
-        <v>270</v>
-      </c>
-      <c r="B69" s="248"/>
+      <c r="F68" s="194"/>
+    </row>
+    <row r="69" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="245" t="s">
+        <v>258</v>
+      </c>
+      <c r="B69" s="246"/>
       <c r="C69" s="29"/>
       <c r="D69" s="30">
         <v>140000</v>
       </c>
       <c r="E69" s="34" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="F69" s="50"/>
     </row>
-    <row r="70" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="247" t="s">
-        <v>267</v>
-      </c>
-      <c r="B70" s="248"/>
+    <row r="70" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="245" t="s">
+        <v>255</v>
+      </c>
+      <c r="B70" s="246"/>
       <c r="C70" s="29"/>
       <c r="D70" s="30">
         <v>31400</v>
       </c>
       <c r="E70" s="34" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="F70" s="50"/>
     </row>
-    <row r="71" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="247" t="s">
-        <v>269</v>
-      </c>
-      <c r="B71" s="248"/>
+    <row r="71" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="245" t="s">
+        <v>257</v>
+      </c>
+      <c r="B71" s="246"/>
       <c r="C71" s="29"/>
       <c r="D71" s="30">
         <v>140000</v>
       </c>
       <c r="E71" s="34" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="F71" s="50"/>
     </row>
-    <row r="72" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="247" t="s">
-        <v>285</v>
-      </c>
-      <c r="B72" s="248"/>
+    <row r="72" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="245" t="s">
+        <v>273</v>
+      </c>
+      <c r="B72" s="246"/>
       <c r="C72" s="29"/>
       <c r="D72" s="30">
         <v>42400</v>
       </c>
       <c r="E72" s="34" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="F72" s="50"/>
     </row>
-    <row r="73" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="247" t="s">
-        <v>247</v>
-      </c>
-      <c r="B73" s="248"/>
+    <row r="73" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="245" t="s">
+        <v>237</v>
+      </c>
+      <c r="B73" s="246"/>
       <c r="C73" s="29"/>
       <c r="D73" s="30">
         <v>9000</v>
       </c>
       <c r="E73" s="159" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="F73" s="50"/>
     </row>
-    <row r="74" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="87" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="B74" s="17"/>
       <c r="C74" s="29"/>
@@ -3640,25 +3593,25 @@
         <v>158400</v>
       </c>
       <c r="E74" s="159" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="F74" s="50"/>
     </row>
-    <row r="75" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="247" t="s">
-        <v>287</v>
-      </c>
-      <c r="B75" s="248"/>
+    <row r="75" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="245" t="s">
+        <v>275</v>
+      </c>
+      <c r="B75" s="246"/>
       <c r="C75" s="29"/>
       <c r="D75" s="30">
         <v>215000</v>
       </c>
       <c r="E75" s="159" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="F75" s="50"/>
     </row>
-    <row r="76" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="87" t="s">
         <v>198</v>
       </c>
@@ -3670,11 +3623,11 @@
       <c r="E76" s="159"/>
       <c r="F76" s="50"/>
     </row>
-    <row r="77" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="247" t="s">
-        <v>238</v>
-      </c>
-      <c r="B77" s="248"/>
+    <row r="77" spans="1:7" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="245" t="s">
+        <v>228</v>
+      </c>
+      <c r="B77" s="246"/>
       <c r="C77" s="29"/>
       <c r="D77" s="30">
         <v>0</v>
@@ -3682,7 +3635,7 @@
       <c r="E77" s="159"/>
       <c r="F77" s="50"/>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="21" t="s">
         <v>0</v>
       </c>
@@ -3694,7 +3647,7 @@
         <v>4322690</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="14" t="s">
         <v>112</v>
       </c>
@@ -3703,62 +3656,62 @@
       <c r="D79" s="15"/>
       <c r="E79" s="145"/>
     </row>
-    <row r="80" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="247" t="s">
-        <v>239</v>
-      </c>
-      <c r="B80" s="248"/>
+    <row r="80" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="245" t="s">
+        <v>229</v>
+      </c>
+      <c r="B80" s="246"/>
       <c r="C80" s="18"/>
-      <c r="D80" s="311">
+      <c r="D80" s="220">
         <v>781000</v>
       </c>
       <c r="E80" s="159" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="G80" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="247" t="s">
-        <v>250</v>
-      </c>
-      <c r="B81" s="248"/>
+    <row r="81" spans="1:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="245" t="s">
+        <v>238</v>
+      </c>
+      <c r="B81" s="246"/>
       <c r="C81" s="18"/>
-      <c r="D81" s="312">
+      <c r="D81" s="221">
         <v>630000</v>
       </c>
       <c r="E81" s="159" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="16" t="s">
         <v>162</v>
       </c>
       <c r="B82" s="17"/>
       <c r="C82" s="18"/>
-      <c r="D82" s="312">
+      <c r="D82" s="221">
         <v>250000</v>
       </c>
       <c r="E82" s="159" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="87" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="B83" s="17"/>
       <c r="C83" s="18"/>
-      <c r="D83" s="312">
+      <c r="D83" s="221">
         <v>50000</v>
       </c>
       <c r="E83" s="159" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="21" t="s">
         <v>105</v>
       </c>
@@ -3770,7 +3723,7 @@
         <v>1711000</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="14" t="s">
         <v>113</v>
       </c>
@@ -3779,30 +3732,30 @@
       <c r="D85" s="38"/>
       <c r="E85" s="41"/>
     </row>
-    <row r="86" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="245" t="s">
-        <v>272</v>
-      </c>
-      <c r="B86" s="246"/>
+    <row r="86" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="247" t="s">
+        <v>260</v>
+      </c>
+      <c r="B86" s="248"/>
       <c r="C86" s="86"/>
-      <c r="D86" s="214">
+      <c r="D86" s="210">
         <f>65000+29590.38</f>
         <v>94590.38</v>
       </c>
       <c r="E86" s="154"/>
     </row>
-    <row r="87" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="245" t="s">
+    <row r="87" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="247" t="s">
         <v>213</v>
       </c>
-      <c r="B87" s="246"/>
+      <c r="B87" s="248"/>
       <c r="C87" s="86"/>
-      <c r="D87" s="214">
+      <c r="D87" s="210">
         <v>305996.14</v>
       </c>
       <c r="E87" s="154"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="39" t="s">
         <v>105</v>
       </c>
@@ -3814,14 +3767,14 @@
         <v>400586.52</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="29"/>
       <c r="B89" s="29"/>
       <c r="C89" s="29"/>
       <c r="D89" s="42"/>
       <c r="E89" s="43"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="44" t="s">
         <v>114</v>
       </c>
@@ -3832,13 +3785,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="47"/>
       <c r="D91" s="48"/>
       <c r="E91" s="49"/>
       <c r="F91" s="50"/>
     </row>
-    <row r="92" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="51" t="s">
         <v>115</v>
       </c>
@@ -3857,16 +3810,16 @@
         <v>12817690.029999999</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="D93" s="48"/>
       <c r="E93" s="48"/>
     </row>
-    <row r="94" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D94" s="48"/>
       <c r="E94" s="48"/>
       <c r="H94" s="57"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="11" t="s">
         <v>116</v>
       </c>
@@ -3875,34 +3828,34 @@
       <c r="D95" s="58"/>
       <c r="E95" s="59"/>
     </row>
-    <row r="96" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="249"/>
-      <c r="B96" s="249"/>
+    <row r="96" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="262"/>
+      <c r="B96" s="262"/>
       <c r="C96" s="31"/>
-      <c r="D96" s="241"/>
-      <c r="E96" s="243"/>
-    </row>
-    <row r="97" spans="1:5" ht="1.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="249"/>
-      <c r="B97" s="249"/>
+      <c r="D96" s="258"/>
+      <c r="E96" s="260"/>
+    </row>
+    <row r="97" spans="1:5" ht="1.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="262"/>
+      <c r="B97" s="262"/>
       <c r="C97" s="31"/>
-      <c r="D97" s="242"/>
-      <c r="E97" s="244"/>
-    </row>
-    <row r="98" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D97" s="259"/>
+      <c r="E97" s="261"/>
+    </row>
+    <row r="98" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="29"/>
       <c r="B98" s="29"/>
       <c r="D98" s="42"/>
       <c r="E98" s="42"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="24"/>
       <c r="B99" s="61"/>
       <c r="C99" s="29"/>
       <c r="D99" s="35"/>
       <c r="E99" s="60"/>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="62" t="s">
         <v>144</v>
       </c>
@@ -3914,15 +3867,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D101" s="48"/>
       <c r="E101" s="48"/>
     </row>
-    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D102" s="48"/>
       <c r="E102" s="48"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="44" t="s">
         <v>117</v>
       </c>
@@ -3933,11 +3886,11 @@
         <v>4500000</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D104" s="48"/>
       <c r="E104" s="48"/>
     </row>
-    <row r="105" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="51" t="s">
         <v>118</v>
       </c>
@@ -3949,11 +3902,11 @@
         <v>4500000</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D106" s="48"/>
       <c r="E106" s="48"/>
     </row>
-    <row r="107" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="64" t="s">
         <v>119</v>
       </c>
@@ -3964,7 +3917,7 @@
       <c r="D107" s="48"/>
       <c r="E107" s="48"/>
     </row>
-    <row r="108" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" s="64" t="s">
         <v>120</v>
       </c>
@@ -3975,7 +3928,7 @@
       <c r="D108" s="48"/>
       <c r="E108" s="48"/>
     </row>
-    <row r="109" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" s="64" t="s">
         <v>121</v>
       </c>
@@ -3986,7 +3939,7 @@
       <c r="D109" s="48"/>
       <c r="E109" s="48"/>
     </row>
-    <row r="110" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A110" s="64" t="s">
         <v>122</v>
       </c>
@@ -3997,217 +3950,217 @@
       <c r="D110" s="48"/>
       <c r="E110" s="48"/>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D111" s="48"/>
       <c r="E111" s="48"/>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D112" s="48"/>
       <c r="E112" s="48"/>
     </row>
-    <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="259" t="s">
+    <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="250" t="s">
         <v>171</v>
       </c>
-      <c r="B113" s="259"/>
+      <c r="B113" s="250"/>
       <c r="D113" s="48"/>
       <c r="E113" s="48"/>
     </row>
-    <row r="114" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="259"/>
-      <c r="B114" s="259"/>
+    <row r="114" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="250"/>
+      <c r="B114" s="250"/>
       <c r="D114" s="48"/>
       <c r="E114" s="48"/>
     </row>
-    <row r="115" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="259"/>
-      <c r="B115" s="259"/>
+    <row r="115" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="250"/>
+      <c r="B115" s="250"/>
       <c r="D115" s="48"/>
       <c r="E115" s="48"/>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D116" s="48"/>
       <c r="E116" s="48"/>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A117" s="259" t="s">
-        <v>220</v>
-      </c>
-      <c r="B117" s="259"/>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A117" s="250" t="s">
+        <v>219</v>
+      </c>
+      <c r="B117" s="250"/>
       <c r="D117" s="48"/>
       <c r="E117" s="48"/>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A118" s="259"/>
-      <c r="B118" s="259"/>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A118" s="250"/>
+      <c r="B118" s="250"/>
       <c r="D118" s="48"/>
       <c r="E118" s="48"/>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A119" s="259"/>
-      <c r="B119" s="259"/>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A119" s="250"/>
+      <c r="B119" s="250"/>
       <c r="D119" s="48"/>
       <c r="E119" s="48"/>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D120" s="48"/>
       <c r="E120" s="48"/>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A121" s="259" t="s">
-        <v>221</v>
-      </c>
-      <c r="B121" s="259"/>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A121" s="250" t="s">
+        <v>220</v>
+      </c>
+      <c r="B121" s="250"/>
       <c r="D121" s="48"/>
       <c r="E121" s="48"/>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A122" s="259"/>
-      <c r="B122" s="259"/>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122" s="250"/>
+      <c r="B122" s="250"/>
       <c r="D122" s="48"/>
       <c r="E122" s="48"/>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A123" s="259"/>
-      <c r="B123" s="259"/>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A123" s="250"/>
+      <c r="B123" s="250"/>
       <c r="D123" s="48"/>
       <c r="E123" s="48"/>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D124" s="48"/>
       <c r="E124" s="48"/>
     </row>
-    <row r="125" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="259" t="s">
+    <row r="125" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="250" t="s">
         <v>197</v>
       </c>
-      <c r="B125" s="259"/>
+      <c r="B125" s="250"/>
       <c r="D125" s="48"/>
       <c r="E125" s="48"/>
     </row>
-    <row r="126" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="259"/>
-      <c r="B126" s="259"/>
+    <row r="126" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="250"/>
+      <c r="B126" s="250"/>
       <c r="D126" s="48"/>
       <c r="E126" s="48"/>
     </row>
-    <row r="127" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="259"/>
-      <c r="B127" s="259"/>
+    <row r="127" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="250"/>
+      <c r="B127" s="250"/>
       <c r="D127" s="48"/>
       <c r="E127" s="48"/>
     </row>
-    <row r="128" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D128" s="48"/>
       <c r="E128" s="48"/>
-      <c r="F128" s="197"/>
-    </row>
-    <row r="129" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="259" t="s">
+      <c r="F128" s="193"/>
+    </row>
+    <row r="129" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="250" t="s">
         <v>178</v>
       </c>
-      <c r="B129" s="259"/>
+      <c r="B129" s="250"/>
       <c r="D129" s="48"/>
       <c r="E129" s="48"/>
     </row>
-    <row r="130" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="259"/>
-      <c r="B130" s="259"/>
+    <row r="130" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="250"/>
+      <c r="B130" s="250"/>
       <c r="D130" s="48"/>
       <c r="E130" s="48"/>
     </row>
-    <row r="131" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="259"/>
-      <c r="B131" s="259"/>
+    <row r="131" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="250"/>
+      <c r="B131" s="250"/>
       <c r="D131" s="48"/>
       <c r="E131" s="48"/>
     </row>
-    <row r="132" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D132" s="48"/>
       <c r="E132" s="48"/>
     </row>
-    <row r="133" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="259" t="s">
+    <row r="133" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="250" t="s">
         <v>181</v>
       </c>
-      <c r="B133" s="259"/>
+      <c r="B133" s="250"/>
       <c r="D133" s="48"/>
       <c r="E133" s="48"/>
     </row>
-    <row r="134" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="259"/>
-      <c r="B134" s="259"/>
+    <row r="134" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="250"/>
+      <c r="B134" s="250"/>
       <c r="D134" s="48"/>
       <c r="E134" s="48"/>
     </row>
-    <row r="135" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="259"/>
-      <c r="B135" s="259"/>
+    <row r="135" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A135" s="250"/>
+      <c r="B135" s="250"/>
       <c r="D135" s="48"/>
       <c r="E135" s="48"/>
     </row>
-    <row r="136" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D136" s="48"/>
       <c r="E136" s="48"/>
     </row>
-    <row r="137" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="259" t="s">
+    <row r="137" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="250" t="s">
         <v>180</v>
       </c>
-      <c r="B137" s="259"/>
+      <c r="B137" s="250"/>
       <c r="D137" s="48"/>
       <c r="E137" s="48"/>
     </row>
-    <row r="138" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="259"/>
-      <c r="B138" s="259"/>
+    <row r="138" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="250"/>
+      <c r="B138" s="250"/>
       <c r="D138" s="48"/>
       <c r="E138" s="48"/>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A139" s="259"/>
-      <c r="B139" s="259"/>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A139" s="250"/>
+      <c r="B139" s="250"/>
       <c r="D139" s="48"/>
       <c r="E139" s="48"/>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D140" s="48"/>
       <c r="E140" s="48"/>
     </row>
-    <row r="141" spans="1:6" s="68" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:6" s="68" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A141"/>
       <c r="B141" s="66"/>
       <c r="C141" s="67"/>
       <c r="D141" s="156"/>
       <c r="E141" s="156"/>
     </row>
-    <row r="142" spans="1:6" s="68" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="206" t="s">
+    <row r="142" spans="1:6" s="68" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A142" s="202" t="s">
         <v>187</v>
       </c>
-      <c r="B142" s="308">
+      <c r="B142" s="217">
         <v>1544535.81</v>
       </c>
       <c r="C142" s="67"/>
       <c r="D142" s="157"/>
       <c r="E142" s="157"/>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A143" s="208" t="s">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143" s="204" t="s">
         <v>143</v>
       </c>
-      <c r="B143" s="209">
+      <c r="B143" s="205">
         <f>-B108-B109</f>
         <v>-23084688.289999999</v>
       </c>
       <c r="D143" s="48"/>
       <c r="E143" s="48"/>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A144" s="208" t="s">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A144" s="204" t="s">
         <v>123</v>
       </c>
-      <c r="B144" s="210">
+      <c r="B144" s="206">
         <f>B174</f>
         <v>0</v>
       </c>
@@ -4215,11 +4168,11 @@
       <c r="E144" s="48"/>
       <c r="F144" s="66"/>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A145" s="208" t="s">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A145" s="204" t="s">
         <v>2</v>
       </c>
-      <c r="B145" s="211">
+      <c r="B145" s="207">
         <f>PRORRATEO!F119</f>
         <v>20030676.670000002</v>
       </c>
@@ -4227,210 +4180,210 @@
       <c r="E145" s="48"/>
       <c r="F145" s="66"/>
     </row>
-    <row r="146" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A146" s="208" t="s">
-        <v>286</v>
-      </c>
-      <c r="B146" s="313">
+    <row r="146" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A146" s="204" t="s">
+        <v>274</v>
+      </c>
+      <c r="B146" s="222">
         <v>-140000</v>
       </c>
       <c r="D146" s="48"/>
       <c r="E146" s="48"/>
       <c r="F146" s="66"/>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A147" s="208" t="s">
-        <v>256</v>
-      </c>
-      <c r="B147" s="313">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A147" s="204" t="s">
+        <v>244</v>
+      </c>
+      <c r="B147" s="222">
         <v>-24000</v>
       </c>
       <c r="D147" s="48"/>
       <c r="E147" s="48"/>
       <c r="F147" s="66"/>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A148" s="208" t="s">
-        <v>276</v>
-      </c>
-      <c r="B148" s="313">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A148" s="204" t="s">
+        <v>264</v>
+      </c>
+      <c r="B148" s="222">
         <v>-200000</v>
       </c>
       <c r="D148" s="48"/>
       <c r="E148" s="48"/>
       <c r="F148" s="66"/>
     </row>
-    <row r="149" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="208" t="s">
+    <row r="149" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A149" s="204" t="s">
         <v>216</v>
       </c>
-      <c r="B149" s="313">
+      <c r="B149" s="222">
         <v>-5877</v>
       </c>
       <c r="D149" s="48"/>
       <c r="E149" s="48"/>
       <c r="F149" s="66"/>
     </row>
-    <row r="150" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="204" t="s">
+    <row r="150" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A150" s="200" t="s">
         <v>159</v>
       </c>
-      <c r="B150" s="205">
+      <c r="B150" s="201">
         <f>SUM(B142:C149)</f>
         <v>-1879352.8099999987</v>
       </c>
-      <c r="D150" s="215"/>
+      <c r="D150" s="211"/>
       <c r="E150" s="50"/>
       <c r="F150" s="50"/>
     </row>
-    <row r="151" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D151" s="48"/>
     </row>
-    <row r="152" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="260" t="s">
-        <v>283</v>
-      </c>
-      <c r="B152" s="260"/>
-      <c r="C152" s="260"/>
-      <c r="D152" s="260"/>
-    </row>
-    <row r="153" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="260"/>
-      <c r="B153" s="260"/>
-      <c r="C153" s="260"/>
-      <c r="D153" s="260"/>
-    </row>
-    <row r="154" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="260"/>
-      <c r="B154" s="260"/>
-      <c r="C154" s="260"/>
-      <c r="D154" s="260"/>
-    </row>
-    <row r="155" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="260"/>
-      <c r="B155" s="260"/>
-      <c r="C155" s="260"/>
-      <c r="D155" s="260"/>
-    </row>
-    <row r="156" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="260"/>
-      <c r="B156" s="260"/>
-      <c r="C156" s="260"/>
-      <c r="D156" s="260"/>
-    </row>
-    <row r="157" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="260"/>
-      <c r="B157" s="260"/>
-      <c r="C157" s="260"/>
-      <c r="D157" s="260"/>
-    </row>
-    <row r="158" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="260"/>
-      <c r="B158" s="260"/>
-      <c r="C158" s="260"/>
-      <c r="D158" s="260"/>
-    </row>
-    <row r="159" spans="1:6" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A152" s="251" t="s">
+        <v>271</v>
+      </c>
+      <c r="B152" s="251"/>
+      <c r="C152" s="251"/>
+      <c r="D152" s="251"/>
+    </row>
+    <row r="153" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="251"/>
+      <c r="B153" s="251"/>
+      <c r="C153" s="251"/>
+      <c r="D153" s="251"/>
+    </row>
+    <row r="154" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A154" s="251"/>
+      <c r="B154" s="251"/>
+      <c r="C154" s="251"/>
+      <c r="D154" s="251"/>
+    </row>
+    <row r="155" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A155" s="251"/>
+      <c r="B155" s="251"/>
+      <c r="C155" s="251"/>
+      <c r="D155" s="251"/>
+    </row>
+    <row r="156" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A156" s="251"/>
+      <c r="B156" s="251"/>
+      <c r="C156" s="251"/>
+      <c r="D156" s="251"/>
+    </row>
+    <row r="157" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A157" s="251"/>
+      <c r="B157" s="251"/>
+      <c r="C157" s="251"/>
+      <c r="D157" s="251"/>
+    </row>
+    <row r="158" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A158" s="251"/>
+      <c r="B158" s="251"/>
+      <c r="C158" s="251"/>
+      <c r="D158" s="251"/>
+    </row>
+    <row r="159" spans="1:6" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D159" s="48"/>
     </row>
-    <row r="160" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="206" t="s">
-        <v>279</v>
-      </c>
-      <c r="B160" s="207">
+    <row r="160" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A160" s="202" t="s">
+        <v>267</v>
+      </c>
+      <c r="B160" s="203">
         <v>0</v>
       </c>
       <c r="D160" s="48"/>
     </row>
-    <row r="161" spans="1:13" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A161" s="208" t="s">
-        <v>281</v>
-      </c>
-      <c r="B161" s="211">
+    <row r="161" spans="1:13" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A161" s="204" t="s">
+        <v>269</v>
+      </c>
+      <c r="B161" s="207">
         <v>320000</v>
       </c>
       <c r="D161" s="48"/>
     </row>
-    <row r="162" spans="1:13" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="204" t="s">
-        <v>280</v>
-      </c>
-      <c r="B162" s="205">
+    <row r="162" spans="1:13" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A162" s="200" t="s">
+        <v>268</v>
+      </c>
+      <c r="B162" s="201">
         <f>SUM(B160:C161)</f>
         <v>320000</v>
       </c>
       <c r="D162" s="48"/>
     </row>
-    <row r="163" spans="1:13" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:13" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D163" s="48"/>
     </row>
-    <row r="164" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="206" t="s">
-        <v>226</v>
-      </c>
-      <c r="B164" s="308">
+    <row r="164" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A164" s="202" t="s">
+        <v>225</v>
+      </c>
+      <c r="B164" s="217">
         <v>1506421.54</v>
       </c>
       <c r="D164" s="48"/>
     </row>
-    <row r="165" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="212" t="s">
-        <v>225</v>
-      </c>
-      <c r="B165" s="213">
+    <row r="165" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A165" s="208" t="s">
+        <v>224</v>
+      </c>
+      <c r="B165" s="209">
         <f>B166-B164</f>
         <v>23256.959999999963</v>
       </c>
       <c r="D165" s="48"/>
     </row>
-    <row r="166" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="204" t="s">
-        <v>292</v>
-      </c>
-      <c r="B166" s="205">
+    <row r="166" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A166" s="200" t="s">
+        <v>280</v>
+      </c>
+      <c r="B166" s="201">
         <v>1529678.5</v>
       </c>
       <c r="D166" s="48"/>
     </row>
-    <row r="167" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D167" s="48"/>
     </row>
-    <row r="168" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D168" s="48"/>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A169" s="258" t="s">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A169" s="249" t="s">
         <v>124</v>
       </c>
-      <c r="B169" s="258"/>
-      <c r="C169" s="258"/>
+      <c r="B169" s="249"/>
+      <c r="C169" s="249"/>
       <c r="D169" s="48"/>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A170" s="258"/>
-      <c r="B170" s="258"/>
-      <c r="C170" s="258"/>
+    <row r="170" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A170" s="249"/>
+      <c r="B170" s="249"/>
+      <c r="C170" s="249"/>
       <c r="D170" s="48"/>
     </row>
-    <row r="171" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="69"/>
       <c r="B171" s="110"/>
       <c r="C171" s="70"/>
-      <c r="D171" s="216"/>
-    </row>
-    <row r="172" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D171" s="212"/>
+    </row>
+    <row r="172" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="69"/>
       <c r="B172" s="110"/>
       <c r="C172" s="70"/>
-      <c r="D172" s="216"/>
-    </row>
-    <row r="173" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D172" s="212"/>
+    </row>
+    <row r="173" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="69"/>
       <c r="B173" s="110"/>
       <c r="C173" s="70"/>
       <c r="D173" s="56"/>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A174" s="71" t="s">
         <v>0</v>
       </c>
@@ -4440,28 +4393,19 @@
       </c>
       <c r="C174" s="73"/>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M175" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="A169:C170"/>
-    <mergeCell ref="A125:B127"/>
-    <mergeCell ref="A137:B139"/>
-    <mergeCell ref="A133:B135"/>
-    <mergeCell ref="A113:B115"/>
-    <mergeCell ref="A129:B131"/>
-    <mergeCell ref="A117:B119"/>
-    <mergeCell ref="A121:B123"/>
-    <mergeCell ref="A152:D158"/>
+    <mergeCell ref="D96:D97"/>
+    <mergeCell ref="E96:E97"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A96:B97"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="A86:B86"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A80:B80"/>
@@ -4478,14 +4422,23 @@
     <mergeCell ref="A66:B66"/>
     <mergeCell ref="A73:B73"/>
     <mergeCell ref="A52:B52"/>
-    <mergeCell ref="D96:D97"/>
-    <mergeCell ref="E96:E97"/>
-    <mergeCell ref="A87:B87"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="A96:B97"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="A169:C170"/>
+    <mergeCell ref="A125:B127"/>
+    <mergeCell ref="A137:B139"/>
+    <mergeCell ref="A133:B135"/>
+    <mergeCell ref="A113:B115"/>
+    <mergeCell ref="A129:B131"/>
+    <mergeCell ref="A117:B119"/>
+    <mergeCell ref="A121:B123"/>
+    <mergeCell ref="A152:D158"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A69:B69"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="90" orientation="portrait" r:id="rId1"/>
@@ -4496,55 +4449,55 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{533DB7A7-09F4-49CF-B824-70F15C1FF525}">
   <dimension ref="A1:Q135"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="25.5703125" customWidth="1"/>
-    <col min="3" max="3" width="0.140625" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" customWidth="1"/>
-    <col min="8" max="8" width="9.5703125" customWidth="1"/>
-    <col min="9" max="9" width="12.42578125" customWidth="1"/>
-    <col min="10" max="11" width="16.28515625" customWidth="1"/>
-    <col min="12" max="12" width="12.28515625" customWidth="1"/>
-    <col min="13" max="13" width="16.140625" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" customWidth="1"/>
-    <col min="16" max="16" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="25.5546875" customWidth="1"/>
+    <col min="3" max="3" width="0.109375" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
+    <col min="7" max="7" width="10.5546875" customWidth="1"/>
+    <col min="8" max="8" width="9.5546875" customWidth="1"/>
+    <col min="9" max="9" width="12.44140625" customWidth="1"/>
+    <col min="10" max="11" width="16.33203125" customWidth="1"/>
+    <col min="12" max="12" width="12.33203125" customWidth="1"/>
+    <col min="13" max="13" width="16.109375" customWidth="1"/>
+    <col min="14" max="14" width="14.6640625" customWidth="1"/>
+    <col min="15" max="15" width="14.33203125" customWidth="1"/>
+    <col min="16" max="16" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="88"/>
       <c r="B1" s="89"/>
       <c r="C1" s="89"/>
-      <c r="D1" s="262"/>
-      <c r="E1" s="262"/>
-      <c r="F1" s="262"/>
-      <c r="G1" s="262"/>
-      <c r="H1" s="262"/>
-      <c r="I1" s="262"/>
-      <c r="J1" s="262"/>
-      <c r="K1" s="262"/>
-      <c r="L1" s="262"/>
-      <c r="M1" s="262"/>
-      <c r="N1" s="262"/>
+      <c r="D1" s="278"/>
+      <c r="E1" s="278"/>
+      <c r="F1" s="278"/>
+      <c r="G1" s="278"/>
+      <c r="H1" s="278"/>
+      <c r="I1" s="278"/>
+      <c r="J1" s="278"/>
+      <c r="K1" s="278"/>
+      <c r="L1" s="278"/>
+      <c r="M1" s="278"/>
+      <c r="N1" s="278"/>
       <c r="O1" s="90"/>
     </row>
-    <row r="2" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="91"/>
       <c r="B2" s="92"/>
       <c r="C2" s="93"/>
       <c r="D2" s="93" t="s">
         <v>125</v>
       </c>
-      <c r="E2" s="286">
+      <c r="E2" s="300">
         <v>4500000</v>
       </c>
-      <c r="F2" s="286"/>
+      <c r="F2" s="300"/>
       <c r="G2" s="93"/>
       <c r="H2" s="93"/>
       <c r="I2" s="93" t="s">
@@ -4567,7 +4520,7 @@
         <v>13312274.1</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="97"/>
       <c r="B3" s="98"/>
       <c r="C3" s="98"/>
@@ -4585,241 +4538,241 @@
       <c r="O3" s="101"/>
       <c r="P3" s="75"/>
     </row>
-    <row r="4" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="263" t="s">
+    <row r="4" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="279" t="s">
         <v>158</v>
       </c>
-      <c r="B4" s="264"/>
-      <c r="C4" s="264"/>
-      <c r="D4" s="264"/>
-      <c r="E4" s="264"/>
-      <c r="F4" s="264"/>
-      <c r="G4" s="264"/>
-      <c r="H4" s="264"/>
-      <c r="I4" s="264"/>
-      <c r="J4" s="264"/>
-      <c r="K4" s="264"/>
-      <c r="L4" s="264"/>
-      <c r="M4" s="264"/>
-      <c r="N4" s="264"/>
-      <c r="O4" s="265"/>
+      <c r="B4" s="280"/>
+      <c r="C4" s="280"/>
+      <c r="D4" s="280"/>
+      <c r="E4" s="280"/>
+      <c r="F4" s="280"/>
+      <c r="G4" s="280"/>
+      <c r="H4" s="280"/>
+      <c r="I4" s="280"/>
+      <c r="J4" s="280"/>
+      <c r="K4" s="280"/>
+      <c r="L4" s="280"/>
+      <c r="M4" s="280"/>
+      <c r="N4" s="280"/>
+      <c r="O4" s="281"/>
       <c r="P4" s="75"/>
     </row>
-    <row r="5" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="266"/>
-      <c r="B5" s="267"/>
-      <c r="C5" s="267"/>
-      <c r="D5" s="267"/>
-      <c r="E5" s="267"/>
-      <c r="F5" s="267"/>
-      <c r="G5" s="267"/>
-      <c r="H5" s="267"/>
-      <c r="I5" s="267"/>
-      <c r="J5" s="267"/>
-      <c r="K5" s="267"/>
-      <c r="L5" s="267"/>
-      <c r="M5" s="267"/>
-      <c r="N5" s="267"/>
-      <c r="O5" s="268"/>
+    <row r="5" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="282"/>
+      <c r="B5" s="283"/>
+      <c r="C5" s="283"/>
+      <c r="D5" s="283"/>
+      <c r="E5" s="283"/>
+      <c r="F5" s="283"/>
+      <c r="G5" s="283"/>
+      <c r="H5" s="283"/>
+      <c r="I5" s="283"/>
+      <c r="J5" s="283"/>
+      <c r="K5" s="283"/>
+      <c r="L5" s="283"/>
+      <c r="M5" s="283"/>
+      <c r="N5" s="283"/>
+      <c r="O5" s="284"/>
       <c r="P5" s="75"/>
     </row>
-    <row r="6" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="266"/>
-      <c r="B6" s="267"/>
-      <c r="C6" s="267"/>
-      <c r="D6" s="267"/>
-      <c r="E6" s="267"/>
-      <c r="F6" s="267"/>
-      <c r="G6" s="267"/>
-      <c r="H6" s="267"/>
-      <c r="I6" s="267"/>
-      <c r="J6" s="267"/>
-      <c r="K6" s="267"/>
-      <c r="L6" s="267"/>
-      <c r="M6" s="267"/>
-      <c r="N6" s="267"/>
-      <c r="O6" s="268"/>
+    <row r="6" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="282"/>
+      <c r="B6" s="283"/>
+      <c r="C6" s="283"/>
+      <c r="D6" s="283"/>
+      <c r="E6" s="283"/>
+      <c r="F6" s="283"/>
+      <c r="G6" s="283"/>
+      <c r="H6" s="283"/>
+      <c r="I6" s="283"/>
+      <c r="J6" s="283"/>
+      <c r="K6" s="283"/>
+      <c r="L6" s="283"/>
+      <c r="M6" s="283"/>
+      <c r="N6" s="283"/>
+      <c r="O6" s="284"/>
       <c r="P6" s="75"/>
     </row>
-    <row r="7" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="266"/>
-      <c r="B7" s="267"/>
-      <c r="C7" s="267"/>
-      <c r="D7" s="267"/>
-      <c r="E7" s="267"/>
-      <c r="F7" s="267"/>
-      <c r="G7" s="267"/>
-      <c r="H7" s="267"/>
-      <c r="I7" s="267"/>
-      <c r="J7" s="267"/>
-      <c r="K7" s="267"/>
-      <c r="L7" s="267"/>
-      <c r="M7" s="267"/>
-      <c r="N7" s="267"/>
-      <c r="O7" s="268"/>
+    <row r="7" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="282"/>
+      <c r="B7" s="283"/>
+      <c r="C7" s="283"/>
+      <c r="D7" s="283"/>
+      <c r="E7" s="283"/>
+      <c r="F7" s="283"/>
+      <c r="G7" s="283"/>
+      <c r="H7" s="283"/>
+      <c r="I7" s="283"/>
+      <c r="J7" s="283"/>
+      <c r="K7" s="283"/>
+      <c r="L7" s="283"/>
+      <c r="M7" s="283"/>
+      <c r="N7" s="283"/>
+      <c r="O7" s="284"/>
       <c r="P7" s="75"/>
     </row>
-    <row r="8" spans="1:17" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="269"/>
-      <c r="B8" s="270"/>
-      <c r="C8" s="270"/>
-      <c r="D8" s="270"/>
-      <c r="E8" s="270"/>
-      <c r="F8" s="270"/>
-      <c r="G8" s="270"/>
-      <c r="H8" s="270"/>
-      <c r="I8" s="270"/>
-      <c r="J8" s="270"/>
-      <c r="K8" s="270"/>
-      <c r="L8" s="270"/>
-      <c r="M8" s="270"/>
-      <c r="N8" s="270"/>
-      <c r="O8" s="271"/>
-    </row>
-    <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="280" t="s">
+    <row r="8" spans="1:17" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="285"/>
+      <c r="B8" s="286"/>
+      <c r="C8" s="286"/>
+      <c r="D8" s="286"/>
+      <c r="E8" s="286"/>
+      <c r="F8" s="286"/>
+      <c r="G8" s="286"/>
+      <c r="H8" s="286"/>
+      <c r="I8" s="286"/>
+      <c r="J8" s="286"/>
+      <c r="K8" s="286"/>
+      <c r="L8" s="286"/>
+      <c r="M8" s="286"/>
+      <c r="N8" s="286"/>
+      <c r="O8" s="287"/>
+    </row>
+    <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="294" t="s">
         <v>156</v>
       </c>
-      <c r="B9" s="281"/>
-      <c r="C9" s="281"/>
-      <c r="D9" s="281"/>
-      <c r="E9" s="281"/>
-      <c r="F9" s="281"/>
-      <c r="G9" s="281"/>
-      <c r="H9" s="281"/>
-      <c r="I9" s="281"/>
-      <c r="J9" s="281"/>
-      <c r="K9" s="281"/>
-      <c r="L9" s="281"/>
-      <c r="M9" s="281"/>
-      <c r="N9" s="281"/>
-      <c r="O9" s="282"/>
-    </row>
-    <row r="10" spans="1:17" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="291" t="s">
+      <c r="B9" s="295"/>
+      <c r="C9" s="295"/>
+      <c r="D9" s="295"/>
+      <c r="E9" s="295"/>
+      <c r="F9" s="295"/>
+      <c r="G9" s="295"/>
+      <c r="H9" s="295"/>
+      <c r="I9" s="295"/>
+      <c r="J9" s="295"/>
+      <c r="K9" s="295"/>
+      <c r="L9" s="295"/>
+      <c r="M9" s="295"/>
+      <c r="N9" s="295"/>
+      <c r="O9" s="296"/>
+    </row>
+    <row r="10" spans="1:17" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="267" t="s">
         <v>210</v>
       </c>
-      <c r="B10" s="292"/>
-      <c r="C10" s="292"/>
-      <c r="D10" s="292"/>
-      <c r="E10" s="292"/>
-      <c r="F10" s="292"/>
-      <c r="G10" s="292"/>
-      <c r="H10" s="292"/>
-      <c r="I10" s="292"/>
-      <c r="J10" s="292"/>
-      <c r="K10" s="292"/>
-      <c r="L10" s="292"/>
-      <c r="M10" s="292"/>
-      <c r="N10" s="292"/>
-      <c r="O10" s="293"/>
-    </row>
-    <row r="11" spans="1:17" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="294" t="s">
+      <c r="B10" s="268"/>
+      <c r="C10" s="268"/>
+      <c r="D10" s="268"/>
+      <c r="E10" s="268"/>
+      <c r="F10" s="268"/>
+      <c r="G10" s="268"/>
+      <c r="H10" s="268"/>
+      <c r="I10" s="268"/>
+      <c r="J10" s="268"/>
+      <c r="K10" s="268"/>
+      <c r="L10" s="268"/>
+      <c r="M10" s="268"/>
+      <c r="N10" s="268"/>
+      <c r="O10" s="269"/>
+    </row>
+    <row r="11" spans="1:17" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="270" t="s">
         <v>211</v>
       </c>
-      <c r="B11" s="295"/>
-      <c r="C11" s="295"/>
-      <c r="D11" s="295"/>
-      <c r="E11" s="295"/>
-      <c r="F11" s="295"/>
-      <c r="G11" s="295"/>
-      <c r="H11" s="295"/>
-      <c r="I11" s="295"/>
-      <c r="J11" s="295"/>
-      <c r="K11" s="295"/>
-      <c r="L11" s="295"/>
-      <c r="M11" s="295"/>
-      <c r="N11" s="295"/>
-      <c r="O11" s="296"/>
-    </row>
-    <row r="12" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="283" t="s">
+      <c r="B11" s="271"/>
+      <c r="C11" s="271"/>
+      <c r="D11" s="271"/>
+      <c r="E11" s="271"/>
+      <c r="F11" s="271"/>
+      <c r="G11" s="271"/>
+      <c r="H11" s="271"/>
+      <c r="I11" s="271"/>
+      <c r="J11" s="271"/>
+      <c r="K11" s="271"/>
+      <c r="L11" s="271"/>
+      <c r="M11" s="271"/>
+      <c r="N11" s="271"/>
+      <c r="O11" s="272"/>
+    </row>
+    <row r="12" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="297" t="s">
         <v>157</v>
       </c>
-      <c r="B12" s="284"/>
-      <c r="C12" s="284"/>
-      <c r="D12" s="284"/>
-      <c r="E12" s="284"/>
-      <c r="F12" s="284"/>
-      <c r="G12" s="284"/>
-      <c r="H12" s="284"/>
-      <c r="I12" s="284"/>
-      <c r="J12" s="284"/>
-      <c r="K12" s="284"/>
-      <c r="L12" s="284"/>
-      <c r="M12" s="284"/>
-      <c r="N12" s="284"/>
-      <c r="O12" s="285"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="272" t="s">
+      <c r="B12" s="298"/>
+      <c r="C12" s="298"/>
+      <c r="D12" s="298"/>
+      <c r="E12" s="298"/>
+      <c r="F12" s="298"/>
+      <c r="G12" s="298"/>
+      <c r="H12" s="298"/>
+      <c r="I12" s="298"/>
+      <c r="J12" s="298"/>
+      <c r="K12" s="298"/>
+      <c r="L12" s="298"/>
+      <c r="M12" s="298"/>
+      <c r="N12" s="298"/>
+      <c r="O12" s="299"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A13" s="288" t="s">
         <v>127</v>
       </c>
-      <c r="B13" s="274" t="s">
+      <c r="B13" s="290" t="s">
         <v>128</v>
       </c>
-      <c r="C13" s="274" t="s">
+      <c r="C13" s="290" t="s">
         <v>129</v>
       </c>
-      <c r="D13" s="274" t="s">
+      <c r="D13" s="290" t="s">
         <v>130</v>
       </c>
-      <c r="E13" s="276" t="s">
+      <c r="E13" s="265" t="s">
         <v>131</v>
       </c>
-      <c r="F13" s="274" t="s">
+      <c r="F13" s="290" t="s">
         <v>132</v>
       </c>
-      <c r="G13" s="278" t="s">
+      <c r="G13" s="292" t="s">
         <v>133</v>
       </c>
-      <c r="H13" s="276" t="s">
+      <c r="H13" s="265" t="s">
         <v>134</v>
       </c>
-      <c r="I13" s="276" t="s">
+      <c r="I13" s="265" t="s">
         <v>126</v>
       </c>
-      <c r="J13" s="276" t="s">
+      <c r="J13" s="265" t="s">
         <v>125</v>
       </c>
-      <c r="K13" s="299" t="s">
+      <c r="K13" s="275" t="s">
         <v>217</v>
       </c>
-      <c r="L13" s="287" t="s">
+      <c r="L13" s="301" t="s">
         <v>173</v>
       </c>
-      <c r="M13" s="289" t="s">
+      <c r="M13" s="263" t="s">
         <v>179</v>
       </c>
       <c r="N13" s="138" t="s">
         <v>206</v>
       </c>
-      <c r="O13" s="297" t="s">
+      <c r="O13" s="273" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="273"/>
-      <c r="B14" s="275"/>
-      <c r="C14" s="275"/>
-      <c r="D14" s="275"/>
-      <c r="E14" s="277"/>
-      <c r="F14" s="275"/>
-      <c r="G14" s="279"/>
-      <c r="H14" s="277"/>
-      <c r="I14" s="277"/>
-      <c r="J14" s="277"/>
-      <c r="K14" s="300"/>
-      <c r="L14" s="288"/>
-      <c r="M14" s="290"/>
+    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="289"/>
+      <c r="B14" s="291"/>
+      <c r="C14" s="291"/>
+      <c r="D14" s="291"/>
+      <c r="E14" s="266"/>
+      <c r="F14" s="291"/>
+      <c r="G14" s="293"/>
+      <c r="H14" s="266"/>
+      <c r="I14" s="266"/>
+      <c r="J14" s="266"/>
+      <c r="K14" s="276"/>
+      <c r="L14" s="302"/>
+      <c r="M14" s="264"/>
       <c r="N14" s="139" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 16/10</v>
       </c>
-      <c r="O14" s="298"/>
-    </row>
-    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O14" s="274"/>
+    </row>
+    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="124">
         <v>1</v>
       </c>
@@ -4871,48 +4824,48 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="178">
+    <row r="16" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="174">
         <v>2</v>
       </c>
-      <c r="B16" s="187" t="s">
+      <c r="B16" s="183" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="188"/>
-      <c r="D16" s="189">
+      <c r="C16" s="184"/>
+      <c r="D16" s="185">
         <v>1.18</v>
       </c>
-      <c r="E16" s="190">
+      <c r="E16" s="186">
         <v>4571515.0199999996</v>
       </c>
-      <c r="F16" s="190"/>
-      <c r="G16" s="191">
+      <c r="F16" s="186"/>
+      <c r="G16" s="187">
         <f t="shared" si="0"/>
         <v>4571515.0199999996</v>
       </c>
-      <c r="H16" s="191">
+      <c r="H16" s="187">
         <f t="shared" ref="H16:H79" si="3">IF(G16&gt;0,G16*3%,0)</f>
         <v>137145.45059999998</v>
       </c>
-      <c r="I16" s="192">
+      <c r="I16" s="188">
         <f t="shared" ref="I16:I46" si="4">J$2*D16/100</f>
         <v>106200</v>
       </c>
-      <c r="J16" s="192">
+      <c r="J16" s="188">
         <f t="shared" si="1"/>
         <v>53100</v>
       </c>
-      <c r="K16" s="192">
+      <c r="K16" s="188">
         <f t="shared" ref="K16:K79" si="5">M$2*D16/100</f>
         <v>121150.579468</v>
       </c>
-      <c r="L16" s="192"/>
-      <c r="M16" s="193"/>
-      <c r="N16" s="194">
+      <c r="L16" s="188"/>
+      <c r="M16" s="189"/>
+      <c r="N16" s="190">
         <f>ROUND(SUM(G16:M16),0) + P16</f>
         <v>4989111.0199999996</v>
       </c>
-      <c r="O16" s="195">
+      <c r="O16" s="191">
         <f t="shared" si="2"/>
         <v>5138784.0199999996</v>
       </c>
@@ -4924,7 +4877,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="125">
         <v>3</v>
       </c>
@@ -4977,7 +4930,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="125">
         <v>4</v>
       </c>
@@ -5030,7 +4983,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="125">
         <v>5</v>
       </c>
@@ -5082,7 +5035,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="125">
         <v>6</v>
       </c>
@@ -5134,7 +5087,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="125">
         <v>7</v>
       </c>
@@ -5187,7 +5140,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="125">
         <v>8</v>
       </c>
@@ -5240,7 +5193,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="124">
         <v>9</v>
       </c>
@@ -5292,7 +5245,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="124">
         <v>10</v>
       </c>
@@ -5345,7 +5298,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="124">
         <v>11</v>
       </c>
@@ -5398,50 +5351,50 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="178">
+    <row r="26" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="174">
         <v>12</v>
       </c>
-      <c r="B26" s="187" t="s">
+      <c r="B26" s="183" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="188"/>
-      <c r="D26" s="189">
+      <c r="C26" s="184"/>
+      <c r="D26" s="185">
         <v>1.17</v>
       </c>
-      <c r="E26" s="190">
+      <c r="E26" s="186">
         <v>5623045.1200000001</v>
       </c>
-      <c r="F26" s="190">
-        <v>0</v>
-      </c>
-      <c r="G26" s="191">
+      <c r="F26" s="186">
+        <v>0</v>
+      </c>
+      <c r="G26" s="187">
         <f t="shared" si="0"/>
         <v>5623045.1200000001</v>
       </c>
-      <c r="H26" s="191">
+      <c r="H26" s="187">
         <f t="shared" si="3"/>
         <v>168691.3536</v>
       </c>
-      <c r="I26" s="192">
+      <c r="I26" s="188">
         <f t="shared" si="4"/>
         <v>105300</v>
       </c>
-      <c r="J26" s="192">
+      <c r="J26" s="188">
         <f t="shared" si="1"/>
         <v>52650</v>
       </c>
-      <c r="K26" s="192">
+      <c r="K26" s="188">
         <f t="shared" si="5"/>
         <v>120123.879642</v>
       </c>
-      <c r="L26" s="192"/>
-      <c r="M26" s="193"/>
-      <c r="N26" s="194">
+      <c r="L26" s="188"/>
+      <c r="M26" s="189"/>
+      <c r="N26" s="190">
         <f t="shared" si="6"/>
         <v>6069810.1200000001</v>
       </c>
-      <c r="O26" s="195">
+      <c r="O26" s="191">
         <f t="shared" si="2"/>
         <v>6251904.1200000001</v>
       </c>
@@ -5450,7 +5403,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="124">
         <v>13</v>
       </c>
@@ -5503,7 +5456,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="124">
         <v>14</v>
       </c>
@@ -5553,7 +5506,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="125">
         <v>15</v>
       </c>
@@ -5606,7 +5559,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="124">
         <v>16</v>
       </c>
@@ -5659,7 +5612,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="124">
         <v>17</v>
       </c>
@@ -5709,7 +5662,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="125">
         <v>18</v>
       </c>
@@ -5762,7 +5715,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="125">
         <v>19</v>
       </c>
@@ -5818,7 +5771,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="126">
         <v>20</v>
       </c>
@@ -5869,10 +5822,10 @@
         <v>0.20000000000000004</v>
       </c>
       <c r="Q34" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="125">
         <v>21</v>
       </c>
@@ -5925,7 +5878,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="125">
         <f>A35+1</f>
         <v>22</v>
@@ -5979,7 +5932,7 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="124">
         <f t="shared" ref="A37:A100" si="10">A36+1</f>
         <v>23</v>
@@ -6033,7 +5986,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="124">
         <f t="shared" si="10"/>
         <v>24</v>
@@ -6087,7 +6040,7 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="124">
         <f t="shared" si="10"/>
         <v>25</v>
@@ -6138,7 +6091,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="125">
         <f t="shared" si="10"/>
         <v>26</v>
@@ -6192,7 +6145,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="125">
         <f t="shared" si="10"/>
         <v>27</v>
@@ -6246,7 +6199,7 @@
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="125">
         <f t="shared" si="10"/>
         <v>28</v>
@@ -6300,10 +6253,10 @@
         <v>0.28000000000000008</v>
       </c>
       <c r="Q42" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="125">
         <f t="shared" si="10"/>
         <v>29</v>
@@ -6360,12 +6313,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A44" s="125">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A44" s="309">
         <f t="shared" si="10"/>
         <v>30</v>
       </c>
-      <c r="B44" s="109" t="s">
+      <c r="B44" s="310" t="s">
         <v>31</v>
       </c>
       <c r="C44" s="108"/>
@@ -6414,7 +6367,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="124">
         <f t="shared" si="10"/>
         <v>31</v>
@@ -6468,7 +6421,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="124">
         <f t="shared" si="10"/>
         <v>32</v>
@@ -6522,7 +6475,7 @@
         <v>0.32000000000000012</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="126">
         <f t="shared" si="10"/>
         <v>33</v>
@@ -6577,10 +6530,10 @@
         <v>0.33000000000000013</v>
       </c>
       <c r="Q47" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="124">
         <f t="shared" si="10"/>
         <v>34</v>
@@ -6634,16 +6587,16 @@
         <v>0.34000000000000014</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A49" s="180">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A49" s="176">
         <f t="shared" si="10"/>
         <v>35</v>
       </c>
-      <c r="B49" s="181" t="s">
+      <c r="B49" s="177" t="s">
         <v>36</v>
       </c>
-      <c r="C49" s="182"/>
-      <c r="D49" s="183">
+      <c r="C49" s="178"/>
+      <c r="D49" s="179">
         <v>1.1200000000000001</v>
       </c>
       <c r="E49" s="79">
@@ -6653,19 +6606,19 @@
         <f>E49</f>
         <v>246400.35</v>
       </c>
-      <c r="G49" s="184">
+      <c r="G49" s="180">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H49" s="184">
+      <c r="H49" s="180">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I49" s="185">
+      <c r="I49" s="181">
         <f t="shared" si="13"/>
         <v>100800.00000000001</v>
       </c>
-      <c r="J49" s="185">
+      <c r="J49" s="181">
         <f t="shared" si="14"/>
         <v>50400.000000000007</v>
       </c>
@@ -6673,8 +6626,8 @@
         <f t="shared" si="5"/>
         <v>114990.380512</v>
       </c>
-      <c r="L49" s="185"/>
-      <c r="M49" s="186"/>
+      <c r="L49" s="181"/>
+      <c r="M49" s="182"/>
       <c r="N49" s="107">
         <f t="shared" si="6"/>
         <v>266190.34999999998</v>
@@ -6691,7 +6644,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="124">
         <f t="shared" si="10"/>
         <v>36</v>
@@ -6748,7 +6701,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="124">
         <f t="shared" si="10"/>
         <v>37</v>
@@ -6802,7 +6755,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="126">
         <f t="shared" si="10"/>
         <v>38</v>
@@ -6856,10 +6809,10 @@
         <v>0.38000000000000017</v>
       </c>
       <c r="Q52" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="124">
         <f t="shared" si="10"/>
         <v>39</v>
@@ -6913,7 +6866,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="124">
         <f t="shared" si="10"/>
         <v>40</v>
@@ -6964,7 +6917,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="124">
         <f t="shared" si="10"/>
         <v>41</v>
@@ -7018,7 +6971,7 @@
         <v>0.4100000000000002</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="126">
         <f t="shared" si="10"/>
         <v>42</v>
@@ -7074,22 +7027,22 @@
         <v>0.42000000000000021</v>
       </c>
       <c r="Q56" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A57" s="125">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A57" s="223">
         <f t="shared" si="10"/>
         <v>43</v>
       </c>
-      <c r="B57" s="109" t="s">
+      <c r="B57" s="224" t="s">
         <v>99</v>
       </c>
       <c r="C57" s="108"/>
       <c r="D57" s="105">
         <v>0.82</v>
       </c>
-      <c r="E57" s="203">
+      <c r="E57" s="199">
         <v>180400.43</v>
       </c>
       <c r="F57" s="79"/>
@@ -7130,10 +7083,10 @@
         <v>0.43000000000000022</v>
       </c>
       <c r="Q57" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="125">
         <f t="shared" si="10"/>
         <v>44</v>
@@ -7190,7 +7143,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="125">
         <f t="shared" si="10"/>
         <v>45</v>
@@ -7244,7 +7197,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="125">
         <f t="shared" si="10"/>
         <v>46</v>
@@ -7300,7 +7253,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="126">
         <f t="shared" si="10"/>
         <v>47</v>
@@ -7355,7 +7308,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="125">
         <f t="shared" si="10"/>
         <v>48</v>
@@ -7412,7 +7365,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="125">
         <f t="shared" si="10"/>
         <v>49</v>
@@ -7466,7 +7419,7 @@
         <v>0.49000000000000027</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="125">
         <f t="shared" si="10"/>
         <v>50</v>
@@ -7517,7 +7470,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="125">
         <f t="shared" si="10"/>
         <v>51</v>
@@ -7571,7 +7524,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="125">
         <f t="shared" si="10"/>
         <v>52</v>
@@ -7625,7 +7578,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="125">
         <f t="shared" si="10"/>
         <v>53</v>
@@ -7679,7 +7632,7 @@
         <v>0.53000000000000025</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="125">
         <f t="shared" si="10"/>
         <v>54</v>
@@ -7732,7 +7685,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="125">
         <f t="shared" si="10"/>
         <v>55</v>
@@ -7786,12 +7739,12 @@
         <v>0.55000000000000027</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A70" s="125">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A70" s="235">
         <f t="shared" si="10"/>
         <v>56</v>
       </c>
-      <c r="B70" s="109" t="s">
+      <c r="B70" s="236" t="s">
         <v>55</v>
       </c>
       <c r="C70" s="108"/>
@@ -7839,7 +7792,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="125">
         <f t="shared" si="10"/>
         <v>57</v>
@@ -7896,7 +7849,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="125">
         <f t="shared" si="10"/>
         <v>58</v>
@@ -7953,7 +7906,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="125">
         <f t="shared" si="10"/>
         <v>59</v>
@@ -8007,7 +7960,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="125">
         <f t="shared" si="10"/>
         <v>60</v>
@@ -8061,7 +8014,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="125">
         <f t="shared" si="10"/>
         <v>61</v>
@@ -8115,7 +8068,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="125">
         <f t="shared" si="10"/>
         <v>62</v>
@@ -8169,7 +8122,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="125">
         <f t="shared" si="10"/>
         <v>63</v>
@@ -8226,7 +8179,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="125">
         <f t="shared" si="10"/>
         <v>64</v>
@@ -8279,7 +8232,7 @@
         <v>0.64000000000000035</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="125">
         <f t="shared" si="10"/>
         <v>65</v>
@@ -8294,7 +8247,7 @@
       <c r="E79" s="79">
         <v>424018.65</v>
       </c>
-      <c r="F79" s="309">
+      <c r="F79" s="218">
         <v>280000.65000000002</v>
       </c>
       <c r="G79" s="106">
@@ -8335,7 +8288,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="125">
         <f t="shared" si="10"/>
         <v>66</v>
@@ -8388,7 +8341,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="125">
         <f t="shared" si="10"/>
         <v>67</v>
@@ -8442,53 +8395,53 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A82" s="178">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A82" s="174">
         <f t="shared" si="10"/>
         <v>68</v>
       </c>
-      <c r="B82" s="179" t="s">
+      <c r="B82" s="175" t="s">
         <v>67</v>
       </c>
-      <c r="C82" s="188"/>
-      <c r="D82" s="189">
+      <c r="C82" s="184"/>
+      <c r="D82" s="185">
         <v>1.17</v>
       </c>
-      <c r="E82" s="190">
+      <c r="E82" s="186">
         <v>8488408.6799999997</v>
       </c>
-      <c r="F82" s="190">
-        <v>0</v>
-      </c>
-      <c r="G82" s="191">
+      <c r="F82" s="186">
+        <v>0</v>
+      </c>
+      <c r="G82" s="187">
         <f t="shared" si="17"/>
         <v>8488408.6799999997</v>
       </c>
-      <c r="H82" s="191">
+      <c r="H82" s="187">
         <f t="shared" si="20"/>
         <v>254652.26039999997</v>
       </c>
-      <c r="I82" s="192">
+      <c r="I82" s="188">
         <f t="shared" si="18"/>
         <v>105300</v>
       </c>
-      <c r="J82" s="192">
+      <c r="J82" s="188">
         <f t="shared" si="19"/>
         <v>52650</v>
       </c>
-      <c r="K82" s="192">
+      <c r="K82" s="188">
         <f t="shared" si="21"/>
         <v>120123.879642</v>
       </c>
-      <c r="L82" s="192">
+      <c r="L82" s="188">
         <v>95000</v>
       </c>
-      <c r="M82" s="193"/>
-      <c r="N82" s="194">
+      <c r="M82" s="189"/>
+      <c r="N82" s="190">
         <f t="shared" si="22"/>
         <v>9116135.6799999997</v>
       </c>
-      <c r="O82" s="195">
+      <c r="O82" s="191">
         <f t="shared" si="9"/>
         <v>9389619.6799999997</v>
       </c>
@@ -8497,12 +8450,12 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A83" s="125">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A83" s="241">
         <f t="shared" si="10"/>
         <v>69</v>
       </c>
-      <c r="B83" s="109" t="s">
+      <c r="B83" s="242" t="s">
         <v>68</v>
       </c>
       <c r="C83" s="108"/>
@@ -8552,7 +8505,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" s="125">
         <f t="shared" si="10"/>
         <v>70</v>
@@ -8606,7 +8559,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" s="125">
         <f t="shared" si="10"/>
         <v>71</v>
@@ -8660,7 +8613,7 @@
         <v>0.71000000000000041</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" s="125">
         <f t="shared" si="10"/>
         <v>72</v>
@@ -8714,7 +8667,7 @@
         <v>0.72000000000000042</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" s="125">
         <f t="shared" si="10"/>
         <v>73</v>
@@ -8765,7 +8718,7 @@
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" s="126">
         <f t="shared" si="10"/>
         <v>74</v>
@@ -8820,10 +8773,10 @@
         <v>0.74000000000000044</v>
       </c>
       <c r="Q88" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" s="124">
         <f t="shared" si="10"/>
         <v>75</v>
@@ -8876,7 +8829,7 @@
         <v>0.75000000000000044</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" s="125">
         <f t="shared" si="10"/>
         <v>76</v>
@@ -8930,7 +8883,7 @@
         <v>0.76000000000000045</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" s="124">
         <f t="shared" si="10"/>
         <v>77</v>
@@ -8984,12 +8937,12 @@
         <v>0.77000000000000046</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A92" s="126">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A92" s="229">
         <f t="shared" si="10"/>
         <v>78</v>
       </c>
-      <c r="B92" s="114" t="s">
+      <c r="B92" s="230" t="s">
         <v>77</v>
       </c>
       <c r="C92" s="115"/>
@@ -9037,10 +8990,10 @@
         <v>0.78000000000000047</v>
       </c>
       <c r="Q92" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" s="124">
         <f t="shared" si="10"/>
         <v>79</v>
@@ -9097,7 +9050,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" s="125">
         <f t="shared" si="10"/>
         <v>80</v>
@@ -9151,7 +9104,7 @@
         <v>0.80000000000000049</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" s="125">
         <f t="shared" si="10"/>
         <v>81</v>
@@ -9208,7 +9161,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" s="125">
         <f t="shared" si="10"/>
         <v>82</v>
@@ -9262,7 +9215,7 @@
         <v>0.82000000000000051</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" s="125">
         <f t="shared" si="10"/>
         <v>83</v>
@@ -9316,7 +9269,7 @@
         <v>0.83000000000000052</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" s="125">
         <f t="shared" si="10"/>
         <v>84</v>
@@ -9367,7 +9320,7 @@
         <v>0.84000000000000052</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99" s="124">
         <f t="shared" si="10"/>
         <v>85</v>
@@ -9421,7 +9374,7 @@
         <v>0.85000000000000053</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100" s="125">
         <f t="shared" si="10"/>
         <v>86</v>
@@ -9475,7 +9428,7 @@
         <v>0.86000000000000054</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101" s="124">
         <f t="shared" ref="A101:A117" si="27">A100+1</f>
         <v>87</v>
@@ -9529,7 +9482,7 @@
         <v>0.87000000000000055</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102" s="124">
         <f t="shared" si="27"/>
         <v>88</v>
@@ -9583,7 +9536,7 @@
         <v>0.88000000000000056</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A103" s="124">
         <f t="shared" si="27"/>
         <v>89</v>
@@ -9637,7 +9590,7 @@
         <v>0.89000000000000057</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A104" s="124">
         <f t="shared" si="27"/>
         <v>90</v>
@@ -9691,7 +9644,7 @@
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105" s="124">
         <f t="shared" si="27"/>
         <v>91</v>
@@ -9745,7 +9698,7 @@
         <v>0.91000000000000059</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A106" s="124">
         <f t="shared" si="27"/>
         <v>92</v>
@@ -9798,7 +9751,7 @@
         <v>0.9200000000000006</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A107" s="125">
         <f t="shared" si="27"/>
         <v>93</v>
@@ -9852,7 +9805,7 @@
         <v>0.9300000000000006</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" s="125">
         <f t="shared" si="27"/>
         <v>94</v>
@@ -9906,7 +9859,7 @@
         <v>0.94000000000000061</v>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="125">
         <f t="shared" si="27"/>
         <v>95</v>
@@ -9960,7 +9913,7 @@
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A110" s="125">
         <f t="shared" si="27"/>
         <v>96</v>
@@ -10017,7 +9970,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" s="125">
         <f t="shared" si="27"/>
         <v>97</v>
@@ -10071,7 +10024,7 @@
         <v>0.97000000000000064</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A112" s="125">
         <f t="shared" si="27"/>
         <v>98</v>
@@ -10125,7 +10078,7 @@
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A113" s="125">
         <f t="shared" si="27"/>
         <v>99</v>
@@ -10179,7 +10132,7 @@
         <v>0.99000000000000066</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A114" s="125">
         <f t="shared" si="27"/>
         <v>100</v>
@@ -10230,7 +10183,7 @@
         <v>1.0000000000000007</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A115" s="125">
         <f t="shared" si="27"/>
         <v>101</v>
@@ -10284,7 +10237,7 @@
         <v>1.0100000000000007</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A116" s="125">
         <f t="shared" si="27"/>
         <v>102</v>
@@ -10338,7 +10291,7 @@
         <v>1.0200000000000007</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A117" s="125">
         <f t="shared" si="27"/>
         <v>103</v>
@@ -10392,7 +10345,7 @@
         <v>1.0300000000000007</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A118" s="125"/>
       <c r="B118" s="103"/>
       <c r="C118" s="108"/>
@@ -10410,7 +10363,7 @@
       <c r="O118" s="135"/>
       <c r="P118" s="50"/>
     </row>
-    <row r="119" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A119" s="127"/>
       <c r="B119" s="128"/>
       <c r="C119" s="128"/>
@@ -10422,7 +10375,7 @@
         <f t="shared" si="31"/>
         <v>47168728.960000001</v>
       </c>
-      <c r="F119" s="217">
+      <c r="F119" s="213">
         <f>SUM(F15:F118)</f>
         <v>20030676.670000002</v>
       </c>
@@ -10454,117 +10407,117 @@
         <v>54447842.560000002</v>
       </c>
     </row>
-    <row r="120" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B120" s="84"/>
       <c r="C120" s="84"/>
     </row>
-    <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="122" spans="1:16" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B122" s="261" t="s">
+    <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="122" spans="1:16" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B122" s="277" t="s">
         <v>103</v>
       </c>
-      <c r="C122" s="261"/>
-      <c r="D122" s="261"/>
-      <c r="E122" s="261"/>
-      <c r="F122" s="261"/>
-      <c r="G122" s="261"/>
-      <c r="H122" s="261"/>
-      <c r="I122" s="261"/>
-      <c r="J122" s="261"/>
-      <c r="K122" s="261"/>
-      <c r="L122" s="261"/>
-      <c r="M122" s="261"/>
-      <c r="N122" s="261"/>
-    </row>
-    <row r="123" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B123" s="261"/>
-      <c r="C123" s="261"/>
-      <c r="D123" s="261"/>
-      <c r="E123" s="261"/>
-      <c r="F123" s="261"/>
-      <c r="G123" s="261"/>
-      <c r="H123" s="261"/>
-      <c r="I123" s="261"/>
-      <c r="J123" s="261"/>
-      <c r="K123" s="261"/>
-      <c r="L123" s="261"/>
-      <c r="M123" s="261"/>
-      <c r="N123" s="261"/>
-    </row>
-    <row r="124" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B124" s="261"/>
-      <c r="C124" s="261"/>
-      <c r="D124" s="261"/>
-      <c r="E124" s="261"/>
-      <c r="F124" s="261"/>
-      <c r="G124" s="261"/>
-      <c r="H124" s="261"/>
-      <c r="I124" s="261"/>
-      <c r="J124" s="261"/>
-      <c r="K124" s="261"/>
-      <c r="L124" s="261"/>
-      <c r="M124" s="261"/>
-      <c r="N124" s="261"/>
-    </row>
-    <row r="125" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B125" s="261"/>
-      <c r="C125" s="261"/>
-      <c r="D125" s="261"/>
-      <c r="E125" s="261"/>
-      <c r="F125" s="261"/>
-      <c r="G125" s="261"/>
-      <c r="H125" s="261"/>
-      <c r="I125" s="261"/>
-      <c r="J125" s="261"/>
-      <c r="K125" s="261"/>
-      <c r="L125" s="261"/>
-      <c r="M125" s="261"/>
-      <c r="N125" s="261"/>
-    </row>
-    <row r="126" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B126" s="261"/>
-      <c r="C126" s="261"/>
-      <c r="D126" s="261"/>
-      <c r="E126" s="261"/>
-      <c r="F126" s="261"/>
-      <c r="G126" s="261"/>
-      <c r="H126" s="261"/>
-      <c r="I126" s="261"/>
-      <c r="J126" s="261"/>
-      <c r="K126" s="261"/>
-      <c r="L126" s="261"/>
-      <c r="M126" s="261"/>
-      <c r="N126" s="261"/>
-    </row>
-    <row r="127" spans="1:16" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B127" s="261"/>
-      <c r="C127" s="261"/>
-      <c r="D127" s="261"/>
-      <c r="E127" s="261"/>
-      <c r="F127" s="261"/>
-      <c r="G127" s="261"/>
-      <c r="H127" s="261"/>
-      <c r="I127" s="261"/>
-      <c r="J127" s="261"/>
-      <c r="K127" s="261"/>
-      <c r="L127" s="261"/>
-      <c r="M127" s="261"/>
-      <c r="N127" s="261"/>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C122" s="277"/>
+      <c r="D122" s="277"/>
+      <c r="E122" s="277"/>
+      <c r="F122" s="277"/>
+      <c r="G122" s="277"/>
+      <c r="H122" s="277"/>
+      <c r="I122" s="277"/>
+      <c r="J122" s="277"/>
+      <c r="K122" s="277"/>
+      <c r="L122" s="277"/>
+      <c r="M122" s="277"/>
+      <c r="N122" s="277"/>
+    </row>
+    <row r="123" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B123" s="277"/>
+      <c r="C123" s="277"/>
+      <c r="D123" s="277"/>
+      <c r="E123" s="277"/>
+      <c r="F123" s="277"/>
+      <c r="G123" s="277"/>
+      <c r="H123" s="277"/>
+      <c r="I123" s="277"/>
+      <c r="J123" s="277"/>
+      <c r="K123" s="277"/>
+      <c r="L123" s="277"/>
+      <c r="M123" s="277"/>
+      <c r="N123" s="277"/>
+    </row>
+    <row r="124" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B124" s="277"/>
+      <c r="C124" s="277"/>
+      <c r="D124" s="277"/>
+      <c r="E124" s="277"/>
+      <c r="F124" s="277"/>
+      <c r="G124" s="277"/>
+      <c r="H124" s="277"/>
+      <c r="I124" s="277"/>
+      <c r="J124" s="277"/>
+      <c r="K124" s="277"/>
+      <c r="L124" s="277"/>
+      <c r="M124" s="277"/>
+      <c r="N124" s="277"/>
+    </row>
+    <row r="125" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B125" s="277"/>
+      <c r="C125" s="277"/>
+      <c r="D125" s="277"/>
+      <c r="E125" s="277"/>
+      <c r="F125" s="277"/>
+      <c r="G125" s="277"/>
+      <c r="H125" s="277"/>
+      <c r="I125" s="277"/>
+      <c r="J125" s="277"/>
+      <c r="K125" s="277"/>
+      <c r="L125" s="277"/>
+      <c r="M125" s="277"/>
+      <c r="N125" s="277"/>
+    </row>
+    <row r="126" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B126" s="277"/>
+      <c r="C126" s="277"/>
+      <c r="D126" s="277"/>
+      <c r="E126" s="277"/>
+      <c r="F126" s="277"/>
+      <c r="G126" s="277"/>
+      <c r="H126" s="277"/>
+      <c r="I126" s="277"/>
+      <c r="J126" s="277"/>
+      <c r="K126" s="277"/>
+      <c r="L126" s="277"/>
+      <c r="M126" s="277"/>
+      <c r="N126" s="277"/>
+    </row>
+    <row r="127" spans="1:16" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B127" s="277"/>
+      <c r="C127" s="277"/>
+      <c r="D127" s="277"/>
+      <c r="E127" s="277"/>
+      <c r="F127" s="277"/>
+      <c r="G127" s="277"/>
+      <c r="H127" s="277"/>
+      <c r="I127" s="277"/>
+      <c r="J127" s="277"/>
+      <c r="K127" s="277"/>
+      <c r="L127" s="277"/>
+      <c r="M127" s="277"/>
+      <c r="N127" s="277"/>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B130">
         <v>1631378.049999997</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>216</v>
       </c>
-      <c r="B134" s="196">
+      <c r="B134" s="192">
         <v>-3942</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>215</v>
       </c>
@@ -10574,12 +10527,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="A10:O10"/>
-    <mergeCell ref="A11:O11"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="K13:K14"/>
     <mergeCell ref="B122:N127"/>
     <mergeCell ref="D1:N1"/>
     <mergeCell ref="A4:O8"/>
@@ -10596,6 +10543,12 @@
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="I13:I14"/>
     <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A11:O11"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="K13:K14"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="70" orientation="landscape" r:id="rId1"/>
@@ -10604,21 +10557,21 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56D35F41-74CB-4294-A7A2-EC3C67574818}">
-  <dimension ref="C3:N61"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="C3:N41"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C3" s="19"/>
     </row>
-    <row r="4" spans="3:14" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C4" s="164" t="s">
+    <row r="4" spans="3:14" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="195" t="s">
         <v>188</v>
       </c>
-      <c r="D4" s="165">
+      <c r="D4" s="196">
         <v>1</v>
       </c>
       <c r="E4" s="161"/>
@@ -10631,11 +10584,11 @@
       <c r="L4" s="19"/>
       <c r="M4" s="19"/>
     </row>
-    <row r="5" spans="3:14" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C5" s="166" t="s">
+    <row r="5" spans="3:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C5" s="197" t="s">
         <v>189</v>
       </c>
-      <c r="D5" s="167"/>
+      <c r="D5" s="198"/>
       <c r="E5" t="s">
         <v>190</v>
       </c>
@@ -10643,16 +10596,16 @@
         <v>191</v>
       </c>
       <c r="J5" s="163"/>
-      <c r="K5" s="240"/>
-      <c r="L5" s="240"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
       <c r="M5" s="19"/>
       <c r="N5" s="19"/>
     </row>
-    <row r="6" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C6" s="166" t="s">
+    <row r="6" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C6" s="197" t="s">
         <v>192</v>
       </c>
-      <c r="D6" s="167" t="s">
+      <c r="D6" s="198" t="s">
         <v>193</v>
       </c>
       <c r="E6" t="s">
@@ -10662,89 +10615,69 @@
         <v>127</v>
       </c>
       <c r="H6" t="s">
-        <v>219</v>
+        <v>281</v>
       </c>
       <c r="J6" s="163"/>
-      <c r="K6" s="240"/>
-      <c r="L6" s="240"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
       <c r="M6" s="19"/>
       <c r="N6" s="19"/>
     </row>
-    <row r="7" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C7" s="47" t="s">
         <v>195</v>
       </c>
       <c r="J7" s="163"/>
-      <c r="K7" s="240"/>
-      <c r="L7" s="240"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
       <c r="M7" s="19"/>
       <c r="N7" s="19"/>
     </row>
-    <row r="8" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C8" s="301" t="s">
-        <v>227</v>
-      </c>
-      <c r="D8" s="302"/>
-      <c r="E8" s="302"/>
-      <c r="F8" s="302"/>
-      <c r="G8" s="302"/>
-      <c r="H8" s="302"/>
-      <c r="I8" s="302"/>
-      <c r="J8" s="303"/>
-      <c r="K8" s="240"/>
-      <c r="L8" s="240"/>
+    <row r="8" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C8" s="303" t="s">
+        <v>282</v>
+      </c>
+      <c r="D8" s="304"/>
+      <c r="E8" s="304"/>
+      <c r="F8" s="304"/>
+      <c r="G8" s="304"/>
+      <c r="H8" s="304"/>
+      <c r="I8" s="304"/>
+      <c r="J8" s="305"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
       <c r="M8" s="19"/>
       <c r="N8" s="19"/>
     </row>
-    <row r="9" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="304"/>
-      <c r="D9" s="305"/>
-      <c r="E9" s="305"/>
-      <c r="F9" s="305"/>
-      <c r="G9" s="305"/>
-      <c r="H9" s="305"/>
-      <c r="I9" s="305"/>
-      <c r="J9" s="306"/>
+    <row r="9" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C9" s="306"/>
+      <c r="D9" s="307"/>
+      <c r="E9" s="307"/>
+      <c r="F9" s="307"/>
+      <c r="G9" s="307"/>
+      <c r="H9" s="307"/>
+      <c r="I9" s="307"/>
+      <c r="J9" s="308"/>
       <c r="K9" s="19"/>
       <c r="L9" s="19"/>
       <c r="M9" s="19"/>
       <c r="N9" s="19"/>
     </row>
-    <row r="10" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C10" s="225"/>
-      <c r="D10" s="225"/>
-      <c r="E10" s="225"/>
-      <c r="F10" s="225"/>
-      <c r="G10" s="225"/>
-      <c r="H10" s="225"/>
-      <c r="I10" s="225"/>
-      <c r="J10" s="225"/>
+    <row r="10" spans="3:14" x14ac:dyDescent="0.3">
       <c r="K10" s="19"/>
       <c r="L10" s="19"/>
       <c r="M10" s="19"/>
-      <c r="N10" s="19"/>
-    </row>
-    <row r="11" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C11" s="225"/>
       <c r="D11" s="225"/>
-      <c r="E11" s="225"/>
-      <c r="F11" s="225"/>
-      <c r="G11" s="225"/>
-      <c r="H11" s="225"/>
-      <c r="I11" s="225"/>
-      <c r="J11" s="225"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="19"/>
-    </row>
-    <row r="12" spans="3:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C12" s="226" t="s">
         <v>188</v>
       </c>
       <c r="D12" s="227">
-        <f>D4+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" s="161"/>
       <c r="F12" s="161"/>
@@ -10752,33 +10685,28 @@
       <c r="H12" s="161"/>
       <c r="I12" s="161"/>
       <c r="J12" s="162"/>
-      <c r="K12" s="240"/>
-      <c r="L12" s="240"/>
-      <c r="M12" s="19"/>
-      <c r="N12" s="19"/>
-    </row>
-    <row r="13" spans="3:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C13" s="228" t="s">
         <v>189</v>
       </c>
-      <c r="D13" s="229"/>
+      <c r="D13" s="225"/>
       <c r="E13" t="s">
         <v>190</v>
       </c>
       <c r="G13" t="s">
         <v>191</v>
       </c>
+      <c r="H13" t="s">
+        <v>284</v>
+      </c>
       <c r="J13" s="163"/>
-      <c r="K13" s="240"/>
-      <c r="L13" s="240"/>
-      <c r="M13" s="19"/>
-      <c r="N13" s="19"/>
-    </row>
-    <row r="14" spans="3:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C14" s="228" t="s">
         <v>192</v>
       </c>
-      <c r="D14" s="229" t="s">
+      <c r="D14" s="225" t="s">
         <v>193</v>
       </c>
       <c r="E14" t="s">
@@ -10788,522 +10716,269 @@
         <v>127</v>
       </c>
       <c r="H14" t="s">
-        <v>233</v>
+        <v>283</v>
       </c>
       <c r="J14" s="163"/>
-      <c r="K14" s="240"/>
-      <c r="L14" s="240"/>
-      <c r="M14" s="19"/>
-      <c r="N14" s="19"/>
-    </row>
-    <row r="15" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C15" s="47" t="s">
         <v>195</v>
       </c>
       <c r="J15" s="163"/>
-      <c r="K15" s="240"/>
-      <c r="L15" s="240"/>
-      <c r="M15" s="19"/>
-      <c r="N15" s="19"/>
-    </row>
-    <row r="16" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C16" s="301" t="s">
-        <v>232</v>
-      </c>
-      <c r="D16" s="302"/>
-      <c r="E16" s="302"/>
-      <c r="F16" s="302"/>
-      <c r="G16" s="302"/>
-      <c r="H16" s="302"/>
-      <c r="I16" s="302"/>
-      <c r="J16" s="303"/>
-      <c r="K16" s="240"/>
-      <c r="L16" s="240"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="19"/>
-    </row>
-    <row r="17" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="304"/>
-      <c r="D17" s="305"/>
-      <c r="E17" s="305"/>
-      <c r="F17" s="305"/>
-      <c r="G17" s="305"/>
-      <c r="H17" s="305"/>
-      <c r="I17" s="305"/>
-      <c r="J17" s="306"/>
-    </row>
-    <row r="21" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C22" s="199" t="s">
+    </row>
+    <row r="16" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C16" s="303" t="s">
+        <v>285</v>
+      </c>
+      <c r="D16" s="304"/>
+      <c r="E16" s="304"/>
+      <c r="F16" s="304"/>
+      <c r="G16" s="304"/>
+      <c r="H16" s="304"/>
+      <c r="I16" s="304"/>
+      <c r="J16" s="305"/>
+    </row>
+    <row r="17" spans="3:10" ht="53.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C17" s="306"/>
+      <c r="D17" s="307"/>
+      <c r="E17" s="307"/>
+      <c r="F17" s="307"/>
+      <c r="G17" s="307"/>
+      <c r="H17" s="307"/>
+      <c r="I17" s="307"/>
+      <c r="J17" s="308"/>
+    </row>
+    <row r="19" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C20" s="231" t="s">
         <v>188</v>
       </c>
-      <c r="D22" s="200">
-        <f>D4+1</f>
-        <v>2</v>
-      </c>
-      <c r="E22" s="161"/>
-      <c r="F22" s="161"/>
-      <c r="G22" s="161"/>
-      <c r="H22" s="161"/>
-      <c r="I22" s="161"/>
-      <c r="J22" s="162"/>
-      <c r="K22" s="240"/>
-      <c r="L22" s="240"/>
-      <c r="M22" s="240"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C23" s="201" t="s">
+      <c r="D20" s="232">
+        <v>1</v>
+      </c>
+      <c r="E20" s="161"/>
+      <c r="F20" s="161"/>
+      <c r="G20" s="161"/>
+      <c r="H20" s="161"/>
+      <c r="I20" s="161"/>
+      <c r="J20" s="162"/>
+    </row>
+    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C21" s="233" t="s">
         <v>189</v>
       </c>
-      <c r="D23" s="202"/>
-      <c r="E23" t="s">
+      <c r="D21" s="234"/>
+      <c r="E21" t="s">
         <v>190</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G21" t="s">
         <v>191</v>
       </c>
+      <c r="J21" s="163"/>
+    </row>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C22" s="233" t="s">
+        <v>192</v>
+      </c>
+      <c r="D22" s="234" t="s">
+        <v>193</v>
+      </c>
+      <c r="E22" t="s">
+        <v>194</v>
+      </c>
+      <c r="G22" t="s">
+        <v>127</v>
+      </c>
+      <c r="H22" t="s">
+        <v>288</v>
+      </c>
+      <c r="J22" s="163"/>
+    </row>
+    <row r="23" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C23" s="47" t="s">
+        <v>195</v>
+      </c>
       <c r="J23" s="163"/>
-      <c r="K23" s="240"/>
-      <c r="L23" s="240"/>
-      <c r="M23" s="240"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C24" s="201" t="s">
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C24" s="303" t="s">
+        <v>289</v>
+      </c>
+      <c r="D24" s="304"/>
+      <c r="E24" s="304"/>
+      <c r="F24" s="304"/>
+      <c r="G24" s="304"/>
+      <c r="H24" s="304"/>
+      <c r="I24" s="304"/>
+      <c r="J24" s="305"/>
+    </row>
+    <row r="25" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C25" s="306"/>
+      <c r="D25" s="307"/>
+      <c r="E25" s="307"/>
+      <c r="F25" s="307"/>
+      <c r="G25" s="307"/>
+      <c r="H25" s="307"/>
+      <c r="I25" s="307"/>
+      <c r="J25" s="308"/>
+    </row>
+    <row r="27" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C28" s="237" t="s">
+        <v>188</v>
+      </c>
+      <c r="D28" s="238">
+        <v>1</v>
+      </c>
+      <c r="E28" s="161"/>
+      <c r="F28" s="161"/>
+      <c r="G28" s="161"/>
+      <c r="H28" s="161"/>
+      <c r="I28" s="161"/>
+      <c r="J28" s="162"/>
+    </row>
+    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C29" s="239" t="s">
+        <v>189</v>
+      </c>
+      <c r="D29" s="240"/>
+      <c r="E29" t="s">
+        <v>190</v>
+      </c>
+      <c r="G29" t="s">
+        <v>191</v>
+      </c>
+      <c r="J29" s="163"/>
+    </row>
+    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C30" s="239" t="s">
         <v>192</v>
       </c>
-      <c r="D24" s="202" t="s">
+      <c r="D30" s="240" t="s">
         <v>193</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E30" t="s">
         <v>194</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G30" t="s">
         <v>127</v>
       </c>
-      <c r="J24" s="163"/>
-      <c r="K24" s="240"/>
-      <c r="L24" s="240"/>
-      <c r="M24" s="240"/>
-    </row>
-    <row r="25" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C25" s="47" t="s">
+      <c r="H30" t="s">
+        <v>286</v>
+      </c>
+      <c r="J30" s="163"/>
+    </row>
+    <row r="31" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C31" s="239" t="s">
         <v>195</v>
       </c>
-      <c r="J25" s="163"/>
-      <c r="K25" s="240"/>
-      <c r="L25" s="240"/>
-      <c r="M25" s="240"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C26" s="301" t="s">
-        <v>228</v>
-      </c>
-      <c r="D26" s="302"/>
-      <c r="E26" s="302"/>
-      <c r="F26" s="302"/>
-      <c r="G26" s="302"/>
-      <c r="H26" s="302"/>
-      <c r="I26" s="302"/>
-      <c r="J26" s="303"/>
-      <c r="K26" s="240"/>
-      <c r="L26" s="240"/>
-      <c r="M26" s="240"/>
-    </row>
-    <row r="27" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C27" s="304"/>
-      <c r="D27" s="305"/>
-      <c r="E27" s="305"/>
-      <c r="F27" s="305"/>
-      <c r="G27" s="305"/>
-      <c r="H27" s="305"/>
-      <c r="I27" s="305"/>
-      <c r="J27" s="306"/>
-      <c r="K27" s="240"/>
-      <c r="L27" s="240"/>
-      <c r="M27" s="240"/>
-    </row>
-    <row r="29" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C30" s="218" t="s">
+      <c r="D31" s="240"/>
+      <c r="J31" s="163"/>
+    </row>
+    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C32" s="303" t="s">
+        <v>287</v>
+      </c>
+      <c r="D32" s="304"/>
+      <c r="E32" s="304"/>
+      <c r="F32" s="304"/>
+      <c r="G32" s="304"/>
+      <c r="H32" s="304"/>
+      <c r="I32" s="304"/>
+      <c r="J32" s="305"/>
+    </row>
+    <row r="33" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C33" s="306"/>
+      <c r="D33" s="307"/>
+      <c r="E33" s="307"/>
+      <c r="F33" s="307"/>
+      <c r="G33" s="307"/>
+      <c r="H33" s="307"/>
+      <c r="I33" s="307"/>
+      <c r="J33" s="308"/>
+    </row>
+    <row r="35" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="36" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C36" s="311" t="s">
         <v>188</v>
       </c>
-      <c r="D30" s="219">
-        <f>D22+1</f>
-        <v>3</v>
-      </c>
-      <c r="E30" s="161"/>
-      <c r="F30" s="161"/>
-      <c r="G30" s="161"/>
-      <c r="H30" s="161"/>
-      <c r="I30" s="161"/>
-      <c r="J30" s="162"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C31" s="220" t="s">
+      <c r="D36" s="312">
+        <v>1</v>
+      </c>
+      <c r="E36" s="161"/>
+      <c r="F36" s="161"/>
+      <c r="G36" s="161"/>
+      <c r="H36" s="161"/>
+      <c r="I36" s="161"/>
+      <c r="J36" s="162"/>
+    </row>
+    <row r="37" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C37" s="313" t="s">
         <v>189</v>
       </c>
-      <c r="D31" s="19"/>
-      <c r="E31" t="s">
+      <c r="D37" s="314"/>
+      <c r="E37" t="s">
         <v>190</v>
       </c>
-      <c r="G31" t="s">
+      <c r="G37" t="s">
         <v>191</v>
       </c>
-      <c r="J31" s="163"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C32" s="220" t="s">
+      <c r="J37" s="163"/>
+    </row>
+    <row r="38" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C38" s="313" t="s">
         <v>192</v>
       </c>
-      <c r="D32" s="19" t="s">
+      <c r="D38" s="314" t="s">
         <v>193</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E38" t="s">
         <v>194</v>
       </c>
-      <c r="G32" t="s">
+      <c r="G38" t="s">
         <v>127</v>
       </c>
-      <c r="H32">
-        <v>0</v>
-      </c>
-      <c r="J32" s="163"/>
-    </row>
-    <row r="33" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C33" s="220" t="s">
+      <c r="H38" t="s">
+        <v>290</v>
+      </c>
+      <c r="J38" s="163"/>
+    </row>
+    <row r="39" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C39" s="313" t="s">
         <v>195</v>
       </c>
-      <c r="D33" s="19"/>
-      <c r="J33" s="163"/>
-    </row>
-    <row r="34" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C34" s="301" t="s">
-        <v>229</v>
-      </c>
-      <c r="D34" s="302"/>
-      <c r="E34" s="302"/>
-      <c r="F34" s="302"/>
-      <c r="G34" s="302"/>
-      <c r="H34" s="302"/>
-      <c r="I34" s="302"/>
-      <c r="J34" s="303"/>
-    </row>
-    <row r="35" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C35" s="304"/>
-      <c r="D35" s="305"/>
-      <c r="E35" s="305"/>
-      <c r="F35" s="305"/>
-      <c r="G35" s="305"/>
-      <c r="H35" s="305"/>
-      <c r="I35" s="305"/>
-      <c r="J35" s="306"/>
-    </row>
-    <row r="37" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="38" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C38" s="221" t="s">
-        <v>188</v>
-      </c>
-      <c r="D38" s="222">
-        <f>D30+1</f>
-        <v>4</v>
-      </c>
-      <c r="E38" s="161"/>
-      <c r="F38" s="161"/>
-      <c r="G38" s="161"/>
-      <c r="H38" s="161"/>
-      <c r="I38" s="161"/>
-      <c r="J38" s="162"/>
-    </row>
-    <row r="39" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C39" s="223" t="s">
-        <v>189</v>
-      </c>
-      <c r="D39" s="224"/>
-      <c r="E39" t="s">
-        <v>190</v>
-      </c>
-      <c r="G39" t="s">
-        <v>191</v>
-      </c>
+      <c r="D39" s="314"/>
       <c r="J39" s="163"/>
-      <c r="K39" s="240"/>
-      <c r="L39" s="240"/>
-      <c r="M39" s="240"/>
-    </row>
-    <row r="40" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C40" s="223" t="s">
-        <v>192</v>
-      </c>
-      <c r="D40" s="224" t="s">
-        <v>193</v>
-      </c>
-      <c r="E40" t="s">
-        <v>194</v>
-      </c>
-      <c r="G40" t="s">
-        <v>127</v>
-      </c>
-      <c r="H40" t="s">
-        <v>230</v>
-      </c>
-      <c r="J40" s="163"/>
-      <c r="K40" s="240"/>
-      <c r="L40" s="240"/>
-      <c r="M40" s="240"/>
-    </row>
-    <row r="41" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="220" t="s">
-        <v>195</v>
-      </c>
-      <c r="D41" s="19"/>
-      <c r="J41" s="163"/>
-      <c r="K41" s="240"/>
-      <c r="L41" s="240"/>
-      <c r="M41" s="240"/>
-    </row>
-    <row r="42" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C42" s="301" t="s">
-        <v>231</v>
-      </c>
-      <c r="D42" s="302"/>
-      <c r="E42" s="302"/>
-      <c r="F42" s="302"/>
-      <c r="G42" s="302"/>
-      <c r="H42" s="302"/>
-      <c r="I42" s="302"/>
-      <c r="J42" s="303"/>
-      <c r="K42" s="240"/>
-      <c r="L42" s="240"/>
-      <c r="M42" s="240"/>
-    </row>
-    <row r="43" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C43" s="304"/>
-      <c r="D43" s="305"/>
-      <c r="E43" s="305"/>
-      <c r="F43" s="305"/>
-      <c r="G43" s="305"/>
-      <c r="H43" s="305"/>
-      <c r="I43" s="305"/>
-      <c r="J43" s="306"/>
-      <c r="K43" s="240"/>
-      <c r="L43" s="240"/>
-      <c r="M43" s="240"/>
-    </row>
-    <row r="45" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="46" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C46" s="230" t="s">
-        <v>188</v>
-      </c>
-      <c r="D46" s="231">
-        <f>D38+1</f>
-        <v>5</v>
-      </c>
-      <c r="E46" s="161"/>
-      <c r="F46" s="161"/>
-      <c r="G46" s="161"/>
-      <c r="H46" s="161"/>
-      <c r="I46" s="161"/>
-      <c r="J46" s="162"/>
-      <c r="K46" s="240"/>
-      <c r="L46" s="240"/>
-      <c r="M46" s="240"/>
-    </row>
-    <row r="47" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C47" s="232" t="s">
-        <v>189</v>
-      </c>
-      <c r="D47" s="233"/>
-      <c r="E47" t="s">
-        <v>190</v>
-      </c>
-      <c r="G47" t="s">
-        <v>191</v>
-      </c>
-      <c r="J47" s="163"/>
-      <c r="K47" s="240"/>
-      <c r="L47" s="240"/>
-      <c r="M47" s="240"/>
-    </row>
-    <row r="48" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C48" s="232" t="s">
-        <v>192</v>
-      </c>
-      <c r="D48" s="233" t="s">
-        <v>193</v>
-      </c>
-      <c r="E48" t="s">
-        <v>194</v>
-      </c>
-      <c r="G48" t="s">
-        <v>127</v>
-      </c>
-      <c r="H48" t="s">
-        <v>234</v>
-      </c>
-      <c r="J48" s="163"/>
-      <c r="K48" s="240"/>
-      <c r="L48" s="240"/>
-      <c r="M48" s="240"/>
-    </row>
-    <row r="49" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C49" s="232" t="s">
-        <v>195</v>
-      </c>
-      <c r="D49" s="233"/>
-      <c r="J49" s="163"/>
-      <c r="K49" s="240"/>
-      <c r="L49" s="240"/>
-      <c r="M49" s="240"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C50" s="301" t="s">
-        <v>235</v>
-      </c>
-      <c r="D50" s="302"/>
-      <c r="E50" s="302"/>
-      <c r="F50" s="302"/>
-      <c r="G50" s="302"/>
-      <c r="H50" s="302"/>
-      <c r="I50" s="302"/>
-      <c r="J50" s="303"/>
-      <c r="K50" s="240"/>
-      <c r="L50" s="240"/>
-      <c r="M50" s="240"/>
-    </row>
-    <row r="51" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C51" s="304"/>
-      <c r="D51" s="305"/>
-      <c r="E51" s="305"/>
-      <c r="F51" s="305"/>
-      <c r="G51" s="305"/>
-      <c r="H51" s="305"/>
-      <c r="I51" s="305"/>
-      <c r="J51" s="306"/>
-      <c r="K51" s="240"/>
-      <c r="L51" s="240"/>
-      <c r="M51" s="240"/>
-    </row>
-    <row r="53" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C54" s="235" t="s">
-        <v>188</v>
-      </c>
-      <c r="D54" s="236">
-        <f>D46+1</f>
-        <v>6</v>
-      </c>
-      <c r="E54" s="161"/>
-      <c r="F54" s="161"/>
-      <c r="G54" s="161"/>
-      <c r="H54" s="161"/>
-      <c r="I54" s="161"/>
-      <c r="J54" s="162"/>
-      <c r="K54" s="240"/>
-      <c r="L54" s="240"/>
-      <c r="M54" s="240"/>
-      <c r="N54" s="240"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C55" s="237" t="s">
-        <v>189</v>
-      </c>
-      <c r="D55" s="238"/>
-      <c r="E55" t="s">
-        <v>190</v>
-      </c>
-      <c r="G55" t="s">
-        <v>191</v>
-      </c>
-      <c r="J55" s="163"/>
-      <c r="K55" s="240"/>
-      <c r="L55" s="240"/>
-      <c r="M55" s="240"/>
-      <c r="N55" s="240"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C56" s="237" t="s">
-        <v>192</v>
-      </c>
-      <c r="D56" s="238" t="s">
-        <v>193</v>
-      </c>
-      <c r="E56" t="s">
-        <v>194</v>
-      </c>
-      <c r="G56" t="s">
-        <v>127</v>
-      </c>
-      <c r="H56" t="s">
-        <v>249</v>
-      </c>
-      <c r="J56" s="163"/>
-      <c r="K56" s="240"/>
-      <c r="L56" s="240"/>
-      <c r="M56" s="240"/>
-      <c r="N56" s="240"/>
-    </row>
-    <row r="57" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C57" s="237" t="s">
-        <v>195</v>
-      </c>
-      <c r="D57" s="238"/>
-      <c r="J57" s="163"/>
-      <c r="K57" s="240"/>
-      <c r="L57" s="240"/>
-      <c r="M57" s="240"/>
-      <c r="N57" s="240"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C58" s="301" t="s">
-        <v>248</v>
-      </c>
-      <c r="D58" s="302"/>
-      <c r="E58" s="302"/>
-      <c r="F58" s="302"/>
-      <c r="G58" s="302"/>
-      <c r="H58" s="302"/>
-      <c r="I58" s="302"/>
-      <c r="J58" s="303"/>
-      <c r="K58" s="240"/>
-      <c r="L58" s="240"/>
-      <c r="M58" s="240"/>
-      <c r="N58" s="240"/>
-    </row>
-    <row r="59" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C59" s="304"/>
-      <c r="D59" s="305"/>
-      <c r="E59" s="305"/>
-      <c r="F59" s="305"/>
-      <c r="G59" s="305"/>
-      <c r="H59" s="305"/>
-      <c r="I59" s="305"/>
-      <c r="J59" s="306"/>
-      <c r="K59" s="240"/>
-      <c r="L59" s="240"/>
-      <c r="M59" s="240"/>
-      <c r="N59" s="240"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="K60" s="240"/>
-      <c r="L60" s="240"/>
-      <c r="M60" s="240"/>
-      <c r="N60" s="240"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="K61" s="240"/>
-      <c r="L61" s="240"/>
-      <c r="M61" s="240"/>
-      <c r="N61" s="240"/>
+    </row>
+    <row r="40" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C40" s="303" t="s">
+        <v>291</v>
+      </c>
+      <c r="D40" s="304"/>
+      <c r="E40" s="304"/>
+      <c r="F40" s="304"/>
+      <c r="G40" s="304"/>
+      <c r="H40" s="304"/>
+      <c r="I40" s="304"/>
+      <c r="J40" s="305"/>
+    </row>
+    <row r="41" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C41" s="306"/>
+      <c r="D41" s="307"/>
+      <c r="E41" s="307"/>
+      <c r="F41" s="307"/>
+      <c r="G41" s="307"/>
+      <c r="H41" s="307"/>
+      <c r="I41" s="307"/>
+      <c r="J41" s="308"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="C58:J59"/>
-    <mergeCell ref="C50:J51"/>
+  <mergeCells count="5">
     <mergeCell ref="C8:J9"/>
-    <mergeCell ref="C26:J27"/>
-    <mergeCell ref="C34:J35"/>
-    <mergeCell ref="C42:J43"/>
     <mergeCell ref="C16:J17"/>
+    <mergeCell ref="C24:J25"/>
+    <mergeCell ref="C32:J33"/>
+    <mergeCell ref="C40:J41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
